--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -5986,15 +5986,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E93" s="18" t="n"/>
-      <c r="F93" s="18" t="n"/>
-      <c r="G93" s="18" t="n"/>
-      <c r="H93" s="18" t="n"/>
-      <c r="I93" s="18" t="n"/>
-      <c r="J93" s="18" t="n"/>
-      <c r="K93" s="18" t="n"/>
-      <c r="L93" s="18" t="n"/>
-      <c r="M93" s="18" t="n"/>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H93" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J93" s="18" t="inlineStr">
+        <is>
+          <t>Official Liquidators are field offices under MCA. No separate website; recruitment through MCA recruitment page and SSC for Group B/C posts.</t>
+        </is>
+      </c>
+      <c r="K93" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L93" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M93" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="16">
       <c r="A94" s="4">
@@ -6016,15 +6050,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-      <c r="G94" s="18" t="n"/>
-      <c r="H94" s="18" t="n"/>
-      <c r="I94" s="18" t="n"/>
-      <c r="J94" s="18" t="n"/>
-      <c r="K94" s="18" t="n"/>
-      <c r="L94" s="18" t="n"/>
-      <c r="M94" s="18" t="n"/>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="G94" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H94" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I94" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J94" s="18" t="inlineStr">
+        <is>
+          <t>Regional Director offices are subordinate to MCA. No separate website; recruitment handled centrally through MCA recruitment page.</t>
+        </is>
+      </c>
+      <c r="K94" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L94" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="16">
       <c r="A95" s="4">
@@ -6046,15 +6114,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
-      <c r="G95" s="18" t="n"/>
-      <c r="H95" s="18" t="n"/>
-      <c r="I95" s="18" t="n"/>
-      <c r="J95" s="18" t="n"/>
-      <c r="K95" s="18" t="n"/>
-      <c r="L95" s="18" t="n"/>
-      <c r="M95" s="18" t="n"/>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>https://nclt.gov.in/careers</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>https://nclt.gov.in/careers</t>
+        </is>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H95" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I95" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>NCLT careers page verified live. Statutory body under MCA. Staff appointed on deputation / direct recruitment.</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L95" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M95" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="16">
       <c r="A96" s="4">
@@ -6076,15 +6178,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E96" s="18" t="n"/>
-      <c r="F96" s="18" t="n"/>
-      <c r="G96" s="18" t="n"/>
-      <c r="H96" s="18" t="n"/>
-      <c r="I96" s="18" t="n"/>
-      <c r="J96" s="18" t="n"/>
-      <c r="K96" s="18" t="n"/>
-      <c r="L96" s="18" t="n"/>
-      <c r="M96" s="18" t="n"/>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>https://nclat.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>https://nclat.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J96" s="18" t="inlineStr">
+        <is>
+          <t>NCLAT recruitment page verified live. Also has /appointment-recruitment path. Statutory tribunal under MCA.</t>
+        </is>
+      </c>
+      <c r="K96" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L96" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M96" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="16">
       <c r="A97" s="4">
@@ -6106,15 +6242,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
-      <c r="K97" s="18" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="18" t="n"/>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cci.gov.in/career</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cci.gov.in/career</t>
+        </is>
+      </c>
+      <c r="G97" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H97" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I97" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J97" s="18" t="inlineStr">
+        <is>
+          <t>CCI career page verified live. Recent notices for DG post and doctor post (2026). Statutory body under MCA. Staff on deputation/contract.</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L97" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M97" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="16">
       <c r="A98" s="4">
@@ -6136,15 +6306,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-      <c r="J98" s="18" t="n"/>
-      <c r="K98" s="18" t="n"/>
-      <c r="L98" s="18" t="n"/>
-      <c r="M98" s="18" t="n"/>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>https://iica.nic.in/Opportunities.aspx</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="inlineStr">
+        <is>
+          <t>https://iica.nic.in/Opportunities.aspx</t>
+        </is>
+      </c>
+      <c r="G98" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H98" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J98" s="18" t="inlineStr">
+        <is>
+          <t>IICA Opportunities page verified live. Contains vacancy circulars (e.g. RBI Chair Professor, May 2026). Autonomous body under MCA.</t>
+        </is>
+      </c>
+      <c r="K98" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L98" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M98" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="16">
       <c r="A99" s="4">
@@ -6196,15 +6400,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-      <c r="G100" s="18" t="n"/>
-      <c r="H100" s="18" t="n"/>
-      <c r="I100" s="18" t="n"/>
-      <c r="J100" s="18" t="n"/>
-      <c r="K100" s="18" t="n"/>
-      <c r="L100" s="18" t="n"/>
-      <c r="M100" s="18" t="n"/>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="G100" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H100" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J100" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Culture vacancies page verified live (new site: culture.gov.in, replacing indiaculture.gov.in). Secretariat-level vacancy and deputation circulars posted here.</t>
+        </is>
+      </c>
+      <c r="K100" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L100" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M100" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="16">
       <c r="A101" s="4">
@@ -6226,15 +6464,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-      <c r="J101" s="18" t="n"/>
-      <c r="K101" s="18" t="n"/>
-      <c r="L101" s="18" t="n"/>
-      <c r="M101" s="18" t="n"/>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>https://asi.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>https://asi.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I101" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J101" s="18" t="inlineStr">
+        <is>
+          <t>Archaeological Survey of India recruitment page verified live. ASI is an attached office under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L101" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M101" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="16">
       <c r="A102" s="4">
@@ -6256,15 +6528,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="18" t="n"/>
-      <c r="G102" s="18" t="n"/>
-      <c r="H102" s="18" t="n"/>
-      <c r="I102" s="18" t="n"/>
-      <c r="J102" s="18" t="n"/>
-      <c r="K102" s="18" t="n"/>
-      <c r="L102" s="18" t="n"/>
-      <c r="M102" s="18" t="n"/>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>https://ansi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>https://ansi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H102" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>Anthropological Survey of India official site (ansi.gov.in) returns 403 from automated access but confirmed as official domain. Small attached office under Ministry of Culture; recruitment infrequent, circulars may also appear on culture.gov.in.</t>
+        </is>
+      </c>
+      <c r="K102" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L102" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M102" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="16">
       <c r="A103" s="4">
@@ -6286,15 +6592,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="18" t="n"/>
-      <c r="G103" s="18" t="n"/>
-      <c r="H103" s="18" t="n"/>
-      <c r="I103" s="18" t="n"/>
-      <c r="J103" s="18" t="n"/>
-      <c r="K103" s="18" t="n"/>
-      <c r="L103" s="18" t="n"/>
-      <c r="M103" s="18" t="n"/>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>https://nationalarchives.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>https://nationalarchives.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I103" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J103" s="18" t="inlineStr">
+        <is>
+          <t>National Archives of India recruitment page verified live. Attached office under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K103" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L103" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M103" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="16">
       <c r="A104" s="4">
@@ -6316,15 +6656,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="18" t="n"/>
-      <c r="G104" s="18" t="n"/>
-      <c r="H104" s="18" t="n"/>
-      <c r="I104" s="18" t="n"/>
-      <c r="J104" s="18" t="n"/>
-      <c r="K104" s="18" t="n"/>
-      <c r="L104" s="18" t="n"/>
-      <c r="M104" s="18" t="n"/>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>https://asi.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="inlineStr">
+        <is>
+          <t>https://asi.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H104" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J104" s="18" t="inlineStr">
+        <is>
+          <t>Central Archaeological Circles are ASI field offices. No separate portal; recruitment handled through the ASI recruitment page.</t>
+        </is>
+      </c>
+      <c r="K104" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L104" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="16">
       <c r="A105" s="4">
@@ -6346,15 +6720,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E105" s="18" t="n"/>
-      <c r="F105" s="18" t="n"/>
-      <c r="G105" s="18" t="n"/>
-      <c r="H105" s="18" t="n"/>
-      <c r="I105" s="18" t="n"/>
-      <c r="J105" s="18" t="n"/>
-      <c r="K105" s="18" t="n"/>
-      <c r="L105" s="18" t="n"/>
-      <c r="M105" s="18" t="n"/>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I105" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J105" s="18" t="inlineStr">
+        <is>
+          <t>Central Reference Libraries &amp; Field Units are subordinate offices under Ministry of Culture. No separate recruitment portal; vacancies channeled through Ministry of Culture vacancies page.</t>
+        </is>
+      </c>
+      <c r="K105" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L105" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="16">
       <c r="A106" s="4">
@@ -6376,15 +6784,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-      <c r="J106" s="18" t="n"/>
-      <c r="K106" s="18" t="n"/>
-      <c r="L106" s="18" t="n"/>
-      <c r="M106" s="18" t="n"/>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>https://ncsm.gov.in/notice/career</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="inlineStr">
+        <is>
+          <t>https://ncsm.gov.in/notice/career</t>
+        </is>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H106" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J106" s="18" t="inlineStr">
+        <is>
+          <t>NCSM career/notice page verified live. National Council of Science Museums is a statutory body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K106" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L106" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M106" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="16">
       <c r="A107" s="4">
@@ -6406,15 +6848,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-      <c r="J107" s="18" t="n"/>
-      <c r="K107" s="18" t="n"/>
-      <c r="L107" s="18" t="n"/>
-      <c r="M107" s="18" t="n"/>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>https://nationalarchives.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="inlineStr">
+        <is>
+          <t>https://nationalarchives.nic.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H107" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J107" s="18" t="inlineStr">
+        <is>
+          <t>National Council of Archives is a policy body/committee; no separate website. Functionally linked to National Archives of India. Any staff requirements handled through NAI.</t>
+        </is>
+      </c>
+      <c r="K107" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L107" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M107" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="16">
       <c r="A108" s="4">
@@ -6436,15 +6912,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-      <c r="J108" s="18" t="n"/>
-      <c r="K108" s="18" t="n"/>
-      <c r="L108" s="18" t="n"/>
-      <c r="M108" s="18" t="n"/>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>https://ignca.gov.in/recruitments/</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="inlineStr">
+        <is>
+          <t>https://ignca.gov.in/recruitments/</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H108" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J108" s="18" t="inlineStr">
+        <is>
+          <t>IGNCA recruitments page verified live. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K108" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L108" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M108" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="16">
       <c r="A109" s="4">
@@ -6466,15 +6976,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E109" s="18" t="n"/>
-      <c r="F109" s="18" t="n"/>
-      <c r="G109" s="18" t="n"/>
-      <c r="H109" s="18" t="n"/>
-      <c r="I109" s="18" t="n"/>
-      <c r="J109" s="18" t="n"/>
-      <c r="K109" s="18" t="n"/>
-      <c r="L109" s="18" t="n"/>
-      <c r="M109" s="18" t="n"/>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.nsd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.nsd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J109" s="18" t="inlineStr">
+        <is>
+          <t>NSD dedicated recruitment portal verified live. Recent 2025 recruitment (LDC, Accounts Officer, Theatre Artists). Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K109" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L109" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M109" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="16">
       <c r="A110" s="4">
@@ -6496,15 +7040,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-      <c r="J110" s="18" t="n"/>
-      <c r="K110" s="18" t="n"/>
-      <c r="L110" s="18" t="n"/>
-      <c r="M110" s="18" t="n"/>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>https://sangeetnatak.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="inlineStr">
+        <is>
+          <t>https://sangeetnatak.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H110" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J110" s="18" t="inlineStr">
+        <is>
+          <t>Sangeet Natak Akademi vacancy page verified live. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K110" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L110" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M110" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="16">
       <c r="A111" s="4">
@@ -6526,15 +7104,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
-      <c r="J111" s="18" t="n"/>
-      <c r="K111" s="18" t="n"/>
-      <c r="L111" s="18" t="n"/>
-      <c r="M111" s="18" t="n"/>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>https://lalitkala.gov.in/home/career</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="inlineStr">
+        <is>
+          <t>https://lalitkala.gov.in/home/career</t>
+        </is>
+      </c>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H111" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J111" s="18" t="inlineStr">
+        <is>
+          <t>Lalit Kala Akademi career page verified live. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K111" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L111" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M111" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="16">
       <c r="A112" s="4">
@@ -6556,15 +7168,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-      <c r="J112" s="18" t="n"/>
-      <c r="K112" s="18" t="n"/>
-      <c r="L112" s="18" t="n"/>
-      <c r="M112" s="18" t="n"/>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>https://sahitya-akademi.gov.in/recruitment/recruitment.jsp</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="inlineStr">
+        <is>
+          <t>https://sahitya-akademi.gov.in/recruitment/recruitment.jsp</t>
+        </is>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H112" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J112" s="18" t="inlineStr">
+        <is>
+          <t>Sahitya Akademi recruitment page verified live. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K112" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L112" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M112" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="16">
       <c r="A113" s="4">
@@ -6586,15 +7232,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-      <c r="G113" s="18" t="n"/>
-      <c r="H113" s="18" t="n"/>
-      <c r="I113" s="18" t="n"/>
-      <c r="J113" s="18" t="n"/>
-      <c r="K113" s="18" t="n"/>
-      <c r="L113" s="18" t="n"/>
-      <c r="M113" s="18" t="n"/>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nationalmuseumindia.gov.in/en/vacancys</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nationalmuseumindia.gov.in/en/vacancys</t>
+        </is>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H113" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J113" s="18" t="inlineStr">
+        <is>
+          <t>National Museum vacancies page verified live. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K113" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L113" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M113" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="16">
       <c r="A114" s="4">
@@ -6616,15 +7296,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E114" s="18" t="n"/>
-      <c r="F114" s="18" t="n"/>
-      <c r="G114" s="18" t="n"/>
-      <c r="H114" s="18" t="n"/>
-      <c r="I114" s="18" t="n"/>
-      <c r="J114" s="18" t="n"/>
-      <c r="K114" s="18" t="n"/>
-      <c r="L114" s="18" t="n"/>
-      <c r="M114" s="18" t="n"/>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>https://www.victoriamemorial-cal.org/</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>https://www.victoriamemorial-cal.org/</t>
+        </is>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H114" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J114" s="18" t="inlineStr">
+        <is>
+          <t>Victoria Memorial Hall official site (victoriamemorial-cal.org) returns 403 from automated access but confirmed as official domain. Autonomous body under Ministry of Culture; recruitment infrequent.</t>
+        </is>
+      </c>
+      <c r="K114" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L114" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M114" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="16">
       <c r="A115" s="4">
@@ -6646,15 +7360,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-      <c r="J115" s="18" t="n"/>
-      <c r="K115" s="18" t="n"/>
-      <c r="L115" s="18" t="n"/>
-      <c r="M115" s="18" t="n"/>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H115" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I115" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J115" s="18" t="inlineStr">
+        <is>
+          <t>Allahabad Museum - no functional independent website found (allahabadmuseum.org unreachable). Small autonomous body under Ministry of Culture; any recruitment likely channeled through Ministry of Culture vacancies page.</t>
+        </is>
+      </c>
+      <c r="K115" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L115" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M115" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="16">
       <c r="A116" s="4">
@@ -6676,15 +7424,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-      <c r="J116" s="18" t="n"/>
-      <c r="K116" s="18" t="n"/>
-      <c r="L116" s="18" t="n"/>
-      <c r="M116" s="18" t="n"/>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>https://www.indianmuseumkolkata.org/</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>https://www.indianmuseumkolkata.org/</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J116" s="18" t="inlineStr">
+        <is>
+          <t>Indian Museum Kolkata official site (indianmuseumkolkata.org) returns 403 from automated access but confirmed as official domain. Autonomous body under Ministry of Culture.</t>
+        </is>
+      </c>
+      <c r="K116" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L116" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M116" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="16">
       <c r="A117" s="4">
@@ -6736,15 +7518,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E118" s="18" t="n"/>
-      <c r="F118" s="18" t="n"/>
-      <c r="G118" s="18" t="n"/>
-      <c r="H118" s="18" t="n"/>
-      <c r="I118" s="18" t="n"/>
-      <c r="J118" s="18" t="n"/>
-      <c r="K118" s="18" t="n"/>
-      <c r="L118" s="18" t="n"/>
-      <c r="M118" s="18" t="n"/>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G118" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H118" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr">
+        <is>
+          <t>Department of Defence is under MoD. mod.gov.in is the official site but unreachable from this environment (connectivity/WAF issue). Deputation / civilian recruitment circulars posted on the MoD website. Confirmed official domain from multiple sources.</t>
+        </is>
+      </c>
+      <c r="K118" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L118" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M118" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="16">
       <c r="A119" s="4">
@@ -6766,15 +7582,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-      <c r="J119" s="18" t="n"/>
-      <c r="K119" s="18" t="n"/>
-      <c r="L119" s="18" t="n"/>
-      <c r="M119" s="18" t="n"/>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>https://ddpmod.gov.in/offerings/careers</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>https://ddpmod.gov.in/offerings/careers</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I119" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J119" s="18" t="inlineStr">
+        <is>
+          <t>Department of Defence Production careers page verified live. Handles policy for defence PSUs.</t>
+        </is>
+      </c>
+      <c r="K119" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L119" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M119" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="16">
       <c r="A120" s="4">
@@ -6796,15 +7646,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-      <c r="J120" s="18" t="n"/>
-      <c r="K120" s="18" t="n"/>
-      <c r="L120" s="18" t="n"/>
-      <c r="M120" s="18" t="n"/>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H120" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J120" s="18" t="inlineStr">
+        <is>
+          <t>Department of Military Affairs (DMA) has no separate website. Functions under MoD; civilian recruitment circulars through mod.gov.in. Site unreachable from this environment.</t>
+        </is>
+      </c>
+      <c r="K120" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L120" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M120" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="16">
       <c r="A121" s="4">
@@ -6826,15 +7710,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
-      <c r="G121" s="18" t="n"/>
-      <c r="H121" s="18" t="n"/>
-      <c r="I121" s="18" t="n"/>
-      <c r="J121" s="18" t="n"/>
-      <c r="K121" s="18" t="n"/>
-      <c r="L121" s="18" t="n"/>
-      <c r="M121" s="18" t="n"/>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>https://desw.gov.in/</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>https://desw.gov.in/</t>
+        </is>
+      </c>
+      <c r="G121" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H121" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I121" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J121" s="18" t="inlineStr">
+        <is>
+          <t>Department of Ex-Servicemen Welfare official site (desw.gov.in). Unreachable from this environment but confirmed as official domain. Handles ECHS and related welfare schemes.</t>
+        </is>
+      </c>
+      <c r="K121" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L121" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M121" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="16">
       <c r="A122" s="4">
@@ -6856,15 +7774,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-      <c r="J122" s="18" t="n"/>
-      <c r="K122" s="18" t="n"/>
-      <c r="L122" s="18" t="n"/>
-      <c r="M122" s="18" t="n"/>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I122" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J122" s="18" t="inlineStr">
+        <is>
+          <t>Integrated Defence Staff (IDS) has no independent recruitment portal. Functions under MoD; civilian posts on deputation via mod.gov.in circulars.</t>
+        </is>
+      </c>
+      <c r="K122" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L122" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M122" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="16">
       <c r="A123" s="4">
@@ -6886,15 +7838,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-      <c r="J123" s="18" t="n"/>
-      <c r="K123" s="18" t="n"/>
-      <c r="L123" s="18" t="n"/>
-      <c r="M123" s="18" t="n"/>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgqadefence.gov.in/</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgqadefence.gov.in/</t>
+        </is>
+      </c>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H123" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I123" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J123" s="18" t="inlineStr">
+        <is>
+          <t>DGQA official site (dgqadefence.gov.in). Unreachable from this environment but confirmed as official domain. Recruitment for civilian technical posts (Group B/C) through SSC and deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K123" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L123" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M123" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="16">
       <c r="A124" s="4">
@@ -6916,15 +7902,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E124" s="18" t="n"/>
-      <c r="F124" s="18" t="n"/>
-      <c r="G124" s="18" t="n"/>
-      <c r="H124" s="18" t="n"/>
-      <c r="I124" s="18" t="n"/>
-      <c r="J124" s="18" t="n"/>
-      <c r="K124" s="18" t="n"/>
-      <c r="L124" s="18" t="n"/>
-      <c r="M124" s="18" t="n"/>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H124" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I124" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J124" s="18" t="inlineStr">
+        <is>
+          <t>DGAQA - no independent public website found. Attached office under MoD handling aeronautical quality assurance. Recruitment through MoD/DDP channels.</t>
+        </is>
+      </c>
+      <c r="K124" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L124" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M124" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="16">
       <c r="A125" s="4">
@@ -6946,15 +7966,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-      <c r="G125" s="18" t="n"/>
-      <c r="H125" s="18" t="n"/>
-      <c r="I125" s="18" t="n"/>
-      <c r="J125" s="18" t="n"/>
-      <c r="K125" s="18" t="n"/>
-      <c r="L125" s="18" t="n"/>
-      <c r="M125" s="18" t="n"/>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G125" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H125" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J125" s="18" t="inlineStr">
+        <is>
+          <t>DGAV (Directorate General of Armoured Vehicles) - no independent public website found. Attached office under MoD. Civilian recruitment through MoD channels.</t>
+        </is>
+      </c>
+      <c r="K125" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L125" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M125" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="16">
       <c r="A126" s="4">
@@ -6976,15 +8030,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="18" t="n"/>
-      <c r="G126" s="18" t="n"/>
-      <c r="H126" s="18" t="n"/>
-      <c r="I126" s="18" t="n"/>
-      <c r="J126" s="18" t="n"/>
-      <c r="K126" s="18" t="n"/>
-      <c r="L126" s="18" t="n"/>
-      <c r="M126" s="18" t="n"/>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I126" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="inlineStr">
+        <is>
+          <t>Directorate of Standardisation - no independent public website found. Attached office under MoD. Recruitment through MoD channels and SSC for Group B/C.</t>
+        </is>
+      </c>
+      <c r="K126" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L126" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M126" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="16">
       <c r="A127" s="4">
@@ -7006,15 +8094,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-      <c r="J127" s="18" t="n"/>
-      <c r="K127" s="18" t="n"/>
-      <c r="L127" s="18" t="n"/>
-      <c r="M127" s="18" t="n"/>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>https://joinindianarmy.nic.in/</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>https://joinindianarmy.nic.in/</t>
+        </is>
+      </c>
+      <c r="G127" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H127" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I127" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>Army Headquarters civilian recruitment through joinindianarmy.nic.in and MoD circulars. Site unreachable from this environment but confirmed as official recruitment portal for Indian Army (both officer and civilian entries).</t>
+        </is>
+      </c>
+      <c r="K127" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L127" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M127" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="16">
       <c r="A128" s="4">
@@ -7036,15 +8158,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E128" s="18" t="n"/>
-      <c r="F128" s="18" t="n"/>
-      <c r="G128" s="18" t="n"/>
-      <c r="H128" s="18" t="n"/>
-      <c r="I128" s="18" t="n"/>
-      <c r="J128" s="18" t="n"/>
-      <c r="K128" s="18" t="n"/>
-      <c r="L128" s="18" t="n"/>
-      <c r="M128" s="18" t="n"/>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>https://www.joinindiannavy.gov.in/</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>https://www.joinindiannavy.gov.in/</t>
+        </is>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H128" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I128" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>Navy Headquarters uses joinindiannavy.gov.in for officer/sailor entries and civilian recruitment. Site unreachable from this environment but confirmed as official portal.</t>
+        </is>
+      </c>
+      <c r="K128" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L128" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M128" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="16">
       <c r="A129" s="4">
@@ -7066,15 +8222,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E129" s="18" t="n"/>
-      <c r="F129" s="18" t="n"/>
-      <c r="G129" s="18" t="n"/>
-      <c r="H129" s="18" t="n"/>
-      <c r="I129" s="18" t="n"/>
-      <c r="J129" s="18" t="n"/>
-      <c r="K129" s="18" t="n"/>
-      <c r="L129" s="18" t="n"/>
-      <c r="M129" s="18" t="n"/>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>https://indianairforce.nic.in/</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="inlineStr">
+        <is>
+          <t>https://indianairforce.nic.in/</t>
+        </is>
+      </c>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H129" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I129" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J129" s="18" t="inlineStr">
+        <is>
+          <t>Air Headquarters uses indianairforce.nic.in and afcat.cdac.in for recruitment. Site unreachable from this environment but confirmed as official domain. Civilian posts through SSC and MoD channels.</t>
+        </is>
+      </c>
+      <c r="K129" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L129" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M129" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="16">
       <c r="A130" s="4">
@@ -7096,15 +8286,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E130" s="18" t="n"/>
-      <c r="F130" s="18" t="n"/>
-      <c r="G130" s="18" t="n"/>
-      <c r="H130" s="18" t="n"/>
-      <c r="I130" s="18" t="n"/>
-      <c r="J130" s="18" t="n"/>
-      <c r="K130" s="18" t="n"/>
-      <c r="L130" s="18" t="n"/>
-      <c r="M130" s="18" t="n"/>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>https://www.indiancoastguard.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="inlineStr">
+        <is>
+          <t>https://www.indiancoastguard.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H130" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>Indian Coast Guard recruitment page verified live. Contains both uniformed and civilian post recruitment.</t>
+        </is>
+      </c>
+      <c r="K130" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L130" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M130" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="16">
       <c r="A131" s="4">
@@ -7126,15 +8350,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="18" t="n"/>
-      <c r="G131" s="18" t="n"/>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
-      <c r="J131" s="18" t="n"/>
-      <c r="K131" s="18" t="n"/>
-      <c r="L131" s="18" t="n"/>
-      <c r="M131" s="18" t="n"/>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>https://www.drdo.gov.in/drdo/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="inlineStr">
+        <is>
+          <t>https://www.drdo.gov.in/drdo/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I131" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J131" s="18" t="inlineStr">
+        <is>
+          <t>DRDO vacancies page verified live. RAC (Recruitment &amp; Assessment Centre) at rac.gov.in handles scientist recruitment (unreachable from here). Main DRDO page covers all vacancy categories.</t>
+        </is>
+      </c>
+      <c r="K131" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L131" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M131" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="16">
       <c r="A132" s="4">
@@ -7156,15 +8414,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E132" s="18" t="n"/>
-      <c r="F132" s="18" t="n"/>
-      <c r="G132" s="18" t="n"/>
-      <c r="H132" s="18" t="n"/>
-      <c r="I132" s="18" t="n"/>
-      <c r="J132" s="18" t="n"/>
-      <c r="K132" s="18" t="n"/>
-      <c r="L132" s="18" t="n"/>
-      <c r="M132" s="18" t="n"/>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>https://idsa.in/about/job</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>https://idsa.in/about/job</t>
+        </is>
+      </c>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H132" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I132" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J132" s="18" t="inlineStr">
+        <is>
+          <t>IDSA (now Manohar Parrikar Institute for Defence Studies and Analyses - MP-IDSA) job page verified live. Autonomous body under MoD.</t>
+        </is>
+      </c>
+      <c r="K132" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L132" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M132" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="16">
       <c r="A133" s="4">
@@ -7186,15 +8478,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E133" s="18" t="n"/>
-      <c r="F133" s="18" t="n"/>
-      <c r="G133" s="18" t="n"/>
-      <c r="H133" s="18" t="n"/>
-      <c r="I133" s="18" t="n"/>
-      <c r="J133" s="18" t="n"/>
-      <c r="K133" s="18" t="n"/>
-      <c r="L133" s="18" t="n"/>
-      <c r="M133" s="18" t="n"/>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>https://canttboardrecruit.org/</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr">
+        <is>
+          <t>https://canttboardrecruit.org/</t>
+        </is>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H133" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I133" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J133" s="18" t="inlineStr">
+        <is>
+          <t>Cantonment Board Recruitment portal verified live. Centralized portal for all Cantonment Boards across India. Statutory bodies under MoD.</t>
+        </is>
+      </c>
+      <c r="K133" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L133" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M133" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="16">
       <c r="A134" s="4">
@@ -7216,15 +8542,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E134" s="18" t="n"/>
-      <c r="F134" s="18" t="n"/>
-      <c r="G134" s="18" t="n"/>
-      <c r="H134" s="18" t="n"/>
-      <c r="I134" s="18" t="n"/>
-      <c r="J134" s="18" t="n"/>
-      <c r="K134" s="18" t="n"/>
-      <c r="L134" s="18" t="n"/>
-      <c r="M134" s="18" t="n"/>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>https://echs.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>https://echs.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H134" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I134" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J134" s="18" t="inlineStr">
+        <is>
+          <t>ECHS recruitment page verified live. Ex-Servicemen Contributory Health Scheme recruits medical and paramedical staff on contract/deputation basis.</t>
+        </is>
+      </c>
+      <c r="K134" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L134" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M134" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="16">
       <c r="A135" s="4">
@@ -7246,15 +8606,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E135" s="18" t="n"/>
-      <c r="F135" s="18" t="n"/>
-      <c r="G135" s="18" t="n"/>
-      <c r="H135" s="18" t="n"/>
-      <c r="I135" s="18" t="n"/>
-      <c r="J135" s="18" t="n"/>
-      <c r="K135" s="18" t="n"/>
-      <c r="L135" s="18" t="n"/>
-      <c r="M135" s="18" t="n"/>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>https://hal-india.co.in/careers</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>https://hal-india.co.in/careers</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>HAL careers page verified live. Major defence PSU under DDP/MoD.</t>
+        </is>
+      </c>
+      <c r="K135" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L135" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M135" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="16">
       <c r="A136" s="4">
@@ -7276,15 +8670,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="18" t="n"/>
-      <c r="G136" s="18" t="n"/>
-      <c r="H136" s="18" t="n"/>
-      <c r="I136" s="18" t="n"/>
-      <c r="J136" s="18" t="n"/>
-      <c r="K136" s="18" t="n"/>
-      <c r="L136" s="18" t="n"/>
-      <c r="M136" s="18" t="n"/>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>https://bel-india.in/job-notifications/</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>https://bel-india.in/job-notifications/</t>
+        </is>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H136" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="inlineStr">
+        <is>
+          <t>BEL job notifications page verified live. Defence PSU under DDP/MoD.</t>
+        </is>
+      </c>
+      <c r="K136" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L136" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M136" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="16">
       <c r="A137" s="4">
@@ -7306,15 +8734,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E137" s="18" t="n"/>
-      <c r="F137" s="18" t="n"/>
-      <c r="G137" s="18" t="n"/>
-      <c r="H137" s="18" t="n"/>
-      <c r="I137" s="18" t="n"/>
-      <c r="J137" s="18" t="n"/>
-      <c r="K137" s="18" t="n"/>
-      <c r="L137" s="18" t="n"/>
-      <c r="M137" s="18" t="n"/>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>https://bdl-india.in/recruitments</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>https://bdl-india.in/recruitments</t>
+        </is>
+      </c>
+      <c r="G137" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H137" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I137" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J137" s="18" t="inlineStr">
+        <is>
+          <t>BDL recruitments page verified live. Defence PSU under DDP/MoD.</t>
+        </is>
+      </c>
+      <c r="K137" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L137" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M137" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="16">
       <c r="A138" s="4">
@@ -7336,15 +8798,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E138" s="18" t="n"/>
-      <c r="F138" s="18" t="n"/>
-      <c r="G138" s="18" t="n"/>
-      <c r="H138" s="18" t="n"/>
-      <c r="I138" s="18" t="n"/>
-      <c r="J138" s="18" t="n"/>
-      <c r="K138" s="18" t="n"/>
-      <c r="L138" s="18" t="n"/>
-      <c r="M138" s="18" t="n"/>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>https://mazagondock.in/Career</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>https://mazagondock.in/Career</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J138" s="18" t="inlineStr">
+        <is>
+          <t>Mazagon Dock Shipbuilders career page verified live. Defence PSU under DDP/MoD.</t>
+        </is>
+      </c>
+      <c r="K138" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L138" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M138" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="16">
       <c r="A139" s="4">
@@ -7366,15 +8862,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E139" s="18" t="n"/>
-      <c r="F139" s="18" t="n"/>
-      <c r="G139" s="18" t="n"/>
-      <c r="H139" s="18" t="n"/>
-      <c r="I139" s="18" t="n"/>
-      <c r="J139" s="18" t="n"/>
-      <c r="K139" s="18" t="n"/>
-      <c r="L139" s="18" t="n"/>
-      <c r="M139" s="18" t="n"/>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>https://www.grse.in/career/</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr">
+        <is>
+          <t>https://www.grse.in/career/</t>
+        </is>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H139" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I139" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J139" s="18" t="inlineStr">
+        <is>
+          <t>GRSE career page verified live. Garden Reach Shipbuilders &amp; Engineers - defence PSU under DDP/MoD.</t>
+        </is>
+      </c>
+      <c r="K139" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L139" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M139" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="16">
       <c r="A140" s="4">
@@ -7426,15 +8956,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E141" s="18" t="n"/>
-      <c r="F141" s="18" t="n"/>
-      <c r="G141" s="18" t="n"/>
-      <c r="H141" s="18" t="n"/>
-      <c r="I141" s="18" t="n"/>
-      <c r="J141" s="18" t="n"/>
-      <c r="K141" s="18" t="n"/>
-      <c r="L141" s="18" t="n"/>
-      <c r="M141" s="18" t="n"/>
+      <c r="E141" s="17" t="inlineStr">
+        <is>
+          <t>https://mdoner.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr">
+        <is>
+          <t>https://mdoner.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G141" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H141" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I141" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J141" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of DoNER vacancy page verified live. Secretariat-level deputation and direct recruitment circulars posted here.</t>
+        </is>
+      </c>
+      <c r="K141" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L141" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M141" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="16">
       <c r="A142" s="4">
@@ -7456,15 +9020,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E142" s="18" t="n"/>
-      <c r="F142" s="18" t="n"/>
-      <c r="G142" s="18" t="n"/>
-      <c r="H142" s="18" t="n"/>
-      <c r="I142" s="18" t="n"/>
-      <c r="J142" s="18" t="n"/>
-      <c r="K142" s="18" t="n"/>
-      <c r="L142" s="18" t="n"/>
-      <c r="M142" s="18" t="n"/>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>https://necouncil.gov.in/index.php/notices/vacancy</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="inlineStr">
+        <is>
+          <t>https://necouncil.gov.in/index.php/notices/vacancy</t>
+        </is>
+      </c>
+      <c r="G142" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H142" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J142" s="18" t="inlineStr">
+        <is>
+          <t>North Eastern Council vacancy page verified live. Statutory body under Ministry of DoNER.</t>
+        </is>
+      </c>
+      <c r="K142" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L142" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M142" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="16">
       <c r="A143" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -9084,15 +9084,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-      <c r="G143" s="18" t="n"/>
-      <c r="H143" s="18" t="n"/>
-      <c r="I143" s="18" t="n"/>
-      <c r="J143" s="18" t="n"/>
-      <c r="K143" s="18" t="n"/>
-      <c r="L143" s="18" t="n"/>
-      <c r="M143" s="18" t="n"/>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nedfi.com/nedfi-recruitment/</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nedfi.com/nedfi-recruitment/</t>
+        </is>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H143" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I143" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="inlineStr">
+        <is>
+          <t>NEDFi recruitment page verified live. Autonomous body under Ministry of DoNER.</t>
+        </is>
+      </c>
+      <c r="K143" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L143" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M143" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="16">
       <c r="A144" s="4">
@@ -9114,15 +9148,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E144" s="18" t="n"/>
-      <c r="F144" s="18" t="n"/>
-      <c r="G144" s="18" t="n"/>
-      <c r="H144" s="18" t="n"/>
-      <c r="I144" s="18" t="n"/>
-      <c r="J144" s="18" t="n"/>
-      <c r="K144" s="18" t="n"/>
-      <c r="L144" s="18" t="n"/>
-      <c r="M144" s="18" t="n"/>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>https://necouncil.gov.in/index.php/notices/vacancy</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>https://necouncil.gov.in/index.php/notices/vacancy</t>
+        </is>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H144" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J144" s="18" t="inlineStr">
+        <is>
+          <t>NEC Regional/Field Offices have no separate website. Vacancies channeled through NEC vacancy page.</t>
+        </is>
+      </c>
+      <c r="K144" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L144" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M144" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="16">
       <c r="A145" s="4">
@@ -9174,15 +9242,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E146" s="18" t="n"/>
-      <c r="F146" s="18" t="n"/>
-      <c r="G146" s="18" t="n"/>
-      <c r="H146" s="18" t="n"/>
-      <c r="I146" s="18" t="n"/>
-      <c r="J146" s="18" t="n"/>
-      <c r="K146" s="18" t="n"/>
-      <c r="L146" s="18" t="n"/>
-      <c r="M146" s="18" t="n"/>
+      <c r="E146" s="17" t="inlineStr">
+        <is>
+          <t>https://moes.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>https://moes.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G146" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Earth Sciences vacancies page verified live. Secretariat-level recruitment and deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K146" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L146" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M146" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="16">
       <c r="A147" s="4">
@@ -9204,15 +9306,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E147" s="18" t="n"/>
-      <c r="F147" s="18" t="n"/>
-      <c r="G147" s="18" t="n"/>
-      <c r="H147" s="18" t="n"/>
-      <c r="I147" s="18" t="n"/>
-      <c r="J147" s="18" t="n"/>
-      <c r="K147" s="18" t="n"/>
-      <c r="L147" s="18" t="n"/>
-      <c r="M147" s="18" t="n"/>
+      <c r="E147" s="17" t="inlineStr">
+        <is>
+          <t>https://internal.imd.gov.in/pages/recruits_mausam.php</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>https://internal.imd.gov.in/pages/recruits_mausam.php</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="inlineStr">
+        <is>
+          <t>IMD recruitment page verified live (accessed via mausam.imd.gov.in portal). Contains both direct recruitment and deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K147" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L147" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M147" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="16">
       <c r="A148" s="4">
@@ -9234,15 +9370,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E148" s="18" t="n"/>
-      <c r="F148" s="18" t="n"/>
-      <c r="G148" s="18" t="n"/>
-      <c r="H148" s="18" t="n"/>
-      <c r="I148" s="18" t="n"/>
-      <c r="J148" s="18" t="n"/>
-      <c r="K148" s="18" t="n"/>
-      <c r="L148" s="18" t="n"/>
-      <c r="M148" s="18" t="n"/>
+      <c r="E148" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J148" s="18" t="inlineStr">
+        <is>
+          <t>GSI official site verified live. No deep-linkable recruitment sub-page found from this environment (JS-rendered portal). Recruitment primarily through UPSC (Geologist exam) and internal deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K148" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L148" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M148" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="16">
       <c r="A149" s="4">
@@ -9264,15 +9434,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E149" s="18" t="n"/>
-      <c r="F149" s="18" t="n"/>
-      <c r="G149" s="18" t="n"/>
-      <c r="H149" s="18" t="n"/>
-      <c r="I149" s="18" t="n"/>
-      <c r="J149" s="18" t="n"/>
-      <c r="K149" s="18" t="n"/>
-      <c r="L149" s="18" t="n"/>
-      <c r="M149" s="18" t="n"/>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>https://ncpor.res.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>https://ncpor.res.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J149" s="18" t="inlineStr">
+        <is>
+          <t>NCPOR recruitment page verified live. Autonomous body under MoES.</t>
+        </is>
+      </c>
+      <c r="K149" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L149" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M149" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="16">
       <c r="A150" s="4">
@@ -9294,15 +9498,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E150" s="18" t="n"/>
-      <c r="F150" s="18" t="n"/>
-      <c r="G150" s="18" t="n"/>
-      <c r="H150" s="18" t="n"/>
-      <c r="I150" s="18" t="n"/>
-      <c r="J150" s="18" t="n"/>
-      <c r="K150" s="18" t="n"/>
-      <c r="L150" s="18" t="n"/>
-      <c r="M150" s="18" t="n"/>
+      <c r="E150" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niot.res.in/recruitment_details.php</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niot.res.in/recruitment_details.php</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I150" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J150" s="18" t="inlineStr">
+        <is>
+          <t>NIOT recruitment details page verified live. Autonomous body under MoES.</t>
+        </is>
+      </c>
+      <c r="K150" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L150" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M150" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="16">
       <c r="A151" s="4">
@@ -9324,15 +9562,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E151" s="18" t="n"/>
-      <c r="F151" s="18" t="n"/>
-      <c r="G151" s="18" t="n"/>
-      <c r="H151" s="18" t="n"/>
-      <c r="I151" s="18" t="n"/>
-      <c r="J151" s="18" t="n"/>
-      <c r="K151" s="18" t="n"/>
-      <c r="L151" s="18" t="n"/>
-      <c r="M151" s="18" t="n"/>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>https://incois.gov.in/</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>https://incois.gov.in/</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J151" s="18" t="inlineStr">
+        <is>
+          <t>INCOIS official site verified live. No dedicated recruitment sub-page found from this environment. Recruitment notices appear on the main site. Autonomous body under MoES.</t>
+        </is>
+      </c>
+      <c r="K151" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L151" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M151" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="16">
       <c r="A152" s="4">
@@ -9354,15 +9626,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="18" t="n"/>
-      <c r="G152" s="18" t="n"/>
-      <c r="H152" s="18" t="n"/>
-      <c r="I152" s="18" t="n"/>
-      <c r="J152" s="18" t="n"/>
-      <c r="K152" s="18" t="n"/>
-      <c r="L152" s="18" t="n"/>
-      <c r="M152" s="18" t="n"/>
+      <c r="E152" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nccr.gov.in/?q=recruitment-view</t>
+        </is>
+      </c>
+      <c r="F152" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nccr.gov.in/?q=recruitment-view</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I152" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J152" s="18" t="inlineStr">
+        <is>
+          <t>NCCR recruitment page verified live. Autonomous body under MoES.</t>
+        </is>
+      </c>
+      <c r="K152" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L152" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M152" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="16">
       <c r="A153" s="4">
@@ -9384,15 +9690,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E153" s="18" t="n"/>
-      <c r="F153" s="18" t="n"/>
-      <c r="G153" s="18" t="n"/>
-      <c r="H153" s="18" t="n"/>
-      <c r="I153" s="18" t="n"/>
-      <c r="J153" s="18" t="n"/>
-      <c r="K153" s="18" t="n"/>
-      <c r="L153" s="18" t="n"/>
-      <c r="M153" s="18" t="n"/>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>https://internal.imd.gov.in/pages/recruits_mausam.php</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="inlineStr">
+        <is>
+          <t>https://internal.imd.gov.in/pages/recruits_mausam.php</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J153" s="18" t="inlineStr">
+        <is>
+          <t>IMD Regional/Field Offices recruit through the central IMD recruitment page. No separate portals.</t>
+        </is>
+      </c>
+      <c r="K153" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L153" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M153" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="16">
       <c r="A154" s="4">
@@ -9414,15 +9754,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E154" s="18" t="n"/>
-      <c r="F154" s="18" t="n"/>
-      <c r="G154" s="18" t="n"/>
-      <c r="H154" s="18" t="n"/>
-      <c r="I154" s="18" t="n"/>
-      <c r="J154" s="18" t="n"/>
-      <c r="K154" s="18" t="n"/>
-      <c r="L154" s="18" t="n"/>
-      <c r="M154" s="18" t="n"/>
+      <c r="E154" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F154" s="17" t="inlineStr">
+        <is>
+          <t>https://www.gsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J154" s="18" t="inlineStr">
+        <is>
+          <t>GSI Regional/State Units recruit through the central GSI portal. No separate recruitment pages.</t>
+        </is>
+      </c>
+      <c r="K154" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L154" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M154" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="16">
       <c r="A155" s="4">
@@ -9474,15 +9848,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E156" s="18" t="n"/>
-      <c r="F156" s="18" t="n"/>
-      <c r="G156" s="18" t="n"/>
-      <c r="H156" s="18" t="n"/>
-      <c r="I156" s="18" t="n"/>
-      <c r="J156" s="18" t="n"/>
-      <c r="K156" s="18" t="n"/>
-      <c r="L156" s="18" t="n"/>
-      <c r="M156" s="18" t="n"/>
+      <c r="E156" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J156" s="18" t="inlineStr">
+        <is>
+          <t>Department of School Education &amp; Literacy vacancies page verified live (shared Ministry of Education site).</t>
+        </is>
+      </c>
+      <c r="K156" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L156" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M156" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="16">
       <c r="A157" s="4">
@@ -9504,15 +9912,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E157" s="18" t="n"/>
-      <c r="F157" s="18" t="n"/>
-      <c r="G157" s="18" t="n"/>
-      <c r="H157" s="18" t="n"/>
-      <c r="I157" s="18" t="n"/>
-      <c r="J157" s="18" t="n"/>
-      <c r="K157" s="18" t="n"/>
-      <c r="L157" s="18" t="n"/>
-      <c r="M157" s="18" t="n"/>
+      <c r="E157" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J157" s="18" t="inlineStr">
+        <is>
+          <t>Department of Higher Education uses the same Ministry of Education vacancies page.</t>
+        </is>
+      </c>
+      <c r="K157" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L157" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M157" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="16">
       <c r="A158" s="4">
@@ -9534,15 +9976,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E158" s="18" t="n"/>
-      <c r="F158" s="18" t="n"/>
-      <c r="G158" s="18" t="n"/>
-      <c r="H158" s="18" t="n"/>
-      <c r="I158" s="18" t="n"/>
-      <c r="J158" s="18" t="n"/>
-      <c r="K158" s="18" t="n"/>
-      <c r="L158" s="18" t="n"/>
-      <c r="M158" s="18" t="n"/>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>https://kvsangathan.nic.in/</t>
+        </is>
+      </c>
+      <c r="F158" s="17" t="inlineStr">
+        <is>
+          <t>https://kvsangathan.nic.in/</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I158" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J158" s="18" t="inlineStr">
+        <is>
+          <t>KVS official site (kvsangathan.nic.in). Unreachable from this environment but confirmed as official domain. Major recruitment drives (TGT/PGT/PRT) via this portal.</t>
+        </is>
+      </c>
+      <c r="K158" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L158" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M158" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="16">
       <c r="A159" s="4">
@@ -9564,15 +10040,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="18" t="n"/>
-      <c r="G159" s="18" t="n"/>
-      <c r="H159" s="18" t="n"/>
-      <c r="I159" s="18" t="n"/>
-      <c r="J159" s="18" t="n"/>
-      <c r="K159" s="18" t="n"/>
-      <c r="L159" s="18" t="n"/>
-      <c r="M159" s="18" t="n"/>
+      <c r="E159" s="17" t="inlineStr">
+        <is>
+          <t>https://navodaya.gov.in/nvs/en/Recruitment/Recruitment.html</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="inlineStr">
+        <is>
+          <t>https://navodaya.gov.in/nvs/en/Recruitment/Recruitment.html</t>
+        </is>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H159" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I159" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J159" s="18" t="inlineStr">
+        <is>
+          <t>NVS recruitment page. Site unreachable from this environment but confirmed as official URL from multiple sources. Large recruitment drives for teachers and non-teaching staff.</t>
+        </is>
+      </c>
+      <c r="K159" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L159" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M159" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="16">
       <c r="A160" s="4">
@@ -9594,15 +10104,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E160" s="18" t="n"/>
-      <c r="F160" s="18" t="n"/>
-      <c r="G160" s="18" t="n"/>
-      <c r="H160" s="18" t="n"/>
-      <c r="I160" s="18" t="n"/>
-      <c r="J160" s="18" t="n"/>
-      <c r="K160" s="18" t="n"/>
-      <c r="L160" s="18" t="n"/>
-      <c r="M160" s="18" t="n"/>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>https://ncert.nic.in/</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="inlineStr">
+        <is>
+          <t>https://ncert.nic.in/</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I160" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J160" s="18" t="inlineStr">
+        <is>
+          <t>NCERT official site (ncert.nic.in). Unreachable from this environment but confirmed as official domain. Recruitment for academic and non-academic posts.</t>
+        </is>
+      </c>
+      <c r="K160" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L160" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M160" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="16">
       <c r="A161" s="4">
@@ -9624,15 +10168,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E161" s="18" t="n"/>
-      <c r="F161" s="18" t="n"/>
-      <c r="G161" s="18" t="n"/>
-      <c r="H161" s="18" t="n"/>
-      <c r="I161" s="18" t="n"/>
-      <c r="J161" s="18" t="n"/>
-      <c r="K161" s="18" t="n"/>
-      <c r="L161" s="18" t="n"/>
-      <c r="M161" s="18" t="n"/>
+      <c r="E161" s="17" t="inlineStr">
+        <is>
+          <t>https://ctsa.nic.in/</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="inlineStr">
+        <is>
+          <t>https://ctsa.nic.in/</t>
+        </is>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H161" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I161" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J161" s="18" t="inlineStr">
+        <is>
+          <t>CTSA (Central Tibetan Schools Administration) site unreachable from this environment. Confirmed as official domain. Small attached office under Ministry of Education.</t>
+        </is>
+      </c>
+      <c r="K161" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L161" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M161" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="16">
       <c r="A162" s="4">
@@ -9654,15 +10232,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E162" s="18" t="n"/>
-      <c r="F162" s="18" t="n"/>
-      <c r="G162" s="18" t="n"/>
-      <c r="H162" s="18" t="n"/>
-      <c r="I162" s="18" t="n"/>
-      <c r="J162" s="18" t="n"/>
-      <c r="K162" s="18" t="n"/>
-      <c r="L162" s="18" t="n"/>
-      <c r="M162" s="18" t="n"/>
+      <c r="E162" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ugc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F162" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ugc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H162" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I162" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J162" s="18" t="inlineStr">
+        <is>
+          <t>UGC official site returns 403 from automated access but confirmed as official domain. Statutory body under Ministry of Education. Recruitment for UGC posts on website.</t>
+        </is>
+      </c>
+      <c r="K162" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L162" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M162" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="16">
       <c r="A163" s="4">
@@ -9684,15 +10296,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="18" t="n"/>
-      <c r="G163" s="18" t="n"/>
-      <c r="H163" s="18" t="n"/>
-      <c r="I163" s="18" t="n"/>
-      <c r="J163" s="18" t="n"/>
-      <c r="K163" s="18" t="n"/>
-      <c r="L163" s="18" t="n"/>
-      <c r="M163" s="18" t="n"/>
+      <c r="E163" s="17" t="inlineStr">
+        <is>
+          <t>https://www.aicte-india.org/</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="inlineStr">
+        <is>
+          <t>https://www.aicte-india.org/</t>
+        </is>
+      </c>
+      <c r="G163" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H163" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I163" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J163" s="18" t="inlineStr">
+        <is>
+          <t>AICTE official site. Unreachable from this environment but confirmed as official domain. Statutory body under Ministry of Education.</t>
+        </is>
+      </c>
+      <c r="K163" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L163" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M163" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="16">
       <c r="A164" s="4">
@@ -9714,15 +10360,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E164" s="18" t="n"/>
-      <c r="F164" s="18" t="n"/>
-      <c r="G164" s="18" t="n"/>
-      <c r="H164" s="18" t="n"/>
-      <c r="I164" s="18" t="n"/>
-      <c r="J164" s="18" t="n"/>
-      <c r="K164" s="18" t="n"/>
-      <c r="L164" s="18" t="n"/>
-      <c r="M164" s="18" t="n"/>
+      <c r="E164" s="17" t="inlineStr">
+        <is>
+          <t>https://ncte.gov.in/</t>
+        </is>
+      </c>
+      <c r="F164" s="17" t="inlineStr">
+        <is>
+          <t>https://ncte.gov.in/</t>
+        </is>
+      </c>
+      <c r="G164" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H164" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I164" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J164" s="18" t="inlineStr">
+        <is>
+          <t>NCTE official site. Unreachable from this environment but confirmed as official domain. Statutory body under Ministry of Education.</t>
+        </is>
+      </c>
+      <c r="K164" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L164" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M164" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="16">
       <c r="A165" s="4">
@@ -9744,15 +10424,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
-      <c r="G165" s="18" t="n"/>
-      <c r="H165" s="18" t="n"/>
-      <c r="I165" s="18" t="n"/>
-      <c r="J165" s="18" t="n"/>
-      <c r="K165" s="18" t="n"/>
-      <c r="L165" s="18" t="n"/>
-      <c r="M165" s="18" t="n"/>
+      <c r="E165" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F165" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H165" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I165" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J165" s="18" t="inlineStr">
+        <is>
+          <t>IITs recruit independently through their own websites. This is a collective entry; Ministry of Education vacancies page is the parent reference. Individual IIT recruitment at respective iitX.ac.in/careers pages.</t>
+        </is>
+      </c>
+      <c r="K165" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L165" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M165" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="16">
       <c r="A166" s="4">
@@ -9774,15 +10488,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-      <c r="G166" s="18" t="n"/>
-      <c r="H166" s="18" t="n"/>
-      <c r="I166" s="18" t="n"/>
-      <c r="J166" s="18" t="n"/>
-      <c r="K166" s="18" t="n"/>
-      <c r="L166" s="18" t="n"/>
-      <c r="M166" s="18" t="n"/>
+      <c r="E166" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F166" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G166" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H166" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I166" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J166" s="18" t="inlineStr">
+        <is>
+          <t>IIMs recruit independently through their own websites. Collective entry; Ministry of Education vacancies page as parent reference. Individual IIM recruitment at respective iimX.ac.in/careers pages.</t>
+        </is>
+      </c>
+      <c r="K166" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L166" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M166" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="16">
       <c r="A167" s="4">
@@ -9804,15 +10552,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E167" s="18" t="n"/>
-      <c r="F167" s="18" t="n"/>
-      <c r="G167" s="18" t="n"/>
-      <c r="H167" s="18" t="n"/>
-      <c r="I167" s="18" t="n"/>
-      <c r="J167" s="18" t="n"/>
-      <c r="K167" s="18" t="n"/>
-      <c r="L167" s="18" t="n"/>
-      <c r="M167" s="18" t="n"/>
+      <c r="E167" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F167" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H167" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I167" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J167" s="18" t="inlineStr">
+        <is>
+          <t>Central Universities recruit independently. Collective entry; Ministry of Education vacancies page as parent reference. Individual university recruitment at respective university websites.</t>
+        </is>
+      </c>
+      <c r="K167" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L167" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M167" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="16">
       <c r="A168" s="4">
@@ -9834,15 +10616,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E168" s="18" t="n"/>
-      <c r="F168" s="18" t="n"/>
-      <c r="G168" s="18" t="n"/>
-      <c r="H168" s="18" t="n"/>
-      <c r="I168" s="18" t="n"/>
-      <c r="J168" s="18" t="n"/>
-      <c r="K168" s="18" t="n"/>
-      <c r="L168" s="18" t="n"/>
-      <c r="M168" s="18" t="n"/>
+      <c r="E168" s="17" t="inlineStr">
+        <is>
+          <t>https://niepa.ac.in/jobs.aspx</t>
+        </is>
+      </c>
+      <c r="F168" s="17" t="inlineStr">
+        <is>
+          <t>https://niepa.ac.in/jobs.aspx</t>
+        </is>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H168" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I168" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J168" s="18" t="inlineStr">
+        <is>
+          <t>NIEPA jobs page verified live. Autonomous body under Ministry of Education.</t>
+        </is>
+      </c>
+      <c r="K168" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L168" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M168" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="16">
       <c r="A169" s="4">
@@ -9864,15 +10680,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
-      <c r="H169" s="18" t="n"/>
-      <c r="I169" s="18" t="n"/>
-      <c r="J169" s="18" t="n"/>
-      <c r="K169" s="18" t="n"/>
-      <c r="L169" s="18" t="n"/>
-      <c r="M169" s="18" t="n"/>
+      <c r="E169" s="17" t="inlineStr">
+        <is>
+          <t>https://nta.ac.in/</t>
+        </is>
+      </c>
+      <c r="F169" s="17" t="inlineStr">
+        <is>
+          <t>https://nta.ac.in/</t>
+        </is>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H169" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I169" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J169" s="18" t="inlineStr">
+        <is>
+          <t>NTA official site verified live. Recruitment portal at ntarecruitment.ntaonline.in (unreachable from here). NTA primarily conducts exams; internal staff recruitment through nta.ac.in.</t>
+        </is>
+      </c>
+      <c r="K169" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L169" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M169" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="16">
       <c r="A170" s="4">
@@ -9894,15 +10744,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="18" t="n"/>
-      <c r="G170" s="18" t="n"/>
-      <c r="H170" s="18" t="n"/>
-      <c r="I170" s="18" t="n"/>
-      <c r="J170" s="18" t="n"/>
-      <c r="K170" s="18" t="n"/>
-      <c r="L170" s="18" t="n"/>
-      <c r="M170" s="18" t="n"/>
+      <c r="E170" s="17" t="inlineStr">
+        <is>
+          <t>https://kvsangathan.nic.in/</t>
+        </is>
+      </c>
+      <c r="F170" s="17" t="inlineStr">
+        <is>
+          <t>https://kvsangathan.nic.in/</t>
+        </is>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H170" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I170" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J170" s="18" t="inlineStr">
+        <is>
+          <t>Regional offices of KVS/NVS recruit through their respective central portals (kvsangathan.nic.in / navodaya.gov.in). No separate regional recruitment pages.</t>
+        </is>
+      </c>
+      <c r="K170" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L170" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M170" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="16">
       <c r="A171" s="4">
@@ -9954,15 +10838,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="18" t="n"/>
-      <c r="G172" s="18" t="n"/>
-      <c r="H172" s="18" t="n"/>
-      <c r="I172" s="18" t="n"/>
-      <c r="J172" s="18" t="n"/>
-      <c r="K172" s="18" t="n"/>
-      <c r="L172" s="18" t="n"/>
-      <c r="M172" s="18" t="n"/>
+      <c r="E172" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F172" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H172" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I172" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J172" s="18" t="inlineStr">
+        <is>
+          <t>MeitY vacancies page verified live. Secretariat-level recruitment and deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K172" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L172" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M172" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="16">
       <c r="A173" s="4">
@@ -9984,15 +10902,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E173" s="18" t="n"/>
-      <c r="F173" s="18" t="n"/>
-      <c r="G173" s="18" t="n"/>
-      <c r="H173" s="18" t="n"/>
-      <c r="I173" s="18" t="n"/>
-      <c r="J173" s="18" t="n"/>
-      <c r="K173" s="18" t="n"/>
-      <c r="L173" s="18" t="n"/>
-      <c r="M173" s="18" t="n"/>
+      <c r="E173" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nic.in/careers</t>
+        </is>
+      </c>
+      <c r="F173" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nic.in/careers</t>
+        </is>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H173" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I173" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J173" s="18" t="inlineStr">
+        <is>
+          <t>NIC careers page verified live. Attached office under MeitY. Scientist recruitment through NIC's own portal.</t>
+        </is>
+      </c>
+      <c r="K173" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L173" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M173" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="16">
       <c r="A174" s="4">
@@ -10014,15 +10966,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E174" s="18" t="n"/>
-      <c r="F174" s="18" t="n"/>
-      <c r="G174" s="18" t="n"/>
-      <c r="H174" s="18" t="n"/>
-      <c r="I174" s="18" t="n"/>
-      <c r="J174" s="18" t="n"/>
-      <c r="K174" s="18" t="n"/>
-      <c r="L174" s="18" t="n"/>
-      <c r="M174" s="18" t="n"/>
+      <c r="E174" s="17" t="inlineStr">
+        <is>
+          <t>https://stqc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F174" s="17" t="inlineStr">
+        <is>
+          <t>https://stqc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H174" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I174" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J174" s="18" t="inlineStr">
+        <is>
+          <t>STQC official site (stqc.gov.in). Unreachable from this environment but confirmed as official domain. Attached office under MeitY.</t>
+        </is>
+      </c>
+      <c r="K174" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L174" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M174" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="16">
       <c r="A175" s="4">
@@ -10044,15 +11030,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E175" s="18" t="n"/>
-      <c r="F175" s="18" t="n"/>
-      <c r="G175" s="18" t="n"/>
-      <c r="H175" s="18" t="n"/>
-      <c r="I175" s="18" t="n"/>
-      <c r="J175" s="18" t="n"/>
-      <c r="K175" s="18" t="n"/>
-      <c r="L175" s="18" t="n"/>
-      <c r="M175" s="18" t="n"/>
+      <c r="E175" s="17" t="inlineStr">
+        <is>
+          <t>https://cca.gov.in/</t>
+        </is>
+      </c>
+      <c r="F175" s="17" t="inlineStr">
+        <is>
+          <t>https://cca.gov.in/</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H175" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I175" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J175" s="18" t="inlineStr">
+        <is>
+          <t>CCA (Controller of Certifying Authorities) site verified live. Attached office under MeitY. Small office; recruitment via MeitY/DoPT channels.</t>
+        </is>
+      </c>
+      <c r="K175" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L175" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M175" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="16">
       <c r="A176" s="4">
@@ -10074,15 +11094,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-      <c r="G176" s="18" t="n"/>
-      <c r="H176" s="18" t="n"/>
-      <c r="I176" s="18" t="n"/>
-      <c r="J176" s="18" t="n"/>
-      <c r="K176" s="18" t="n"/>
-      <c r="L176" s="18" t="n"/>
-      <c r="M176" s="18" t="n"/>
+      <c r="E176" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cdac.in/index.aspx?id=st_careers</t>
+        </is>
+      </c>
+      <c r="F176" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cdac.in/index.aspx?id=st_careers</t>
+        </is>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H176" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I176" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J176" s="18" t="inlineStr">
+        <is>
+          <t>C-DAC careers page verified live. Autonomous body under MeitY. Active recruitment for Project Engineers and Scientists.</t>
+        </is>
+      </c>
+      <c r="K176" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L176" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M176" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="15.75" customHeight="1" s="16">
       <c r="A177" s="4">
@@ -10104,15 +11158,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E177" s="18" t="n"/>
-      <c r="F177" s="18" t="n"/>
-      <c r="G177" s="18" t="n"/>
-      <c r="H177" s="18" t="n"/>
-      <c r="I177" s="18" t="n"/>
-      <c r="J177" s="18" t="n"/>
-      <c r="K177" s="18" t="n"/>
-      <c r="L177" s="18" t="n"/>
-      <c r="M177" s="18" t="n"/>
+      <c r="E177" s="17" t="inlineStr">
+        <is>
+          <t>https://negd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F177" s="17" t="inlineStr">
+        <is>
+          <t>https://negd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H177" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I177" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J177" s="18" t="inlineStr">
+        <is>
+          <t>NeGD official site verified live. Autonomous body under MeitY. Small team; recruitment mainly on contract/deputation.</t>
+        </is>
+      </c>
+      <c r="K177" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L177" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M177" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="15.75" customHeight="1" s="16">
       <c r="A178" s="4">
@@ -10134,15 +11222,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="18" t="n"/>
-      <c r="G178" s="18" t="n"/>
-      <c r="H178" s="18" t="n"/>
-      <c r="I178" s="18" t="n"/>
-      <c r="J178" s="18" t="n"/>
-      <c r="K178" s="18" t="n"/>
-      <c r="L178" s="18" t="n"/>
-      <c r="M178" s="18" t="n"/>
+      <c r="E178" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sameer.gov.in/</t>
+        </is>
+      </c>
+      <c r="F178" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sameer.gov.in/</t>
+        </is>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H178" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I178" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J178" s="18" t="inlineStr">
+        <is>
+          <t>SAMEER official site returns 500 error. Confirmed as official domain from multiple sources. Autonomous body under MeitY. Recruitment for Scientists/Engineers.</t>
+        </is>
+      </c>
+      <c r="K178" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L178" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M178" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="16">
       <c r="A179" s="4">
@@ -10164,15 +11286,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E179" s="18" t="n"/>
-      <c r="F179" s="18" t="n"/>
-      <c r="G179" s="18" t="n"/>
-      <c r="H179" s="18" t="n"/>
-      <c r="I179" s="18" t="n"/>
-      <c r="J179" s="18" t="n"/>
-      <c r="K179" s="18" t="n"/>
-      <c r="L179" s="18" t="n"/>
-      <c r="M179" s="18" t="n"/>
+      <c r="E179" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cert-in.org.in/</t>
+        </is>
+      </c>
+      <c r="F179" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cert-in.org.in/</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H179" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I179" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J179" s="18" t="inlineStr">
+        <is>
+          <t>CERT-In official site verified live. Autonomous body under MeitY. Staff primarily on deputation from other government departments.</t>
+        </is>
+      </c>
+      <c r="K179" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L179" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M179" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="16">
       <c r="A180" s="4">
@@ -10194,15 +11350,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-      <c r="G180" s="18" t="n"/>
-      <c r="H180" s="18" t="n"/>
-      <c r="I180" s="18" t="n"/>
-      <c r="J180" s="18" t="n"/>
-      <c r="K180" s="18" t="n"/>
-      <c r="L180" s="18" t="n"/>
-      <c r="M180" s="18" t="n"/>
+      <c r="E180" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F180" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H180" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I180" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J180" s="18" t="inlineStr">
+        <is>
+          <t>Digital Personal Data Protection Board (DPDP Board) is newly constituted (2024). No independent website yet. Recruitment through MeitY channels.</t>
+        </is>
+      </c>
+      <c r="K180" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L180" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M180" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="16">
       <c r="A181" s="4">
@@ -10224,15 +11414,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
-      <c r="H181" s="18" t="n"/>
-      <c r="I181" s="18" t="n"/>
-      <c r="J181" s="18" t="n"/>
-      <c r="K181" s="18" t="n"/>
-      <c r="L181" s="18" t="n"/>
-      <c r="M181" s="18" t="n"/>
+      <c r="E181" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nic.in/careers</t>
+        </is>
+      </c>
+      <c r="F181" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nic.in/careers</t>
+        </is>
+      </c>
+      <c r="G181" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H181" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I181" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J181" s="18" t="inlineStr">
+        <is>
+          <t>NIC State/District Informatics Units are field offices of NIC. Recruitment handled centrally through NIC careers page.</t>
+        </is>
+      </c>
+      <c r="K181" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L181" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M181" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="16">
       <c r="A182" s="4">
@@ -10284,15 +11508,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="18" t="n"/>
-      <c r="G183" s="18" t="n"/>
-      <c r="H183" s="18" t="n"/>
-      <c r="I183" s="18" t="n"/>
-      <c r="J183" s="18" t="n"/>
-      <c r="K183" s="18" t="n"/>
-      <c r="L183" s="18" t="n"/>
-      <c r="M183" s="18" t="n"/>
+      <c r="E183" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F183" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H183" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I183" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J183" s="18" t="inlineStr">
+        <is>
+          <t>MoEFCC Secretariat vacancy circulars page verified live. Contains deputation and direct recruitment circulars.</t>
+        </is>
+      </c>
+      <c r="K183" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L183" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M183" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="16">
       <c r="A184" s="4">
@@ -10314,15 +11572,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E184" s="18" t="n"/>
-      <c r="F184" s="18" t="n"/>
-      <c r="G184" s="18" t="n"/>
-      <c r="H184" s="18" t="n"/>
-      <c r="I184" s="18" t="n"/>
-      <c r="J184" s="18" t="n"/>
-      <c r="K184" s="18" t="n"/>
-      <c r="L184" s="18" t="n"/>
-      <c r="M184" s="18" t="n"/>
+      <c r="E184" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F184" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H184" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I184" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J184" s="18" t="inlineStr">
+        <is>
+          <t>Forest Conservation Division is a division within MoEFCC Secretariat. No separate website; vacancy circulars on parent ministry page.</t>
+        </is>
+      </c>
+      <c r="K184" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L184" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M184" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="16">
       <c r="A185" s="4">
@@ -10344,15 +11636,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E185" s="18" t="n"/>
-      <c r="F185" s="18" t="n"/>
-      <c r="G185" s="18" t="n"/>
-      <c r="H185" s="18" t="n"/>
-      <c r="I185" s="18" t="n"/>
-      <c r="J185" s="18" t="n"/>
-      <c r="K185" s="18" t="n"/>
-      <c r="L185" s="18" t="n"/>
-      <c r="M185" s="18" t="n"/>
+      <c r="E185" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F185" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H185" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I185" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J185" s="18" t="inlineStr">
+        <is>
+          <t>Wildlife Division is a division within MoEFCC Secretariat. No separate website; vacancy circulars on parent ministry page.</t>
+        </is>
+      </c>
+      <c r="K185" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L185" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M185" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="16">
       <c r="A186" s="4">
@@ -10374,15 +11700,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E186" s="18" t="n"/>
-      <c r="F186" s="18" t="n"/>
-      <c r="G186" s="18" t="n"/>
-      <c r="H186" s="18" t="n"/>
-      <c r="I186" s="18" t="n"/>
-      <c r="J186" s="18" t="n"/>
-      <c r="K186" s="18" t="n"/>
-      <c r="L186" s="18" t="n"/>
-      <c r="M186" s="18" t="n"/>
+      <c r="E186" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F186" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H186" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I186" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J186" s="18" t="inlineStr">
+        <is>
+          <t>Climate Change Division is within MoEFCC Secretariat. No separate website.</t>
+        </is>
+      </c>
+      <c r="K186" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L186" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M186" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="16">
       <c r="A187" s="4">
@@ -10404,15 +11764,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E187" s="18" t="n"/>
-      <c r="F187" s="18" t="n"/>
-      <c r="G187" s="18" t="n"/>
-      <c r="H187" s="18" t="n"/>
-      <c r="I187" s="18" t="n"/>
-      <c r="J187" s="18" t="n"/>
-      <c r="K187" s="18" t="n"/>
-      <c r="L187" s="18" t="n"/>
-      <c r="M187" s="18" t="n"/>
+      <c r="E187" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F187" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G187" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H187" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I187" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J187" s="18" t="inlineStr">
+        <is>
+          <t>EIA Division is within MoEFCC Secretariat. No separate website.</t>
+        </is>
+      </c>
+      <c r="K187" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L187" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M187" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="16">
       <c r="A188" s="4">
@@ -10434,15 +11828,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E188" s="18" t="n"/>
-      <c r="F188" s="18" t="n"/>
-      <c r="G188" s="18" t="n"/>
-      <c r="H188" s="18" t="n"/>
-      <c r="I188" s="18" t="n"/>
-      <c r="J188" s="18" t="n"/>
-      <c r="K188" s="18" t="n"/>
-      <c r="L188" s="18" t="n"/>
-      <c r="M188" s="18" t="n"/>
+      <c r="E188" s="17" t="inlineStr">
+        <is>
+          <t>https://bsi.gov.in/page/en/vacancies</t>
+        </is>
+      </c>
+      <c r="F188" s="17" t="inlineStr">
+        <is>
+          <t>https://bsi.gov.in/page/en/vacancies</t>
+        </is>
+      </c>
+      <c r="G188" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H188" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I188" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J188" s="18" t="inlineStr">
+        <is>
+          <t>Botanical Survey of India vacancies page verified live. Attached office under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K188" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L188" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M188" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="16">
       <c r="A189" s="4">
@@ -10464,15 +11892,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E189" s="18" t="n"/>
-      <c r="F189" s="18" t="n"/>
-      <c r="G189" s="18" t="n"/>
-      <c r="H189" s="18" t="n"/>
-      <c r="I189" s="18" t="n"/>
-      <c r="J189" s="18" t="n"/>
-      <c r="K189" s="18" t="n"/>
-      <c r="L189" s="18" t="n"/>
-      <c r="M189" s="18" t="n"/>
+      <c r="E189" s="17" t="inlineStr">
+        <is>
+          <t>https://zsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F189" s="17" t="inlineStr">
+        <is>
+          <t>https://zsi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G189" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H189" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I189" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J189" s="18" t="inlineStr">
+        <is>
+          <t>Zoological Survey of India official site (zsi.gov.in). Unreachable from this environment but confirmed as official domain. Attached office under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K189" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L189" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M189" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="16">
       <c r="A190" s="4">
@@ -10494,15 +11956,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E190" s="18" t="n"/>
-      <c r="F190" s="18" t="n"/>
-      <c r="G190" s="18" t="n"/>
-      <c r="H190" s="18" t="n"/>
-      <c r="I190" s="18" t="n"/>
-      <c r="J190" s="18" t="n"/>
-      <c r="K190" s="18" t="n"/>
-      <c r="L190" s="18" t="n"/>
-      <c r="M190" s="18" t="n"/>
+      <c r="E190" s="17" t="inlineStr">
+        <is>
+          <t>https://fsi.nic.in/</t>
+        </is>
+      </c>
+      <c r="F190" s="17" t="inlineStr">
+        <is>
+          <t>https://fsi.nic.in/</t>
+        </is>
+      </c>
+      <c r="G190" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H190" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I190" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J190" s="18" t="inlineStr">
+        <is>
+          <t>Forest Survey of India site verified live. No dedicated recruitment sub-page found; recruitment through MoEFCC/IFS cadre channels. Attached office under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K190" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L190" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M190" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="16">
       <c r="A191" s="4">
@@ -10524,15 +12020,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E191" s="18" t="n"/>
-      <c r="F191" s="18" t="n"/>
-      <c r="G191" s="18" t="n"/>
-      <c r="H191" s="18" t="n"/>
-      <c r="I191" s="18" t="n"/>
-      <c r="J191" s="18" t="n"/>
-      <c r="K191" s="18" t="n"/>
-      <c r="L191" s="18" t="n"/>
-      <c r="M191" s="18" t="n"/>
+      <c r="E191" s="17" t="inlineStr">
+        <is>
+          <t>https://wii.gov.in/recruitments</t>
+        </is>
+      </c>
+      <c r="F191" s="17" t="inlineStr">
+        <is>
+          <t>https://wii.gov.in/recruitments</t>
+        </is>
+      </c>
+      <c r="G191" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H191" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I191" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J191" s="18" t="inlineStr">
+        <is>
+          <t>Wildlife Institute of India recruitments page verified live. Autonomous/attached body under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K191" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L191" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M191" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="16">
       <c r="A192" s="4">
@@ -10554,15 +12084,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E192" s="18" t="n"/>
-      <c r="F192" s="18" t="n"/>
-      <c r="G192" s="18" t="n"/>
-      <c r="H192" s="18" t="n"/>
-      <c r="I192" s="18" t="n"/>
-      <c r="J192" s="18" t="n"/>
-      <c r="K192" s="18" t="n"/>
-      <c r="L192" s="18" t="n"/>
-      <c r="M192" s="18" t="n"/>
+      <c r="E192" s="17" t="inlineStr">
+        <is>
+          <t>https://ignfa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F192" s="17" t="inlineStr">
+        <is>
+          <t>https://ignfa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G192" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H192" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I192" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J192" s="18" t="inlineStr">
+        <is>
+          <t>IGNFA official site returns 403 from automated access but confirmed as official domain. Premier training academy for IFS officers under MoEFCC. Limited external recruitment.</t>
+        </is>
+      </c>
+      <c r="K192" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L192" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M192" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="16">
       <c r="A193" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -12148,15 +12148,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E193" s="18" t="n"/>
-      <c r="F193" s="18" t="n"/>
-      <c r="G193" s="18" t="n"/>
-      <c r="H193" s="18" t="n"/>
-      <c r="I193" s="18" t="n"/>
-      <c r="J193" s="18" t="n"/>
-      <c r="K193" s="18" t="n"/>
-      <c r="L193" s="18" t="n"/>
-      <c r="M193" s="18" t="n"/>
+      <c r="E193" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.icfre.gov.in/</t>
+        </is>
+      </c>
+      <c r="F193" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.icfre.gov.in/</t>
+        </is>
+      </c>
+      <c r="G193" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H193" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I193" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J193" s="18" t="inlineStr">
+        <is>
+          <t>ICFRE dedicated recruitment portal verified live. Attached office under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K193" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L193" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M193" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="16">
       <c r="A194" s="4">
@@ -12178,15 +12212,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E194" s="18" t="n"/>
-      <c r="F194" s="18" t="n"/>
-      <c r="G194" s="18" t="n"/>
-      <c r="H194" s="18" t="n"/>
-      <c r="I194" s="18" t="n"/>
-      <c r="J194" s="18" t="n"/>
-      <c r="K194" s="18" t="n"/>
-      <c r="L194" s="18" t="n"/>
-      <c r="M194" s="18" t="n"/>
+      <c r="E194" s="17" t="inlineStr">
+        <is>
+          <t>https://cpcb.nic.in/recruitment/</t>
+        </is>
+      </c>
+      <c r="F194" s="17" t="inlineStr">
+        <is>
+          <t>https://cpcb.nic.in/recruitment/</t>
+        </is>
+      </c>
+      <c r="G194" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H194" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I194" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J194" s="18" t="inlineStr">
+        <is>
+          <t>CPCB recruitment page verified live. Statutory body under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K194" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L194" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M194" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="16">
       <c r="A195" s="4">
@@ -12208,15 +12276,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E195" s="18" t="n"/>
-      <c r="F195" s="18" t="n"/>
-      <c r="G195" s="18" t="n"/>
-      <c r="H195" s="18" t="n"/>
-      <c r="I195" s="18" t="n"/>
-      <c r="J195" s="18" t="n"/>
-      <c r="K195" s="18" t="n"/>
-      <c r="L195" s="18" t="n"/>
-      <c r="M195" s="18" t="n"/>
+      <c r="E195" s="17" t="inlineStr">
+        <is>
+          <t>http://nbaindia.org/</t>
+        </is>
+      </c>
+      <c r="F195" s="17" t="inlineStr">
+        <is>
+          <t>http://nbaindia.org/</t>
+        </is>
+      </c>
+      <c r="G195" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H195" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I195" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J195" s="18" t="inlineStr">
+        <is>
+          <t>NBA official site verified live (HTTP only). No dedicated recruitment sub-page found; notices appear on main site. Statutory body under MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K195" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L195" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M195" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="16">
       <c r="A196" s="4">
@@ -12238,15 +12340,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E196" s="18" t="n"/>
-      <c r="F196" s="18" t="n"/>
-      <c r="G196" s="18" t="n"/>
-      <c r="H196" s="18" t="n"/>
-      <c r="I196" s="18" t="n"/>
-      <c r="J196" s="18" t="n"/>
-      <c r="K196" s="18" t="n"/>
-      <c r="L196" s="18" t="n"/>
-      <c r="M196" s="18" t="n"/>
+      <c r="E196" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ntca.gov.in/</t>
+        </is>
+      </c>
+      <c r="F196" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ntca.gov.in/</t>
+        </is>
+      </c>
+      <c r="G196" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H196" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I196" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J196" s="18" t="inlineStr">
+        <is>
+          <t>NTCA site returns 406 from automated access. Confirmed as official domain. Statutory body under MoEFCC. Small staff primarily on deputation.</t>
+        </is>
+      </c>
+      <c r="K196" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L196" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M196" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="16">
       <c r="A197" s="4">
@@ -12268,15 +12404,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E197" s="18" t="n"/>
-      <c r="F197" s="18" t="n"/>
-      <c r="G197" s="18" t="n"/>
-      <c r="H197" s="18" t="n"/>
-      <c r="I197" s="18" t="n"/>
-      <c r="J197" s="18" t="n"/>
-      <c r="K197" s="18" t="n"/>
-      <c r="L197" s="18" t="n"/>
-      <c r="M197" s="18" t="n"/>
+      <c r="E197" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F197" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G197" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H197" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I197" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J197" s="18" t="inlineStr">
+        <is>
+          <t>NCZMA is a policy authority under MoEFCC with no separate website. Any recruitment through parent ministry vacancy circulars.</t>
+        </is>
+      </c>
+      <c r="K197" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L197" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M197" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="16">
       <c r="A198" s="4">
@@ -12298,15 +12468,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E198" s="18" t="n"/>
-      <c r="F198" s="18" t="n"/>
-      <c r="G198" s="18" t="n"/>
-      <c r="H198" s="18" t="n"/>
-      <c r="I198" s="18" t="n"/>
-      <c r="J198" s="18" t="n"/>
-      <c r="K198" s="18" t="n"/>
-      <c r="L198" s="18" t="n"/>
-      <c r="M198" s="18" t="n"/>
+      <c r="E198" s="17" t="inlineStr">
+        <is>
+          <t>https://neeri.res.in/</t>
+        </is>
+      </c>
+      <c r="F198" s="17" t="inlineStr">
+        <is>
+          <t>https://neeri.res.in/</t>
+        </is>
+      </c>
+      <c r="G198" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H198" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I198" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J198" s="18" t="inlineStr">
+        <is>
+          <t>NEERI official site verified live. CSIR-NEERI (Council of Scientific &amp; Industrial Research lab). Recruitment through CSIR channels. NOTE: NEERI is technically under CSIR/DSIR, not MoEFCC directly - may be misclassified.</t>
+        </is>
+      </c>
+      <c r="K198" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L198" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M198" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="16">
       <c r="A199" s="4">
@@ -12328,15 +12532,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E199" s="18" t="n"/>
-      <c r="F199" s="18" t="n"/>
-      <c r="G199" s="18" t="n"/>
-      <c r="H199" s="18" t="n"/>
-      <c r="I199" s="18" t="n"/>
-      <c r="J199" s="18" t="n"/>
-      <c r="K199" s="18" t="n"/>
-      <c r="L199" s="18" t="n"/>
-      <c r="M199" s="18" t="n"/>
+      <c r="E199" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F199" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G199" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H199" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I199" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J199" s="18" t="inlineStr">
+        <is>
+          <t>SACON (Salim Ali Centre) - very small autonomous research institute. No independent recruitment portal found. Likely channels through MoEFCC.</t>
+        </is>
+      </c>
+      <c r="K199" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L199" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M199" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="16">
       <c r="A200" s="4">
@@ -12358,15 +12596,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E200" s="18" t="n"/>
-      <c r="F200" s="18" t="n"/>
-      <c r="G200" s="18" t="n"/>
-      <c r="H200" s="18" t="n"/>
-      <c r="I200" s="18" t="n"/>
-      <c r="J200" s="18" t="n"/>
-      <c r="K200" s="18" t="n"/>
-      <c r="L200" s="18" t="n"/>
-      <c r="M200" s="18" t="n"/>
+      <c r="E200" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F200" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G200" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H200" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I200" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J200" s="18" t="inlineStr">
+        <is>
+          <t>MoEFCC Regional Offices are subordinate field formations. Recruitment through parent ministry vacancy circulars page.</t>
+        </is>
+      </c>
+      <c r="K200" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L200" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M200" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="16">
       <c r="A201" s="4">
@@ -12388,15 +12660,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E201" s="18" t="n"/>
-      <c r="F201" s="18" t="n"/>
-      <c r="G201" s="18" t="n"/>
-      <c r="H201" s="18" t="n"/>
-      <c r="I201" s="18" t="n"/>
-      <c r="J201" s="18" t="n"/>
-      <c r="K201" s="18" t="n"/>
-      <c r="L201" s="18" t="n"/>
-      <c r="M201" s="18" t="n"/>
+      <c r="E201" s="17" t="inlineStr">
+        <is>
+          <t>https://bsi.gov.in/page/en/vacancies</t>
+        </is>
+      </c>
+      <c r="F201" s="17" t="inlineStr">
+        <is>
+          <t>https://bsi.gov.in/page/en/vacancies</t>
+        </is>
+      </c>
+      <c r="G201" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H201" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I201" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J201" s="18" t="inlineStr">
+        <is>
+          <t>BSI/ZSI Regional Centres recruit through their respective parent organisation pages. BSI vacancies page mapped as primary reference.</t>
+        </is>
+      </c>
+      <c r="K201" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L201" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M201" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="16">
       <c r="A202" s="4">
@@ -12448,15 +12754,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E203" s="18" t="n"/>
-      <c r="F203" s="18" t="n"/>
-      <c r="G203" s="18" t="n"/>
-      <c r="H203" s="18" t="n"/>
-      <c r="I203" s="18" t="n"/>
-      <c r="J203" s="18" t="n"/>
-      <c r="K203" s="18" t="n"/>
-      <c r="L203" s="18" t="n"/>
-      <c r="M203" s="18" t="n"/>
+      <c r="E203" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F203" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G203" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H203" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I203" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J203" s="18" t="inlineStr">
+        <is>
+          <t>MEA job openings page verified live. Contains deputation / contract vacancies for Secretariat and missions.</t>
+        </is>
+      </c>
+      <c r="K203" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L203" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M203" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="16">
       <c r="A204" s="4">
@@ -12478,15 +12818,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E204" s="18" t="n"/>
-      <c r="F204" s="18" t="n"/>
-      <c r="G204" s="18" t="n"/>
-      <c r="H204" s="18" t="n"/>
-      <c r="I204" s="18" t="n"/>
-      <c r="J204" s="18" t="n"/>
-      <c r="K204" s="18" t="n"/>
-      <c r="L204" s="18" t="n"/>
-      <c r="M204" s="18" t="n"/>
+      <c r="E204" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F204" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G204" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I204" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J204" s="18" t="inlineStr">
+        <is>
+          <t>CPV Division is within MEA Secretariat. Vacancies posted on MEA job openings page.</t>
+        </is>
+      </c>
+      <c r="K204" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L204" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M204" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="16">
       <c r="A205" s="4">
@@ -12508,15 +12882,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E205" s="18" t="n"/>
-      <c r="F205" s="18" t="n"/>
-      <c r="G205" s="18" t="n"/>
-      <c r="H205" s="18" t="n"/>
-      <c r="I205" s="18" t="n"/>
-      <c r="J205" s="18" t="n"/>
-      <c r="K205" s="18" t="n"/>
-      <c r="L205" s="18" t="n"/>
-      <c r="M205" s="18" t="n"/>
+      <c r="E205" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F205" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G205" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H205" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I205" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J205" s="18" t="inlineStr">
+        <is>
+          <t>Territorial Divisions are within MEA Secretariat. No separate recruitment page.</t>
+        </is>
+      </c>
+      <c r="K205" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L205" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M205" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="16">
       <c r="A206" s="4">
@@ -12538,15 +12946,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E206" s="18" t="n"/>
-      <c r="F206" s="18" t="n"/>
-      <c r="G206" s="18" t="n"/>
-      <c r="H206" s="18" t="n"/>
-      <c r="I206" s="18" t="n"/>
-      <c r="J206" s="18" t="n"/>
-      <c r="K206" s="18" t="n"/>
-      <c r="L206" s="18" t="n"/>
-      <c r="M206" s="18" t="n"/>
+      <c r="E206" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F206" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G206" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H206" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I206" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J206" s="18" t="inlineStr">
+        <is>
+          <t>Policy Planning &amp; Research Division is within MEA. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K206" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L206" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M206" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="16">
       <c r="A207" s="4">
@@ -12568,15 +13010,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E207" s="18" t="n"/>
-      <c r="F207" s="18" t="n"/>
-      <c r="G207" s="18" t="n"/>
-      <c r="H207" s="18" t="n"/>
-      <c r="I207" s="18" t="n"/>
-      <c r="J207" s="18" t="n"/>
-      <c r="K207" s="18" t="n"/>
-      <c r="L207" s="18" t="n"/>
-      <c r="M207" s="18" t="n"/>
+      <c r="E207" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F207" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G207" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H207" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I207" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J207" s="18" t="inlineStr">
+        <is>
+          <t>Administration &amp; Establishment Divisions are within MEA. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K207" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L207" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M207" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="16">
       <c r="A208" s="4">
@@ -12598,15 +13074,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E208" s="18" t="n"/>
-      <c r="F208" s="18" t="n"/>
-      <c r="G208" s="18" t="n"/>
-      <c r="H208" s="18" t="n"/>
-      <c r="I208" s="18" t="n"/>
-      <c r="J208" s="18" t="n"/>
-      <c r="K208" s="18" t="n"/>
-      <c r="L208" s="18" t="n"/>
-      <c r="M208" s="18" t="n"/>
+      <c r="E208" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F208" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G208" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H208" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I208" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J208" s="18" t="inlineStr">
+        <is>
+          <t>Indian Missions &amp; Posts Abroad recruit locally engaged staff through individual mission websites; IFS officers through UPSC. MEA job page for deputation/contract.</t>
+        </is>
+      </c>
+      <c r="K208" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L208" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M208" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="16">
       <c r="A209" s="4">
@@ -12628,15 +13138,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E209" s="18" t="n"/>
-      <c r="F209" s="18" t="n"/>
-      <c r="G209" s="18" t="n"/>
-      <c r="H209" s="18" t="n"/>
-      <c r="I209" s="18" t="n"/>
-      <c r="J209" s="18" t="n"/>
-      <c r="K209" s="18" t="n"/>
-      <c r="L209" s="18" t="n"/>
-      <c r="M209" s="18" t="n"/>
+      <c r="E209" s="17" t="inlineStr">
+        <is>
+          <t>https://passportindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F209" s="17" t="inlineStr">
+        <is>
+          <t>https://passportindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G209" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H209" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I209" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J209" s="18" t="inlineStr">
+        <is>
+          <t>Passport Offices (CPV network) verified live. Recruitment for Passport Office staff through SSC and MEA deputation circulars.</t>
+        </is>
+      </c>
+      <c r="K209" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L209" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M209" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="16">
       <c r="A210" s="4">
@@ -12658,15 +13202,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E210" s="18" t="n"/>
-      <c r="F210" s="18" t="n"/>
-      <c r="G210" s="18" t="n"/>
-      <c r="H210" s="18" t="n"/>
-      <c r="I210" s="18" t="n"/>
-      <c r="J210" s="18" t="n"/>
-      <c r="K210" s="18" t="n"/>
-      <c r="L210" s="18" t="n"/>
-      <c r="M210" s="18" t="n"/>
+      <c r="E210" s="17" t="inlineStr">
+        <is>
+          <t>https://iccr.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F210" s="17" t="inlineStr">
+        <is>
+          <t>https://iccr.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G210" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H210" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I210" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J210" s="18" t="inlineStr">
+        <is>
+          <t>ICCR vacancy page verified live. Autonomous body under MEA.</t>
+        </is>
+      </c>
+      <c r="K210" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L210" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M210" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="16">
       <c r="A211" s="4">
@@ -12688,15 +13266,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E211" s="18" t="n"/>
-      <c r="F211" s="18" t="n"/>
-      <c r="G211" s="18" t="n"/>
-      <c r="H211" s="18" t="n"/>
-      <c r="I211" s="18" t="n"/>
-      <c r="J211" s="18" t="n"/>
-      <c r="K211" s="18" t="n"/>
-      <c r="L211" s="18" t="n"/>
-      <c r="M211" s="18" t="n"/>
+      <c r="E211" s="17" t="inlineStr">
+        <is>
+          <t>https://ris.org.in/</t>
+        </is>
+      </c>
+      <c r="F211" s="17" t="inlineStr">
+        <is>
+          <t>https://ris.org.in/</t>
+        </is>
+      </c>
+      <c r="G211" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H211" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I211" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J211" s="18" t="inlineStr">
+        <is>
+          <t>RIS official site verified live. No dedicated recruitment sub-page found. Small autonomous research body under MEA.</t>
+        </is>
+      </c>
+      <c r="K211" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L211" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M211" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="16">
       <c r="A212" s="4">
@@ -12718,15 +13330,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E212" s="18" t="n"/>
-      <c r="F212" s="18" t="n"/>
-      <c r="G212" s="18" t="n"/>
-      <c r="H212" s="18" t="n"/>
-      <c r="I212" s="18" t="n"/>
-      <c r="J212" s="18" t="n"/>
-      <c r="K212" s="18" t="n"/>
-      <c r="L212" s="18" t="n"/>
-      <c r="M212" s="18" t="n"/>
+      <c r="E212" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F212" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G212" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H212" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I212" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J212" s="18" t="inlineStr">
+        <is>
+          <t>Branch Secretariats / Regional Passport Offices are subordinate to MEA. Recruitment through MEA job openings and SSC.</t>
+        </is>
+      </c>
+      <c r="K212" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L212" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M212" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="16">
       <c r="A213" s="4">
@@ -12778,15 +13424,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E214" s="18" t="n"/>
-      <c r="F214" s="18" t="n"/>
-      <c r="G214" s="18" t="n"/>
-      <c r="H214" s="18" t="n"/>
-      <c r="I214" s="18" t="n"/>
-      <c r="J214" s="18" t="n"/>
-      <c r="K214" s="18" t="n"/>
-      <c r="L214" s="18" t="n"/>
-      <c r="M214" s="18" t="n"/>
+      <c r="E214" s="17" t="inlineStr">
+        <is>
+          <t>https://dea.gov.in/career-vacancy</t>
+        </is>
+      </c>
+      <c r="F214" s="17" t="inlineStr">
+        <is>
+          <t>https://dea.gov.in/career-vacancy</t>
+        </is>
+      </c>
+      <c r="G214" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H214" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I214" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J214" s="18" t="inlineStr">
+        <is>
+          <t>Department of Economic Affairs career/vacancy page verified live.</t>
+        </is>
+      </c>
+      <c r="K214" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L214" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M214" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="16">
       <c r="A215" s="4">
@@ -12808,15 +13488,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E215" s="18" t="n"/>
-      <c r="F215" s="18" t="n"/>
-      <c r="G215" s="18" t="n"/>
-      <c r="H215" s="18" t="n"/>
-      <c r="I215" s="18" t="n"/>
-      <c r="J215" s="18" t="n"/>
-      <c r="K215" s="18" t="n"/>
-      <c r="L215" s="18" t="n"/>
-      <c r="M215" s="18" t="n"/>
+      <c r="E215" s="17" t="inlineStr">
+        <is>
+          <t>https://doe.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F215" s="17" t="inlineStr">
+        <is>
+          <t>https://doe.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G215" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H215" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I215" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J215" s="18" t="inlineStr">
+        <is>
+          <t>Department of Expenditure vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K215" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L215" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M215" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="16">
       <c r="A216" s="4">
@@ -12838,15 +13552,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E216" s="18" t="n"/>
-      <c r="F216" s="18" t="n"/>
-      <c r="G216" s="18" t="n"/>
-      <c r="H216" s="18" t="n"/>
-      <c r="I216" s="18" t="n"/>
-      <c r="J216" s="18" t="n"/>
-      <c r="K216" s="18" t="n"/>
-      <c r="L216" s="18" t="n"/>
-      <c r="M216" s="18" t="n"/>
+      <c r="E216" s="17" t="inlineStr">
+        <is>
+          <t>https://dor.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F216" s="17" t="inlineStr">
+        <is>
+          <t>https://dor.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G216" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H216" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I216" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J216" s="18" t="inlineStr">
+        <is>
+          <t>Department of Revenue vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K216" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L216" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M216" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="16">
       <c r="A217" s="4">
@@ -12868,15 +13616,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E217" s="18" t="n"/>
-      <c r="F217" s="18" t="n"/>
-      <c r="G217" s="18" t="n"/>
-      <c r="H217" s="18" t="n"/>
-      <c r="I217" s="18" t="n"/>
-      <c r="J217" s="18" t="n"/>
-      <c r="K217" s="18" t="n"/>
-      <c r="L217" s="18" t="n"/>
-      <c r="M217" s="18" t="n"/>
+      <c r="E217" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F217" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G217" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H217" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I217" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J217" s="18" t="inlineStr">
+        <is>
+          <t>Department of Financial Services vacancies page verified live. Recent vacancy circular (May 2026).</t>
+        </is>
+      </c>
+      <c r="K217" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L217" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M217" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="16">
       <c r="A218" s="4">
@@ -12898,15 +13680,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E218" s="18" t="n"/>
-      <c r="F218" s="18" t="n"/>
-      <c r="G218" s="18" t="n"/>
-      <c r="H218" s="18" t="n"/>
-      <c r="I218" s="18" t="n"/>
-      <c r="J218" s="18" t="n"/>
-      <c r="K218" s="18" t="n"/>
-      <c r="L218" s="18" t="n"/>
-      <c r="M218" s="18" t="n"/>
+      <c r="E218" s="17" t="inlineStr">
+        <is>
+          <t>https://dipam.gov.in/</t>
+        </is>
+      </c>
+      <c r="F218" s="17" t="inlineStr">
+        <is>
+          <t>https://dipam.gov.in/</t>
+        </is>
+      </c>
+      <c r="G218" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H218" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I218" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J218" s="18" t="inlineStr">
+        <is>
+          <t>DIPAM official site verified live. No dedicated vacancy sub-page found; small department, recruitment through DoPT/parent ministry channels.</t>
+        </is>
+      </c>
+      <c r="K218" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L218" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M218" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="16">
       <c r="A219" s="4">
@@ -12924,15 +13740,49 @@
         </is>
       </c>
       <c r="D219" s="4" t="n"/>
-      <c r="E219" s="18" t="n"/>
-      <c r="F219" s="18" t="n"/>
-      <c r="G219" s="18" t="n"/>
-      <c r="H219" s="18" t="n"/>
-      <c r="I219" s="18" t="n"/>
-      <c r="J219" s="18" t="n"/>
-      <c r="K219" s="18" t="n"/>
-      <c r="L219" s="18" t="n"/>
-      <c r="M219" s="18" t="n"/>
+      <c r="E219" s="17" t="inlineStr">
+        <is>
+          <t>https://www.incometaxindia.gov.in/recruitment-notices</t>
+        </is>
+      </c>
+      <c r="F219" s="17" t="inlineStr">
+        <is>
+          <t>https://www.incometaxindia.gov.in/recruitment-notices</t>
+        </is>
+      </c>
+      <c r="G219" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H219" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I219" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J219" s="18" t="inlineStr">
+        <is>
+          <t>CBDT/Income Tax recruitment notices page. Site returns 403 from automated access but confirmed as official URL. Recruitment for IRS officers through UPSC; Group B/C through SSC.</t>
+        </is>
+      </c>
+      <c r="K219" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L219" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M219" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="16">
       <c r="A220" s="4">
@@ -12954,15 +13804,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E220" s="18" t="n"/>
-      <c r="F220" s="18" t="n"/>
-      <c r="G220" s="18" t="n"/>
-      <c r="H220" s="18" t="n"/>
-      <c r="I220" s="18" t="n"/>
-      <c r="J220" s="18" t="n"/>
-      <c r="K220" s="18" t="n"/>
-      <c r="L220" s="18" t="n"/>
-      <c r="M220" s="18" t="n"/>
+      <c r="E220" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbic.gov.in/</t>
+        </is>
+      </c>
+      <c r="F220" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbic.gov.in/</t>
+        </is>
+      </c>
+      <c r="G220" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H220" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I220" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J220" s="18" t="inlineStr">
+        <is>
+          <t>CBIC official site verified live. Has vacancy circulars section. Recruitment for IRS (Customs) through UPSC; Group B/C through SSC.</t>
+        </is>
+      </c>
+      <c r="K220" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L220" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M220" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="16">
       <c r="A221" s="4">
@@ -12984,15 +13868,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E221" s="18" t="n"/>
-      <c r="F221" s="18" t="n"/>
-      <c r="G221" s="18" t="n"/>
-      <c r="H221" s="18" t="n"/>
-      <c r="I221" s="18" t="n"/>
-      <c r="J221" s="18" t="n"/>
-      <c r="K221" s="18" t="n"/>
-      <c r="L221" s="18" t="n"/>
-      <c r="M221" s="18" t="n"/>
+      <c r="E221" s="17" t="inlineStr">
+        <is>
+          <t>https://www.incometaxindia.gov.in/recruitment-notices</t>
+        </is>
+      </c>
+      <c r="F221" s="17" t="inlineStr">
+        <is>
+          <t>https://www.incometaxindia.gov.in/recruitment-notices</t>
+        </is>
+      </c>
+      <c r="G221" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H221" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I221" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J221" s="18" t="inlineStr">
+        <is>
+          <t>Income Tax field formations recruit through CBDT/SSC. Mapped to IT Dept recruitment notices page.</t>
+        </is>
+      </c>
+      <c r="K221" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L221" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M221" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="16">
       <c r="A222" s="4">
@@ -13014,15 +13932,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E222" s="18" t="n"/>
-      <c r="F222" s="18" t="n"/>
-      <c r="G222" s="18" t="n"/>
-      <c r="H222" s="18" t="n"/>
-      <c r="I222" s="18" t="n"/>
-      <c r="J222" s="18" t="n"/>
-      <c r="K222" s="18" t="n"/>
-      <c r="L222" s="18" t="n"/>
-      <c r="M222" s="18" t="n"/>
+      <c r="E222" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbic.gov.in/</t>
+        </is>
+      </c>
+      <c r="F222" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbic.gov.in/</t>
+        </is>
+      </c>
+      <c r="G222" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H222" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I222" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J222" s="18" t="inlineStr">
+        <is>
+          <t>GST &amp; Customs field formations recruit through CBIC/SSC. Mapped to CBIC site.</t>
+        </is>
+      </c>
+      <c r="K222" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L222" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M222" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="16">
       <c r="A223" s="4">
@@ -13044,15 +13996,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E223" s="18" t="n"/>
-      <c r="F223" s="18" t="n"/>
-      <c r="G223" s="18" t="n"/>
-      <c r="H223" s="18" t="n"/>
-      <c r="I223" s="18" t="n"/>
-      <c r="J223" s="18" t="n"/>
-      <c r="K223" s="18" t="n"/>
-      <c r="L223" s="18" t="n"/>
-      <c r="M223" s="18" t="n"/>
+      <c r="E223" s="17" t="inlineStr">
+        <is>
+          <t>https://cga.nic.in/</t>
+        </is>
+      </c>
+      <c r="F223" s="17" t="inlineStr">
+        <is>
+          <t>https://cga.nic.in/</t>
+        </is>
+      </c>
+      <c r="G223" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H223" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I223" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J223" s="18" t="inlineStr">
+        <is>
+          <t>CGA offices site verified live. Has circulars section. Subordinate accounting offices under Department of Expenditure.</t>
+        </is>
+      </c>
+      <c r="K223" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L223" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M223" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15.75" customHeight="1" s="16">
       <c r="A224" s="4">
@@ -13074,15 +14060,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E224" s="18" t="n"/>
-      <c r="F224" s="18" t="n"/>
-      <c r="G224" s="18" t="n"/>
-      <c r="H224" s="18" t="n"/>
-      <c r="I224" s="18" t="n"/>
-      <c r="J224" s="18" t="n"/>
-      <c r="K224" s="18" t="n"/>
-      <c r="L224" s="18" t="n"/>
-      <c r="M224" s="18" t="n"/>
+      <c r="E224" s="17" t="inlineStr">
+        <is>
+          <t>https://doe.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F224" s="17" t="inlineStr">
+        <is>
+          <t>https://doe.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G224" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H224" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I224" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J224" s="18" t="inlineStr">
+        <is>
+          <t>Pr.CCA offices are subordinate to DoE. Recruitment through Department of Expenditure vacancies page.</t>
+        </is>
+      </c>
+      <c r="K224" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L224" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M224" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="15.75" customHeight="1" s="16">
       <c r="A225" s="4">
@@ -13104,15 +14124,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E225" s="18" t="n"/>
-      <c r="F225" s="18" t="n"/>
-      <c r="G225" s="18" t="n"/>
-      <c r="H225" s="18" t="n"/>
-      <c r="I225" s="18" t="n"/>
-      <c r="J225" s="18" t="n"/>
-      <c r="K225" s="18" t="n"/>
-      <c r="L225" s="18" t="n"/>
-      <c r="M225" s="18" t="n"/>
+      <c r="E225" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sebi.gov.in/sebiweb/other/OtherAction.do?doRecruit=yes</t>
+        </is>
+      </c>
+      <c r="F225" s="17" t="inlineStr">
+        <is>
+          <t>https://www.sebi.gov.in/sebiweb/other/OtherAction.do?doRecruit=yes</t>
+        </is>
+      </c>
+      <c r="G225" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H225" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I225" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J225" s="18" t="inlineStr">
+        <is>
+          <t>SEBI recruitment page verified live. Statutory body. Recruits Officers and other posts through own exams.</t>
+        </is>
+      </c>
+      <c r="K225" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L225" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M225" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15.75" customHeight="1" s="16">
       <c r="A226" s="4">
@@ -13134,15 +14188,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E226" s="18" t="n"/>
-      <c r="F226" s="18" t="n"/>
-      <c r="G226" s="18" t="n"/>
-      <c r="H226" s="18" t="n"/>
-      <c r="I226" s="18" t="n"/>
-      <c r="J226" s="18" t="n"/>
-      <c r="K226" s="18" t="n"/>
-      <c r="L226" s="18" t="n"/>
-      <c r="M226" s="18" t="n"/>
+      <c r="E226" s="17" t="inlineStr">
+        <is>
+          <t>https://www.irdai.gov.in/</t>
+        </is>
+      </c>
+      <c r="F226" s="17" t="inlineStr">
+        <is>
+          <t>https://www.irdai.gov.in/</t>
+        </is>
+      </c>
+      <c r="G226" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H226" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I226" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J226" s="18" t="inlineStr">
+        <is>
+          <t>IRDAI site returns 403 from automated access but confirmed as official domain. Statutory body under DFS. Staff mostly on deputation.</t>
+        </is>
+      </c>
+      <c r="K226" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L226" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M226" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="16">
       <c r="A227" s="4">
@@ -13164,15 +14252,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E227" s="18" t="n"/>
-      <c r="F227" s="18" t="n"/>
-      <c r="G227" s="18" t="n"/>
-      <c r="H227" s="18" t="n"/>
-      <c r="I227" s="18" t="n"/>
-      <c r="J227" s="18" t="n"/>
-      <c r="K227" s="18" t="n"/>
-      <c r="L227" s="18" t="n"/>
-      <c r="M227" s="18" t="n"/>
+      <c r="E227" s="17" t="inlineStr">
+        <is>
+          <t>https://www.pfrda.org.in/get-to-know/careers</t>
+        </is>
+      </c>
+      <c r="F227" s="17" t="inlineStr">
+        <is>
+          <t>https://www.pfrda.org.in/get-to-know/careers</t>
+        </is>
+      </c>
+      <c r="G227" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H227" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I227" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J227" s="18" t="inlineStr">
+        <is>
+          <t>PFRDA careers page verified live. Statutory body under DFS.</t>
+        </is>
+      </c>
+      <c r="K227" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L227" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M227" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="16">
       <c r="A228" s="4">
@@ -13194,15 +14316,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E228" s="18" t="n"/>
-      <c r="F228" s="18" t="n"/>
-      <c r="G228" s="18" t="n"/>
-      <c r="H228" s="18" t="n"/>
-      <c r="I228" s="18" t="n"/>
-      <c r="J228" s="18" t="n"/>
-      <c r="K228" s="18" t="n"/>
-      <c r="L228" s="18" t="n"/>
-      <c r="M228" s="18" t="n"/>
+      <c r="E228" s="17" t="inlineStr">
+        <is>
+          <t>https://ibbi.gov.in/home/career</t>
+        </is>
+      </c>
+      <c r="F228" s="17" t="inlineStr">
+        <is>
+          <t>https://ibbi.gov.in/home/career</t>
+        </is>
+      </c>
+      <c r="G228" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H228" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I228" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J228" s="18" t="inlineStr">
+        <is>
+          <t>IBBI career page verified live. Statutory body under MCA/Finance.</t>
+        </is>
+      </c>
+      <c r="K228" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L228" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M228" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="16">
       <c r="A229" s="4">
@@ -13224,15 +14380,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E229" s="18" t="n"/>
-      <c r="F229" s="18" t="n"/>
-      <c r="G229" s="18" t="n"/>
-      <c r="H229" s="18" t="n"/>
-      <c r="I229" s="18" t="n"/>
-      <c r="J229" s="18" t="n"/>
-      <c r="K229" s="18" t="n"/>
-      <c r="L229" s="18" t="n"/>
-      <c r="M229" s="18" t="n"/>
+      <c r="E229" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipfp.org.in/careers-index-page/</t>
+        </is>
+      </c>
+      <c r="F229" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nipfp.org.in/careers-index-page/</t>
+        </is>
+      </c>
+      <c r="G229" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H229" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I229" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J229" s="18" t="inlineStr">
+        <is>
+          <t>NIPFP careers page verified live. Autonomous body under Ministry of Finance.</t>
+        </is>
+      </c>
+      <c r="K229" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L229" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M229" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="16">
       <c r="A230" s="4">
@@ -13254,15 +14444,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E230" s="18" t="n"/>
-      <c r="F230" s="18" t="n"/>
-      <c r="G230" s="18" t="n"/>
-      <c r="H230" s="18" t="n"/>
-      <c r="I230" s="18" t="n"/>
-      <c r="J230" s="18" t="n"/>
-      <c r="K230" s="18" t="n"/>
-      <c r="L230" s="18" t="n"/>
-      <c r="M230" s="18" t="n"/>
+      <c r="E230" s="17" t="inlineStr">
+        <is>
+          <t>https://nifm.ac.in/</t>
+        </is>
+      </c>
+      <c r="F230" s="17" t="inlineStr">
+        <is>
+          <t>https://nifm.ac.in/</t>
+        </is>
+      </c>
+      <c r="G230" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H230" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I230" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J230" s="18" t="inlineStr">
+        <is>
+          <t>NIFM site returns 403 from automated access. Confirmed as official domain. Autonomous body under Ministry of Finance.</t>
+        </is>
+      </c>
+      <c r="K230" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L230" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M230" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="16">
       <c r="A231" s="4">
@@ -13284,15 +14508,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E231" s="18" t="n"/>
-      <c r="F231" s="18" t="n"/>
-      <c r="G231" s="18" t="n"/>
-      <c r="H231" s="18" t="n"/>
-      <c r="I231" s="18" t="n"/>
-      <c r="J231" s="18" t="n"/>
-      <c r="K231" s="18" t="n"/>
-      <c r="L231" s="18" t="n"/>
-      <c r="M231" s="18" t="n"/>
+      <c r="E231" s="17" t="inlineStr">
+        <is>
+          <t>https://www.iibf.org.in/</t>
+        </is>
+      </c>
+      <c r="F231" s="17" t="inlineStr">
+        <is>
+          <t>https://www.iibf.org.in/</t>
+        </is>
+      </c>
+      <c r="G231" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H231" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I231" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J231" s="18" t="inlineStr">
+        <is>
+          <t>IIBF is primarily a training/certification body for banking sector, not a typical recruiter. Official site iibf.org.in. Small staff.</t>
+        </is>
+      </c>
+      <c r="K231" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L231" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M231" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="16">
       <c r="A232" s="4">
@@ -13314,15 +14572,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E232" s="18" t="n"/>
-      <c r="F232" s="18" t="n"/>
-      <c r="G232" s="18" t="n"/>
-      <c r="H232" s="18" t="n"/>
-      <c r="I232" s="18" t="n"/>
-      <c r="J232" s="18" t="n"/>
-      <c r="K232" s="18" t="n"/>
-      <c r="L232" s="18" t="n"/>
-      <c r="M232" s="18" t="n"/>
+      <c r="E232" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F232" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G232" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H232" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I232" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J232" s="18" t="inlineStr">
+        <is>
+          <t>Public Sector Banks recruit independently (IBPS/individual bank portals). This is a policy/admin entry; DFS vacancies page as parent reference for board-level appointments.</t>
+        </is>
+      </c>
+      <c r="K232" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L232" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M232" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="16">
       <c r="A233" s="4">
@@ -13344,15 +14636,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E233" s="18" t="n"/>
-      <c r="F233" s="18" t="n"/>
-      <c r="G233" s="18" t="n"/>
-      <c r="H233" s="18" t="n"/>
-      <c r="I233" s="18" t="n"/>
-      <c r="J233" s="18" t="n"/>
-      <c r="K233" s="18" t="n"/>
-      <c r="L233" s="18" t="n"/>
-      <c r="M233" s="18" t="n"/>
+      <c r="E233" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F233" s="17" t="inlineStr">
+        <is>
+          <t>https://financialservices.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G233" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H233" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I233" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J233" s="18" t="inlineStr">
+        <is>
+          <t>PS Insurance Companies recruit independently. Policy/admin entry; DFS vacancies page for board-level appointments.</t>
+        </is>
+      </c>
+      <c r="K233" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L233" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M233" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="15.75" customHeight="1" s="16">
       <c r="A234" s="4">
@@ -13404,15 +14730,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E235" s="18" t="n"/>
-      <c r="F235" s="18" t="n"/>
-      <c r="G235" s="18" t="n"/>
-      <c r="H235" s="18" t="n"/>
-      <c r="I235" s="18" t="n"/>
-      <c r="J235" s="18" t="n"/>
-      <c r="K235" s="18" t="n"/>
-      <c r="L235" s="18" t="n"/>
-      <c r="M235" s="18" t="n"/>
+      <c r="E235" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F235" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G235" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H235" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I235" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J235" s="18" t="inlineStr">
+        <is>
+          <t>Department of Fisheries recruitment page verified live.</t>
+        </is>
+      </c>
+      <c r="K235" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L235" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M235" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15.75" customHeight="1" s="16">
       <c r="A236" s="4">
@@ -13434,15 +14794,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E236" s="18" t="n"/>
-      <c r="F236" s="18" t="n"/>
-      <c r="G236" s="18" t="n"/>
-      <c r="H236" s="18" t="n"/>
-      <c r="I236" s="18" t="n"/>
-      <c r="J236" s="18" t="n"/>
-      <c r="K236" s="18" t="n"/>
-      <c r="L236" s="18" t="n"/>
-      <c r="M236" s="18" t="n"/>
+      <c r="E236" s="17" t="inlineStr">
+        <is>
+          <t>https://dahd.gov.in/office_order_circular/vacancy_recruitment_advertisement</t>
+        </is>
+      </c>
+      <c r="F236" s="17" t="inlineStr">
+        <is>
+          <t>https://dahd.gov.in/office_order_circular/vacancy_recruitment_advertisement</t>
+        </is>
+      </c>
+      <c r="G236" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H236" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I236" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J236" s="18" t="inlineStr">
+        <is>
+          <t>DAHD vacancy/recruitment page verified live. Recent June 2026 vacancy circulars found.</t>
+        </is>
+      </c>
+      <c r="K236" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L236" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M236" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15.75" customHeight="1" s="16">
       <c r="A237" s="4">
@@ -13464,15 +14858,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E237" s="18" t="n"/>
-      <c r="F237" s="18" t="n"/>
-      <c r="G237" s="18" t="n"/>
-      <c r="H237" s="18" t="n"/>
-      <c r="I237" s="18" t="n"/>
-      <c r="J237" s="18" t="n"/>
-      <c r="K237" s="18" t="n"/>
-      <c r="L237" s="18" t="n"/>
-      <c r="M237" s="18" t="n"/>
+      <c r="E237" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cifnet.nic.in/</t>
+        </is>
+      </c>
+      <c r="F237" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cifnet.nic.in/</t>
+        </is>
+      </c>
+      <c r="G237" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H237" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I237" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J237" s="18" t="inlineStr">
+        <is>
+          <t>CIFNET site unreachable from this environment. Confirmed as official domain. Attached office under Dept of Fisheries.</t>
+        </is>
+      </c>
+      <c r="K237" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L237" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M237" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="16">
       <c r="A238" s="4">
@@ -13494,15 +14922,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E238" s="18" t="n"/>
-      <c r="F238" s="18" t="n"/>
-      <c r="G238" s="18" t="n"/>
-      <c r="H238" s="18" t="n"/>
-      <c r="I238" s="18" t="n"/>
-      <c r="J238" s="18" t="n"/>
-      <c r="K238" s="18" t="n"/>
-      <c r="L238" s="18" t="n"/>
-      <c r="M238" s="18" t="n"/>
+      <c r="E238" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cift.res.in/job-opportunities</t>
+        </is>
+      </c>
+      <c r="F238" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cift.res.in/job-opportunities</t>
+        </is>
+      </c>
+      <c r="G238" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H238" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I238" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J238" s="18" t="inlineStr">
+        <is>
+          <t>CIFT job opportunities page verified (found on site). ICAR institute.</t>
+        </is>
+      </c>
+      <c r="K238" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L238" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M238" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="16">
       <c r="A239" s="4">
@@ -13524,15 +14986,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E239" s="18" t="n"/>
-      <c r="F239" s="18" t="n"/>
-      <c r="G239" s="18" t="n"/>
-      <c r="H239" s="18" t="n"/>
-      <c r="I239" s="18" t="n"/>
-      <c r="J239" s="18" t="n"/>
-      <c r="K239" s="18" t="n"/>
-      <c r="L239" s="18" t="n"/>
-      <c r="M239" s="18" t="n"/>
+      <c r="E239" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cmfri.org.in/career</t>
+        </is>
+      </c>
+      <c r="F239" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cmfri.org.in/career</t>
+        </is>
+      </c>
+      <c r="G239" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H239" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I239" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J239" s="18" t="inlineStr">
+        <is>
+          <t>CMFRI career page verified (found on site). ICAR institute.</t>
+        </is>
+      </c>
+      <c r="K239" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L239" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M239" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="16">
       <c r="A240" s="4">
@@ -13554,15 +15050,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E240" s="18" t="n"/>
-      <c r="F240" s="18" t="n"/>
-      <c r="G240" s="18" t="n"/>
-      <c r="H240" s="18" t="n"/>
-      <c r="I240" s="18" t="n"/>
-      <c r="J240" s="18" t="n"/>
-      <c r="K240" s="18" t="n"/>
-      <c r="L240" s="18" t="n"/>
-      <c r="M240" s="18" t="n"/>
+      <c r="E240" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cifri.res.in/</t>
+        </is>
+      </c>
+      <c r="F240" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cifri.res.in/</t>
+        </is>
+      </c>
+      <c r="G240" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H240" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I240" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J240" s="18" t="inlineStr">
+        <is>
+          <t>CIFRI site unreachable from this environment. Confirmed as official domain. ICAR institute.</t>
+        </is>
+      </c>
+      <c r="K240" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L240" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M240" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="16">
       <c r="A241" s="4">
@@ -13584,15 +15114,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E241" s="18" t="n"/>
-      <c r="F241" s="18" t="n"/>
-      <c r="G241" s="18" t="n"/>
-      <c r="H241" s="18" t="n"/>
-      <c r="I241" s="18" t="n"/>
-      <c r="J241" s="18" t="n"/>
-      <c r="K241" s="18" t="n"/>
-      <c r="L241" s="18" t="n"/>
-      <c r="M241" s="18" t="n"/>
+      <c r="E241" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nbfgr.res.in/</t>
+        </is>
+      </c>
+      <c r="F241" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nbfgr.res.in/</t>
+        </is>
+      </c>
+      <c r="G241" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H241" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I241" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J241" s="18" t="inlineStr">
+        <is>
+          <t>NBFGR official site verified live. ICAR institute. Recruitment through ICAR/ASRB channels.</t>
+        </is>
+      </c>
+      <c r="K241" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L241" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M241" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="16">
       <c r="A242" s="4">
@@ -13614,15 +15178,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E242" s="18" t="n"/>
-      <c r="F242" s="18" t="n"/>
-      <c r="G242" s="18" t="n"/>
-      <c r="H242" s="18" t="n"/>
-      <c r="I242" s="18" t="n"/>
-      <c r="J242" s="18" t="n"/>
-      <c r="K242" s="18" t="n"/>
-      <c r="L242" s="18" t="n"/>
-      <c r="M242" s="18" t="n"/>
+      <c r="E242" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nddb.coop/</t>
+        </is>
+      </c>
+      <c r="F242" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nddb.coop/</t>
+        </is>
+      </c>
+      <c r="G242" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H242" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I242" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J242" s="18" t="inlineStr">
+        <is>
+          <t>NDDB official site (nddb.coop). Unreachable from this environment but confirmed as official domain. Statutory body under Ministry of Fisheries/AH&amp;D.</t>
+        </is>
+      </c>
+      <c r="K242" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L242" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M242" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="16">
       <c r="A243" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -15242,15 +15242,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E243" s="18" t="n"/>
-      <c r="F243" s="18" t="n"/>
-      <c r="G243" s="18" t="n"/>
-      <c r="H243" s="18" t="n"/>
-      <c r="I243" s="18" t="n"/>
-      <c r="J243" s="18" t="n"/>
-      <c r="K243" s="18" t="n"/>
-      <c r="L243" s="18" t="n"/>
-      <c r="M243" s="18" t="n"/>
+      <c r="E243" s="17" t="inlineStr">
+        <is>
+          <t>https://www.fssai.gov.in/cms/recruitment.php</t>
+        </is>
+      </c>
+      <c r="F243" s="17" t="inlineStr">
+        <is>
+          <t>https://www.fssai.gov.in/cms/recruitment.php</t>
+        </is>
+      </c>
+      <c r="G243" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H243" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I243" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J243" s="18" t="inlineStr">
+        <is>
+          <t>FSSAI recruitment page verified live. Statutory body. Active 2026 recruitment (Group A &amp; C posts).</t>
+        </is>
+      </c>
+      <c r="K243" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L243" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M243" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="16">
       <c r="A244" s="4">
@@ -15272,15 +15306,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E244" s="18" t="n"/>
-      <c r="F244" s="18" t="n"/>
-      <c r="G244" s="18" t="n"/>
-      <c r="H244" s="18" t="n"/>
-      <c r="I244" s="18" t="n"/>
-      <c r="J244" s="18" t="n"/>
-      <c r="K244" s="18" t="n"/>
-      <c r="L244" s="18" t="n"/>
-      <c r="M244" s="18" t="n"/>
+      <c r="E244" s="17" t="inlineStr">
+        <is>
+          <t>https://niab.org.in/</t>
+        </is>
+      </c>
+      <c r="F244" s="17" t="inlineStr">
+        <is>
+          <t>https://niab.org.in/</t>
+        </is>
+      </c>
+      <c r="G244" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H244" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I244" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J244" s="18" t="inlineStr">
+        <is>
+          <t>NIAB site verified live. No dedicated recruitment sub-page found; vacancies appear on main site. Autonomous body under Dept of Biotechnology (may be misclassified under Fisheries/AH&amp;D).</t>
+        </is>
+      </c>
+      <c r="K244" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L244" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M244" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="16">
       <c r="A245" s="4">
@@ -15302,15 +15370,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E245" s="18" t="n"/>
-      <c r="F245" s="18" t="n"/>
-      <c r="G245" s="18" t="n"/>
-      <c r="H245" s="18" t="n"/>
-      <c r="I245" s="18" t="n"/>
-      <c r="J245" s="18" t="n"/>
-      <c r="K245" s="18" t="n"/>
-      <c r="L245" s="18" t="n"/>
-      <c r="M245" s="18" t="n"/>
+      <c r="E245" s="17" t="inlineStr">
+        <is>
+          <t>https://www.icar.org.in/en/vacancies</t>
+        </is>
+      </c>
+      <c r="F245" s="17" t="inlineStr">
+        <is>
+          <t>https://www.icar.org.in/en/vacancies</t>
+        </is>
+      </c>
+      <c r="G245" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H245" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I245" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J245" s="18" t="inlineStr">
+        <is>
+          <t>ICAR vacancies page verified live. Covers animal sciences institutes. Recruitment through ASRB.</t>
+        </is>
+      </c>
+      <c r="K245" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L245" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M245" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="16">
       <c r="A246" s="4">
@@ -15332,15 +15434,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E246" s="18" t="n"/>
-      <c r="F246" s="18" t="n"/>
-      <c r="G246" s="18" t="n"/>
-      <c r="H246" s="18" t="n"/>
-      <c r="I246" s="18" t="n"/>
-      <c r="J246" s="18" t="n"/>
-      <c r="K246" s="18" t="n"/>
-      <c r="L246" s="18" t="n"/>
-      <c r="M246" s="18" t="n"/>
+      <c r="E246" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F246" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G246" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H246" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I246" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J246" s="18" t="inlineStr">
+        <is>
+          <t>Fisheries Development Field Offices recruit through the Dept of Fisheries recruitment page.</t>
+        </is>
+      </c>
+      <c r="K246" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L246" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M246" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="16">
       <c r="A247" s="4">
@@ -15362,15 +15498,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E247" s="18" t="n"/>
-      <c r="F247" s="18" t="n"/>
-      <c r="G247" s="18" t="n"/>
-      <c r="H247" s="18" t="n"/>
-      <c r="I247" s="18" t="n"/>
-      <c r="J247" s="18" t="n"/>
-      <c r="K247" s="18" t="n"/>
-      <c r="L247" s="18" t="n"/>
-      <c r="M247" s="18" t="n"/>
+      <c r="E247" s="17" t="inlineStr">
+        <is>
+          <t>https://dahd.gov.in/office_order_circular/vacancy_recruitment_advertisement</t>
+        </is>
+      </c>
+      <c r="F247" s="17" t="inlineStr">
+        <is>
+          <t>https://dahd.gov.in/office_order_circular/vacancy_recruitment_advertisement</t>
+        </is>
+      </c>
+      <c r="G247" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H247" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I247" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J247" s="18" t="inlineStr">
+        <is>
+          <t>Animal Husbandry Field Formations recruit through DAHD vacancy page.</t>
+        </is>
+      </c>
+      <c r="K247" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L247" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M247" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="16">
       <c r="A248" s="4">
@@ -15422,15 +15592,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E249" s="18" t="n"/>
-      <c r="F249" s="18" t="n"/>
-      <c r="G249" s="18" t="n"/>
-      <c r="H249" s="18" t="n"/>
-      <c r="I249" s="18" t="n"/>
-      <c r="J249" s="18" t="n"/>
-      <c r="K249" s="18" t="n"/>
-      <c r="L249" s="18" t="n"/>
-      <c r="M249" s="18" t="n"/>
+      <c r="E249" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F249" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G249" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H249" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I249" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J249" s="18" t="inlineStr">
+        <is>
+          <t>MoFPI careers page verified live.</t>
+        </is>
+      </c>
+      <c r="K249" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L249" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M249" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="16">
       <c r="A250" s="4">
@@ -15452,15 +15656,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E250" s="18" t="n"/>
-      <c r="F250" s="18" t="n"/>
-      <c r="G250" s="18" t="n"/>
-      <c r="H250" s="18" t="n"/>
-      <c r="I250" s="18" t="n"/>
-      <c r="J250" s="18" t="n"/>
-      <c r="K250" s="18" t="n"/>
-      <c r="L250" s="18" t="n"/>
-      <c r="M250" s="18" t="n"/>
+      <c r="E250" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F250" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G250" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H250" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I250" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J250" s="18" t="inlineStr">
+        <is>
+          <t>Directorate of Sugar is within MoFPI. Vacancies on parent ministry careers page.</t>
+        </is>
+      </c>
+      <c r="K250" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L250" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M250" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="16">
       <c r="A251" s="4">
@@ -15482,15 +15720,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E251" s="18" t="n"/>
-      <c r="F251" s="18" t="n"/>
-      <c r="G251" s="18" t="n"/>
-      <c r="H251" s="18" t="n"/>
-      <c r="I251" s="18" t="n"/>
-      <c r="J251" s="18" t="n"/>
-      <c r="K251" s="18" t="n"/>
-      <c r="L251" s="18" t="n"/>
-      <c r="M251" s="18" t="n"/>
+      <c r="E251" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F251" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G251" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H251" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I251" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J251" s="18" t="inlineStr">
+        <is>
+          <t>Directorate of Vanaspati, Vegetable Oils &amp; Fats within MoFPI. No separate site.</t>
+        </is>
+      </c>
+      <c r="K251" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L251" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M251" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="16">
       <c r="A252" s="4">
@@ -15512,15 +15784,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E252" s="18" t="n"/>
-      <c r="F252" s="18" t="n"/>
-      <c r="G252" s="18" t="n"/>
-      <c r="H252" s="18" t="n"/>
-      <c r="I252" s="18" t="n"/>
-      <c r="J252" s="18" t="n"/>
-      <c r="K252" s="18" t="n"/>
-      <c r="L252" s="18" t="n"/>
-      <c r="M252" s="18" t="n"/>
+      <c r="E252" s="17" t="inlineStr">
+        <is>
+          <t>https://www.iifpt.edu.in/</t>
+        </is>
+      </c>
+      <c r="F252" s="17" t="inlineStr">
+        <is>
+          <t>https://www.iifpt.edu.in/</t>
+        </is>
+      </c>
+      <c r="G252" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H252" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I252" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J252" s="18" t="inlineStr">
+        <is>
+          <t>IIFPT site unreachable from this environment. Confirmed as official domain. Autonomous body under MoFPI.</t>
+        </is>
+      </c>
+      <c r="K252" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L252" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M252" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="16">
       <c r="A253" s="4">
@@ -15542,15 +15848,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E253" s="18" t="n"/>
-      <c r="F253" s="18" t="n"/>
-      <c r="G253" s="18" t="n"/>
-      <c r="H253" s="18" t="n"/>
-      <c r="I253" s="18" t="n"/>
-      <c r="J253" s="18" t="n"/>
-      <c r="K253" s="18" t="n"/>
-      <c r="L253" s="18" t="n"/>
-      <c r="M253" s="18" t="n"/>
+      <c r="E253" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niftem.ac.in/career</t>
+        </is>
+      </c>
+      <c r="F253" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niftem.ac.in/career</t>
+        </is>
+      </c>
+      <c r="G253" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H253" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I253" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J253" s="18" t="inlineStr">
+        <is>
+          <t>NIFTEM Kundli career page verified live. Autonomous body under MoFPI.</t>
+        </is>
+      </c>
+      <c r="K253" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L253" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M253" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="16">
       <c r="A254" s="4">
@@ -15572,15 +15912,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E254" s="18" t="n"/>
-      <c r="F254" s="18" t="n"/>
-      <c r="G254" s="18" t="n"/>
-      <c r="H254" s="18" t="n"/>
-      <c r="I254" s="18" t="n"/>
-      <c r="J254" s="18" t="n"/>
-      <c r="K254" s="18" t="n"/>
-      <c r="L254" s="18" t="n"/>
-      <c r="M254" s="18" t="n"/>
+      <c r="E254" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niftem.ac.in/career</t>
+        </is>
+      </c>
+      <c r="F254" s="17" t="inlineStr">
+        <is>
+          <t>https://www.niftem.ac.in/career</t>
+        </is>
+      </c>
+      <c r="G254" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H254" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I254" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J254" s="18" t="inlineStr">
+        <is>
+          <t>NIFTEM Thanjavur - second campus; recruitment through main NIFTEM career page.</t>
+        </is>
+      </c>
+      <c r="K254" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L254" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M254" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="16">
       <c r="A255" s="4">
@@ -15602,15 +15976,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E255" s="18" t="n"/>
-      <c r="F255" s="18" t="n"/>
-      <c r="G255" s="18" t="n"/>
-      <c r="H255" s="18" t="n"/>
-      <c r="I255" s="18" t="n"/>
-      <c r="J255" s="18" t="n"/>
-      <c r="K255" s="18" t="n"/>
-      <c r="L255" s="18" t="n"/>
-      <c r="M255" s="18" t="n"/>
+      <c r="E255" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F255" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G255" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H255" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I255" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J255" s="18" t="inlineStr">
+        <is>
+          <t>Sugar Commissionerate Field Offices are subordinate to MoFPI. No separate site.</t>
+        </is>
+      </c>
+      <c r="K255" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L255" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M255" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="16">
       <c r="A256" s="4">
@@ -15632,15 +16040,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E256" s="18" t="n"/>
-      <c r="F256" s="18" t="n"/>
-      <c r="G256" s="18" t="n"/>
-      <c r="H256" s="18" t="n"/>
-      <c r="I256" s="18" t="n"/>
-      <c r="J256" s="18" t="n"/>
-      <c r="K256" s="18" t="n"/>
-      <c r="L256" s="18" t="n"/>
-      <c r="M256" s="18" t="n"/>
+      <c r="E256" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F256" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G256" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H256" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I256" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J256" s="18" t="inlineStr">
+        <is>
+          <t>Food Processing Field/Regional Offices are subordinate to MoFPI. No separate site.</t>
+        </is>
+      </c>
+      <c r="K256" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L256" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M256" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="16">
       <c r="A257" s="4">
@@ -15692,15 +16134,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E258" s="18" t="n"/>
-      <c r="F258" s="18" t="n"/>
-      <c r="G258" s="18" t="n"/>
-      <c r="H258" s="18" t="n"/>
-      <c r="I258" s="18" t="n"/>
-      <c r="J258" s="18" t="n"/>
-      <c r="K258" s="18" t="n"/>
-      <c r="L258" s="18" t="n"/>
-      <c r="M258" s="18" t="n"/>
+      <c r="E258" s="17" t="inlineStr">
+        <is>
+          <t>https://dhr.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F258" s="17" t="inlineStr">
+        <is>
+          <t>https://dhr.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G258" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H258" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I258" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J258" s="18" t="inlineStr">
+        <is>
+          <t>Department of Health Research vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K258" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L258" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M258" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N258" s="14" t="n"/>
       <c r="O258" s="14" t="n"/>
       <c r="P258" s="14" t="n"/>
@@ -15733,15 +16209,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E259" s="18" t="n"/>
-      <c r="F259" s="18" t="n"/>
-      <c r="G259" s="18" t="n"/>
-      <c r="H259" s="18" t="n"/>
-      <c r="I259" s="18" t="n"/>
-      <c r="J259" s="18" t="n"/>
-      <c r="K259" s="18" t="n"/>
-      <c r="L259" s="18" t="n"/>
-      <c r="M259" s="18" t="n"/>
+      <c r="E259" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F259" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G259" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H259" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I259" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J259" s="18" t="inlineStr">
+        <is>
+          <t>Department of Health and Family Welfare vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K259" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L259" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M259" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N259" s="14" t="n"/>
       <c r="O259" s="14" t="n"/>
       <c r="P259" s="14" t="n"/>
@@ -15774,15 +16284,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E260" s="18" t="n"/>
-      <c r="F260" s="18" t="n"/>
-      <c r="G260" s="18" t="n"/>
-      <c r="H260" s="18" t="n"/>
-      <c r="I260" s="18" t="n"/>
-      <c r="J260" s="18" t="n"/>
-      <c r="K260" s="18" t="n"/>
-      <c r="L260" s="18" t="n"/>
-      <c r="M260" s="18" t="n"/>
+      <c r="E260" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F260" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G260" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H260" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I260" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J260" s="18" t="inlineStr">
+        <is>
+          <t>National Programme for Control of Blindness is a division/attached office under DoHFW. No separate recruitment page.</t>
+        </is>
+      </c>
+      <c r="K260" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L260" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M260" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N260" s="14" t="n"/>
       <c r="O260" s="14" t="n"/>
       <c r="P260" s="14" t="n"/>
@@ -15815,15 +16359,49 @@
           <t>Academies / Institutions</t>
         </is>
       </c>
-      <c r="E261" s="18" t="n"/>
-      <c r="F261" s="18" t="n"/>
-      <c r="G261" s="18" t="n"/>
-      <c r="H261" s="18" t="n"/>
-      <c r="I261" s="18" t="n"/>
-      <c r="J261" s="18" t="n"/>
-      <c r="K261" s="18" t="n"/>
-      <c r="L261" s="18" t="n"/>
-      <c r="M261" s="18" t="n"/>
+      <c r="E261" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F261" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G261" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H261" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I261" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J261" s="18" t="inlineStr">
+        <is>
+          <t>Central Leprosy Teaching and Research Institute. Small institution; recruitment through MoHFW channels.</t>
+        </is>
+      </c>
+      <c r="K261" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L261" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M261" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N261" s="14" t="n"/>
       <c r="O261" s="14" t="n"/>
       <c r="P261" s="14" t="n"/>
@@ -15856,15 +16434,49 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="E262" s="18" t="n"/>
-      <c r="F262" s="18" t="n"/>
-      <c r="G262" s="18" t="n"/>
-      <c r="H262" s="18" t="n"/>
-      <c r="I262" s="18" t="n"/>
-      <c r="J262" s="18" t="n"/>
-      <c r="K262" s="18" t="n"/>
-      <c r="L262" s="18" t="n"/>
-      <c r="M262" s="18" t="n"/>
+      <c r="E262" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F262" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G262" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H262" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I262" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J262" s="18" t="inlineStr">
+        <is>
+          <t>NOTTO is under DoHFW. Small body; recruitment through MoHFW.</t>
+        </is>
+      </c>
+      <c r="K262" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L262" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M262" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N262" s="14" t="n"/>
       <c r="O262" s="14" t="n"/>
       <c r="P262" s="14" t="n"/>
@@ -15897,15 +16509,49 @@
           <t>Attached / Subordinated Offices</t>
         </is>
       </c>
-      <c r="E263" s="18" t="n"/>
-      <c r="F263" s="18" t="n"/>
-      <c r="G263" s="18" t="n"/>
-      <c r="H263" s="18" t="n"/>
-      <c r="I263" s="18" t="n"/>
-      <c r="J263" s="18" t="n"/>
-      <c r="K263" s="18" t="n"/>
-      <c r="L263" s="18" t="n"/>
-      <c r="M263" s="18" t="n"/>
+      <c r="E263" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F263" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G263" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H263" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I263" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J263" s="18" t="inlineStr">
+        <is>
+          <t>Medical Stores Organisation is an attached/subordinate office under MoHFW.</t>
+        </is>
+      </c>
+      <c r="K263" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L263" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M263" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N263" s="14" t="n"/>
       <c r="O263" s="14" t="n"/>
       <c r="P263" s="14" t="n"/>
@@ -15938,15 +16584,49 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="E264" s="18" t="n"/>
-      <c r="F264" s="18" t="n"/>
-      <c r="G264" s="18" t="n"/>
-      <c r="H264" s="18" t="n"/>
-      <c r="I264" s="18" t="n"/>
-      <c r="J264" s="18" t="n"/>
-      <c r="K264" s="18" t="n"/>
-      <c r="L264" s="18" t="n"/>
-      <c r="M264" s="18" t="n"/>
+      <c r="E264" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F264" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G264" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H264" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I264" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J264" s="18" t="inlineStr">
+        <is>
+          <t>Central TB Division is within DoHFW. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K264" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L264" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M264" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N264" s="14" t="n"/>
       <c r="O264" s="14" t="n"/>
       <c r="P264" s="14" t="n"/>
@@ -15979,15 +16659,49 @@
           <t>Attached / Subordinated Offices</t>
         </is>
       </c>
-      <c r="E265" s="18" t="n"/>
-      <c r="F265" s="18" t="n"/>
-      <c r="G265" s="18" t="n"/>
-      <c r="H265" s="18" t="n"/>
-      <c r="I265" s="18" t="n"/>
-      <c r="J265" s="18" t="n"/>
-      <c r="K265" s="18" t="n"/>
-      <c r="L265" s="18" t="n"/>
-      <c r="M265" s="18" t="n"/>
+      <c r="E265" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F265" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G265" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H265" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I265" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J265" s="18" t="inlineStr">
+        <is>
+          <t>BCG Vaccine Laboratory Chennai. Small attached office; recruitment through MoHFW.</t>
+        </is>
+      </c>
+      <c r="K265" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L265" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M265" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N265" s="14" t="n"/>
       <c r="O265" s="14" t="n"/>
       <c r="P265" s="14" t="n"/>
@@ -16020,15 +16734,49 @@
           <t>Academies / Institutions</t>
         </is>
       </c>
-      <c r="E266" s="18" t="n"/>
-      <c r="F266" s="18" t="n"/>
-      <c r="G266" s="18" t="n"/>
-      <c r="H266" s="18" t="n"/>
-      <c r="I266" s="18" t="n"/>
-      <c r="J266" s="18" t="n"/>
-      <c r="K266" s="18" t="n"/>
-      <c r="L266" s="18" t="n"/>
-      <c r="M266" s="18" t="n"/>
+      <c r="E266" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F266" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G266" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H266" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I266" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J266" s="18" t="inlineStr">
+        <is>
+          <t>Regional Institute of Pharmaceutical Science and Technology. Small institute under MoHFW.</t>
+        </is>
+      </c>
+      <c r="K266" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L266" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M266" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N266" s="14" t="n"/>
       <c r="O266" s="14" t="n"/>
       <c r="P266" s="14" t="n"/>
@@ -16061,15 +16809,49 @@
           <t>Others</t>
         </is>
       </c>
-      <c r="E267" s="18" t="n"/>
-      <c r="F267" s="18" t="n"/>
-      <c r="G267" s="18" t="n"/>
-      <c r="H267" s="18" t="n"/>
-      <c r="I267" s="18" t="n"/>
-      <c r="J267" s="18" t="n"/>
-      <c r="K267" s="18" t="n"/>
-      <c r="L267" s="18" t="n"/>
-      <c r="M267" s="18" t="n"/>
+      <c r="E267" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F267" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G267" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H267" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I267" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J267" s="18" t="inlineStr">
+        <is>
+          <t>Central Drugs Laboratory Kasauli. Subordinate office; recruitment through MoHFW/CDSCO channels.</t>
+        </is>
+      </c>
+      <c r="K267" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L267" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M267" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N267" s="14" t="n"/>
       <c r="O267" s="14" t="n"/>
       <c r="P267" s="14" t="n"/>
@@ -16143,15 +16925,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E269" s="18" t="n"/>
-      <c r="F269" s="18" t="n"/>
-      <c r="G269" s="18" t="n"/>
-      <c r="H269" s="18" t="n"/>
-      <c r="I269" s="18" t="n"/>
-      <c r="J269" s="18" t="n"/>
-      <c r="K269" s="18" t="n"/>
-      <c r="L269" s="18" t="n"/>
-      <c r="M269" s="18" t="n"/>
+      <c r="E269" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F269" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G269" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H269" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I269" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J269" s="18" t="inlineStr">
+        <is>
+          <t>MHA vacancies page verified live (HTTP 200). Secretariat-level recruitment.</t>
+        </is>
+      </c>
+      <c r="K269" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L269" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M269" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="16">
       <c r="A270" s="4">
@@ -16173,15 +16989,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E270" s="18" t="n"/>
-      <c r="F270" s="18" t="n"/>
-      <c r="G270" s="18" t="n"/>
-      <c r="H270" s="18" t="n"/>
-      <c r="I270" s="18" t="n"/>
-      <c r="J270" s="18" t="n"/>
-      <c r="K270" s="18" t="n"/>
-      <c r="L270" s="18" t="n"/>
-      <c r="M270" s="18" t="n"/>
+      <c r="E270" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F270" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G270" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H270" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I270" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J270" s="18" t="inlineStr">
+        <is>
+          <t>Internal Security Division is within MHA Secretariat. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K270" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L270" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M270" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="16">
       <c r="A271" s="4">
@@ -16203,15 +17053,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E271" s="18" t="n"/>
-      <c r="F271" s="18" t="n"/>
-      <c r="G271" s="18" t="n"/>
-      <c r="H271" s="18" t="n"/>
-      <c r="I271" s="18" t="n"/>
-      <c r="J271" s="18" t="n"/>
-      <c r="K271" s="18" t="n"/>
-      <c r="L271" s="18" t="n"/>
-      <c r="M271" s="18" t="n"/>
+      <c r="E271" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F271" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G271" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H271" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I271" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J271" s="18" t="inlineStr">
+        <is>
+          <t>Border Management Division is within MHA Secretariat.</t>
+        </is>
+      </c>
+      <c r="K271" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L271" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M271" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="16">
       <c r="A272" s="4">
@@ -16233,15 +17117,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E272" s="18" t="n"/>
-      <c r="F272" s="18" t="n"/>
-      <c r="G272" s="18" t="n"/>
-      <c r="H272" s="18" t="n"/>
-      <c r="I272" s="18" t="n"/>
-      <c r="J272" s="18" t="n"/>
-      <c r="K272" s="18" t="n"/>
-      <c r="L272" s="18" t="n"/>
-      <c r="M272" s="18" t="n"/>
+      <c r="E272" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F272" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G272" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H272" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I272" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J272" s="18" t="inlineStr">
+        <is>
+          <t>Police Division is within MHA Secretariat.</t>
+        </is>
+      </c>
+      <c r="K272" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L272" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M272" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="16">
       <c r="A273" s="4">
@@ -16263,15 +17181,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E273" s="18" t="n"/>
-      <c r="F273" s="18" t="n"/>
-      <c r="G273" s="18" t="n"/>
-      <c r="H273" s="18" t="n"/>
-      <c r="I273" s="18" t="n"/>
-      <c r="J273" s="18" t="n"/>
-      <c r="K273" s="18" t="n"/>
-      <c r="L273" s="18" t="n"/>
-      <c r="M273" s="18" t="n"/>
+      <c r="E273" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F273" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G273" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H273" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I273" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J273" s="18" t="inlineStr">
+        <is>
+          <t>Union Territories Division is within MHA.</t>
+        </is>
+      </c>
+      <c r="K273" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L273" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M273" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="16">
       <c r="A274" s="4">
@@ -16293,15 +17245,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E274" s="18" t="n"/>
-      <c r="F274" s="18" t="n"/>
-      <c r="G274" s="18" t="n"/>
-      <c r="H274" s="18" t="n"/>
-      <c r="I274" s="18" t="n"/>
-      <c r="J274" s="18" t="n"/>
-      <c r="K274" s="18" t="n"/>
-      <c r="L274" s="18" t="n"/>
-      <c r="M274" s="18" t="n"/>
+      <c r="E274" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F274" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G274" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H274" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I274" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J274" s="18" t="inlineStr">
+        <is>
+          <t>Judicial Division is within MHA.</t>
+        </is>
+      </c>
+      <c r="K274" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L274" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M274" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="16">
       <c r="A275" s="4">
@@ -16323,15 +17309,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E275" s="18" t="n"/>
-      <c r="F275" s="18" t="n"/>
-      <c r="G275" s="18" t="n"/>
-      <c r="H275" s="18" t="n"/>
-      <c r="I275" s="18" t="n"/>
-      <c r="J275" s="18" t="n"/>
-      <c r="K275" s="18" t="n"/>
-      <c r="L275" s="18" t="n"/>
-      <c r="M275" s="18" t="n"/>
+      <c r="E275" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F275" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G275" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H275" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I275" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J275" s="18" t="inlineStr">
+        <is>
+          <t>Disaster Management Division within MHA. NDMA recruitment handled separately.</t>
+        </is>
+      </c>
+      <c r="K275" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L275" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M275" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="16">
       <c r="A276" s="4">
@@ -16353,15 +17373,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E276" s="18" t="n"/>
-      <c r="F276" s="18" t="n"/>
-      <c r="G276" s="18" t="n"/>
-      <c r="H276" s="18" t="n"/>
-      <c r="I276" s="18" t="n"/>
-      <c r="J276" s="18" t="n"/>
-      <c r="K276" s="18" t="n"/>
-      <c r="L276" s="18" t="n"/>
-      <c r="M276" s="18" t="n"/>
+      <c r="E276" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F276" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G276" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H276" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I276" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J276" s="18" t="inlineStr">
+        <is>
+          <t>Intelligence Bureau (IB). Recruitment through MHA; recent 2025-26 Security Assistant recruitment (4987 posts) via mha.gov.in.</t>
+        </is>
+      </c>
+      <c r="K276" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L276" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M276" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="16">
       <c r="A277" s="4">
@@ -16383,15 +17437,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E277" s="18" t="n"/>
-      <c r="F277" s="18" t="n"/>
-      <c r="G277" s="18" t="n"/>
-      <c r="H277" s="18" t="n"/>
-      <c r="I277" s="18" t="n"/>
-      <c r="J277" s="18" t="n"/>
-      <c r="K277" s="18" t="n"/>
-      <c r="L277" s="18" t="n"/>
-      <c r="M277" s="18" t="n"/>
+      <c r="E277" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ncrb.gov.in/</t>
+        </is>
+      </c>
+      <c r="F277" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ncrb.gov.in/</t>
+        </is>
+      </c>
+      <c r="G277" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H277" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I277" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J277" s="18" t="inlineStr">
+        <is>
+          <t>NCRB official site verified live. Attached office under MHA. Staff mostly on deputation.</t>
+        </is>
+      </c>
+      <c r="K277" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L277" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M277" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="16">
       <c r="A278" s="4">
@@ -16413,15 +17501,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E278" s="18" t="n"/>
-      <c r="F278" s="18" t="n"/>
-      <c r="G278" s="18" t="n"/>
-      <c r="H278" s="18" t="n"/>
-      <c r="I278" s="18" t="n"/>
-      <c r="J278" s="18" t="n"/>
-      <c r="K278" s="18" t="n"/>
-      <c r="L278" s="18" t="n"/>
-      <c r="M278" s="18" t="n"/>
+      <c r="E278" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F278" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G278" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H278" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I278" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J278" s="18" t="inlineStr">
+        <is>
+          <t>BPR&amp;D is an attached office under MHA. No independent recruitment portal found. Staff on deputation.</t>
+        </is>
+      </c>
+      <c r="K278" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L278" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M278" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="16">
       <c r="A279" s="4">
@@ -16443,15 +17565,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E279" s="18" t="n"/>
-      <c r="F279" s="18" t="n"/>
-      <c r="G279" s="18" t="n"/>
-      <c r="H279" s="18" t="n"/>
-      <c r="I279" s="18" t="n"/>
-      <c r="J279" s="18" t="n"/>
-      <c r="K279" s="18" t="n"/>
-      <c r="L279" s="18" t="n"/>
-      <c r="M279" s="18" t="n"/>
+      <c r="E279" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F279" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G279" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H279" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I279" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J279" s="18" t="inlineStr">
+        <is>
+          <t>CFSL HQ under MHA. Recruitment through MHA/SSC channels.</t>
+        </is>
+      </c>
+      <c r="K279" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L279" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M279" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="16">
       <c r="A280" s="4">
@@ -16473,15 +17629,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E280" s="18" t="n"/>
-      <c r="F280" s="18" t="n"/>
-      <c r="G280" s="18" t="n"/>
-      <c r="H280" s="18" t="n"/>
-      <c r="I280" s="18" t="n"/>
-      <c r="J280" s="18" t="n"/>
-      <c r="K280" s="18" t="n"/>
-      <c r="L280" s="18" t="n"/>
-      <c r="M280" s="18" t="n"/>
+      <c r="E280" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F280" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G280" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H280" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I280" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J280" s="18" t="inlineStr">
+        <is>
+          <t>Registrar General &amp; Census Commissioner (RGI). Recruitment through MHA/SSC. Census operations staff.</t>
+        </is>
+      </c>
+      <c r="K280" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L280" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M280" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="16">
       <c r="A281" s="4">
@@ -16503,15 +17693,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E281" s="18" t="n"/>
-      <c r="F281" s="18" t="n"/>
-      <c r="G281" s="18" t="n"/>
-      <c r="H281" s="18" t="n"/>
-      <c r="I281" s="18" t="n"/>
-      <c r="J281" s="18" t="n"/>
-      <c r="K281" s="18" t="n"/>
-      <c r="L281" s="18" t="n"/>
-      <c r="M281" s="18" t="n"/>
+      <c r="E281" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F281" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G281" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H281" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I281" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J281" s="18" t="inlineStr">
+        <is>
+          <t>CAPF HQ (BSF/CRPF/CISF/ITBP/SSB). Each force recruits through its own website but policy under MHA. Central deputation via MHA vacancies.</t>
+        </is>
+      </c>
+      <c r="K281" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L281" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M281" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="16">
       <c r="A282" s="4">
@@ -16533,15 +17757,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E282" s="18" t="n"/>
-      <c r="F282" s="18" t="n"/>
-      <c r="G282" s="18" t="n"/>
-      <c r="H282" s="18" t="n"/>
-      <c r="I282" s="18" t="n"/>
-      <c r="J282" s="18" t="n"/>
-      <c r="K282" s="18" t="n"/>
-      <c r="L282" s="18" t="n"/>
-      <c r="M282" s="18" t="n"/>
+      <c r="E282" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F282" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G282" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H282" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I282" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J282" s="18" t="inlineStr">
+        <is>
+          <t>CAPF Field Formations. Individual force recruitment portals (crpf.gov.in, bsf.gov.in, cisf.gov.in etc. verified live). Deputation through MHA.</t>
+        </is>
+      </c>
+      <c r="K282" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L282" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M282" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="16">
       <c r="A283" s="4">
@@ -16563,15 +17821,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E283" s="18" t="n"/>
-      <c r="F283" s="18" t="n"/>
-      <c r="G283" s="18" t="n"/>
-      <c r="H283" s="18" t="n"/>
-      <c r="I283" s="18" t="n"/>
-      <c r="J283" s="18" t="n"/>
-      <c r="K283" s="18" t="n"/>
-      <c r="L283" s="18" t="n"/>
-      <c r="M283" s="18" t="n"/>
+      <c r="E283" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F283" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G283" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H283" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I283" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J283" s="18" t="inlineStr">
+        <is>
+          <t>CFSL Regional Labs subordinate to CFSL HQ/MHA.</t>
+        </is>
+      </c>
+      <c r="K283" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L283" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M283" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="16">
       <c r="A284" s="4">
@@ -16593,15 +17885,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E284" s="18" t="n"/>
-      <c r="F284" s="18" t="n"/>
-      <c r="G284" s="18" t="n"/>
-      <c r="H284" s="18" t="n"/>
-      <c r="I284" s="18" t="n"/>
-      <c r="J284" s="18" t="n"/>
-      <c r="K284" s="18" t="n"/>
-      <c r="L284" s="18" t="n"/>
-      <c r="M284" s="18" t="n"/>
+      <c r="E284" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F284" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G284" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H284" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I284" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J284" s="18" t="inlineStr">
+        <is>
+          <t>Census Field Directorates subordinate to RGI/MHA.</t>
+        </is>
+      </c>
+      <c r="K284" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L284" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M284" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="16">
       <c r="A285" s="4">
@@ -16623,15 +17949,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E285" s="18" t="n"/>
-      <c r="F285" s="18" t="n"/>
-      <c r="G285" s="18" t="n"/>
-      <c r="H285" s="18" t="n"/>
-      <c r="I285" s="18" t="n"/>
-      <c r="J285" s="18" t="n"/>
-      <c r="K285" s="18" t="n"/>
-      <c r="L285" s="18" t="n"/>
-      <c r="M285" s="18" t="n"/>
+      <c r="E285" s="17" t="inlineStr">
+        <is>
+          <t>https://ndma.gov.in/</t>
+        </is>
+      </c>
+      <c r="F285" s="17" t="inlineStr">
+        <is>
+          <t>https://ndma.gov.in/</t>
+        </is>
+      </c>
+      <c r="G285" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H285" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I285" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J285" s="18" t="inlineStr">
+        <is>
+          <t>NDMA official site (ndma.gov.in). Unreachable from this environment but confirmed as official domain. Statutory body under MHA.</t>
+        </is>
+      </c>
+      <c r="K285" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L285" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M285" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="16">
       <c r="A286" s="4">
@@ -16653,15 +18013,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E286" s="18" t="n"/>
-      <c r="F286" s="18" t="n"/>
-      <c r="G286" s="18" t="n"/>
-      <c r="H286" s="18" t="n"/>
-      <c r="I286" s="18" t="n"/>
-      <c r="J286" s="18" t="n"/>
-      <c r="K286" s="18" t="n"/>
-      <c r="L286" s="18" t="n"/>
-      <c r="M286" s="18" t="n"/>
+      <c r="E286" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nia.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F286" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nia.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G286" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H286" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I286" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J286" s="18" t="inlineStr">
+        <is>
+          <t>NIA recruitment page verified live. Statutory body under MHA.</t>
+        </is>
+      </c>
+      <c r="K286" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L286" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M286" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="16">
       <c r="A287" s="4">
@@ -16683,15 +18077,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E287" s="18" t="n"/>
-      <c r="F287" s="18" t="n"/>
-      <c r="G287" s="18" t="n"/>
-      <c r="H287" s="18" t="n"/>
-      <c r="I287" s="18" t="n"/>
-      <c r="J287" s="18" t="n"/>
-      <c r="K287" s="18" t="n"/>
-      <c r="L287" s="18" t="n"/>
-      <c r="M287" s="18" t="n"/>
+      <c r="E287" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F287" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G287" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H287" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I287" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J287" s="18" t="inlineStr">
+        <is>
+          <t>Inter-State Council Secretariat is under MHA. Very small body; staff on deputation via MHA channels.</t>
+        </is>
+      </c>
+      <c r="K287" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L287" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M287" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="16">
       <c r="A288" s="4">
@@ -16713,15 +18141,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E288" s="18" t="n"/>
-      <c r="F288" s="18" t="n"/>
-      <c r="G288" s="18" t="n"/>
-      <c r="H288" s="18" t="n"/>
-      <c r="I288" s="18" t="n"/>
-      <c r="J288" s="18" t="n"/>
-      <c r="K288" s="18" t="n"/>
-      <c r="L288" s="18" t="n"/>
-      <c r="M288" s="18" t="n"/>
+      <c r="E288" s="17" t="inlineStr">
+        <is>
+          <t>https://www.svpnpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F288" s="17" t="inlineStr">
+        <is>
+          <t>https://www.svpnpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G288" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H288" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I288" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J288" s="18" t="inlineStr">
+        <is>
+          <t>SVPNPA (National Police Academy) site unreachable from this environment. Confirmed as official domain. Autonomous body under MHA. Training academy; limited external recruitment.</t>
+        </is>
+      </c>
+      <c r="K288" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L288" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M288" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="16">
       <c r="A289" s="4">
@@ -16743,15 +18205,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E289" s="18" t="n"/>
-      <c r="F289" s="18" t="n"/>
-      <c r="G289" s="18" t="n"/>
-      <c r="H289" s="18" t="n"/>
-      <c r="I289" s="18" t="n"/>
-      <c r="J289" s="18" t="n"/>
-      <c r="K289" s="18" t="n"/>
-      <c r="L289" s="18" t="n"/>
-      <c r="M289" s="18" t="n"/>
+      <c r="E289" s="17" t="inlineStr">
+        <is>
+          <t>https://www.lbsnaa.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F289" s="17" t="inlineStr">
+        <is>
+          <t>https://www.lbsnaa.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G289" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H289" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I289" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J289" s="18" t="inlineStr">
+        <is>
+          <t>LBSNAA vacancy page verified live. Autonomous training academy under MHA/DoPT.</t>
+        </is>
+      </c>
+      <c r="K289" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L289" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M289" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="16">
       <c r="A290" s="4">
@@ -16803,15 +18299,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E291" s="18" t="n"/>
-      <c r="F291" s="18" t="n"/>
-      <c r="G291" s="18" t="n"/>
-      <c r="H291" s="18" t="n"/>
-      <c r="I291" s="18" t="n"/>
-      <c r="J291" s="18" t="n"/>
-      <c r="K291" s="18" t="n"/>
-      <c r="L291" s="18" t="n"/>
-      <c r="M291" s="18" t="n"/>
+      <c r="E291" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F291" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G291" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H291" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I291" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J291" s="18" t="inlineStr">
+        <is>
+          <t>MoHUA official site (mohua.gov.in). Unreachable from this environment but confirmed as official domain. Vacancy circulars posted on site.</t>
+        </is>
+      </c>
+      <c r="K291" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L291" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M291" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="16">
       <c r="A292" s="4">
@@ -16833,15 +18363,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E292" s="18" t="n"/>
-      <c r="F292" s="18" t="n"/>
-      <c r="G292" s="18" t="n"/>
-      <c r="H292" s="18" t="n"/>
-      <c r="I292" s="18" t="n"/>
-      <c r="J292" s="18" t="n"/>
-      <c r="K292" s="18" t="n"/>
-      <c r="L292" s="18" t="n"/>
-      <c r="M292" s="18" t="n"/>
+      <c r="E292" s="17" t="inlineStr">
+        <is>
+          <t>https://cpwd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F292" s="17" t="inlineStr">
+        <is>
+          <t>https://cpwd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G292" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H292" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I292" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J292" s="18" t="inlineStr">
+        <is>
+          <t>CPWD official site (cpwd.gov.in). Unreachable from this environment but confirmed as official domain. Major attached office under MoHUA. Recruitment via SSC and departmental exams.</t>
+        </is>
+      </c>
+      <c r="K292" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L292" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M292" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="16">
       <c r="A293" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -18427,15 +18427,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E293" s="18" t="n"/>
-      <c r="F293" s="18" t="n"/>
-      <c r="G293" s="18" t="n"/>
-      <c r="H293" s="18" t="n"/>
-      <c r="I293" s="18" t="n"/>
-      <c r="J293" s="18" t="n"/>
-      <c r="K293" s="18" t="n"/>
-      <c r="L293" s="18" t="n"/>
-      <c r="M293" s="18" t="n"/>
+      <c r="E293" s="17" t="inlineStr">
+        <is>
+          <t>https://estates.gov.in/</t>
+        </is>
+      </c>
+      <c r="F293" s="17" t="inlineStr">
+        <is>
+          <t>https://estates.gov.in/</t>
+        </is>
+      </c>
+      <c r="G293" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H293" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I293" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J293" s="18" t="inlineStr">
+        <is>
+          <t>Directorate of Estates (estates.gov.in). Unreachable from this environment but confirmed as official domain. Attached office under MoHUA.</t>
+        </is>
+      </c>
+      <c r="K293" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L293" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M293" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="16">
       <c r="A294" s="4">
@@ -18457,15 +18491,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E294" s="18" t="n"/>
-      <c r="F294" s="18" t="n"/>
-      <c r="G294" s="18" t="n"/>
-      <c r="H294" s="18" t="n"/>
-      <c r="I294" s="18" t="n"/>
-      <c r="J294" s="18" t="n"/>
-      <c r="K294" s="18" t="n"/>
-      <c r="L294" s="18" t="n"/>
-      <c r="M294" s="18" t="n"/>
+      <c r="E294" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F294" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G294" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H294" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I294" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J294" s="18" t="inlineStr">
+        <is>
+          <t>TCPO (Town &amp; Country Planning Organisation) is a small attached office under MoHUA. No separate website found; recruitment through MoHUA channels.</t>
+        </is>
+      </c>
+      <c r="K294" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L294" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M294" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="16">
       <c r="A295" s="4">
@@ -18487,15 +18555,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E295" s="18" t="n"/>
-      <c r="F295" s="18" t="n"/>
-      <c r="G295" s="18" t="n"/>
-      <c r="H295" s="18" t="n"/>
-      <c r="I295" s="18" t="n"/>
-      <c r="J295" s="18" t="n"/>
-      <c r="K295" s="18" t="n"/>
-      <c r="L295" s="18" t="n"/>
-      <c r="M295" s="18" t="n"/>
+      <c r="E295" s="17" t="inlineStr">
+        <is>
+          <t>https://cpwd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F295" s="17" t="inlineStr">
+        <is>
+          <t>https://cpwd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G295" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H295" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I295" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J295" s="18" t="inlineStr">
+        <is>
+          <t>CPWD Field Units/Zones are subordinate to CPWD. Recruitment through central CPWD portal.</t>
+        </is>
+      </c>
+      <c r="K295" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L295" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M295" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="16">
       <c r="A296" s="4">
@@ -18517,15 +18619,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E296" s="18" t="n"/>
-      <c r="F296" s="18" t="n"/>
-      <c r="G296" s="18" t="n"/>
-      <c r="H296" s="18" t="n"/>
-      <c r="I296" s="18" t="n"/>
-      <c r="J296" s="18" t="n"/>
-      <c r="K296" s="18" t="n"/>
-      <c r="L296" s="18" t="n"/>
-      <c r="M296" s="18" t="n"/>
+      <c r="E296" s="17" t="inlineStr">
+        <is>
+          <t>https://estates.gov.in/</t>
+        </is>
+      </c>
+      <c r="F296" s="17" t="inlineStr">
+        <is>
+          <t>https://estates.gov.in/</t>
+        </is>
+      </c>
+      <c r="G296" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H296" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I296" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J296" s="18" t="inlineStr">
+        <is>
+          <t>Directorate of Estates Regional Offices subordinate to the Directorate. No separate site.</t>
+        </is>
+      </c>
+      <c r="K296" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L296" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M296" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="16">
       <c r="A297" s="4">
@@ -18547,15 +18683,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E297" s="18" t="n"/>
-      <c r="F297" s="18" t="n"/>
-      <c r="G297" s="18" t="n"/>
-      <c r="H297" s="18" t="n"/>
-      <c r="I297" s="18" t="n"/>
-      <c r="J297" s="18" t="n"/>
-      <c r="K297" s="18" t="n"/>
-      <c r="L297" s="18" t="n"/>
-      <c r="M297" s="18" t="n"/>
+      <c r="E297" s="17" t="inlineStr">
+        <is>
+          <t>https://dda.gov.in/latest-jobs</t>
+        </is>
+      </c>
+      <c r="F297" s="17" t="inlineStr">
+        <is>
+          <t>https://dda.gov.in/latest-jobs</t>
+        </is>
+      </c>
+      <c r="G297" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H297" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I297" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J297" s="18" t="inlineStr">
+        <is>
+          <t>DDA latest-jobs page verified live. Statutory body under MoHUA.</t>
+        </is>
+      </c>
+      <c r="K297" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L297" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M297" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="16">
       <c r="A298" s="4">
@@ -18577,15 +18747,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E298" s="18" t="n"/>
-      <c r="F298" s="18" t="n"/>
-      <c r="G298" s="18" t="n"/>
-      <c r="H298" s="18" t="n"/>
-      <c r="I298" s="18" t="n"/>
-      <c r="J298" s="18" t="n"/>
-      <c r="K298" s="18" t="n"/>
-      <c r="L298" s="18" t="n"/>
-      <c r="M298" s="18" t="n"/>
+      <c r="E298" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F298" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G298" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H298" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I298" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J298" s="18" t="inlineStr">
+        <is>
+          <t>NKDA (New Town Kolkata Development Authority) - state-level body listed under MoHUA. Limited GoI recruitment involvement. Mapped to parent MoHUA.</t>
+        </is>
+      </c>
+      <c r="K298" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L298" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M298" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="16">
       <c r="A299" s="4">
@@ -18607,15 +18811,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E299" s="18" t="n"/>
-      <c r="F299" s="18" t="n"/>
-      <c r="G299" s="18" t="n"/>
-      <c r="H299" s="18" t="n"/>
-      <c r="I299" s="18" t="n"/>
-      <c r="J299" s="18" t="n"/>
-      <c r="K299" s="18" t="n"/>
-      <c r="L299" s="18" t="n"/>
-      <c r="M299" s="18" t="n"/>
+      <c r="E299" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F299" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G299" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H299" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I299" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J299" s="18" t="inlineStr">
+        <is>
+          <t>Noida Authority is a state-level body (UP Govt). Listed under MoHUA for policy. Mapped to parent ministry.</t>
+        </is>
+      </c>
+      <c r="K299" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L299" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M299" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="16">
       <c r="A300" s="4">
@@ -18637,15 +18875,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E300" s="18" t="n"/>
-      <c r="F300" s="18" t="n"/>
-      <c r="G300" s="18" t="n"/>
-      <c r="H300" s="18" t="n"/>
-      <c r="I300" s="18" t="n"/>
-      <c r="J300" s="18" t="n"/>
-      <c r="K300" s="18" t="n"/>
-      <c r="L300" s="18" t="n"/>
-      <c r="M300" s="18" t="n"/>
+      <c r="E300" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F300" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G300" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H300" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I300" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J300" s="18" t="inlineStr">
+        <is>
+          <t>NBO (National Buildings Organisation) - small body under MoHUA. No independent website found.</t>
+        </is>
+      </c>
+      <c r="K300" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L300" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M300" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="16">
       <c r="A301" s="4">
@@ -18667,15 +18939,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E301" s="18" t="n"/>
-      <c r="F301" s="18" t="n"/>
-      <c r="G301" s="18" t="n"/>
-      <c r="H301" s="18" t="n"/>
-      <c r="I301" s="18" t="n"/>
-      <c r="J301" s="18" t="n"/>
-      <c r="K301" s="18" t="n"/>
-      <c r="L301" s="18" t="n"/>
-      <c r="M301" s="18" t="n"/>
+      <c r="E301" s="17" t="inlineStr">
+        <is>
+          <t>https://niua.in/</t>
+        </is>
+      </c>
+      <c r="F301" s="17" t="inlineStr">
+        <is>
+          <t>https://niua.in/</t>
+        </is>
+      </c>
+      <c r="G301" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H301" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I301" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J301" s="18" t="inlineStr">
+        <is>
+          <t>NIUA official site verified live. Autonomous body under MoHUA.</t>
+        </is>
+      </c>
+      <c r="K301" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L301" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M301" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="16">
       <c r="A302" s="4">
@@ -18697,15 +19003,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E302" s="18" t="n"/>
-      <c r="F302" s="18" t="n"/>
-      <c r="G302" s="18" t="n"/>
-      <c r="H302" s="18" t="n"/>
-      <c r="I302" s="18" t="n"/>
-      <c r="J302" s="18" t="n"/>
-      <c r="K302" s="18" t="n"/>
-      <c r="L302" s="18" t="n"/>
-      <c r="M302" s="18" t="n"/>
+      <c r="E302" s="17" t="inlineStr">
+        <is>
+          <t>https://hudco.org/</t>
+        </is>
+      </c>
+      <c r="F302" s="17" t="inlineStr">
+        <is>
+          <t>https://hudco.org/</t>
+        </is>
+      </c>
+      <c r="G302" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H302" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I302" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J302" s="18" t="inlineStr">
+        <is>
+          <t>HUDCO official site (hudco.org). Unreachable from this environment but confirmed as official domain. PSU under MoHUA.</t>
+        </is>
+      </c>
+      <c r="K302" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L302" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M302" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="15.75" customHeight="1" s="16">
       <c r="A303" s="4">
@@ -18757,15 +19097,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E304" s="18" t="n"/>
-      <c r="F304" s="18" t="n"/>
-      <c r="G304" s="18" t="n"/>
-      <c r="H304" s="18" t="n"/>
-      <c r="I304" s="18" t="n"/>
-      <c r="J304" s="18" t="n"/>
-      <c r="K304" s="18" t="n"/>
-      <c r="L304" s="18" t="n"/>
-      <c r="M304" s="18" t="n"/>
+      <c r="E304" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F304" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G304" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H304" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I304" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J304" s="18" t="inlineStr">
+        <is>
+          <t>MIB vacancies page verified live. Secretariat-level recruitment.</t>
+        </is>
+      </c>
+      <c r="K304" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L304" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M304" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="16">
       <c r="A305" s="4">
@@ -18787,15 +19161,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E305" s="18" t="n"/>
-      <c r="F305" s="18" t="n"/>
-      <c r="G305" s="18" t="n"/>
-      <c r="H305" s="18" t="n"/>
-      <c r="I305" s="18" t="n"/>
-      <c r="J305" s="18" t="n"/>
-      <c r="K305" s="18" t="n"/>
-      <c r="L305" s="18" t="n"/>
-      <c r="M305" s="18" t="n"/>
+      <c r="E305" s="17" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/</t>
+        </is>
+      </c>
+      <c r="F305" s="17" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/</t>
+        </is>
+      </c>
+      <c r="G305" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H305" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I305" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J305" s="18" t="inlineStr">
+        <is>
+          <t>PIB official site verified live. Staff on deputation from Indian Information Service. Recruitment through UPSC for IIS cadre.</t>
+        </is>
+      </c>
+      <c r="K305" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L305" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M305" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="16">
       <c r="A306" s="4">
@@ -18817,15 +19225,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E306" s="18" t="n"/>
-      <c r="F306" s="18" t="n"/>
-      <c r="G306" s="18" t="n"/>
-      <c r="H306" s="18" t="n"/>
-      <c r="I306" s="18" t="n"/>
-      <c r="J306" s="18" t="n"/>
-      <c r="K306" s="18" t="n"/>
-      <c r="L306" s="18" t="n"/>
-      <c r="M306" s="18" t="n"/>
+      <c r="E306" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F306" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G306" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H306" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I306" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J306" s="18" t="inlineStr">
+        <is>
+          <t>CBC (Central Bureau of Communication) is an attached office under MIB. No separate recruitment portal; via MIB vacancies.</t>
+        </is>
+      </c>
+      <c r="K306" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L306" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M306" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="16">
       <c r="A307" s="4">
@@ -18847,15 +19289,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E307" s="18" t="n"/>
-      <c r="F307" s="18" t="n"/>
-      <c r="G307" s="18" t="n"/>
-      <c r="H307" s="18" t="n"/>
-      <c r="I307" s="18" t="n"/>
-      <c r="J307" s="18" t="n"/>
-      <c r="K307" s="18" t="n"/>
-      <c r="L307" s="18" t="n"/>
-      <c r="M307" s="18" t="n"/>
+      <c r="E307" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F307" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G307" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H307" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I307" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J307" s="18" t="inlineStr">
+        <is>
+          <t>New Media Wing is within MIB. No separate recruitment page.</t>
+        </is>
+      </c>
+      <c r="K307" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L307" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M307" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" s="16">
       <c r="A308" s="4">
@@ -18877,15 +19353,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E308" s="18" t="n"/>
-      <c r="F308" s="18" t="n"/>
-      <c r="G308" s="18" t="n"/>
-      <c r="H308" s="18" t="n"/>
-      <c r="I308" s="18" t="n"/>
-      <c r="J308" s="18" t="n"/>
-      <c r="K308" s="18" t="n"/>
-      <c r="L308" s="18" t="n"/>
-      <c r="M308" s="18" t="n"/>
+      <c r="E308" s="17" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/</t>
+        </is>
+      </c>
+      <c r="F308" s="17" t="inlineStr">
+        <is>
+          <t>https://pib.gov.in/</t>
+        </is>
+      </c>
+      <c r="G308" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H308" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I308" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J308" s="18" t="inlineStr">
+        <is>
+          <t>PIB Regional/Field Offices - subordinate to PIB. Recruitment via IIS/UPSC and MIB channels.</t>
+        </is>
+      </c>
+      <c r="K308" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L308" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M308" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="16">
       <c r="A309" s="4">
@@ -18907,15 +19417,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E309" s="18" t="n"/>
-      <c r="F309" s="18" t="n"/>
-      <c r="G309" s="18" t="n"/>
-      <c r="H309" s="18" t="n"/>
-      <c r="I309" s="18" t="n"/>
-      <c r="J309" s="18" t="n"/>
-      <c r="K309" s="18" t="n"/>
-      <c r="L309" s="18" t="n"/>
-      <c r="M309" s="18" t="n"/>
+      <c r="E309" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F309" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G309" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H309" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I309" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J309" s="18" t="inlineStr">
+        <is>
+          <t>CBC Field Units subordinate to CBC/MIB.</t>
+        </is>
+      </c>
+      <c r="K309" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L309" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M309" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="15.75" customHeight="1" s="16">
       <c r="A310" s="4">
@@ -18937,15 +19481,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E310" s="18" t="n"/>
-      <c r="F310" s="18" t="n"/>
-      <c r="G310" s="18" t="n"/>
-      <c r="H310" s="18" t="n"/>
-      <c r="I310" s="18" t="n"/>
-      <c r="J310" s="18" t="n"/>
-      <c r="K310" s="18" t="n"/>
-      <c r="L310" s="18" t="n"/>
-      <c r="M310" s="18" t="n"/>
+      <c r="E310" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbfcindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F310" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cbfcindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G310" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H310" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I310" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J310" s="18" t="inlineStr">
+        <is>
+          <t>CBFC official site verified live. Statutory body under MIB. Staff on deputation/direct.</t>
+        </is>
+      </c>
+      <c r="K310" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L310" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M310" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="16">
       <c r="A311" s="4">
@@ -18967,15 +19545,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E311" s="18" t="n"/>
-      <c r="F311" s="18" t="n"/>
-      <c r="G311" s="18" t="n"/>
-      <c r="H311" s="18" t="n"/>
-      <c r="I311" s="18" t="n"/>
-      <c r="J311" s="18" t="n"/>
-      <c r="K311" s="18" t="n"/>
-      <c r="L311" s="18" t="n"/>
-      <c r="M311" s="18" t="n"/>
+      <c r="E311" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F311" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G311" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H311" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I311" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J311" s="18" t="inlineStr">
+        <is>
+          <t>FCAT is a legacy/dormant body. Tribunal merged into NCLT system. Mapped to MIB vacancies.</t>
+        </is>
+      </c>
+      <c r="K311" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L311" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M311" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="16">
       <c r="A312" s="4">
@@ -18997,15 +19609,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E312" s="18" t="n"/>
-      <c r="F312" s="18" t="n"/>
-      <c r="G312" s="18" t="n"/>
-      <c r="H312" s="18" t="n"/>
-      <c r="I312" s="18" t="n"/>
-      <c r="J312" s="18" t="n"/>
-      <c r="K312" s="18" t="n"/>
-      <c r="L312" s="18" t="n"/>
-      <c r="M312" s="18" t="n"/>
+      <c r="E312" s="17" t="inlineStr">
+        <is>
+          <t>https://prasarbharati.gov.in/pbvacancies/</t>
+        </is>
+      </c>
+      <c r="F312" s="17" t="inlineStr">
+        <is>
+          <t>https://prasarbharati.gov.in/pbvacancies/</t>
+        </is>
+      </c>
+      <c r="G312" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H312" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I312" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J312" s="18" t="inlineStr">
+        <is>
+          <t>Prasar Bharati vacancies page verified live. Autonomous body (DD &amp; AIR) under MIB.</t>
+        </is>
+      </c>
+      <c r="K312" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L312" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M312" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="16">
       <c r="A313" s="4">
@@ -19027,15 +19673,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E313" s="18" t="n"/>
-      <c r="F313" s="18" t="n"/>
-      <c r="G313" s="18" t="n"/>
-      <c r="H313" s="18" t="n"/>
-      <c r="I313" s="18" t="n"/>
-      <c r="J313" s="18" t="n"/>
-      <c r="K313" s="18" t="n"/>
-      <c r="L313" s="18" t="n"/>
-      <c r="M313" s="18" t="n"/>
+      <c r="E313" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F313" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G313" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H313" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I313" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J313" s="18" t="inlineStr">
+        <is>
+          <t>Films Division - merged into NFDC. Legacy entry. Recruitment through MIB/NFDC.</t>
+        </is>
+      </c>
+      <c r="K313" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L313" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M313" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="16">
       <c r="A314" s="4">
@@ -19057,15 +19737,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E314" s="18" t="n"/>
-      <c r="F314" s="18" t="n"/>
-      <c r="G314" s="18" t="n"/>
-      <c r="H314" s="18" t="n"/>
-      <c r="I314" s="18" t="n"/>
-      <c r="J314" s="18" t="n"/>
-      <c r="K314" s="18" t="n"/>
-      <c r="L314" s="18" t="n"/>
-      <c r="M314" s="18" t="n"/>
+      <c r="E314" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F314" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G314" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H314" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I314" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J314" s="18" t="inlineStr">
+        <is>
+          <t>NFDC (National Film Development Corporation). Autonomous body under MIB. Small staff; recruitment through MIB channels.</t>
+        </is>
+      </c>
+      <c r="K314" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L314" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M314" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="16">
       <c r="A315" s="4">
@@ -19087,15 +19801,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E315" s="18" t="n"/>
-      <c r="F315" s="18" t="n"/>
-      <c r="G315" s="18" t="n"/>
-      <c r="H315" s="18" t="n"/>
-      <c r="I315" s="18" t="n"/>
-      <c r="J315" s="18" t="n"/>
-      <c r="K315" s="18" t="n"/>
-      <c r="L315" s="18" t="n"/>
-      <c r="M315" s="18" t="n"/>
+      <c r="E315" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F315" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G315" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H315" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I315" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J315" s="18" t="inlineStr">
+        <is>
+          <t>CFSI (Children's Film Society) - merged/legacy body.</t>
+        </is>
+      </c>
+      <c r="K315" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L315" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M315" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="16">
       <c r="A316" s="4">
@@ -19117,15 +19865,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E316" s="18" t="n"/>
-      <c r="F316" s="18" t="n"/>
-      <c r="G316" s="18" t="n"/>
-      <c r="H316" s="18" t="n"/>
-      <c r="I316" s="18" t="n"/>
-      <c r="J316" s="18" t="n"/>
-      <c r="K316" s="18" t="n"/>
-      <c r="L316" s="18" t="n"/>
-      <c r="M316" s="18" t="n"/>
+      <c r="E316" s="17" t="inlineStr">
+        <is>
+          <t>https://srfti.ac.in/vacancy/</t>
+        </is>
+      </c>
+      <c r="F316" s="17" t="inlineStr">
+        <is>
+          <t>https://srfti.ac.in/vacancy/</t>
+        </is>
+      </c>
+      <c r="G316" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H316" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I316" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J316" s="18" t="inlineStr">
+        <is>
+          <t>SRFTI vacancy page verified live. Autonomous body under MIB.</t>
+        </is>
+      </c>
+      <c r="K316" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L316" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M316" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="16">
       <c r="A317" s="4">
@@ -19147,15 +19929,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E317" s="18" t="n"/>
-      <c r="F317" s="18" t="n"/>
-      <c r="G317" s="18" t="n"/>
-      <c r="H317" s="18" t="n"/>
-      <c r="I317" s="18" t="n"/>
-      <c r="J317" s="18" t="n"/>
-      <c r="K317" s="18" t="n"/>
-      <c r="L317" s="18" t="n"/>
-      <c r="M317" s="18" t="n"/>
+      <c r="E317" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ftii.ac.in/careers</t>
+        </is>
+      </c>
+      <c r="F317" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ftii.ac.in/careers</t>
+        </is>
+      </c>
+      <c r="G317" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H317" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I317" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J317" s="18" t="inlineStr">
+        <is>
+          <t>FTII careers page verified live. Autonomous body under MIB.</t>
+        </is>
+      </c>
+      <c r="K317" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L317" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M317" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="16">
       <c r="A318" s="4">
@@ -19207,15 +20023,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E319" s="18" t="n"/>
-      <c r="F319" s="18" t="n"/>
-      <c r="G319" s="18" t="n"/>
-      <c r="H319" s="18" t="n"/>
-      <c r="I319" s="18" t="n"/>
-      <c r="J319" s="18" t="n"/>
-      <c r="K319" s="18" t="n"/>
-      <c r="L319" s="18" t="n"/>
-      <c r="M319" s="18" t="n"/>
+      <c r="E319" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="F319" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="G319" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H319" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I319" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J319" s="18" t="inlineStr">
+        <is>
+          <t>Dept of Water Resources, RD &amp; GR site verified live. No dedicated vacancy sub-page found from environment; circulars published on main site.</t>
+        </is>
+      </c>
+      <c r="K319" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L319" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M319" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="16">
       <c r="A320" s="4">
@@ -19237,15 +20087,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E320" s="18" t="n"/>
-      <c r="F320" s="18" t="n"/>
-      <c r="G320" s="18" t="n"/>
-      <c r="H320" s="18" t="n"/>
-      <c r="I320" s="18" t="n"/>
-      <c r="J320" s="18" t="n"/>
-      <c r="K320" s="18" t="n"/>
-      <c r="L320" s="18" t="n"/>
-      <c r="M320" s="18" t="n"/>
+      <c r="E320" s="17" t="inlineStr">
+        <is>
+          <t>https://swachhbharatmission.gov.in/</t>
+        </is>
+      </c>
+      <c r="F320" s="17" t="inlineStr">
+        <is>
+          <t>https://swachhbharatmission.gov.in/</t>
+        </is>
+      </c>
+      <c r="G320" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H320" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I320" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J320" s="18" t="inlineStr">
+        <is>
+          <t>Dept of Drinking Water &amp; Sanitation site verified live. Small department; recruitment through parent ministry/DoPT channels.</t>
+        </is>
+      </c>
+      <c r="K320" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L320" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M320" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="16">
       <c r="A321" s="4">
@@ -19267,15 +20151,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E321" s="18" t="n"/>
-      <c r="F321" s="18" t="n"/>
-      <c r="G321" s="18" t="n"/>
-      <c r="H321" s="18" t="n"/>
-      <c r="I321" s="18" t="n"/>
-      <c r="J321" s="18" t="n"/>
-      <c r="K321" s="18" t="n"/>
-      <c r="L321" s="18" t="n"/>
-      <c r="M321" s="18" t="n"/>
+      <c r="E321" s="17" t="inlineStr">
+        <is>
+          <t>https://cwc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F321" s="17" t="inlineStr">
+        <is>
+          <t>https://cwc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G321" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H321" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I321" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J321" s="18" t="inlineStr">
+        <is>
+          <t>CWC official site returns 401 from automated access. Confirmed as official domain. Attached office under Jal Shakti. Engineering cadre via UPSC.</t>
+        </is>
+      </c>
+      <c r="K321" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L321" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M321" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="16">
       <c r="A322" s="4">
@@ -19297,15 +20215,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E322" s="18" t="n"/>
-      <c r="F322" s="18" t="n"/>
-      <c r="G322" s="18" t="n"/>
-      <c r="H322" s="18" t="n"/>
-      <c r="I322" s="18" t="n"/>
-      <c r="J322" s="18" t="n"/>
-      <c r="K322" s="18" t="n"/>
-      <c r="L322" s="18" t="n"/>
-      <c r="M322" s="18" t="n"/>
+      <c r="E322" s="17" t="inlineStr">
+        <is>
+          <t>https://cgwb.gov.in/</t>
+        </is>
+      </c>
+      <c r="F322" s="17" t="inlineStr">
+        <is>
+          <t>https://cgwb.gov.in/</t>
+        </is>
+      </c>
+      <c r="G322" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H322" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I322" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J322" s="18" t="inlineStr">
+        <is>
+          <t>CGWB official site (cgwb.gov.in). Unreachable from this environment. Attached office under Jal Shakti. Scientific cadre through UPSC.</t>
+        </is>
+      </c>
+      <c r="K322" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L322" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M322" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="16">
       <c r="A323" s="4">
@@ -19327,15 +20279,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E323" s="18" t="n"/>
-      <c r="F323" s="18" t="n"/>
-      <c r="G323" s="18" t="n"/>
-      <c r="H323" s="18" t="n"/>
-      <c r="I323" s="18" t="n"/>
-      <c r="J323" s="18" t="n"/>
-      <c r="K323" s="18" t="n"/>
-      <c r="L323" s="18" t="n"/>
-      <c r="M323" s="18" t="n"/>
+      <c r="E323" s="17" t="inlineStr">
+        <is>
+          <t>https://nmcg.nic.in/</t>
+        </is>
+      </c>
+      <c r="F323" s="17" t="inlineStr">
+        <is>
+          <t>https://nmcg.nic.in/</t>
+        </is>
+      </c>
+      <c r="G323" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H323" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I323" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J323" s="18" t="inlineStr">
+        <is>
+          <t>NMCG site (nmcg.nic.in) unreachable from environment. Confirmed as official domain. Staff on deputation/contract.</t>
+        </is>
+      </c>
+      <c r="K323" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L323" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M323" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="16">
       <c r="A324" s="4">
@@ -19357,15 +20343,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E324" s="18" t="n"/>
-      <c r="F324" s="18" t="n"/>
-      <c r="G324" s="18" t="n"/>
-      <c r="H324" s="18" t="n"/>
-      <c r="I324" s="18" t="n"/>
-      <c r="J324" s="18" t="n"/>
-      <c r="K324" s="18" t="n"/>
-      <c r="L324" s="18" t="n"/>
-      <c r="M324" s="18" t="n"/>
+      <c r="E324" s="17" t="inlineStr">
+        <is>
+          <t>https://cwc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F324" s="17" t="inlineStr">
+        <is>
+          <t>https://cwc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G324" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H324" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I324" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J324" s="18" t="inlineStr">
+        <is>
+          <t>CWC Field/Basin Offices recruit through central CWC.</t>
+        </is>
+      </c>
+      <c r="K324" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L324" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M324" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="16">
       <c r="A325" s="4">
@@ -19387,15 +20407,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E325" s="18" t="n"/>
-      <c r="F325" s="18" t="n"/>
-      <c r="G325" s="18" t="n"/>
-      <c r="H325" s="18" t="n"/>
-      <c r="I325" s="18" t="n"/>
-      <c r="J325" s="18" t="n"/>
-      <c r="K325" s="18" t="n"/>
-      <c r="L325" s="18" t="n"/>
-      <c r="M325" s="18" t="n"/>
+      <c r="E325" s="17" t="inlineStr">
+        <is>
+          <t>https://cgwb.gov.in/</t>
+        </is>
+      </c>
+      <c r="F325" s="17" t="inlineStr">
+        <is>
+          <t>https://cgwb.gov.in/</t>
+        </is>
+      </c>
+      <c r="G325" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H325" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I325" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J325" s="18" t="inlineStr">
+        <is>
+          <t>CGWB Regional/State Units recruit through central CGWB.</t>
+        </is>
+      </c>
+      <c r="K325" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L325" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M325" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="16">
       <c r="A326" s="4">
@@ -19417,15 +20471,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E326" s="18" t="n"/>
-      <c r="F326" s="18" t="n"/>
-      <c r="G326" s="18" t="n"/>
-      <c r="H326" s="18" t="n"/>
-      <c r="I326" s="18" t="n"/>
-      <c r="J326" s="18" t="n"/>
-      <c r="K326" s="18" t="n"/>
-      <c r="L326" s="18" t="n"/>
-      <c r="M326" s="18" t="n"/>
+      <c r="E326" s="17" t="inlineStr">
+        <is>
+          <t>https://nmcg.nic.in/</t>
+        </is>
+      </c>
+      <c r="F326" s="17" t="inlineStr">
+        <is>
+          <t>https://nmcg.nic.in/</t>
+        </is>
+      </c>
+      <c r="G326" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H326" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I326" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J326" s="18" t="inlineStr">
+        <is>
+          <t>Ganga Basin Field Directorates - subordinate to NMCG. No separate portal.</t>
+        </is>
+      </c>
+      <c r="K326" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L326" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M326" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="327" ht="15.75" customHeight="1" s="16">
       <c r="A327" s="4">
@@ -19447,15 +20535,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E327" s="18" t="n"/>
-      <c r="F327" s="18" t="n"/>
-      <c r="G327" s="18" t="n"/>
-      <c r="H327" s="18" t="n"/>
-      <c r="I327" s="18" t="n"/>
-      <c r="J327" s="18" t="n"/>
-      <c r="K327" s="18" t="n"/>
-      <c r="L327" s="18" t="n"/>
-      <c r="M327" s="18" t="n"/>
+      <c r="E327" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="F327" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="G327" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H327" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I327" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J327" s="18" t="inlineStr">
+        <is>
+          <t>Brahmaputra Board - statutory body under Jal Shakti. Very small; staff on deputation. No separate recruitment portal.</t>
+        </is>
+      </c>
+      <c r="K327" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L327" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M327" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="16">
       <c r="A328" s="4">
@@ -19477,15 +20599,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E328" s="18" t="n"/>
-      <c r="F328" s="18" t="n"/>
-      <c r="G328" s="18" t="n"/>
-      <c r="H328" s="18" t="n"/>
-      <c r="I328" s="18" t="n"/>
-      <c r="J328" s="18" t="n"/>
-      <c r="K328" s="18" t="n"/>
-      <c r="L328" s="18" t="n"/>
-      <c r="M328" s="18" t="n"/>
+      <c r="E328" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="F328" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="G328" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H328" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I328" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J328" s="18" t="inlineStr">
+        <is>
+          <t>Betwa River Board - inter-state statutory body. Very small; staff on deputation.</t>
+        </is>
+      </c>
+      <c r="K328" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L328" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M328" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="16">
       <c r="A329" s="4">
@@ -19507,15 +20663,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E329" s="18" t="n"/>
-      <c r="F329" s="18" t="n"/>
-      <c r="G329" s="18" t="n"/>
-      <c r="H329" s="18" t="n"/>
-      <c r="I329" s="18" t="n"/>
-      <c r="J329" s="18" t="n"/>
-      <c r="K329" s="18" t="n"/>
-      <c r="L329" s="18" t="n"/>
-      <c r="M329" s="18" t="n"/>
+      <c r="E329" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nihroorkee.gov.in/</t>
+        </is>
+      </c>
+      <c r="F329" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nihroorkee.gov.in/</t>
+        </is>
+      </c>
+      <c r="G329" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H329" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I329" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J329" s="18" t="inlineStr">
+        <is>
+          <t>NIH Roorkee official site verified live. Autonomous body under Jal Shakti.</t>
+        </is>
+      </c>
+      <c r="K329" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L329" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M329" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="330" ht="15.75" customHeight="1" s="16">
       <c r="A330" s="4">
@@ -19537,15 +20727,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E330" s="18" t="n"/>
-      <c r="F330" s="18" t="n"/>
-      <c r="G330" s="18" t="n"/>
-      <c r="H330" s="18" t="n"/>
-      <c r="I330" s="18" t="n"/>
-      <c r="J330" s="18" t="n"/>
-      <c r="K330" s="18" t="n"/>
-      <c r="L330" s="18" t="n"/>
-      <c r="M330" s="18" t="n"/>
+      <c r="E330" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nwda.gov.in/</t>
+        </is>
+      </c>
+      <c r="F330" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nwda.gov.in/</t>
+        </is>
+      </c>
+      <c r="G330" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H330" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I330" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J330" s="18" t="inlineStr">
+        <is>
+          <t>NWDA official site (nwda.gov.in). Unreachable from this environment. Confirmed as official domain. Autonomous body under Jal Shakti.</t>
+        </is>
+      </c>
+      <c r="K330" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L330" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M330" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="15.75" customHeight="1" s="16">
       <c r="A331" s="4">
@@ -19597,15 +20821,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E332" s="18" t="n"/>
-      <c r="F332" s="18" t="n"/>
-      <c r="G332" s="18" t="n"/>
-      <c r="H332" s="18" t="n"/>
-      <c r="I332" s="18" t="n"/>
-      <c r="J332" s="18" t="n"/>
-      <c r="K332" s="18" t="n"/>
-      <c r="L332" s="18" t="n"/>
-      <c r="M332" s="18" t="n"/>
+      <c r="E332" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F332" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G332" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H332" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I332" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J332" s="18" t="inlineStr">
+        <is>
+          <t>Chief Labour Commissioner (Central) - vacancies through labour.gov.in verified live.</t>
+        </is>
+      </c>
+      <c r="K332" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L332" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M332" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="15.75" customHeight="1" s="16">
       <c r="A333" s="4">
@@ -19627,15 +20885,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E333" s="18" t="n"/>
-      <c r="F333" s="18" t="n"/>
-      <c r="G333" s="18" t="n"/>
-      <c r="H333" s="18" t="n"/>
-      <c r="I333" s="18" t="n"/>
-      <c r="J333" s="18" t="n"/>
-      <c r="K333" s="18" t="n"/>
-      <c r="L333" s="18" t="n"/>
-      <c r="M333" s="18" t="n"/>
+      <c r="E333" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F333" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G333" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H333" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I333" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J333" s="18" t="inlineStr">
+        <is>
+          <t>DGFASLI (Directorate General Factory Advice Service) under Ministry of Labour. Vacancies via labour.gov.in.</t>
+        </is>
+      </c>
+      <c r="K333" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L333" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M333" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="15.75" customHeight="1" s="16">
       <c r="A334" s="4">
@@ -19657,15 +20949,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E334" s="18" t="n"/>
-      <c r="F334" s="18" t="n"/>
-      <c r="G334" s="18" t="n"/>
-      <c r="H334" s="18" t="n"/>
-      <c r="I334" s="18" t="n"/>
-      <c r="J334" s="18" t="n"/>
-      <c r="K334" s="18" t="n"/>
-      <c r="L334" s="18" t="n"/>
-      <c r="M334" s="18" t="n"/>
+      <c r="E334" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F334" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G334" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H334" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I334" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J334" s="18" t="inlineStr">
+        <is>
+          <t>DGE (Directorate General of Employment) under Ministry of Labour. Vacancies via labour.gov.in.</t>
+        </is>
+      </c>
+      <c r="K334" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L334" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M334" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="16">
       <c r="A335" s="4">
@@ -19687,15 +21013,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E335" s="18" t="n"/>
-      <c r="F335" s="18" t="n"/>
-      <c r="G335" s="18" t="n"/>
-      <c r="H335" s="18" t="n"/>
-      <c r="I335" s="18" t="n"/>
-      <c r="J335" s="18" t="n"/>
-      <c r="K335" s="18" t="n"/>
-      <c r="L335" s="18" t="n"/>
-      <c r="M335" s="18" t="n"/>
+      <c r="E335" s="17" t="inlineStr">
+        <is>
+          <t>https://dgms.gov.in/</t>
+        </is>
+      </c>
+      <c r="F335" s="17" t="inlineStr">
+        <is>
+          <t>https://dgms.gov.in/</t>
+        </is>
+      </c>
+      <c r="G335" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H335" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I335" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J335" s="18" t="inlineStr">
+        <is>
+          <t>DGMS official site verified live. Attached office under Ministry of Labour.</t>
+        </is>
+      </c>
+      <c r="K335" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L335" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M335" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="336" ht="15.75" customHeight="1" s="16">
       <c r="A336" s="4">
@@ -19717,15 +21077,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E336" s="18" t="n"/>
-      <c r="F336" s="18" t="n"/>
-      <c r="G336" s="18" t="n"/>
-      <c r="H336" s="18" t="n"/>
-      <c r="I336" s="18" t="n"/>
-      <c r="J336" s="18" t="n"/>
-      <c r="K336" s="18" t="n"/>
-      <c r="L336" s="18" t="n"/>
-      <c r="M336" s="18" t="n"/>
+      <c r="E336" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F336" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G336" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H336" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I336" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J336" s="18" t="inlineStr">
+        <is>
+          <t>Labour Bureau attached office under Ministry of Labour. Vacancies via labour.gov.in.</t>
+        </is>
+      </c>
+      <c r="K336" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L336" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M336" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="337" ht="15.75" customHeight="1" s="16">
       <c r="A337" s="4">
@@ -19747,15 +21141,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E337" s="18" t="n"/>
-      <c r="F337" s="18" t="n"/>
-      <c r="G337" s="18" t="n"/>
-      <c r="H337" s="18" t="n"/>
-      <c r="I337" s="18" t="n"/>
-      <c r="J337" s="18" t="n"/>
-      <c r="K337" s="18" t="n"/>
-      <c r="L337" s="18" t="n"/>
-      <c r="M337" s="18" t="n"/>
+      <c r="E337" s="17" t="inlineStr">
+        <is>
+          <t>https://epfindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F337" s="17" t="inlineStr">
+        <is>
+          <t>https://epfindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G337" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H337" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I337" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J337" s="18" t="inlineStr">
+        <is>
+          <t>EPFO official site (epfindia.gov.in). Redirects observed; confirmed as official domain. Major statutory body under Labour. Large recruitment drives.</t>
+        </is>
+      </c>
+      <c r="K337" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L337" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M337" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="16">
       <c r="A338" s="4">
@@ -19777,15 +21205,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E338" s="18" t="n"/>
-      <c r="F338" s="18" t="n"/>
-      <c r="G338" s="18" t="n"/>
-      <c r="H338" s="18" t="n"/>
-      <c r="I338" s="18" t="n"/>
-      <c r="J338" s="18" t="n"/>
-      <c r="K338" s="18" t="n"/>
-      <c r="L338" s="18" t="n"/>
-      <c r="M338" s="18" t="n"/>
+      <c r="E338" s="17" t="inlineStr">
+        <is>
+          <t>https://www.esic.gov.in/recruitments</t>
+        </is>
+      </c>
+      <c r="F338" s="17" t="inlineStr">
+        <is>
+          <t>https://www.esic.gov.in/recruitments</t>
+        </is>
+      </c>
+      <c r="G338" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H338" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I338" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J338" s="18" t="inlineStr">
+        <is>
+          <t>ESIC recruitments page verified live. Statutory body under Ministry of Labour.</t>
+        </is>
+      </c>
+      <c r="K338" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L338" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M338" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="15.75" customHeight="1" s="16">
       <c r="A339" s="4">
@@ -19807,15 +21269,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E339" s="18" t="n"/>
-      <c r="F339" s="18" t="n"/>
-      <c r="G339" s="18" t="n"/>
-      <c r="H339" s="18" t="n"/>
-      <c r="I339" s="18" t="n"/>
-      <c r="J339" s="18" t="n"/>
-      <c r="K339" s="18" t="n"/>
-      <c r="L339" s="18" t="n"/>
-      <c r="M339" s="18" t="n"/>
+      <c r="E339" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F339" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G339" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H339" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I339" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J339" s="18" t="inlineStr">
+        <is>
+          <t>Dattopant Thengadi National Board for Workers Education. Small autonomous body; recruitment through Ministry of Labour channels.</t>
+        </is>
+      </c>
+      <c r="K339" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L339" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M339" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="15.75" customHeight="1" s="16">
       <c r="A340" s="4">
@@ -19837,15 +21333,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E340" s="18" t="n"/>
-      <c r="F340" s="18" t="n"/>
-      <c r="G340" s="18" t="n"/>
-      <c r="H340" s="18" t="n"/>
-      <c r="I340" s="18" t="n"/>
-      <c r="J340" s="18" t="n"/>
-      <c r="K340" s="18" t="n"/>
-      <c r="L340" s="18" t="n"/>
-      <c r="M340" s="18" t="n"/>
+      <c r="E340" s="17" t="inlineStr">
+        <is>
+          <t>https://vvgnli.gov.in/</t>
+        </is>
+      </c>
+      <c r="F340" s="17" t="inlineStr">
+        <is>
+          <t>https://vvgnli.gov.in/</t>
+        </is>
+      </c>
+      <c r="G340" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H340" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I340" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J340" s="18" t="inlineStr">
+        <is>
+          <t>VVGNLI official site verified live. Autonomous body under Ministry of Labour.</t>
+        </is>
+      </c>
+      <c r="K340" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L340" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M340" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="16">
       <c r="A341" s="4">
@@ -19897,15 +21427,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E342" s="18" t="n"/>
-      <c r="F342" s="18" t="n"/>
-      <c r="G342" s="18" t="n"/>
-      <c r="H342" s="18" t="n"/>
-      <c r="I342" s="18" t="n"/>
-      <c r="J342" s="18" t="n"/>
-      <c r="K342" s="18" t="n"/>
-      <c r="L342" s="18" t="n"/>
-      <c r="M342" s="18" t="n"/>
+      <c r="E342" s="17" t="inlineStr">
+        <is>
+          <t>https://legalaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F342" s="17" t="inlineStr">
+        <is>
+          <t>https://legalaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G342" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H342" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I342" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J342" s="18" t="inlineStr">
+        <is>
+          <t>Department of Legal Affairs. Confirmed as official domain. Staff mostly from legal cadre on deputation.</t>
+        </is>
+      </c>
+      <c r="K342" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L342" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M342" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="15.75" customHeight="1" s="16">
       <c r="A343" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -21491,15 +21491,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E343" s="18" t="n"/>
-      <c r="F343" s="18" t="n"/>
-      <c r="G343" s="18" t="n"/>
-      <c r="H343" s="18" t="n"/>
-      <c r="I343" s="18" t="n"/>
-      <c r="J343" s="18" t="n"/>
-      <c r="K343" s="18" t="n"/>
-      <c r="L343" s="18" t="n"/>
-      <c r="M343" s="18" t="n"/>
+      <c r="E343" s="17" t="inlineStr">
+        <is>
+          <t>https://legislative.gov.in/</t>
+        </is>
+      </c>
+      <c r="F343" s="17" t="inlineStr">
+        <is>
+          <t>https://legislative.gov.in/</t>
+        </is>
+      </c>
+      <c r="G343" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H343" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I343" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J343" s="18" t="inlineStr">
+        <is>
+          <t>Legislative Department site verified live. Attached office under Ministry of Law &amp; Justice.</t>
+        </is>
+      </c>
+      <c r="K343" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L343" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M343" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="15.75" customHeight="1" s="16">
       <c r="A344" s="4">
@@ -21521,15 +21555,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E344" s="18" t="n"/>
-      <c r="F344" s="18" t="n"/>
-      <c r="G344" s="18" t="n"/>
-      <c r="H344" s="18" t="n"/>
-      <c r="I344" s="18" t="n"/>
-      <c r="J344" s="18" t="n"/>
-      <c r="K344" s="18" t="n"/>
-      <c r="L344" s="18" t="n"/>
-      <c r="M344" s="18" t="n"/>
+      <c r="E344" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="F344" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="G344" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H344" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I344" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J344" s="18" t="inlineStr">
+        <is>
+          <t>Department of Justice site verified live.</t>
+        </is>
+      </c>
+      <c r="K344" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L344" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M344" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="15.75" customHeight="1" s="16">
       <c r="A345" s="4">
@@ -21551,15 +21619,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E345" s="18" t="n"/>
-      <c r="F345" s="18" t="n"/>
-      <c r="G345" s="18" t="n"/>
-      <c r="H345" s="18" t="n"/>
-      <c r="I345" s="18" t="n"/>
-      <c r="J345" s="18" t="n"/>
-      <c r="K345" s="18" t="n"/>
-      <c r="L345" s="18" t="n"/>
-      <c r="M345" s="18" t="n"/>
+      <c r="E345" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="F345" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="G345" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H345" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I345" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J345" s="18" t="inlineStr">
+        <is>
+          <t>Law Commission of India (when constituted) - ad hoc body. No permanent recruitment page. Mapped to DoJ.</t>
+        </is>
+      </c>
+      <c r="K345" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L345" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M345" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="15.75" customHeight="1" s="16">
       <c r="A346" s="4">
@@ -21581,15 +21683,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E346" s="18" t="n"/>
-      <c r="F346" s="18" t="n"/>
-      <c r="G346" s="18" t="n"/>
-      <c r="H346" s="18" t="n"/>
-      <c r="I346" s="18" t="n"/>
-      <c r="J346" s="18" t="n"/>
-      <c r="K346" s="18" t="n"/>
-      <c r="L346" s="18" t="n"/>
-      <c r="M346" s="18" t="n"/>
+      <c r="E346" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="F346" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="G346" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H346" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I346" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J346" s="18" t="inlineStr">
+        <is>
+          <t>Central Agency Section (CAS) is subordinate to DoJ. No separate website.</t>
+        </is>
+      </c>
+      <c r="K346" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L346" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M346" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="15.75" customHeight="1" s="16">
       <c r="A347" s="4">
@@ -21611,15 +21747,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E347" s="18" t="n"/>
-      <c r="F347" s="18" t="n"/>
-      <c r="G347" s="18" t="n"/>
-      <c r="H347" s="18" t="n"/>
-      <c r="I347" s="18" t="n"/>
-      <c r="J347" s="18" t="n"/>
-      <c r="K347" s="18" t="n"/>
-      <c r="L347" s="18" t="n"/>
-      <c r="M347" s="18" t="n"/>
+      <c r="E347" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="F347" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="G347" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H347" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I347" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J347" s="18" t="inlineStr">
+        <is>
+          <t>High Court/Subordinate Court Coordination Units - coordination only. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K347" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L347" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M347" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="15.75" customHeight="1" s="16">
       <c r="A348" s="4">
@@ -21641,15 +21811,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E348" s="18" t="n"/>
-      <c r="F348" s="18" t="n"/>
-      <c r="G348" s="18" t="n"/>
-      <c r="H348" s="18" t="n"/>
-      <c r="I348" s="18" t="n"/>
-      <c r="J348" s="18" t="n"/>
-      <c r="K348" s="18" t="n"/>
-      <c r="L348" s="18" t="n"/>
-      <c r="M348" s="18" t="n"/>
+      <c r="E348" s="17" t="inlineStr">
+        <is>
+          <t>https://nalsa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F348" s="17" t="inlineStr">
+        <is>
+          <t>https://nalsa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G348" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H348" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I348" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J348" s="18" t="inlineStr">
+        <is>
+          <t>NALSA official site verified live. Statutory body under Ministry of Law &amp; Justice.</t>
+        </is>
+      </c>
+      <c r="K348" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L348" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M348" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="349" ht="15.75" customHeight="1" s="16">
       <c r="A349" s="4">
@@ -21671,15 +21875,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E349" s="18" t="n"/>
-      <c r="F349" s="18" t="n"/>
-      <c r="G349" s="18" t="n"/>
-      <c r="H349" s="18" t="n"/>
-      <c r="I349" s="18" t="n"/>
-      <c r="J349" s="18" t="n"/>
-      <c r="K349" s="18" t="n"/>
-      <c r="L349" s="18" t="n"/>
-      <c r="M349" s="18" t="n"/>
+      <c r="E349" s="17" t="inlineStr">
+        <is>
+          <t>https://nalsa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F349" s="17" t="inlineStr">
+        <is>
+          <t>https://nalsa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G349" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H349" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I349" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J349" s="18" t="inlineStr">
+        <is>
+          <t>State Legal Services Authorities - state-level bodies. NALSA as central coordination reference.</t>
+        </is>
+      </c>
+      <c r="K349" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L349" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M349" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="350" ht="15.75" customHeight="1" s="16">
       <c r="A350" s="4">
@@ -21701,15 +21939,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E350" s="18" t="n"/>
-      <c r="F350" s="18" t="n"/>
-      <c r="G350" s="18" t="n"/>
-      <c r="H350" s="18" t="n"/>
-      <c r="I350" s="18" t="n"/>
-      <c r="J350" s="18" t="n"/>
-      <c r="K350" s="18" t="n"/>
-      <c r="L350" s="18" t="n"/>
-      <c r="M350" s="18" t="n"/>
+      <c r="E350" s="17" t="inlineStr">
+        <is>
+          <t>https://ili.ac.in/</t>
+        </is>
+      </c>
+      <c r="F350" s="17" t="inlineStr">
+        <is>
+          <t>https://ili.ac.in/</t>
+        </is>
+      </c>
+      <c r="G350" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H350" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I350" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J350" s="18" t="inlineStr">
+        <is>
+          <t>Indian Law Institute site verified live. Autonomous body under Ministry of Law &amp; Justice.</t>
+        </is>
+      </c>
+      <c r="K350" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L350" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M350" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="351" ht="15.75" customHeight="1" s="16">
       <c r="A351" s="4">
@@ -21761,15 +22033,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E352" s="18" t="n"/>
-      <c r="F352" s="18" t="n"/>
-      <c r="G352" s="18" t="n"/>
-      <c r="H352" s="18" t="n"/>
-      <c r="I352" s="18" t="n"/>
-      <c r="J352" s="18" t="n"/>
-      <c r="K352" s="18" t="n"/>
-      <c r="L352" s="18" t="n"/>
-      <c r="M352" s="18" t="n"/>
+      <c r="E352" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F352" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G352" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H352" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I352" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J352" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of MSME vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K352" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L352" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M352" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="353" ht="15.75" customHeight="1" s="16">
       <c r="A353" s="4">
@@ -21791,15 +22097,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E353" s="18" t="n"/>
-      <c r="F353" s="18" t="n"/>
-      <c r="G353" s="18" t="n"/>
-      <c r="H353" s="18" t="n"/>
-      <c r="I353" s="18" t="n"/>
-      <c r="J353" s="18" t="n"/>
-      <c r="K353" s="18" t="n"/>
-      <c r="L353" s="18" t="n"/>
-      <c r="M353" s="18" t="n"/>
+      <c r="E353" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F353" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G353" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H353" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I353" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J353" s="18" t="inlineStr">
+        <is>
+          <t>Office of Development Commissioner (MSME) - attached office. Vacancies via MSME site.</t>
+        </is>
+      </c>
+      <c r="K353" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L353" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M353" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="15.75" customHeight="1" s="16">
       <c r="A354" s="4">
@@ -21821,15 +22161,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E354" s="18" t="n"/>
-      <c r="F354" s="18" t="n"/>
-      <c r="G354" s="18" t="n"/>
-      <c r="H354" s="18" t="n"/>
-      <c r="I354" s="18" t="n"/>
-      <c r="J354" s="18" t="n"/>
-      <c r="K354" s="18" t="n"/>
-      <c r="L354" s="18" t="n"/>
-      <c r="M354" s="18" t="n"/>
+      <c r="E354" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F354" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G354" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H354" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I354" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J354" s="18" t="inlineStr">
+        <is>
+          <t>MSME Development Institutes recruit through central MSME vacancies page.</t>
+        </is>
+      </c>
+      <c r="K354" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L354" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M354" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="15.75" customHeight="1" s="16">
       <c r="A355" s="4">
@@ -21851,15 +22225,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E355" s="18" t="n"/>
-      <c r="F355" s="18" t="n"/>
-      <c r="G355" s="18" t="n"/>
-      <c r="H355" s="18" t="n"/>
-      <c r="I355" s="18" t="n"/>
-      <c r="J355" s="18" t="n"/>
-      <c r="K355" s="18" t="n"/>
-      <c r="L355" s="18" t="n"/>
-      <c r="M355" s="18" t="n"/>
+      <c r="E355" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F355" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G355" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H355" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I355" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J355" s="18" t="inlineStr">
+        <is>
+          <t>Tool Rooms/Technology Centres under MSME. Recruitment via MSME.</t>
+        </is>
+      </c>
+      <c r="K355" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L355" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M355" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="15.75" customHeight="1" s="16">
       <c r="A356" s="4">
@@ -21881,15 +22289,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E356" s="18" t="n"/>
-      <c r="F356" s="18" t="n"/>
-      <c r="G356" s="18" t="n"/>
-      <c r="H356" s="18" t="n"/>
-      <c r="I356" s="18" t="n"/>
-      <c r="J356" s="18" t="n"/>
-      <c r="K356" s="18" t="n"/>
-      <c r="L356" s="18" t="n"/>
-      <c r="M356" s="18" t="n"/>
+      <c r="E356" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F356" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G356" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H356" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I356" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J356" s="18" t="inlineStr">
+        <is>
+          <t>MSME-DI Field/Branch Offices subordinate. Recruitment via central MSME.</t>
+        </is>
+      </c>
+      <c r="K356" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L356" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M356" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="15.75" customHeight="1" s="16">
       <c r="A357" s="4">
@@ -21911,15 +22353,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E357" s="18" t="n"/>
-      <c r="F357" s="18" t="n"/>
-      <c r="G357" s="18" t="n"/>
-      <c r="H357" s="18" t="n"/>
-      <c r="I357" s="18" t="n"/>
-      <c r="J357" s="18" t="n"/>
-      <c r="K357" s="18" t="n"/>
-      <c r="L357" s="18" t="n"/>
-      <c r="M357" s="18" t="n"/>
+      <c r="E357" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F357" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G357" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H357" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I357" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J357" s="18" t="inlineStr">
+        <is>
+          <t>Testing &amp; Training Centre Field Units subordinate to MSME.</t>
+        </is>
+      </c>
+      <c r="K357" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L357" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M357" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="16">
       <c r="A358" s="4">
@@ -21941,15 +22417,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E358" s="18" t="n"/>
-      <c r="F358" s="18" t="n"/>
-      <c r="G358" s="18" t="n"/>
-      <c r="H358" s="18" t="n"/>
-      <c r="I358" s="18" t="n"/>
-      <c r="J358" s="18" t="n"/>
-      <c r="K358" s="18" t="n"/>
-      <c r="L358" s="18" t="n"/>
-      <c r="M358" s="18" t="n"/>
+      <c r="E358" s="17" t="inlineStr">
+        <is>
+          <t>https://kvic.gov.in/</t>
+        </is>
+      </c>
+      <c r="F358" s="17" t="inlineStr">
+        <is>
+          <t>https://kvic.gov.in/</t>
+        </is>
+      </c>
+      <c r="G358" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H358" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I358" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J358" s="18" t="inlineStr">
+        <is>
+          <t>KVIC official site verified live. Statutory body under MSME.</t>
+        </is>
+      </c>
+      <c r="K358" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L358" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M358" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="359" ht="15.75" customHeight="1" s="16">
       <c r="A359" s="4">
@@ -21971,15 +22481,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E359" s="18" t="n"/>
-      <c r="F359" s="18" t="n"/>
-      <c r="G359" s="18" t="n"/>
-      <c r="H359" s="18" t="n"/>
-      <c r="I359" s="18" t="n"/>
-      <c r="J359" s="18" t="n"/>
-      <c r="K359" s="18" t="n"/>
-      <c r="L359" s="18" t="n"/>
-      <c r="M359" s="18" t="n"/>
+      <c r="E359" s="17" t="inlineStr">
+        <is>
+          <t>https://coirboard.gov.in/</t>
+        </is>
+      </c>
+      <c r="F359" s="17" t="inlineStr">
+        <is>
+          <t>https://coirboard.gov.in/</t>
+        </is>
+      </c>
+      <c r="G359" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H359" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I359" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J359" s="18" t="inlineStr">
+        <is>
+          <t>Coir Board site (coirboard.gov.in). Unreachable from this environment but confirmed as official domain. Statutory body under MSME.</t>
+        </is>
+      </c>
+      <c r="K359" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L359" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M359" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="360" ht="15.75" customHeight="1" s="16">
       <c r="A360" s="4">
@@ -22001,15 +22545,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E360" s="18" t="n"/>
-      <c r="F360" s="18" t="n"/>
-      <c r="G360" s="18" t="n"/>
-      <c r="H360" s="18" t="n"/>
-      <c r="I360" s="18" t="n"/>
-      <c r="J360" s="18" t="n"/>
-      <c r="K360" s="18" t="n"/>
-      <c r="L360" s="18" t="n"/>
-      <c r="M360" s="18" t="n"/>
+      <c r="E360" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nsic.co.in/</t>
+        </is>
+      </c>
+      <c r="F360" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nsic.co.in/</t>
+        </is>
+      </c>
+      <c r="G360" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H360" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I360" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J360" s="18" t="inlineStr">
+        <is>
+          <t>NSIC official site verified live. Autonomous body/PSU under MSME.</t>
+        </is>
+      </c>
+      <c r="K360" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L360" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M360" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="361" ht="15.75" customHeight="1" s="16">
       <c r="A361" s="4">
@@ -22031,15 +22609,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E361" s="18" t="n"/>
-      <c r="F361" s="18" t="n"/>
-      <c r="G361" s="18" t="n"/>
-      <c r="H361" s="18" t="n"/>
-      <c r="I361" s="18" t="n"/>
-      <c r="J361" s="18" t="n"/>
-      <c r="K361" s="18" t="n"/>
-      <c r="L361" s="18" t="n"/>
-      <c r="M361" s="18" t="n"/>
+      <c r="E361" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F361" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G361" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H361" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I361" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J361" s="18" t="inlineStr">
+        <is>
+          <t>MGIRI (Mahatma Gandhi Institute for Rural Industrialisation). Small autonomous body under MSME. No independent recruitment portal found.</t>
+        </is>
+      </c>
+      <c r="K361" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L361" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M361" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="362" ht="15.75" customHeight="1" s="16">
       <c r="A362" s="4">
@@ -22091,15 +22703,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E363" s="18" t="n"/>
-      <c r="F363" s="18" t="n"/>
-      <c r="G363" s="18" t="n"/>
-      <c r="H363" s="18" t="n"/>
-      <c r="I363" s="18" t="n"/>
-      <c r="J363" s="18" t="n"/>
-      <c r="K363" s="18" t="n"/>
-      <c r="L363" s="18" t="n"/>
-      <c r="M363" s="18" t="n"/>
+      <c r="E363" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F363" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G363" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H363" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I363" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J363" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Minority Affairs site (minorityaffairs.gov.in). Unreachable from environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K363" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L363" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M363" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="364" ht="15.75" customHeight="1" s="16">
       <c r="A364" s="4">
@@ -22121,15 +22767,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E364" s="18" t="n"/>
-      <c r="F364" s="18" t="n"/>
-      <c r="G364" s="18" t="n"/>
-      <c r="H364" s="18" t="n"/>
-      <c r="I364" s="18" t="n"/>
-      <c r="J364" s="18" t="n"/>
-      <c r="K364" s="18" t="n"/>
-      <c r="L364" s="18" t="n"/>
-      <c r="M364" s="18" t="n"/>
+      <c r="E364" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F364" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G364" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H364" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I364" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J364" s="18" t="inlineStr">
+        <is>
+          <t>Education Division within Ministry of Minority Affairs. No separate site.</t>
+        </is>
+      </c>
+      <c r="K364" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L364" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M364" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="15.75" customHeight="1" s="16">
       <c r="A365" s="4">
@@ -22151,15 +22831,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E365" s="18" t="n"/>
-      <c r="F365" s="18" t="n"/>
-      <c r="G365" s="18" t="n"/>
-      <c r="H365" s="18" t="n"/>
-      <c r="I365" s="18" t="n"/>
-      <c r="J365" s="18" t="n"/>
-      <c r="K365" s="18" t="n"/>
-      <c r="L365" s="18" t="n"/>
-      <c r="M365" s="18" t="n"/>
+      <c r="E365" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F365" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G365" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H365" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I365" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J365" s="18" t="inlineStr">
+        <is>
+          <t>Policy, Planning &amp; Research Division within Ministry. No separate site.</t>
+        </is>
+      </c>
+      <c r="K365" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L365" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M365" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="366" ht="15.75" customHeight="1" s="16">
       <c r="A366" s="4">
@@ -22181,15 +22895,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E366" s="18" t="n"/>
-      <c r="F366" s="18" t="n"/>
-      <c r="G366" s="18" t="n"/>
-      <c r="H366" s="18" t="n"/>
-      <c r="I366" s="18" t="n"/>
-      <c r="J366" s="18" t="n"/>
-      <c r="K366" s="18" t="n"/>
-      <c r="L366" s="18" t="n"/>
-      <c r="M366" s="18" t="n"/>
+      <c r="E366" s="17" t="inlineStr">
+        <is>
+          <t>https://ncm.nic.in/</t>
+        </is>
+      </c>
+      <c r="F366" s="17" t="inlineStr">
+        <is>
+          <t>https://ncm.nic.in/</t>
+        </is>
+      </c>
+      <c r="G366" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H366" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I366" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J366" s="18" t="inlineStr">
+        <is>
+          <t>National Commission for Minorities site verified live. Statutory body.</t>
+        </is>
+      </c>
+      <c r="K366" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L366" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M366" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="15.75" customHeight="1" s="16">
       <c r="A367" s="4">
@@ -22211,15 +22959,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E367" s="18" t="n"/>
-      <c r="F367" s="18" t="n"/>
-      <c r="G367" s="18" t="n"/>
-      <c r="H367" s="18" t="n"/>
-      <c r="I367" s="18" t="n"/>
-      <c r="J367" s="18" t="n"/>
-      <c r="K367" s="18" t="n"/>
-      <c r="L367" s="18" t="n"/>
-      <c r="M367" s="18" t="n"/>
+      <c r="E367" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F367" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G367" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H367" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I367" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J367" s="18" t="inlineStr">
+        <is>
+          <t>MAEF (Maulana Azad Education Foundation). Small autonomous body; recruitment through parent ministry.</t>
+        </is>
+      </c>
+      <c r="K367" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L367" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M367" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="15.75" customHeight="1" s="16">
       <c r="A368" s="4">
@@ -22241,15 +23023,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E368" s="18" t="n"/>
-      <c r="F368" s="18" t="n"/>
-      <c r="G368" s="18" t="n"/>
-      <c r="H368" s="18" t="n"/>
-      <c r="I368" s="18" t="n"/>
-      <c r="J368" s="18" t="n"/>
-      <c r="K368" s="18" t="n"/>
-      <c r="L368" s="18" t="n"/>
-      <c r="M368" s="18" t="n"/>
+      <c r="E368" s="17" t="inlineStr">
+        <is>
+          <t>https://www.amu.ac.in/</t>
+        </is>
+      </c>
+      <c r="F368" s="17" t="inlineStr">
+        <is>
+          <t>https://www.amu.ac.in/</t>
+        </is>
+      </c>
+      <c r="G368" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H368" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I368" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J368" s="18" t="inlineStr">
+        <is>
+          <t>AMU coordination entry. AMU recruits independently at amu.ac.in. Central University under Minority Affairs.</t>
+        </is>
+      </c>
+      <c r="K368" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L368" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M368" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="15.75" customHeight="1" s="16">
       <c r="A369" s="4">
@@ -22271,15 +23087,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E369" s="18" t="n"/>
-      <c r="F369" s="18" t="n"/>
-      <c r="G369" s="18" t="n"/>
-      <c r="H369" s="18" t="n"/>
-      <c r="I369" s="18" t="n"/>
-      <c r="J369" s="18" t="n"/>
-      <c r="K369" s="18" t="n"/>
-      <c r="L369" s="18" t="n"/>
-      <c r="M369" s="18" t="n"/>
+      <c r="E369" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jmi.ac.in/</t>
+        </is>
+      </c>
+      <c r="F369" s="17" t="inlineStr">
+        <is>
+          <t>https://www.jmi.ac.in/</t>
+        </is>
+      </c>
+      <c r="G369" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H369" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I369" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J369" s="18" t="inlineStr">
+        <is>
+          <t>JMI coordination entry. JMI recruits independently at jmi.ac.in. Central University under Minority Affairs.</t>
+        </is>
+      </c>
+      <c r="K369" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L369" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M369" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="370" ht="15.75" customHeight="1" s="16">
       <c r="A370" s="4">
@@ -22301,15 +23151,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E370" s="18" t="n"/>
-      <c r="F370" s="18" t="n"/>
-      <c r="G370" s="18" t="n"/>
-      <c r="H370" s="18" t="n"/>
-      <c r="I370" s="18" t="n"/>
-      <c r="J370" s="18" t="n"/>
-      <c r="K370" s="18" t="n"/>
-      <c r="L370" s="18" t="n"/>
-      <c r="M370" s="18" t="n"/>
+      <c r="E370" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F370" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G370" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H370" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I370" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J370" s="18" t="inlineStr">
+        <is>
+          <t>Regional/Field Offices for scholarship schemes. Subordinate to Ministry.</t>
+        </is>
+      </c>
+      <c r="K370" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L370" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M370" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" s="16">
       <c r="A371" s="4">
@@ -22361,15 +23245,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E372" s="18" t="n"/>
-      <c r="F372" s="18" t="n"/>
-      <c r="G372" s="18" t="n"/>
-      <c r="H372" s="18" t="n"/>
-      <c r="I372" s="18" t="n"/>
-      <c r="J372" s="18" t="n"/>
-      <c r="K372" s="18" t="n"/>
-      <c r="L372" s="18" t="n"/>
-      <c r="M372" s="18" t="n"/>
+      <c r="E372" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F372" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G372" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H372" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I372" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J372" s="18" t="inlineStr">
+        <is>
+          <t>MNRE vacancy circular page verified live.</t>
+        </is>
+      </c>
+      <c r="K372" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L372" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M372" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="373" ht="15.75" customHeight="1" s="16">
       <c r="A373" s="4">
@@ -22391,15 +23309,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E373" s="18" t="n"/>
-      <c r="F373" s="18" t="n"/>
-      <c r="G373" s="18" t="n"/>
-      <c r="H373" s="18" t="n"/>
-      <c r="I373" s="18" t="n"/>
-      <c r="J373" s="18" t="n"/>
-      <c r="K373" s="18" t="n"/>
-      <c r="L373" s="18" t="n"/>
-      <c r="M373" s="18" t="n"/>
+      <c r="E373" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F373" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G373" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H373" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I373" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J373" s="18" t="inlineStr">
+        <is>
+          <t>Solar Energy Division within MNRE. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K373" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L373" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M373" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="374" ht="15.75" customHeight="1" s="16">
       <c r="A374" s="4">
@@ -22421,15 +23373,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E374" s="18" t="n"/>
-      <c r="F374" s="18" t="n"/>
-      <c r="G374" s="18" t="n"/>
-      <c r="H374" s="18" t="n"/>
-      <c r="I374" s="18" t="n"/>
-      <c r="J374" s="18" t="n"/>
-      <c r="K374" s="18" t="n"/>
-      <c r="L374" s="18" t="n"/>
-      <c r="M374" s="18" t="n"/>
+      <c r="E374" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F374" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G374" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H374" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I374" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J374" s="18" t="inlineStr">
+        <is>
+          <t>Wind Energy Division within MNRE.</t>
+        </is>
+      </c>
+      <c r="K374" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L374" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M374" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="375" ht="15.75" customHeight="1" s="16">
       <c r="A375" s="4">
@@ -22451,15 +23437,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E375" s="18" t="n"/>
-      <c r="F375" s="18" t="n"/>
-      <c r="G375" s="18" t="n"/>
-      <c r="H375" s="18" t="n"/>
-      <c r="I375" s="18" t="n"/>
-      <c r="J375" s="18" t="n"/>
-      <c r="K375" s="18" t="n"/>
-      <c r="L375" s="18" t="n"/>
-      <c r="M375" s="18" t="n"/>
+      <c r="E375" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F375" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G375" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H375" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I375" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J375" s="18" t="inlineStr">
+        <is>
+          <t>Small Hydro Power Division within MNRE.</t>
+        </is>
+      </c>
+      <c r="K375" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L375" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M375" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="376" ht="15.75" customHeight="1" s="16">
       <c r="A376" s="4">
@@ -22481,15 +23501,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E376" s="18" t="n"/>
-      <c r="F376" s="18" t="n"/>
-      <c r="G376" s="18" t="n"/>
-      <c r="H376" s="18" t="n"/>
-      <c r="I376" s="18" t="n"/>
-      <c r="J376" s="18" t="n"/>
-      <c r="K376" s="18" t="n"/>
-      <c r="L376" s="18" t="n"/>
-      <c r="M376" s="18" t="n"/>
+      <c r="E376" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F376" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G376" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H376" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I376" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J376" s="18" t="inlineStr">
+        <is>
+          <t>Bio-Energy Division within MNRE.</t>
+        </is>
+      </c>
+      <c r="K376" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L376" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M376" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="377" ht="15.75" customHeight="1" s="16">
       <c r="A377" s="4">
@@ -22511,15 +23565,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E377" s="18" t="n"/>
-      <c r="F377" s="18" t="n"/>
-      <c r="G377" s="18" t="n"/>
-      <c r="H377" s="18" t="n"/>
-      <c r="I377" s="18" t="n"/>
-      <c r="J377" s="18" t="n"/>
-      <c r="K377" s="18" t="n"/>
-      <c r="L377" s="18" t="n"/>
-      <c r="M377" s="18" t="n"/>
+      <c r="E377" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F377" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G377" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H377" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I377" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J377" s="18" t="inlineStr">
+        <is>
+          <t>Green Energy Corridor Division within MNRE.</t>
+        </is>
+      </c>
+      <c r="K377" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L377" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M377" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="378" ht="15.75" customHeight="1" s="16">
       <c r="A378" s="4">
@@ -22541,15 +23629,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E378" s="18" t="n"/>
-      <c r="F378" s="18" t="n"/>
-      <c r="G378" s="18" t="n"/>
-      <c r="H378" s="18" t="n"/>
-      <c r="I378" s="18" t="n"/>
-      <c r="J378" s="18" t="n"/>
-      <c r="K378" s="18" t="n"/>
-      <c r="L378" s="18" t="n"/>
-      <c r="M378" s="18" t="n"/>
+      <c r="E378" s="17" t="inlineStr">
+        <is>
+          <t>https://nise.res.in/</t>
+        </is>
+      </c>
+      <c r="F378" s="17" t="inlineStr">
+        <is>
+          <t>https://nise.res.in/</t>
+        </is>
+      </c>
+      <c r="G378" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H378" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I378" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J378" s="18" t="inlineStr">
+        <is>
+          <t>NISE official site verified live. Autonomous body under MNRE.</t>
+        </is>
+      </c>
+      <c r="K378" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L378" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M378" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="379" ht="15.75" customHeight="1" s="16">
       <c r="A379" s="4">
@@ -22571,15 +23693,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E379" s="18" t="n"/>
-      <c r="F379" s="18" t="n"/>
-      <c r="G379" s="18" t="n"/>
-      <c r="H379" s="18" t="n"/>
-      <c r="I379" s="18" t="n"/>
-      <c r="J379" s="18" t="n"/>
-      <c r="K379" s="18" t="n"/>
-      <c r="L379" s="18" t="n"/>
-      <c r="M379" s="18" t="n"/>
+      <c r="E379" s="17" t="inlineStr">
+        <is>
+          <t>https://niwe.res.in/</t>
+        </is>
+      </c>
+      <c r="F379" s="17" t="inlineStr">
+        <is>
+          <t>https://niwe.res.in/</t>
+        </is>
+      </c>
+      <c r="G379" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H379" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I379" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J379" s="18" t="inlineStr">
+        <is>
+          <t>NIWE official site verified live. Autonomous body under MNRE.</t>
+        </is>
+      </c>
+      <c r="K379" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L379" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M379" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="380" ht="15.75" customHeight="1" s="16">
       <c r="A380" s="4">
@@ -22601,15 +23757,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E380" s="18" t="n"/>
-      <c r="F380" s="18" t="n"/>
-      <c r="G380" s="18" t="n"/>
-      <c r="H380" s="18" t="n"/>
-      <c r="I380" s="18" t="n"/>
-      <c r="J380" s="18" t="n"/>
-      <c r="K380" s="18" t="n"/>
-      <c r="L380" s="18" t="n"/>
-      <c r="M380" s="18" t="n"/>
+      <c r="E380" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F380" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G380" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H380" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I380" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J380" s="18" t="inlineStr">
+        <is>
+          <t>SSS-NIRE Kapurthala. Small institute under MNRE. No independent portal found.</t>
+        </is>
+      </c>
+      <c r="K380" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L380" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M380" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="381" ht="15.75" customHeight="1" s="16">
       <c r="A381" s="4">
@@ -22631,15 +23821,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E381" s="18" t="n"/>
-      <c r="F381" s="18" t="n"/>
-      <c r="G381" s="18" t="n"/>
-      <c r="H381" s="18" t="n"/>
-      <c r="I381" s="18" t="n"/>
-      <c r="J381" s="18" t="n"/>
-      <c r="K381" s="18" t="n"/>
-      <c r="L381" s="18" t="n"/>
-      <c r="M381" s="18" t="n"/>
+      <c r="E381" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ireda.in/</t>
+        </is>
+      </c>
+      <c r="F381" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ireda.in/</t>
+        </is>
+      </c>
+      <c r="G381" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H381" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I381" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J381" s="18" t="inlineStr">
+        <is>
+          <t>IREDA official site verified live. PSU/autonomous body under MNRE.</t>
+        </is>
+      </c>
+      <c r="K381" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L381" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M381" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="382" ht="15.75" customHeight="1" s="16">
       <c r="A382" s="4">
@@ -22661,15 +23885,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E382" s="18" t="n"/>
-      <c r="F382" s="18" t="n"/>
-      <c r="G382" s="18" t="n"/>
-      <c r="H382" s="18" t="n"/>
-      <c r="I382" s="18" t="n"/>
-      <c r="J382" s="18" t="n"/>
-      <c r="K382" s="18" t="n"/>
-      <c r="L382" s="18" t="n"/>
-      <c r="M382" s="18" t="n"/>
+      <c r="E382" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F382" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G382" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H382" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I382" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J382" s="18" t="inlineStr">
+        <is>
+          <t>MNRE Regional/Project Monitoring Units subordinate. No separate sites.</t>
+        </is>
+      </c>
+      <c r="K382" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L382" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M382" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="383" ht="15.75" customHeight="1" s="16">
       <c r="A383" s="4">
@@ -22721,15 +23979,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E384" s="18" t="n"/>
-      <c r="F384" s="18" t="n"/>
-      <c r="G384" s="18" t="n"/>
-      <c r="H384" s="18" t="n"/>
-      <c r="I384" s="18" t="n"/>
-      <c r="J384" s="18" t="n"/>
-      <c r="K384" s="18" t="n"/>
-      <c r="L384" s="18" t="n"/>
-      <c r="M384" s="18" t="n"/>
+      <c r="E384" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="F384" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="G384" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H384" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I384" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J384" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Panchayati Raj site verified live.</t>
+        </is>
+      </c>
+      <c r="K384" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L384" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M384" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="385" ht="15.75" customHeight="1" s="16">
       <c r="A385" s="4">
@@ -22751,15 +24043,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E385" s="18" t="n"/>
-      <c r="F385" s="18" t="n"/>
-      <c r="G385" s="18" t="n"/>
-      <c r="H385" s="18" t="n"/>
-      <c r="I385" s="18" t="n"/>
-      <c r="J385" s="18" t="n"/>
-      <c r="K385" s="18" t="n"/>
-      <c r="L385" s="18" t="n"/>
-      <c r="M385" s="18" t="n"/>
+      <c r="E385" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="F385" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="G385" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H385" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I385" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J385" s="18" t="inlineStr">
+        <is>
+          <t>Panchayati Raj Division within the Ministry.</t>
+        </is>
+      </c>
+      <c r="K385" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L385" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M385" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="386" ht="15.75" customHeight="1" s="16">
       <c r="A386" s="4">
@@ -22781,15 +24107,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E386" s="18" t="n"/>
-      <c r="F386" s="18" t="n"/>
-      <c r="G386" s="18" t="n"/>
-      <c r="H386" s="18" t="n"/>
-      <c r="I386" s="18" t="n"/>
-      <c r="J386" s="18" t="n"/>
-      <c r="K386" s="18" t="n"/>
-      <c r="L386" s="18" t="n"/>
-      <c r="M386" s="18" t="n"/>
+      <c r="E386" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="F386" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="G386" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H386" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I386" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J386" s="18" t="inlineStr">
+        <is>
+          <t>E-Governance &amp; Capacity Building Division within the Ministry.</t>
+        </is>
+      </c>
+      <c r="K386" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L386" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M386" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="387" ht="15.75" customHeight="1" s="16">
       <c r="A387" s="4">
@@ -22811,15 +24171,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E387" s="18" t="n"/>
-      <c r="F387" s="18" t="n"/>
-      <c r="G387" s="18" t="n"/>
-      <c r="H387" s="18" t="n"/>
-      <c r="I387" s="18" t="n"/>
-      <c r="J387" s="18" t="n"/>
-      <c r="K387" s="18" t="n"/>
-      <c r="L387" s="18" t="n"/>
-      <c r="M387" s="18" t="n"/>
+      <c r="E387" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nirdpr.org.in/</t>
+        </is>
+      </c>
+      <c r="F387" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nirdpr.org.in/</t>
+        </is>
+      </c>
+      <c r="G387" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H387" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I387" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J387" s="18" t="inlineStr">
+        <is>
+          <t>NIRDPR official site verified live. Autonomous body under Ministry of Panchayati Raj.</t>
+        </is>
+      </c>
+      <c r="K387" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L387" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M387" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="388" ht="15.75" customHeight="1" s="16">
       <c r="A388" s="4">
@@ -22841,15 +24235,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E388" s="18" t="n"/>
-      <c r="F388" s="18" t="n"/>
-      <c r="G388" s="18" t="n"/>
-      <c r="H388" s="18" t="n"/>
-      <c r="I388" s="18" t="n"/>
-      <c r="J388" s="18" t="n"/>
-      <c r="K388" s="18" t="n"/>
-      <c r="L388" s="18" t="n"/>
-      <c r="M388" s="18" t="n"/>
+      <c r="E388" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="F388" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="G388" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H388" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I388" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J388" s="18" t="inlineStr">
+        <is>
+          <t>Regional/State PR Support Units subordinate to Ministry.</t>
+        </is>
+      </c>
+      <c r="K388" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L388" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M388" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="389" ht="15.75" customHeight="1" s="16">
       <c r="A389" s="4">
@@ -22901,15 +24329,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E390" s="18" t="n"/>
-      <c r="F390" s="18" t="n"/>
-      <c r="G390" s="18" t="n"/>
-      <c r="H390" s="18" t="n"/>
-      <c r="I390" s="18" t="n"/>
-      <c r="J390" s="18" t="n"/>
-      <c r="K390" s="18" t="n"/>
-      <c r="L390" s="18" t="n"/>
-      <c r="M390" s="18" t="n"/>
+      <c r="E390" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F390" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G390" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H390" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I390" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J390" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Parliamentary Affairs site verified live.</t>
+        </is>
+      </c>
+      <c r="K390" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L390" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M390" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="391" ht="15.75" customHeight="1" s="16">
       <c r="A391" s="4">
@@ -22931,15 +24393,49 @@
           <t>attached body</t>
         </is>
       </c>
-      <c r="E391" s="18" t="n"/>
-      <c r="F391" s="18" t="n"/>
-      <c r="G391" s="18" t="n"/>
-      <c r="H391" s="18" t="n"/>
-      <c r="I391" s="18" t="n"/>
-      <c r="J391" s="18" t="n"/>
-      <c r="K391" s="18" t="n"/>
-      <c r="L391" s="18" t="n"/>
-      <c r="M391" s="18" t="n"/>
+      <c r="E391" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F391" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G391" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H391" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I391" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J391" s="18" t="inlineStr">
+        <is>
+          <t>Parliamentary Coordination &amp; Legislation Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K391" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L391" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M391" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="392" ht="15.75" customHeight="1" s="16">
       <c r="A392" s="4">
@@ -22961,15 +24457,49 @@
           <t>attached body</t>
         </is>
       </c>
-      <c r="E392" s="18" t="n"/>
-      <c r="F392" s="18" t="n"/>
-      <c r="G392" s="18" t="n"/>
-      <c r="H392" s="18" t="n"/>
-      <c r="I392" s="18" t="n"/>
-      <c r="J392" s="18" t="n"/>
-      <c r="K392" s="18" t="n"/>
-      <c r="L392" s="18" t="n"/>
-      <c r="M392" s="18" t="n"/>
+      <c r="E392" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F392" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G392" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H392" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I392" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J392" s="18" t="inlineStr">
+        <is>
+          <t>Parliamentary Liaison Units - coordination function within Ministry.</t>
+        </is>
+      </c>
+      <c r="K392" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L392" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M392" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="393" ht="15.75" customHeight="1" s="16">
       <c r="A393" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -24521,15 +24521,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E393" s="18" t="n"/>
-      <c r="F393" s="18" t="n"/>
-      <c r="G393" s="18" t="n"/>
-      <c r="H393" s="18" t="n"/>
-      <c r="I393" s="18" t="n"/>
-      <c r="J393" s="18" t="n"/>
-      <c r="K393" s="18" t="n"/>
-      <c r="L393" s="18" t="n"/>
-      <c r="M393" s="18" t="n"/>
+      <c r="E393" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="F393" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="G393" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H393" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I393" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J393" s="18" t="inlineStr">
+        <is>
+          <t>DoPT site unreachable from this environment. Confirmed official domain. Central cadre management.</t>
+        </is>
+      </c>
+      <c r="K393" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L393" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M393" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="394" ht="15.75" customHeight="1" s="16">
       <c r="A394" s="4">
@@ -24551,15 +24585,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E394" s="18" t="n"/>
-      <c r="F394" s="18" t="n"/>
-      <c r="G394" s="18" t="n"/>
-      <c r="H394" s="18" t="n"/>
-      <c r="I394" s="18" t="n"/>
-      <c r="J394" s="18" t="n"/>
-      <c r="K394" s="18" t="n"/>
-      <c r="L394" s="18" t="n"/>
-      <c r="M394" s="18" t="n"/>
+      <c r="E394" s="17" t="inlineStr">
+        <is>
+          <t>https://darpg.gov.in/</t>
+        </is>
+      </c>
+      <c r="F394" s="17" t="inlineStr">
+        <is>
+          <t>https://darpg.gov.in/</t>
+        </is>
+      </c>
+      <c r="G394" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H394" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I394" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J394" s="18" t="inlineStr">
+        <is>
+          <t>DARPG site verified live. Dept of Administrative Reforms.</t>
+        </is>
+      </c>
+      <c r="K394" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L394" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M394" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="395" ht="15.75" customHeight="1" s="16">
       <c r="A395" s="4">
@@ -24581,15 +24649,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E395" s="18" t="n"/>
-      <c r="F395" s="18" t="n"/>
-      <c r="G395" s="18" t="n"/>
-      <c r="H395" s="18" t="n"/>
-      <c r="I395" s="18" t="n"/>
-      <c r="J395" s="18" t="n"/>
-      <c r="K395" s="18" t="n"/>
-      <c r="L395" s="18" t="n"/>
-      <c r="M395" s="18" t="n"/>
+      <c r="E395" s="17" t="inlineStr">
+        <is>
+          <t>https://doppw.gov.in/</t>
+        </is>
+      </c>
+      <c r="F395" s="17" t="inlineStr">
+        <is>
+          <t>https://doppw.gov.in/</t>
+        </is>
+      </c>
+      <c r="G395" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H395" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I395" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J395" s="18" t="inlineStr">
+        <is>
+          <t>Dept of Pensions &amp; Pensioners' Welfare site verified live.</t>
+        </is>
+      </c>
+      <c r="K395" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L395" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M395" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="396" ht="15.75" customHeight="1" s="16">
       <c r="A396" s="4">
@@ -24611,15 +24713,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E396" s="18" t="n"/>
-      <c r="F396" s="18" t="n"/>
-      <c r="G396" s="18" t="n"/>
-      <c r="H396" s="18" t="n"/>
-      <c r="I396" s="18" t="n"/>
-      <c r="J396" s="18" t="n"/>
-      <c r="K396" s="18" t="n"/>
-      <c r="L396" s="18" t="n"/>
-      <c r="M396" s="18" t="n"/>
+      <c r="E396" s="17" t="inlineStr">
+        <is>
+          <t>https://www.upsc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F396" s="17" t="inlineStr">
+        <is>
+          <t>https://www.upsc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G396" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H396" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I396" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J396" s="18" t="inlineStr">
+        <is>
+          <t>UPSC official site verified live. Constitutional body. Own recruitment for its staff plus conducts exams for GoI.</t>
+        </is>
+      </c>
+      <c r="K396" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L396" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M396" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="397" ht="15.75" customHeight="1" s="16">
       <c r="A397" s="4">
@@ -24641,15 +24777,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E397" s="18" t="n"/>
-      <c r="F397" s="18" t="n"/>
-      <c r="G397" s="18" t="n"/>
-      <c r="H397" s="18" t="n"/>
-      <c r="I397" s="18" t="n"/>
-      <c r="J397" s="18" t="n"/>
-      <c r="K397" s="18" t="n"/>
-      <c r="L397" s="18" t="n"/>
-      <c r="M397" s="18" t="n"/>
+      <c r="E397" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="F397" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="G397" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H397" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I397" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J397" s="18" t="inlineStr">
+        <is>
+          <t>CAT (Central Administrative Tribunal). Statutory body under DoPT. Staff on deputation; recruitment via DoPT channels.</t>
+        </is>
+      </c>
+      <c r="K397" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L397" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M397" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="398" ht="15.75" customHeight="1" s="16">
       <c r="A398" s="4">
@@ -24671,15 +24841,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E398" s="18" t="n"/>
-      <c r="F398" s="18" t="n"/>
-      <c r="G398" s="18" t="n"/>
-      <c r="H398" s="18" t="n"/>
-      <c r="I398" s="18" t="n"/>
-      <c r="J398" s="18" t="n"/>
-      <c r="K398" s="18" t="n"/>
-      <c r="L398" s="18" t="n"/>
-      <c r="M398" s="18" t="n"/>
+      <c r="E398" s="17" t="inlineStr">
+        <is>
+          <t>https://ssc.nic.in/</t>
+        </is>
+      </c>
+      <c r="F398" s="17" t="inlineStr">
+        <is>
+          <t>https://ssc.nic.in/</t>
+        </is>
+      </c>
+      <c r="G398" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H398" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I398" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J398" s="18" t="inlineStr">
+        <is>
+          <t>SSC official site (ssc.nic.in). Unreachable from this environment. Confirmed as official domain. Major recruitment agency.</t>
+        </is>
+      </c>
+      <c r="K398" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L398" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M398" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="15.75" customHeight="1" s="16">
       <c r="A399" s="4">
@@ -24701,15 +24905,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E399" s="18" t="n"/>
-      <c r="F399" s="18" t="n"/>
-      <c r="G399" s="18" t="n"/>
-      <c r="H399" s="18" t="n"/>
-      <c r="I399" s="18" t="n"/>
-      <c r="J399" s="18" t="n"/>
-      <c r="K399" s="18" t="n"/>
-      <c r="L399" s="18" t="n"/>
-      <c r="M399" s="18" t="n"/>
+      <c r="E399" s="17" t="inlineStr">
+        <is>
+          <t>https://cvc.gov.in/</t>
+        </is>
+      </c>
+      <c r="F399" s="17" t="inlineStr">
+        <is>
+          <t>https://cvc.gov.in/</t>
+        </is>
+      </c>
+      <c r="G399" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H399" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I399" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J399" s="18" t="inlineStr">
+        <is>
+          <t>CVC site unreachable from environment. Confirmed as official domain. Staff on deputation.</t>
+        </is>
+      </c>
+      <c r="K399" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L399" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M399" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="16">
       <c r="A400" s="4">
@@ -24731,15 +24969,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E400" s="18" t="n"/>
-      <c r="F400" s="18" t="n"/>
-      <c r="G400" s="18" t="n"/>
-      <c r="H400" s="18" t="n"/>
-      <c r="I400" s="18" t="n"/>
-      <c r="J400" s="18" t="n"/>
-      <c r="K400" s="18" t="n"/>
-      <c r="L400" s="18" t="n"/>
-      <c r="M400" s="18" t="n"/>
+      <c r="E400" s="17" t="inlineStr">
+        <is>
+          <t>https://cic.gov.in/</t>
+        </is>
+      </c>
+      <c r="F400" s="17" t="inlineStr">
+        <is>
+          <t>https://cic.gov.in/</t>
+        </is>
+      </c>
+      <c r="G400" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H400" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I400" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J400" s="18" t="inlineStr">
+        <is>
+          <t>CIC official site verified live. Staff on deputation.</t>
+        </is>
+      </c>
+      <c r="K400" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L400" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M400" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="401" ht="15.75" customHeight="1" s="16">
       <c r="A401" s="4">
@@ -24761,15 +25033,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E401" s="18" t="n"/>
-      <c r="F401" s="18" t="n"/>
-      <c r="G401" s="18" t="n"/>
-      <c r="H401" s="18" t="n"/>
-      <c r="I401" s="18" t="n"/>
-      <c r="J401" s="18" t="n"/>
-      <c r="K401" s="18" t="n"/>
-      <c r="L401" s="18" t="n"/>
-      <c r="M401" s="18" t="n"/>
+      <c r="E401" s="17" t="inlineStr">
+        <is>
+          <t>https://www.lbsnaa.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F401" s="17" t="inlineStr">
+        <is>
+          <t>https://www.lbsnaa.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G401" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H401" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I401" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J401" s="18" t="inlineStr">
+        <is>
+          <t>LBSNAA vacancy page verified live. NOTE: Also listed under MHA (row 289). Autonomous body under DoPT.</t>
+        </is>
+      </c>
+      <c r="K401" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L401" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M401" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="402" ht="15.75" customHeight="1" s="16">
       <c r="A402" s="4">
@@ -24791,15 +25097,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E402" s="18" t="n"/>
-      <c r="F402" s="18" t="n"/>
-      <c r="G402" s="18" t="n"/>
-      <c r="H402" s="18" t="n"/>
-      <c r="I402" s="18" t="n"/>
-      <c r="J402" s="18" t="n"/>
-      <c r="K402" s="18" t="n"/>
-      <c r="L402" s="18" t="n"/>
-      <c r="M402" s="18" t="n"/>
+      <c r="E402" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="F402" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="G402" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H402" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I402" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J402" s="18" t="inlineStr">
+        <is>
+          <t>NCGG (National Centre for Good Governance). Small autonomous body under DoPT. No independent recruitment portal found.</t>
+        </is>
+      </c>
+      <c r="K402" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L402" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M402" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="403" ht="15.75" customHeight="1" s="16">
       <c r="A403" s="4">
@@ -24821,15 +25161,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E403" s="18" t="n"/>
-      <c r="F403" s="18" t="n"/>
-      <c r="G403" s="18" t="n"/>
-      <c r="H403" s="18" t="n"/>
-      <c r="I403" s="18" t="n"/>
-      <c r="J403" s="18" t="n"/>
-      <c r="K403" s="18" t="n"/>
-      <c r="L403" s="18" t="n"/>
-      <c r="M403" s="18" t="n"/>
+      <c r="E403" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="F403" s="17" t="inlineStr">
+        <is>
+          <t>https://dopt.gov.in/</t>
+        </is>
+      </c>
+      <c r="G403" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H403" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I403" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J403" s="18" t="inlineStr">
+        <is>
+          <t>DoPT Cadre Units/Establishment Sections - subordinate to DoPT. No separate site.</t>
+        </is>
+      </c>
+      <c r="K403" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L403" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M403" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="404" ht="15.75" customHeight="1" s="16">
       <c r="A404" s="4">
@@ -24881,15 +25255,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E405" s="18" t="n"/>
-      <c r="F405" s="18" t="n"/>
-      <c r="G405" s="18" t="n"/>
-      <c r="H405" s="18" t="n"/>
-      <c r="I405" s="18" t="n"/>
-      <c r="J405" s="18" t="n"/>
-      <c r="K405" s="18" t="n"/>
-      <c r="L405" s="18" t="n"/>
-      <c r="M405" s="18" t="n"/>
+      <c r="E405" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F405" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G405" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H405" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I405" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J405" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of P&amp;NG site unreachable from environment. Confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K405" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L405" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M405" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="15.75" customHeight="1" s="16">
       <c r="A406" s="4">
@@ -24911,15 +25319,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E406" s="18" t="n"/>
-      <c r="F406" s="18" t="n"/>
-      <c r="G406" s="18" t="n"/>
-      <c r="H406" s="18" t="n"/>
-      <c r="I406" s="18" t="n"/>
-      <c r="J406" s="18" t="n"/>
-      <c r="K406" s="18" t="n"/>
-      <c r="L406" s="18" t="n"/>
-      <c r="M406" s="18" t="n"/>
+      <c r="E406" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F406" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G406" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H406" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I406" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J406" s="18" t="inlineStr">
+        <is>
+          <t>Exploration Division within Ministry. No separate site.</t>
+        </is>
+      </c>
+      <c r="K406" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L406" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M406" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="16">
       <c r="A407" s="4">
@@ -24941,15 +25383,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E407" s="18" t="n"/>
-      <c r="F407" s="18" t="n"/>
-      <c r="G407" s="18" t="n"/>
-      <c r="H407" s="18" t="n"/>
-      <c r="I407" s="18" t="n"/>
-      <c r="J407" s="18" t="n"/>
-      <c r="K407" s="18" t="n"/>
-      <c r="L407" s="18" t="n"/>
-      <c r="M407" s="18" t="n"/>
+      <c r="E407" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F407" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G407" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H407" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I407" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J407" s="18" t="inlineStr">
+        <is>
+          <t>Refineries Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K407" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L407" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M407" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="16">
       <c r="A408" s="4">
@@ -24971,15 +25447,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E408" s="18" t="n"/>
-      <c r="F408" s="18" t="n"/>
-      <c r="G408" s="18" t="n"/>
-      <c r="H408" s="18" t="n"/>
-      <c r="I408" s="18" t="n"/>
-      <c r="J408" s="18" t="n"/>
-      <c r="K408" s="18" t="n"/>
-      <c r="L408" s="18" t="n"/>
-      <c r="M408" s="18" t="n"/>
+      <c r="E408" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F408" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G408" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H408" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I408" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J408" s="18" t="inlineStr">
+        <is>
+          <t>Natural Gas Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K408" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L408" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M408" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="16">
       <c r="A409" s="4">
@@ -25001,15 +25511,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E409" s="18" t="n"/>
-      <c r="F409" s="18" t="n"/>
-      <c r="G409" s="18" t="n"/>
-      <c r="H409" s="18" t="n"/>
-      <c r="I409" s="18" t="n"/>
-      <c r="J409" s="18" t="n"/>
-      <c r="K409" s="18" t="n"/>
-      <c r="L409" s="18" t="n"/>
-      <c r="M409" s="18" t="n"/>
+      <c r="E409" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F409" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G409" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H409" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I409" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J409" s="18" t="inlineStr">
+        <is>
+          <t>Marketing Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K409" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L409" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M409" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="16">
       <c r="A410" s="4">
@@ -25031,15 +25575,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E410" s="18" t="n"/>
-      <c r="F410" s="18" t="n"/>
-      <c r="G410" s="18" t="n"/>
-      <c r="H410" s="18" t="n"/>
-      <c r="I410" s="18" t="n"/>
-      <c r="J410" s="18" t="n"/>
-      <c r="K410" s="18" t="n"/>
-      <c r="L410" s="18" t="n"/>
-      <c r="M410" s="18" t="n"/>
+      <c r="E410" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dghindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F410" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dghindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G410" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H410" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I410" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J410" s="18" t="inlineStr">
+        <is>
+          <t>DGH official site verified live. Attached office under MoPNG.</t>
+        </is>
+      </c>
+      <c r="K410" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L410" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M410" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="16">
       <c r="A411" s="4">
@@ -25061,15 +25639,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E411" s="18" t="n"/>
-      <c r="F411" s="18" t="n"/>
-      <c r="G411" s="18" t="n"/>
-      <c r="H411" s="18" t="n"/>
-      <c r="I411" s="18" t="n"/>
-      <c r="J411" s="18" t="n"/>
-      <c r="K411" s="18" t="n"/>
-      <c r="L411" s="18" t="n"/>
-      <c r="M411" s="18" t="n"/>
+      <c r="E411" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ppac.gov.in/</t>
+        </is>
+      </c>
+      <c r="F411" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ppac.gov.in/</t>
+        </is>
+      </c>
+      <c r="G411" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H411" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I411" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J411" s="18" t="inlineStr">
+        <is>
+          <t>PPAC site verified live. Attached office under MoPNG.</t>
+        </is>
+      </c>
+      <c r="K411" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L411" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M411" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="16">
       <c r="A412" s="4">
@@ -25091,15 +25703,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E412" s="18" t="n"/>
-      <c r="F412" s="18" t="n"/>
-      <c r="G412" s="18" t="n"/>
-      <c r="H412" s="18" t="n"/>
-      <c r="I412" s="18" t="n"/>
-      <c r="J412" s="18" t="n"/>
-      <c r="K412" s="18" t="n"/>
-      <c r="L412" s="18" t="n"/>
-      <c r="M412" s="18" t="n"/>
+      <c r="E412" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dghindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F412" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dghindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G412" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H412" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I412" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J412" s="18" t="inlineStr">
+        <is>
+          <t>DGH Regional/Field Offices subordinate to DGH.</t>
+        </is>
+      </c>
+      <c r="K412" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L412" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M412" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="413" ht="15.75" customHeight="1" s="16">
       <c r="A413" s="4">
@@ -25121,15 +25767,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E413" s="18" t="n"/>
-      <c r="F413" s="18" t="n"/>
-      <c r="G413" s="18" t="n"/>
-      <c r="H413" s="18" t="n"/>
-      <c r="I413" s="18" t="n"/>
-      <c r="J413" s="18" t="n"/>
-      <c r="K413" s="18" t="n"/>
-      <c r="L413" s="18" t="n"/>
-      <c r="M413" s="18" t="n"/>
+      <c r="E413" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ppac.gov.in/</t>
+        </is>
+      </c>
+      <c r="F413" s="17" t="inlineStr">
+        <is>
+          <t>https://www.ppac.gov.in/</t>
+        </is>
+      </c>
+      <c r="G413" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H413" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I413" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J413" s="18" t="inlineStr">
+        <is>
+          <t>PPAC Data &amp; Monitoring Units subordinate to PPAC.</t>
+        </is>
+      </c>
+      <c r="K413" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L413" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M413" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="414" ht="15.75" customHeight="1" s="16">
       <c r="A414" s="4">
@@ -25151,15 +25831,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E414" s="18" t="n"/>
-      <c r="F414" s="18" t="n"/>
-      <c r="G414" s="18" t="n"/>
-      <c r="H414" s="18" t="n"/>
-      <c r="I414" s="18" t="n"/>
-      <c r="J414" s="18" t="n"/>
-      <c r="K414" s="18" t="n"/>
-      <c r="L414" s="18" t="n"/>
-      <c r="M414" s="18" t="n"/>
+      <c r="E414" s="17" t="inlineStr">
+        <is>
+          <t>https://www.pngrb.gov.in/</t>
+        </is>
+      </c>
+      <c r="F414" s="17" t="inlineStr">
+        <is>
+          <t>https://www.pngrb.gov.in/</t>
+        </is>
+      </c>
+      <c r="G414" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H414" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I414" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J414" s="18" t="inlineStr">
+        <is>
+          <t>PNGRB site verified live. Statutory body under MoPNG.</t>
+        </is>
+      </c>
+      <c r="K414" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L414" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M414" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="415" ht="15.75" customHeight="1" s="16">
       <c r="A415" s="4">
@@ -25181,15 +25895,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E415" s="18" t="n"/>
-      <c r="F415" s="18" t="n"/>
-      <c r="G415" s="18" t="n"/>
-      <c r="H415" s="18" t="n"/>
-      <c r="I415" s="18" t="n"/>
-      <c r="J415" s="18" t="n"/>
-      <c r="K415" s="18" t="n"/>
-      <c r="L415" s="18" t="n"/>
-      <c r="M415" s="18" t="n"/>
+      <c r="E415" s="17" t="inlineStr">
+        <is>
+          <t>https://www.rgipt.ac.in/</t>
+        </is>
+      </c>
+      <c r="F415" s="17" t="inlineStr">
+        <is>
+          <t>https://www.rgipt.ac.in/</t>
+        </is>
+      </c>
+      <c r="G415" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H415" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I415" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J415" s="18" t="inlineStr">
+        <is>
+          <t>RGIPT site verified live. Autonomous institution under MoPNG.</t>
+        </is>
+      </c>
+      <c r="K415" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L415" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M415" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="416" ht="15.75" customHeight="1" s="16">
       <c r="A416" s="4">
@@ -25211,15 +25959,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E416" s="18" t="n"/>
-      <c r="F416" s="18" t="n"/>
-      <c r="G416" s="18" t="n"/>
-      <c r="H416" s="18" t="n"/>
-      <c r="I416" s="18" t="n"/>
-      <c r="J416" s="18" t="n"/>
-      <c r="K416" s="18" t="n"/>
-      <c r="L416" s="18" t="n"/>
-      <c r="M416" s="18" t="n"/>
+      <c r="E416" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F416" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G416" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H416" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I416" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J416" s="18" t="inlineStr">
+        <is>
+          <t>ONGC/OIL/GAIL are PSUs recruiting independently. Policy/admin entry. Mapped to parent ministry.</t>
+        </is>
+      </c>
+      <c r="K416" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L416" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M416" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="417" ht="15.75" customHeight="1" s="16">
       <c r="A417" s="4">
@@ -25241,15 +26023,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E417" s="18" t="n"/>
-      <c r="F417" s="18" t="n"/>
-      <c r="G417" s="18" t="n"/>
-      <c r="H417" s="18" t="n"/>
-      <c r="I417" s="18" t="n"/>
-      <c r="J417" s="18" t="n"/>
-      <c r="K417" s="18" t="n"/>
-      <c r="L417" s="18" t="n"/>
-      <c r="M417" s="18" t="n"/>
+      <c r="E417" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F417" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G417" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H417" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I417" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J417" s="18" t="inlineStr">
+        <is>
+          <t>Indian Oil/BPCL/HPCL are PSUs recruiting independently. Policy/admin entry.</t>
+        </is>
+      </c>
+      <c r="K417" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L417" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M417" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="15.75" customHeight="1" s="16">
       <c r="A418" s="4">
@@ -25301,15 +26117,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E419" s="18" t="n"/>
-      <c r="F419" s="18" t="n"/>
-      <c r="G419" s="18" t="n"/>
-      <c r="H419" s="18" t="n"/>
-      <c r="I419" s="18" t="n"/>
-      <c r="J419" s="18" t="n"/>
-      <c r="K419" s="18" t="n"/>
-      <c r="L419" s="18" t="n"/>
-      <c r="M419" s="18" t="n"/>
+      <c r="E419" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F419" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G419" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H419" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I419" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J419" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Ports, Shipping &amp; Waterways site verified live.</t>
+        </is>
+      </c>
+      <c r="K419" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L419" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M419" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="420" ht="15.75" customHeight="1" s="16">
       <c r="A420" s="4">
@@ -25331,15 +26181,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E420" s="18" t="n"/>
-      <c r="F420" s="18" t="n"/>
-      <c r="G420" s="18" t="n"/>
-      <c r="H420" s="18" t="n"/>
-      <c r="I420" s="18" t="n"/>
-      <c r="J420" s="18" t="n"/>
-      <c r="K420" s="18" t="n"/>
-      <c r="L420" s="18" t="n"/>
-      <c r="M420" s="18" t="n"/>
+      <c r="E420" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F420" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G420" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H420" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I420" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J420" s="18" t="inlineStr">
+        <is>
+          <t>Ports Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K420" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L420" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M420" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="421" ht="15.75" customHeight="1" s="16">
       <c r="A421" s="4">
@@ -25361,15 +26245,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E421" s="18" t="n"/>
-      <c r="F421" s="18" t="n"/>
-      <c r="G421" s="18" t="n"/>
-      <c r="H421" s="18" t="n"/>
-      <c r="I421" s="18" t="n"/>
-      <c r="J421" s="18" t="n"/>
-      <c r="K421" s="18" t="n"/>
-      <c r="L421" s="18" t="n"/>
-      <c r="M421" s="18" t="n"/>
+      <c r="E421" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F421" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G421" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H421" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I421" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J421" s="18" t="inlineStr">
+        <is>
+          <t>Shipping Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K421" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L421" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M421" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="15.75" customHeight="1" s="16">
       <c r="A422" s="4">
@@ -25391,15 +26309,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E422" s="18" t="n"/>
-      <c r="F422" s="18" t="n"/>
-      <c r="G422" s="18" t="n"/>
-      <c r="H422" s="18" t="n"/>
-      <c r="I422" s="18" t="n"/>
-      <c r="J422" s="18" t="n"/>
-      <c r="K422" s="18" t="n"/>
-      <c r="L422" s="18" t="n"/>
-      <c r="M422" s="18" t="n"/>
+      <c r="E422" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F422" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G422" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H422" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I422" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J422" s="18" t="inlineStr">
+        <is>
+          <t>Inland Waterways Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K422" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L422" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M422" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="423" ht="15.75" customHeight="1" s="16">
       <c r="A423" s="4">
@@ -25421,15 +26373,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E423" s="18" t="n"/>
-      <c r="F423" s="18" t="n"/>
-      <c r="G423" s="18" t="n"/>
-      <c r="H423" s="18" t="n"/>
-      <c r="I423" s="18" t="n"/>
-      <c r="J423" s="18" t="n"/>
-      <c r="K423" s="18" t="n"/>
-      <c r="L423" s="18" t="n"/>
-      <c r="M423" s="18" t="n"/>
+      <c r="E423" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgshipping.gov.in/</t>
+        </is>
+      </c>
+      <c r="F423" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgshipping.gov.in/</t>
+        </is>
+      </c>
+      <c r="G423" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H423" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I423" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J423" s="18" t="inlineStr">
+        <is>
+          <t>DG Shipping site verified live. Attached office under MoPSW.</t>
+        </is>
+      </c>
+      <c r="K423" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L423" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M423" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="15.75" customHeight="1" s="16">
       <c r="A424" s="4">
@@ -25451,15 +26437,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E424" s="18" t="n"/>
-      <c r="F424" s="18" t="n"/>
-      <c r="G424" s="18" t="n"/>
-      <c r="H424" s="18" t="n"/>
-      <c r="I424" s="18" t="n"/>
-      <c r="J424" s="18" t="n"/>
-      <c r="K424" s="18" t="n"/>
-      <c r="L424" s="18" t="n"/>
-      <c r="M424" s="18" t="n"/>
+      <c r="E424" s="17" t="inlineStr">
+        <is>
+          <t>https://iwai.nic.in/</t>
+        </is>
+      </c>
+      <c r="F424" s="17" t="inlineStr">
+        <is>
+          <t>https://iwai.nic.in/</t>
+        </is>
+      </c>
+      <c r="G424" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H424" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I424" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J424" s="18" t="inlineStr">
+        <is>
+          <t>IWAI site verified live. Statutory body under MoPSW.</t>
+        </is>
+      </c>
+      <c r="K424" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L424" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M424" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="425" ht="15.75" customHeight="1" s="16">
       <c r="A425" s="4">
@@ -25481,15 +26501,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E425" s="18" t="n"/>
-      <c r="F425" s="18" t="n"/>
-      <c r="G425" s="18" t="n"/>
-      <c r="H425" s="18" t="n"/>
-      <c r="I425" s="18" t="n"/>
-      <c r="J425" s="18" t="n"/>
-      <c r="K425" s="18" t="n"/>
-      <c r="L425" s="18" t="n"/>
-      <c r="M425" s="18" t="n"/>
+      <c r="E425" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgshipping.gov.in/</t>
+        </is>
+      </c>
+      <c r="F425" s="17" t="inlineStr">
+        <is>
+          <t>https://www.dgshipping.gov.in/</t>
+        </is>
+      </c>
+      <c r="G425" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H425" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I425" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J425" s="18" t="inlineStr">
+        <is>
+          <t>DGS Regional/Field Offices subordinate to DGS.</t>
+        </is>
+      </c>
+      <c r="K425" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L425" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M425" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="426" ht="15.75" customHeight="1" s="16">
       <c r="A426" s="4">
@@ -25511,15 +26565,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E426" s="18" t="n"/>
-      <c r="F426" s="18" t="n"/>
-      <c r="G426" s="18" t="n"/>
-      <c r="H426" s="18" t="n"/>
-      <c r="I426" s="18" t="n"/>
-      <c r="J426" s="18" t="n"/>
-      <c r="K426" s="18" t="n"/>
-      <c r="L426" s="18" t="n"/>
-      <c r="M426" s="18" t="n"/>
+      <c r="E426" s="17" t="inlineStr">
+        <is>
+          <t>https://iwai.nic.in/</t>
+        </is>
+      </c>
+      <c r="F426" s="17" t="inlineStr">
+        <is>
+          <t>https://iwai.nic.in/</t>
+        </is>
+      </c>
+      <c r="G426" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H426" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I426" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J426" s="18" t="inlineStr">
+        <is>
+          <t>IWAI Regional/Project Units subordinate to IWAI.</t>
+        </is>
+      </c>
+      <c r="K426" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L426" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M426" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="427" ht="15.75" customHeight="1" s="16">
       <c r="A427" s="4">
@@ -25541,15 +26629,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E427" s="18" t="n"/>
-      <c r="F427" s="18" t="n"/>
-      <c r="G427" s="18" t="n"/>
-      <c r="H427" s="18" t="n"/>
-      <c r="I427" s="18" t="n"/>
-      <c r="J427" s="18" t="n"/>
-      <c r="K427" s="18" t="n"/>
-      <c r="L427" s="18" t="n"/>
-      <c r="M427" s="18" t="n"/>
+      <c r="E427" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F427" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G427" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H427" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I427" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J427" s="18" t="inlineStr">
+        <is>
+          <t>Major Port Authorities recruit independently. Statutory bodies. Policy mapped to Ministry.</t>
+        </is>
+      </c>
+      <c r="K427" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L427" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M427" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="428" ht="15.75" customHeight="1" s="16">
       <c r="A428" s="4">
@@ -25571,15 +26693,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E428" s="18" t="n"/>
-      <c r="F428" s="18" t="n"/>
-      <c r="G428" s="18" t="n"/>
-      <c r="H428" s="18" t="n"/>
-      <c r="I428" s="18" t="n"/>
-      <c r="J428" s="18" t="n"/>
-      <c r="K428" s="18" t="n"/>
-      <c r="L428" s="18" t="n"/>
-      <c r="M428" s="18" t="n"/>
+      <c r="E428" s="17" t="inlineStr">
+        <is>
+          <t>https://www.imu.edu.in/</t>
+        </is>
+      </c>
+      <c r="F428" s="17" t="inlineStr">
+        <is>
+          <t>https://www.imu.edu.in/</t>
+        </is>
+      </c>
+      <c r="G428" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H428" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I428" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J428" s="18" t="inlineStr">
+        <is>
+          <t>IMU (Indian Maritime University) site verified live. Autonomous body under MoPSW.</t>
+        </is>
+      </c>
+      <c r="K428" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L428" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M428" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="429" ht="15.75" customHeight="1" s="16">
       <c r="A429" s="4">
@@ -25601,15 +26757,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E429" s="18" t="n"/>
-      <c r="F429" s="18" t="n"/>
-      <c r="G429" s="18" t="n"/>
-      <c r="H429" s="18" t="n"/>
-      <c r="I429" s="18" t="n"/>
-      <c r="J429" s="18" t="n"/>
-      <c r="K429" s="18" t="n"/>
-      <c r="L429" s="18" t="n"/>
-      <c r="M429" s="18" t="n"/>
+      <c r="E429" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F429" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G429" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H429" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I429" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J429" s="18" t="inlineStr">
+        <is>
+          <t>NSB (National Shipping Board) is an advisory body. No separate recruitment.</t>
+        </is>
+      </c>
+      <c r="K429" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L429" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M429" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="430" ht="15.75" customHeight="1" s="16">
       <c r="A430" s="4">
@@ -25661,15 +26851,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E431" s="18" t="n"/>
-      <c r="F431" s="18" t="n"/>
-      <c r="G431" s="18" t="n"/>
-      <c r="H431" s="18" t="n"/>
-      <c r="I431" s="18" t="n"/>
-      <c r="J431" s="18" t="n"/>
-      <c r="K431" s="18" t="n"/>
-      <c r="L431" s="18" t="n"/>
-      <c r="M431" s="18" t="n"/>
+      <c r="E431" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F431" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G431" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H431" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I431" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J431" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Power site verified live.</t>
+        </is>
+      </c>
+      <c r="K431" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L431" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M431" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="432" ht="15.75" customHeight="1" s="16">
       <c r="A432" s="4">
@@ -25691,15 +26915,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E432" s="18" t="n"/>
-      <c r="F432" s="18" t="n"/>
-      <c r="G432" s="18" t="n"/>
-      <c r="H432" s="18" t="n"/>
-      <c r="I432" s="18" t="n"/>
-      <c r="J432" s="18" t="n"/>
-      <c r="K432" s="18" t="n"/>
-      <c r="L432" s="18" t="n"/>
-      <c r="M432" s="18" t="n"/>
+      <c r="E432" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F432" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G432" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H432" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I432" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J432" s="18" t="inlineStr">
+        <is>
+          <t>Power Sector Policy &amp; Planning Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K432" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L432" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M432" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="433" ht="15.75" customHeight="1" s="16">
       <c r="A433" s="4">
@@ -25721,15 +26979,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E433" s="18" t="n"/>
-      <c r="F433" s="18" t="n"/>
-      <c r="G433" s="18" t="n"/>
-      <c r="H433" s="18" t="n"/>
-      <c r="I433" s="18" t="n"/>
-      <c r="J433" s="18" t="n"/>
-      <c r="K433" s="18" t="n"/>
-      <c r="L433" s="18" t="n"/>
-      <c r="M433" s="18" t="n"/>
+      <c r="E433" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F433" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G433" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H433" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I433" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J433" s="18" t="inlineStr">
+        <is>
+          <t>Transmission Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K433" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L433" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M433" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="15.75" customHeight="1" s="16">
       <c r="A434" s="4">
@@ -25751,15 +27043,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E434" s="18" t="n"/>
-      <c r="F434" s="18" t="n"/>
-      <c r="G434" s="18" t="n"/>
-      <c r="H434" s="18" t="n"/>
-      <c r="I434" s="18" t="n"/>
-      <c r="J434" s="18" t="n"/>
-      <c r="K434" s="18" t="n"/>
-      <c r="L434" s="18" t="n"/>
-      <c r="M434" s="18" t="n"/>
+      <c r="E434" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F434" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G434" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H434" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I434" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J434" s="18" t="inlineStr">
+        <is>
+          <t>Distribution Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K434" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L434" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M434" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="435" ht="15.75" customHeight="1" s="16">
       <c r="A435" s="4">
@@ -25781,15 +27107,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E435" s="18" t="n"/>
-      <c r="F435" s="18" t="n"/>
-      <c r="G435" s="18" t="n"/>
-      <c r="H435" s="18" t="n"/>
-      <c r="I435" s="18" t="n"/>
-      <c r="J435" s="18" t="n"/>
-      <c r="K435" s="18" t="n"/>
-      <c r="L435" s="18" t="n"/>
-      <c r="M435" s="18" t="n"/>
+      <c r="E435" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F435" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G435" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H435" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I435" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J435" s="18" t="inlineStr">
+        <is>
+          <t>Hydro Power Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K435" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L435" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M435" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="436" ht="15.75" customHeight="1" s="16">
       <c r="A436" s="4">
@@ -25811,15 +27171,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E436" s="18" t="n"/>
-      <c r="F436" s="18" t="n"/>
-      <c r="G436" s="18" t="n"/>
-      <c r="H436" s="18" t="n"/>
-      <c r="I436" s="18" t="n"/>
-      <c r="J436" s="18" t="n"/>
-      <c r="K436" s="18" t="n"/>
-      <c r="L436" s="18" t="n"/>
-      <c r="M436" s="18" t="n"/>
+      <c r="E436" s="17" t="inlineStr">
+        <is>
+          <t>https://cea.nic.in/</t>
+        </is>
+      </c>
+      <c r="F436" s="17" t="inlineStr">
+        <is>
+          <t>https://cea.nic.in/</t>
+        </is>
+      </c>
+      <c r="G436" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H436" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I436" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J436" s="18" t="inlineStr">
+        <is>
+          <t>CEA (Central Electricity Authority) site unreachable from environment. Confirmed as official domain. Attached office.</t>
+        </is>
+      </c>
+      <c r="K436" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L436" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M436" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="16">
       <c r="A437" s="4">
@@ -25841,15 +27235,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E437" s="18" t="n"/>
-      <c r="F437" s="18" t="n"/>
-      <c r="G437" s="18" t="n"/>
-      <c r="H437" s="18" t="n"/>
-      <c r="I437" s="18" t="n"/>
-      <c r="J437" s="18" t="n"/>
-      <c r="K437" s="18" t="n"/>
-      <c r="L437" s="18" t="n"/>
-      <c r="M437" s="18" t="n"/>
+      <c r="E437" s="17" t="inlineStr">
+        <is>
+          <t>https://beeindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F437" s="17" t="inlineStr">
+        <is>
+          <t>https://beeindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G437" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H437" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I437" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J437" s="18" t="inlineStr">
+        <is>
+          <t>Bureau of Energy Efficiency site verified live. Attached office under Power Ministry.</t>
+        </is>
+      </c>
+      <c r="K437" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L437" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M437" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="16">
       <c r="A438" s="4">
@@ -25871,15 +27299,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E438" s="18" t="n"/>
-      <c r="F438" s="18" t="n"/>
-      <c r="G438" s="18" t="n"/>
-      <c r="H438" s="18" t="n"/>
-      <c r="I438" s="18" t="n"/>
-      <c r="J438" s="18" t="n"/>
-      <c r="K438" s="18" t="n"/>
-      <c r="L438" s="18" t="n"/>
-      <c r="M438" s="18" t="n"/>
+      <c r="E438" s="17" t="inlineStr">
+        <is>
+          <t>https://cea.nic.in/</t>
+        </is>
+      </c>
+      <c r="F438" s="17" t="inlineStr">
+        <is>
+          <t>https://cea.nic.in/</t>
+        </is>
+      </c>
+      <c r="G438" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H438" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I438" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J438" s="18" t="inlineStr">
+        <is>
+          <t>CEA Regional/Field Offices subordinate to CEA.</t>
+        </is>
+      </c>
+      <c r="K438" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L438" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M438" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="16">
       <c r="A439" s="4">
@@ -25901,15 +27363,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E439" s="18" t="n"/>
-      <c r="F439" s="18" t="n"/>
-      <c r="G439" s="18" t="n"/>
-      <c r="H439" s="18" t="n"/>
-      <c r="I439" s="18" t="n"/>
-      <c r="J439" s="18" t="n"/>
-      <c r="K439" s="18" t="n"/>
-      <c r="L439" s="18" t="n"/>
-      <c r="M439" s="18" t="n"/>
+      <c r="E439" s="17" t="inlineStr">
+        <is>
+          <t>https://beeindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F439" s="17" t="inlineStr">
+        <is>
+          <t>https://beeindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G439" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H439" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I439" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J439" s="18" t="inlineStr">
+        <is>
+          <t>BEE State/Regional Units subordinate to BEE.</t>
+        </is>
+      </c>
+      <c r="K439" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L439" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M439" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="16">
       <c r="A440" s="4">
@@ -25931,15 +27427,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E440" s="18" t="n"/>
-      <c r="F440" s="18" t="n"/>
-      <c r="G440" s="18" t="n"/>
-      <c r="H440" s="18" t="n"/>
-      <c r="I440" s="18" t="n"/>
-      <c r="J440" s="18" t="n"/>
-      <c r="K440" s="18" t="n"/>
-      <c r="L440" s="18" t="n"/>
-      <c r="M440" s="18" t="n"/>
+      <c r="E440" s="17" t="inlineStr">
+        <is>
+          <t>https://cercind.gov.in/</t>
+        </is>
+      </c>
+      <c r="F440" s="17" t="inlineStr">
+        <is>
+          <t>https://cercind.gov.in/</t>
+        </is>
+      </c>
+      <c r="G440" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H440" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I440" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J440" s="18" t="inlineStr">
+        <is>
+          <t>CERC site unreachable from environment. Confirmed as official domain. Statutory body.</t>
+        </is>
+      </c>
+      <c r="K440" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L440" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M440" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="441" ht="15.75" customHeight="1" s="16">
       <c r="A441" s="4">
@@ -25961,15 +27491,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E441" s="18" t="n"/>
-      <c r="F441" s="18" t="n"/>
-      <c r="G441" s="18" t="n"/>
-      <c r="H441" s="18" t="n"/>
-      <c r="I441" s="18" t="n"/>
-      <c r="J441" s="18" t="n"/>
-      <c r="K441" s="18" t="n"/>
-      <c r="L441" s="18" t="n"/>
-      <c r="M441" s="18" t="n"/>
+      <c r="E441" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F441" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G441" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H441" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I441" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J441" s="18" t="inlineStr">
+        <is>
+          <t>APTEL (Appellate Tribunal for Electricity). Statutory body. Staff on deputation.</t>
+        </is>
+      </c>
+      <c r="K441" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L441" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M441" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="15.75" customHeight="1" s="16">
       <c r="A442" s="4">
@@ -25991,15 +27555,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E442" s="18" t="n"/>
-      <c r="F442" s="18" t="n"/>
-      <c r="G442" s="18" t="n"/>
-      <c r="H442" s="18" t="n"/>
-      <c r="I442" s="18" t="n"/>
-      <c r="J442" s="18" t="n"/>
-      <c r="K442" s="18" t="n"/>
-      <c r="L442" s="18" t="n"/>
-      <c r="M442" s="18" t="n"/>
+      <c r="E442" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cpri.res.in/</t>
+        </is>
+      </c>
+      <c r="F442" s="17" t="inlineStr">
+        <is>
+          <t>https://www.cpri.res.in/</t>
+        </is>
+      </c>
+      <c r="G442" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H442" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I442" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J442" s="18" t="inlineStr">
+        <is>
+          <t>CPRI official site verified live. Autonomous body under Ministry of Power.</t>
+        </is>
+      </c>
+      <c r="K442" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L442" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M442" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="443" ht="15.75" customHeight="1" s="16">
       <c r="A443" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -27619,15 +27619,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E443" s="18" t="n"/>
-      <c r="F443" s="18" t="n"/>
-      <c r="G443" s="18" t="n"/>
-      <c r="H443" s="18" t="n"/>
-      <c r="I443" s="18" t="n"/>
-      <c r="J443" s="18" t="n"/>
-      <c r="K443" s="18" t="n"/>
-      <c r="L443" s="18" t="n"/>
-      <c r="M443" s="18" t="n"/>
+      <c r="E443" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F443" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G443" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H443" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I443" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J443" s="18" t="inlineStr">
+        <is>
+          <t>NTPC Ltd is a PSU recruiting independently at ntpc.co.in. Policy/admin entry.</t>
+        </is>
+      </c>
+      <c r="K443" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L443" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M443" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="444" ht="15.75" customHeight="1" s="16">
       <c r="A444" s="4">
@@ -27649,15 +27683,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E444" s="18" t="n"/>
-      <c r="F444" s="18" t="n"/>
-      <c r="G444" s="18" t="n"/>
-      <c r="H444" s="18" t="n"/>
-      <c r="I444" s="18" t="n"/>
-      <c r="J444" s="18" t="n"/>
-      <c r="K444" s="18" t="n"/>
-      <c r="L444" s="18" t="n"/>
-      <c r="M444" s="18" t="n"/>
+      <c r="E444" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F444" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G444" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H444" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I444" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J444" s="18" t="inlineStr">
+        <is>
+          <t>PGCIL is a PSU recruiting independently at powergrid.in. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K444" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L444" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M444" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="445" ht="15.75" customHeight="1" s="16">
       <c r="A445" s="4">
@@ -27679,15 +27747,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E445" s="18" t="n"/>
-      <c r="F445" s="18" t="n"/>
-      <c r="G445" s="18" t="n"/>
-      <c r="H445" s="18" t="n"/>
-      <c r="I445" s="18" t="n"/>
-      <c r="J445" s="18" t="n"/>
-      <c r="K445" s="18" t="n"/>
-      <c r="L445" s="18" t="n"/>
-      <c r="M445" s="18" t="n"/>
+      <c r="E445" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F445" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G445" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H445" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I445" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J445" s="18" t="inlineStr">
+        <is>
+          <t>REC Ltd is a PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K445" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L445" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M445" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="446" ht="15.75" customHeight="1" s="16">
       <c r="A446" s="4">
@@ -27709,15 +27811,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E446" s="18" t="n"/>
-      <c r="F446" s="18" t="n"/>
-      <c r="G446" s="18" t="n"/>
-      <c r="H446" s="18" t="n"/>
-      <c r="I446" s="18" t="n"/>
-      <c r="J446" s="18" t="n"/>
-      <c r="K446" s="18" t="n"/>
-      <c r="L446" s="18" t="n"/>
-      <c r="M446" s="18" t="n"/>
+      <c r="E446" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F446" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G446" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H446" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I446" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J446" s="18" t="inlineStr">
+        <is>
+          <t>PFC is a PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K446" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L446" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M446" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="447" ht="15.75" customHeight="1" s="16">
       <c r="A447" s="4">
@@ -27769,15 +27905,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E448" s="18" t="n"/>
-      <c r="F448" s="18" t="n"/>
-      <c r="G448" s="18" t="n"/>
-      <c r="H448" s="18" t="n"/>
-      <c r="I448" s="18" t="n"/>
-      <c r="J448" s="18" t="n"/>
-      <c r="K448" s="18" t="n"/>
-      <c r="L448" s="18" t="n"/>
-      <c r="M448" s="18" t="n"/>
+      <c r="E448" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F448" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G448" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H448" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I448" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J448" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board site. Confirmed official domain. Recruitment via RRBs/RRCs.</t>
+        </is>
+      </c>
+      <c r="K448" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L448" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M448" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="449" ht="15.75" customHeight="1" s="16">
       <c r="A449" s="4">
@@ -27799,15 +27969,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E449" s="18" t="n"/>
-      <c r="F449" s="18" t="n"/>
-      <c r="G449" s="18" t="n"/>
-      <c r="H449" s="18" t="n"/>
-      <c r="I449" s="18" t="n"/>
-      <c r="J449" s="18" t="n"/>
-      <c r="K449" s="18" t="n"/>
-      <c r="L449" s="18" t="n"/>
-      <c r="M449" s="18" t="n"/>
+      <c r="E449" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F449" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G449" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H449" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I449" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J449" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Infrastructure Directorate. No separate site.</t>
+        </is>
+      </c>
+      <c r="K449" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L449" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M449" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="450" ht="15.75" customHeight="1" s="16">
       <c r="A450" s="4">
@@ -27829,15 +28033,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E450" s="18" t="n"/>
-      <c r="F450" s="18" t="n"/>
-      <c r="G450" s="18" t="n"/>
-      <c r="H450" s="18" t="n"/>
-      <c r="I450" s="18" t="n"/>
-      <c r="J450" s="18" t="n"/>
-      <c r="K450" s="18" t="n"/>
-      <c r="L450" s="18" t="n"/>
-      <c r="M450" s="18" t="n"/>
+      <c r="E450" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F450" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G450" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H450" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I450" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J450" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Traffic Directorate.</t>
+        </is>
+      </c>
+      <c r="K450" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L450" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M450" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="15.75" customHeight="1" s="16">
       <c r="A451" s="4">
@@ -27859,15 +28097,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E451" s="18" t="n"/>
-      <c r="F451" s="18" t="n"/>
-      <c r="G451" s="18" t="n"/>
-      <c r="H451" s="18" t="n"/>
-      <c r="I451" s="18" t="n"/>
-      <c r="J451" s="18" t="n"/>
-      <c r="K451" s="18" t="n"/>
-      <c r="L451" s="18" t="n"/>
-      <c r="M451" s="18" t="n"/>
+      <c r="E451" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F451" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G451" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H451" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I451" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J451" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Mechanical Directorate.</t>
+        </is>
+      </c>
+      <c r="K451" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L451" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M451" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="452" ht="15.75" customHeight="1" s="16">
       <c r="A452" s="4">
@@ -27889,15 +28161,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E452" s="18" t="n"/>
-      <c r="F452" s="18" t="n"/>
-      <c r="G452" s="18" t="n"/>
-      <c r="H452" s="18" t="n"/>
-      <c r="I452" s="18" t="n"/>
-      <c r="J452" s="18" t="n"/>
-      <c r="K452" s="18" t="n"/>
-      <c r="L452" s="18" t="n"/>
-      <c r="M452" s="18" t="n"/>
+      <c r="E452" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F452" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G452" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H452" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I452" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J452" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Electrical Directorate.</t>
+        </is>
+      </c>
+      <c r="K452" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L452" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M452" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="453" ht="15.75" customHeight="1" s="16">
       <c r="A453" s="4">
@@ -27919,15 +28225,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E453" s="18" t="n"/>
-      <c r="F453" s="18" t="n"/>
-      <c r="G453" s="18" t="n"/>
-      <c r="H453" s="18" t="n"/>
-      <c r="I453" s="18" t="n"/>
-      <c r="J453" s="18" t="n"/>
-      <c r="K453" s="18" t="n"/>
-      <c r="L453" s="18" t="n"/>
-      <c r="M453" s="18" t="n"/>
+      <c r="E453" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F453" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G453" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H453" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I453" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J453" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Finance Directorate.</t>
+        </is>
+      </c>
+      <c r="K453" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L453" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M453" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="454" ht="15.75" customHeight="1" s="16">
       <c r="A454" s="4">
@@ -27949,15 +28289,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E454" s="18" t="n"/>
-      <c r="F454" s="18" t="n"/>
-      <c r="G454" s="18" t="n"/>
-      <c r="H454" s="18" t="n"/>
-      <c r="I454" s="18" t="n"/>
-      <c r="J454" s="18" t="n"/>
-      <c r="K454" s="18" t="n"/>
-      <c r="L454" s="18" t="n"/>
-      <c r="M454" s="18" t="n"/>
+      <c r="E454" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F454" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G454" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H454" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I454" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J454" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Personnel Directorate.</t>
+        </is>
+      </c>
+      <c r="K454" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L454" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M454" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="455" ht="15.75" customHeight="1" s="16">
       <c r="A455" s="4">
@@ -27979,15 +28353,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E455" s="18" t="n"/>
-      <c r="F455" s="18" t="n"/>
-      <c r="G455" s="18" t="n"/>
-      <c r="H455" s="18" t="n"/>
-      <c r="I455" s="18" t="n"/>
-      <c r="J455" s="18" t="n"/>
-      <c r="K455" s="18" t="n"/>
-      <c r="L455" s="18" t="n"/>
-      <c r="M455" s="18" t="n"/>
+      <c r="E455" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F455" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G455" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H455" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I455" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J455" s="18" t="inlineStr">
+        <is>
+          <t>Railway Board Safety Directorate.</t>
+        </is>
+      </c>
+      <c r="K455" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L455" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M455" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="456" ht="15.75" customHeight="1" s="16">
       <c r="A456" s="4">
@@ -28009,15 +28417,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E456" s="18" t="n"/>
-      <c r="F456" s="18" t="n"/>
-      <c r="G456" s="18" t="n"/>
-      <c r="H456" s="18" t="n"/>
-      <c r="I456" s="18" t="n"/>
-      <c r="J456" s="18" t="n"/>
-      <c r="K456" s="18" t="n"/>
-      <c r="L456" s="18" t="n"/>
-      <c r="M456" s="18" t="n"/>
+      <c r="E456" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F456" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G456" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H456" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I456" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J456" s="18" t="inlineStr">
+        <is>
+          <t>Zonal Railways recruit through RRBs. Subordinate to Railway Board.</t>
+        </is>
+      </c>
+      <c r="K456" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L456" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M456" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="457" ht="15.75" customHeight="1" s="16">
       <c r="A457" s="4">
@@ -28039,15 +28481,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E457" s="18" t="n"/>
-      <c r="F457" s="18" t="n"/>
-      <c r="G457" s="18" t="n"/>
-      <c r="H457" s="18" t="n"/>
-      <c r="I457" s="18" t="n"/>
-      <c r="J457" s="18" t="n"/>
-      <c r="K457" s="18" t="n"/>
-      <c r="L457" s="18" t="n"/>
-      <c r="M457" s="18" t="n"/>
+      <c r="E457" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F457" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G457" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H457" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I457" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J457" s="18" t="inlineStr">
+        <is>
+          <t>Divisional Railway Offices recruit via RRCs and RRBs.</t>
+        </is>
+      </c>
+      <c r="K457" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L457" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M457" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="458" ht="15.75" customHeight="1" s="16">
       <c r="A458" s="4">
@@ -28069,15 +28545,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E458" s="18" t="n"/>
-      <c r="F458" s="18" t="n"/>
-      <c r="G458" s="18" t="n"/>
-      <c r="H458" s="18" t="n"/>
-      <c r="I458" s="18" t="n"/>
-      <c r="J458" s="18" t="n"/>
-      <c r="K458" s="18" t="n"/>
-      <c r="L458" s="18" t="n"/>
-      <c r="M458" s="18" t="n"/>
+      <c r="E458" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F458" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G458" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H458" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I458" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J458" s="18" t="inlineStr">
+        <is>
+          <t>Production Units (CLW/ICF/DLW/RCF/MCF) recruit via RRBs/RRCs.</t>
+        </is>
+      </c>
+      <c r="K458" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L458" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M458" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="459" ht="15.75" customHeight="1" s="16">
       <c r="A459" s="4">
@@ -28099,15 +28609,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E459" s="18" t="n"/>
-      <c r="F459" s="18" t="n"/>
-      <c r="G459" s="18" t="n"/>
-      <c r="H459" s="18" t="n"/>
-      <c r="I459" s="18" t="n"/>
-      <c r="J459" s="18" t="n"/>
-      <c r="K459" s="18" t="n"/>
-      <c r="L459" s="18" t="n"/>
-      <c r="M459" s="18" t="n"/>
+      <c r="E459" s="17" t="inlineStr">
+        <is>
+          <t>https://rrbapply.gov.in/</t>
+        </is>
+      </c>
+      <c r="F459" s="17" t="inlineStr">
+        <is>
+          <t>https://rrbapply.gov.in/</t>
+        </is>
+      </c>
+      <c r="G459" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H459" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I459" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J459" s="18" t="inlineStr">
+        <is>
+          <t>Railway Recruitment Boards - the primary recruitment agency for railways. Active 2026 recruitment. Site uses rrbapply.gov.in for online applications.</t>
+        </is>
+      </c>
+      <c r="K459" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L459" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M459" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="460" ht="15.75" customHeight="1" s="16">
       <c r="A460" s="4">
@@ -28129,15 +28673,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E460" s="18" t="n"/>
-      <c r="F460" s="18" t="n"/>
-      <c r="G460" s="18" t="n"/>
-      <c r="H460" s="18" t="n"/>
-      <c r="I460" s="18" t="n"/>
-      <c r="J460" s="18" t="n"/>
-      <c r="K460" s="18" t="n"/>
-      <c r="L460" s="18" t="n"/>
-      <c r="M460" s="18" t="n"/>
+      <c r="E460" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F460" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G460" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H460" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I460" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J460" s="18" t="inlineStr">
+        <is>
+          <t>Railway Training Institutes subordinate to Railway Board.</t>
+        </is>
+      </c>
+      <c r="K460" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L460" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M460" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="461" ht="15.75" customHeight="1" s="16">
       <c r="A461" s="4">
@@ -28159,15 +28737,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E461" s="18" t="n"/>
-      <c r="F461" s="18" t="n"/>
-      <c r="G461" s="18" t="n"/>
-      <c r="H461" s="18" t="n"/>
-      <c r="I461" s="18" t="n"/>
-      <c r="J461" s="18" t="n"/>
-      <c r="K461" s="18" t="n"/>
-      <c r="L461" s="18" t="n"/>
-      <c r="M461" s="18" t="n"/>
+      <c r="E461" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F461" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G461" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H461" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I461" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J461" s="18" t="inlineStr">
+        <is>
+          <t>NRTI (National Rail &amp; Transportation Institute, now GISMA?). Autonomous body.</t>
+        </is>
+      </c>
+      <c r="K461" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L461" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M461" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="462" ht="15.75" customHeight="1" s="16">
       <c r="A462" s="4">
@@ -28189,15 +28801,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E462" s="18" t="n"/>
-      <c r="F462" s="18" t="n"/>
-      <c r="G462" s="18" t="n"/>
-      <c r="H462" s="18" t="n"/>
-      <c r="I462" s="18" t="n"/>
-      <c r="J462" s="18" t="n"/>
-      <c r="K462" s="18" t="n"/>
-      <c r="L462" s="18" t="n"/>
-      <c r="M462" s="18" t="n"/>
+      <c r="E462" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F462" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G462" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H462" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I462" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J462" s="18" t="inlineStr">
+        <is>
+          <t>IRITM - Railway Institute of Transport Management.</t>
+        </is>
+      </c>
+      <c r="K462" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L462" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M462" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="463" ht="15.75" customHeight="1" s="16">
       <c r="A463" s="4">
@@ -28219,15 +28865,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E463" s="18" t="n"/>
-      <c r="F463" s="18" t="n"/>
-      <c r="G463" s="18" t="n"/>
-      <c r="H463" s="18" t="n"/>
-      <c r="I463" s="18" t="n"/>
-      <c r="J463" s="18" t="n"/>
-      <c r="K463" s="18" t="n"/>
-      <c r="L463" s="18" t="n"/>
-      <c r="M463" s="18" t="n"/>
+      <c r="E463" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F463" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G463" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H463" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I463" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J463" s="18" t="inlineStr">
+        <is>
+          <t>IRCON is a PSU recruiting independently at ircon.org. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K463" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L463" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M463" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="464" ht="15.75" customHeight="1" s="16">
       <c r="A464" s="4">
@@ -28249,15 +28929,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E464" s="18" t="n"/>
-      <c r="F464" s="18" t="n"/>
-      <c r="G464" s="18" t="n"/>
-      <c r="H464" s="18" t="n"/>
-      <c r="I464" s="18" t="n"/>
-      <c r="J464" s="18" t="n"/>
-      <c r="K464" s="18" t="n"/>
-      <c r="L464" s="18" t="n"/>
-      <c r="M464" s="18" t="n"/>
+      <c r="E464" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F464" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G464" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H464" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I464" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J464" s="18" t="inlineStr">
+        <is>
+          <t>RITES is a PSU recruiting independently at rites.com. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K464" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L464" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M464" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="465" ht="15.75" customHeight="1" s="16">
       <c r="A465" s="4">
@@ -28279,15 +28993,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E465" s="18" t="n"/>
-      <c r="F465" s="18" t="n"/>
-      <c r="G465" s="18" t="n"/>
-      <c r="H465" s="18" t="n"/>
-      <c r="I465" s="18" t="n"/>
-      <c r="J465" s="18" t="n"/>
-      <c r="K465" s="18" t="n"/>
-      <c r="L465" s="18" t="n"/>
-      <c r="M465" s="18" t="n"/>
+      <c r="E465" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F465" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G465" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H465" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I465" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J465" s="18" t="inlineStr">
+        <is>
+          <t>RVNL is a PSU recruiting independently. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K465" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L465" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M465" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="466" ht="15.75" customHeight="1" s="16">
       <c r="A466" s="4">
@@ -28309,15 +29057,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E466" s="18" t="n"/>
-      <c r="F466" s="18" t="n"/>
-      <c r="G466" s="18" t="n"/>
-      <c r="H466" s="18" t="n"/>
-      <c r="I466" s="18" t="n"/>
-      <c r="J466" s="18" t="n"/>
-      <c r="K466" s="18" t="n"/>
-      <c r="L466" s="18" t="n"/>
-      <c r="M466" s="18" t="n"/>
+      <c r="E466" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F466" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G466" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H466" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I466" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J466" s="18" t="inlineStr">
+        <is>
+          <t>IRCTC is a PSU recruiting independently at irctc.com. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K466" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L466" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M466" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="467" ht="15.75" customHeight="1" s="16">
       <c r="A467" s="4">
@@ -28339,15 +29121,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E467" s="18" t="n"/>
-      <c r="F467" s="18" t="n"/>
-      <c r="G467" s="18" t="n"/>
-      <c r="H467" s="18" t="n"/>
-      <c r="I467" s="18" t="n"/>
-      <c r="J467" s="18" t="n"/>
-      <c r="K467" s="18" t="n"/>
-      <c r="L467" s="18" t="n"/>
-      <c r="M467" s="18" t="n"/>
+      <c r="E467" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F467" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G467" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H467" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I467" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J467" s="18" t="inlineStr">
+        <is>
+          <t>CONCOR is a PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K467" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L467" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M467" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="468" ht="15.75" customHeight="1" s="16">
       <c r="A468" s="4">
@@ -28399,15 +29215,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E469" s="18" t="n"/>
-      <c r="F469" s="18" t="n"/>
-      <c r="G469" s="18" t="n"/>
-      <c r="H469" s="18" t="n"/>
-      <c r="I469" s="18" t="n"/>
-      <c r="J469" s="18" t="n"/>
-      <c r="K469" s="18" t="n"/>
-      <c r="L469" s="18" t="n"/>
-      <c r="M469" s="18" t="n"/>
+      <c r="E469" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F469" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G469" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H469" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I469" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J469" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Road Transport &amp; Highways site verified live.</t>
+        </is>
+      </c>
+      <c r="K469" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L469" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M469" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="470" ht="15.75" customHeight="1" s="16">
       <c r="A470" s="4">
@@ -28429,15 +29279,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E470" s="18" t="n"/>
-      <c r="F470" s="18" t="n"/>
-      <c r="G470" s="18" t="n"/>
-      <c r="H470" s="18" t="n"/>
-      <c r="I470" s="18" t="n"/>
-      <c r="J470" s="18" t="n"/>
-      <c r="K470" s="18" t="n"/>
-      <c r="L470" s="18" t="n"/>
-      <c r="M470" s="18" t="n"/>
+      <c r="E470" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F470" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G470" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H470" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I470" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J470" s="18" t="inlineStr">
+        <is>
+          <t>Roads Wing within Ministry.</t>
+        </is>
+      </c>
+      <c r="K470" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L470" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M470" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="471" ht="15.75" customHeight="1" s="16">
       <c r="A471" s="4">
@@ -28459,15 +29343,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E471" s="18" t="n"/>
-      <c r="F471" s="18" t="n"/>
-      <c r="G471" s="18" t="n"/>
-      <c r="H471" s="18" t="n"/>
-      <c r="I471" s="18" t="n"/>
-      <c r="J471" s="18" t="n"/>
-      <c r="K471" s="18" t="n"/>
-      <c r="L471" s="18" t="n"/>
-      <c r="M471" s="18" t="n"/>
+      <c r="E471" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F471" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G471" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H471" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I471" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J471" s="18" t="inlineStr">
+        <is>
+          <t>Transport Wing within Ministry.</t>
+        </is>
+      </c>
+      <c r="K471" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L471" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M471" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="472" ht="15.75" customHeight="1" s="16">
       <c r="A472" s="4">
@@ -28489,15 +29407,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E472" s="18" t="n"/>
-      <c r="F472" s="18" t="n"/>
-      <c r="G472" s="18" t="n"/>
-      <c r="H472" s="18" t="n"/>
-      <c r="I472" s="18" t="n"/>
-      <c r="J472" s="18" t="n"/>
-      <c r="K472" s="18" t="n"/>
-      <c r="L472" s="18" t="n"/>
-      <c r="M472" s="18" t="n"/>
+      <c r="E472" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F472" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G472" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H472" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I472" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J472" s="18" t="inlineStr">
+        <is>
+          <t>Standards, Research &amp; QC Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K472" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L472" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M472" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="473" ht="15.75" customHeight="1" s="16">
       <c r="A473" s="4">
@@ -28519,15 +29471,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E473" s="18" t="n"/>
-      <c r="F473" s="18" t="n"/>
-      <c r="G473" s="18" t="n"/>
-      <c r="H473" s="18" t="n"/>
-      <c r="I473" s="18" t="n"/>
-      <c r="J473" s="18" t="n"/>
-      <c r="K473" s="18" t="n"/>
-      <c r="L473" s="18" t="n"/>
-      <c r="M473" s="18" t="n"/>
+      <c r="E473" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F473" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G473" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H473" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I473" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J473" s="18" t="inlineStr">
+        <is>
+          <t>IAHE (Indian Academy of Highway Engineers) under MoRTH.</t>
+        </is>
+      </c>
+      <c r="K473" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L473" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M473" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="474" ht="15.75" customHeight="1" s="16">
       <c r="A474" s="4">
@@ -28549,15 +29535,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E474" s="18" t="n"/>
-      <c r="F474" s="18" t="n"/>
-      <c r="G474" s="18" t="n"/>
-      <c r="H474" s="18" t="n"/>
-      <c r="I474" s="18" t="n"/>
-      <c r="J474" s="18" t="n"/>
-      <c r="K474" s="18" t="n"/>
-      <c r="L474" s="18" t="n"/>
-      <c r="M474" s="18" t="n"/>
+      <c r="E474" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F474" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G474" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H474" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I474" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J474" s="18" t="inlineStr">
+        <is>
+          <t>Regional Offices of MoRTH subordinate.</t>
+        </is>
+      </c>
+      <c r="K474" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L474" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M474" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="475" ht="15.75" customHeight="1" s="16">
       <c r="A475" s="4">
@@ -28579,15 +29599,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E475" s="18" t="n"/>
-      <c r="F475" s="18" t="n"/>
-      <c r="G475" s="18" t="n"/>
-      <c r="H475" s="18" t="n"/>
-      <c r="I475" s="18" t="n"/>
-      <c r="J475" s="18" t="n"/>
-      <c r="K475" s="18" t="n"/>
-      <c r="L475" s="18" t="n"/>
-      <c r="M475" s="18" t="n"/>
+      <c r="E475" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F475" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G475" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H475" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I475" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J475" s="18" t="inlineStr">
+        <is>
+          <t>RTOs - Central Coordination. RTOs are state-level bodies.</t>
+        </is>
+      </c>
+      <c r="K475" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L475" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M475" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="16">
       <c r="A476" s="4">
@@ -28609,15 +29663,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E476" s="18" t="n"/>
-      <c r="F476" s="18" t="n"/>
-      <c r="G476" s="18" t="n"/>
-      <c r="H476" s="18" t="n"/>
-      <c r="I476" s="18" t="n"/>
-      <c r="J476" s="18" t="n"/>
-      <c r="K476" s="18" t="n"/>
-      <c r="L476" s="18" t="n"/>
-      <c r="M476" s="18" t="n"/>
+      <c r="E476" s="17" t="inlineStr">
+        <is>
+          <t>https://nhai.gov.in/</t>
+        </is>
+      </c>
+      <c r="F476" s="17" t="inlineStr">
+        <is>
+          <t>https://nhai.gov.in/</t>
+        </is>
+      </c>
+      <c r="G476" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H476" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I476" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J476" s="18" t="inlineStr">
+        <is>
+          <t>NHAI site verified live. Statutory body under MoRTH. Major recruitment.</t>
+        </is>
+      </c>
+      <c r="K476" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L476" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M476" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="477" ht="15.75" customHeight="1" s="16">
       <c r="A477" s="4">
@@ -28639,15 +29727,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E477" s="18" t="n"/>
-      <c r="F477" s="18" t="n"/>
-      <c r="G477" s="18" t="n"/>
-      <c r="H477" s="18" t="n"/>
-      <c r="I477" s="18" t="n"/>
-      <c r="J477" s="18" t="n"/>
-      <c r="K477" s="18" t="n"/>
-      <c r="L477" s="18" t="n"/>
-      <c r="M477" s="18" t="n"/>
+      <c r="E477" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F477" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G477" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H477" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I477" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J477" s="18" t="inlineStr">
+        <is>
+          <t>NRSA (National Road Safety Authority) - newly formed. No independent site yet.</t>
+        </is>
+      </c>
+      <c r="K477" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L477" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M477" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="478" ht="15.75" customHeight="1" s="16">
       <c r="A478" s="4">
@@ -28669,15 +29791,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E478" s="18" t="n"/>
-      <c r="F478" s="18" t="n"/>
-      <c r="G478" s="18" t="n"/>
-      <c r="H478" s="18" t="n"/>
-      <c r="I478" s="18" t="n"/>
-      <c r="J478" s="18" t="n"/>
-      <c r="K478" s="18" t="n"/>
-      <c r="L478" s="18" t="n"/>
-      <c r="M478" s="18" t="n"/>
+      <c r="E478" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F478" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G478" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H478" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I478" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J478" s="18" t="inlineStr">
+        <is>
+          <t>NITHE training institute under MoRTH.</t>
+        </is>
+      </c>
+      <c r="K478" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L478" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M478" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="479" ht="15.75" customHeight="1" s="16">
       <c r="A479" s="4">
@@ -28729,15 +29885,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E480" s="18" t="n"/>
-      <c r="F480" s="18" t="n"/>
-      <c r="G480" s="18" t="n"/>
-      <c r="H480" s="18" t="n"/>
-      <c r="I480" s="18" t="n"/>
-      <c r="J480" s="18" t="n"/>
-      <c r="K480" s="18" t="n"/>
-      <c r="L480" s="18" t="n"/>
-      <c r="M480" s="18" t="n"/>
+      <c r="E480" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F480" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G480" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H480" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I480" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J480" s="18" t="inlineStr">
+        <is>
+          <t>Department of Science &amp; Technology site verified live.</t>
+        </is>
+      </c>
+      <c r="K480" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L480" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M480" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="481" ht="15.75" customHeight="1" s="16">
       <c r="A481" s="4">
@@ -28759,15 +29949,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E481" s="18" t="n"/>
-      <c r="F481" s="18" t="n"/>
-      <c r="G481" s="18" t="n"/>
-      <c r="H481" s="18" t="n"/>
-      <c r="I481" s="18" t="n"/>
-      <c r="J481" s="18" t="n"/>
-      <c r="K481" s="18" t="n"/>
-      <c r="L481" s="18" t="n"/>
-      <c r="M481" s="18" t="n"/>
+      <c r="E481" s="17" t="inlineStr">
+        <is>
+          <t>https://dbtindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F481" s="17" t="inlineStr">
+        <is>
+          <t>https://dbtindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G481" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H481" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I481" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J481" s="18" t="inlineStr">
+        <is>
+          <t>Dept of Biotechnology site verified live.</t>
+        </is>
+      </c>
+      <c r="K481" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L481" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M481" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="482" ht="15.75" customHeight="1" s="16">
       <c r="A482" s="4">
@@ -28789,15 +30013,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E482" s="18" t="n"/>
-      <c r="F482" s="18" t="n"/>
-      <c r="G482" s="18" t="n"/>
-      <c r="H482" s="18" t="n"/>
-      <c r="I482" s="18" t="n"/>
-      <c r="J482" s="18" t="n"/>
-      <c r="K482" s="18" t="n"/>
-      <c r="L482" s="18" t="n"/>
-      <c r="M482" s="18" t="n"/>
+      <c r="E482" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F482" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G482" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H482" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I482" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J482" s="18" t="inlineStr">
+        <is>
+          <t>DSIR under DST. Shares DST portal.</t>
+        </is>
+      </c>
+      <c r="K482" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L482" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M482" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="483" ht="15.75" customHeight="1" s="16">
       <c r="A483" s="4">
@@ -28819,15 +30077,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E483" s="18" t="n"/>
-      <c r="F483" s="18" t="n"/>
-      <c r="G483" s="18" t="n"/>
-      <c r="H483" s="18" t="n"/>
-      <c r="I483" s="18" t="n"/>
-      <c r="J483" s="18" t="n"/>
-      <c r="K483" s="18" t="n"/>
-      <c r="L483" s="18" t="n"/>
-      <c r="M483" s="18" t="n"/>
+      <c r="E483" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F483" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G483" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H483" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I483" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J483" s="18" t="inlineStr">
+        <is>
+          <t>Office of PSA. No separate recruitment portal.</t>
+        </is>
+      </c>
+      <c r="K483" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L483" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M483" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="484" ht="15.75" customHeight="1" s="16">
       <c r="A484" s="4">
@@ -28849,15 +30141,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E484" s="18" t="n"/>
-      <c r="F484" s="18" t="n"/>
-      <c r="G484" s="18" t="n"/>
-      <c r="H484" s="18" t="n"/>
-      <c r="I484" s="18" t="n"/>
-      <c r="J484" s="18" t="n"/>
-      <c r="K484" s="18" t="n"/>
-      <c r="L484" s="18" t="n"/>
-      <c r="M484" s="18" t="n"/>
+      <c r="E484" s="17" t="inlineStr">
+        <is>
+          <t>https://www.csir.res.in/</t>
+        </is>
+      </c>
+      <c r="F484" s="17" t="inlineStr">
+        <is>
+          <t>https://www.csir.res.in/</t>
+        </is>
+      </c>
+      <c r="G484" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H484" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I484" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J484" s="18" t="inlineStr">
+        <is>
+          <t>CSIR site verified live. Major research organisation. Recruitment through CSIR-NET/ASRB.</t>
+        </is>
+      </c>
+      <c r="K484" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L484" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M484" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="485" ht="15.75" customHeight="1" s="16">
       <c r="A485" s="4">
@@ -28879,15 +30205,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E485" s="18" t="n"/>
-      <c r="F485" s="18" t="n"/>
-      <c r="G485" s="18" t="n"/>
-      <c r="H485" s="18" t="n"/>
-      <c r="I485" s="18" t="n"/>
-      <c r="J485" s="18" t="n"/>
-      <c r="K485" s="18" t="n"/>
-      <c r="L485" s="18" t="n"/>
-      <c r="M485" s="18" t="n"/>
+      <c r="E485" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F485" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G485" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H485" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I485" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J485" s="18" t="inlineStr">
+        <is>
+          <t>DST Autonomous Institutions (IISERs, IIAs, etc.) recruit independently. Parent DST page as reference.</t>
+        </is>
+      </c>
+      <c r="K485" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L485" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M485" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="486" ht="15.75" customHeight="1" s="16">
       <c r="A486" s="4">
@@ -28909,15 +30269,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E486" s="18" t="n"/>
-      <c r="F486" s="18" t="n"/>
-      <c r="G486" s="18" t="n"/>
-      <c r="H486" s="18" t="n"/>
-      <c r="I486" s="18" t="n"/>
-      <c r="J486" s="18" t="n"/>
-      <c r="K486" s="18" t="n"/>
-      <c r="L486" s="18" t="n"/>
-      <c r="M486" s="18" t="n"/>
+      <c r="E486" s="17" t="inlineStr">
+        <is>
+          <t>https://dbtindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="F486" s="17" t="inlineStr">
+        <is>
+          <t>https://dbtindia.gov.in/</t>
+        </is>
+      </c>
+      <c r="G486" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H486" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I486" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J486" s="18" t="inlineStr">
+        <is>
+          <t>BIRAC under DBT. Autonomous body.</t>
+        </is>
+      </c>
+      <c r="K486" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L486" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M486" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="487" ht="15.75" customHeight="1" s="16">
       <c r="A487" s="4">
@@ -28939,15 +30333,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E487" s="18" t="n"/>
-      <c r="F487" s="18" t="n"/>
-      <c r="G487" s="18" t="n"/>
-      <c r="H487" s="18" t="n"/>
-      <c r="I487" s="18" t="n"/>
-      <c r="J487" s="18" t="n"/>
-      <c r="K487" s="18" t="n"/>
-      <c r="L487" s="18" t="n"/>
-      <c r="M487" s="18" t="n"/>
+      <c r="E487" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F487" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G487" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H487" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I487" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J487" s="18" t="inlineStr">
+        <is>
+          <t>Technology Development Board subordinate to DST.</t>
+        </is>
+      </c>
+      <c r="K487" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L487" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M487" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="488" ht="15.75" customHeight="1" s="16">
       <c r="A488" s="4">
@@ -28969,15 +30397,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E488" s="18" t="n"/>
-      <c r="F488" s="18" t="n"/>
-      <c r="G488" s="18" t="n"/>
-      <c r="H488" s="18" t="n"/>
-      <c r="I488" s="18" t="n"/>
-      <c r="J488" s="18" t="n"/>
-      <c r="K488" s="18" t="n"/>
-      <c r="L488" s="18" t="n"/>
-      <c r="M488" s="18" t="n"/>
+      <c r="E488" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F488" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G488" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H488" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I488" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J488" s="18" t="inlineStr">
+        <is>
+          <t>DST/DBT Programme Management Units. No separate site.</t>
+        </is>
+      </c>
+      <c r="K488" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L488" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M488" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="489" ht="15.75" customHeight="1" s="16">
       <c r="A489" s="4">
@@ -28999,15 +30461,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E489" s="18" t="n"/>
-      <c r="F489" s="18" t="n"/>
-      <c r="G489" s="18" t="n"/>
-      <c r="H489" s="18" t="n"/>
-      <c r="I489" s="18" t="n"/>
-      <c r="J489" s="18" t="n"/>
-      <c r="K489" s="18" t="n"/>
-      <c r="L489" s="18" t="n"/>
-      <c r="M489" s="18" t="n"/>
+      <c r="E489" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F489" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G489" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H489" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I489" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J489" s="18" t="inlineStr">
+        <is>
+          <t>NSTEDB under DST. Statutory body.</t>
+        </is>
+      </c>
+      <c r="K489" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L489" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M489" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="490" ht="15.75" customHeight="1" s="16">
       <c r="A490" s="4">
@@ -29059,15 +30555,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E491" s="18" t="n"/>
-      <c r="F491" s="18" t="n"/>
-      <c r="G491" s="18" t="n"/>
-      <c r="H491" s="18" t="n"/>
-      <c r="I491" s="18" t="n"/>
-      <c r="J491" s="18" t="n"/>
-      <c r="K491" s="18" t="n"/>
-      <c r="L491" s="18" t="n"/>
-      <c r="M491" s="18" t="n"/>
+      <c r="E491" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F491" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G491" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H491" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I491" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J491" s="18" t="inlineStr">
+        <is>
+          <t>MSDE Secretariat site verified live.</t>
+        </is>
+      </c>
+      <c r="K491" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L491" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M491" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="492" ht="15.75" customHeight="1" s="16">
       <c r="A492" s="4">
@@ -29089,15 +30619,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E492" s="18" t="n"/>
-      <c r="F492" s="18" t="n"/>
-      <c r="G492" s="18" t="n"/>
-      <c r="H492" s="18" t="n"/>
-      <c r="I492" s="18" t="n"/>
-      <c r="J492" s="18" t="n"/>
-      <c r="K492" s="18" t="n"/>
-      <c r="L492" s="18" t="n"/>
-      <c r="M492" s="18" t="n"/>
+      <c r="E492" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F492" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G492" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H492" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I492" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J492" s="18" t="inlineStr">
+        <is>
+          <t>Directorate General of Training (DGT) under MSDE. dget.gov.in unreachable but confirmed.</t>
+        </is>
+      </c>
+      <c r="K492" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L492" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M492" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="493" ht="15.75" customHeight="1" s="16">
       <c r="A493" s="4">
@@ -29119,15 +30683,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E493" s="18" t="n"/>
-      <c r="F493" s="18" t="n"/>
-      <c r="G493" s="18" t="n"/>
-      <c r="H493" s="18" t="n"/>
-      <c r="I493" s="18" t="n"/>
-      <c r="J493" s="18" t="n"/>
-      <c r="K493" s="18" t="n"/>
-      <c r="L493" s="18" t="n"/>
-      <c r="M493" s="18" t="n"/>
+      <c r="E493" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F493" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G493" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H493" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I493" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J493" s="18" t="inlineStr">
+        <is>
+          <t>Apprenticeship &amp; Training Division within MSDE.</t>
+        </is>
+      </c>
+      <c r="K493" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L493" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M493" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="494" ht="15.75" customHeight="1" s="16">
       <c r="A494" s="4">
@@ -29149,15 +30747,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E494" s="18" t="n"/>
-      <c r="F494" s="18" t="n"/>
-      <c r="G494" s="18" t="n"/>
-      <c r="H494" s="18" t="n"/>
-      <c r="I494" s="18" t="n"/>
-      <c r="J494" s="18" t="n"/>
-      <c r="K494" s="18" t="n"/>
-      <c r="L494" s="18" t="n"/>
-      <c r="M494" s="18" t="n"/>
+      <c r="E494" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F494" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G494" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H494" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I494" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J494" s="18" t="inlineStr">
+        <is>
+          <t>ITIs - Central Coordination. State-run institutions.</t>
+        </is>
+      </c>
+      <c r="K494" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L494" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M494" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="495" ht="15.75" customHeight="1" s="16">
       <c r="A495" s="4">
@@ -29179,15 +30811,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E495" s="18" t="n"/>
-      <c r="F495" s="18" t="n"/>
-      <c r="G495" s="18" t="n"/>
-      <c r="H495" s="18" t="n"/>
-      <c r="I495" s="18" t="n"/>
-      <c r="J495" s="18" t="n"/>
-      <c r="K495" s="18" t="n"/>
-      <c r="L495" s="18" t="n"/>
-      <c r="M495" s="18" t="n"/>
+      <c r="E495" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F495" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G495" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H495" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I495" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J495" s="18" t="inlineStr">
+        <is>
+          <t>NSTIs (National Skill Training Institutes) under DGT.</t>
+        </is>
+      </c>
+      <c r="K495" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L495" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M495" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="16">
       <c r="A496" s="4">
@@ -29209,15 +30875,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E496" s="18" t="n"/>
-      <c r="F496" s="18" t="n"/>
-      <c r="G496" s="18" t="n"/>
-      <c r="H496" s="18" t="n"/>
-      <c r="I496" s="18" t="n"/>
-      <c r="J496" s="18" t="n"/>
-      <c r="K496" s="18" t="n"/>
-      <c r="L496" s="18" t="n"/>
-      <c r="M496" s="18" t="n"/>
+      <c r="E496" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F496" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G496" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H496" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I496" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J496" s="18" t="inlineStr">
+        <is>
+          <t>Regional Directorates of MSDE.</t>
+        </is>
+      </c>
+      <c r="K496" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L496" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M496" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="497" ht="15.75" customHeight="1" s="16">
       <c r="A497" s="4">
@@ -29239,15 +30939,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E497" s="18" t="n"/>
-      <c r="F497" s="18" t="n"/>
-      <c r="G497" s="18" t="n"/>
-      <c r="H497" s="18" t="n"/>
-      <c r="I497" s="18" t="n"/>
-      <c r="J497" s="18" t="n"/>
-      <c r="K497" s="18" t="n"/>
-      <c r="L497" s="18" t="n"/>
-      <c r="M497" s="18" t="n"/>
+      <c r="E497" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nsdc.in/</t>
+        </is>
+      </c>
+      <c r="F497" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nsdc.in/</t>
+        </is>
+      </c>
+      <c r="G497" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H497" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I497" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J497" s="18" t="inlineStr">
+        <is>
+          <t>NSDC site unreachable from environment. Confirmed official domain. Autonomous body under MSDE.</t>
+        </is>
+      </c>
+      <c r="K497" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L497" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M497" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="498" ht="15.75" customHeight="1" s="16">
       <c r="A498" s="4">
@@ -29269,15 +31003,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E498" s="18" t="n"/>
-      <c r="F498" s="18" t="n"/>
-      <c r="G498" s="18" t="n"/>
-      <c r="H498" s="18" t="n"/>
-      <c r="I498" s="18" t="n"/>
-      <c r="J498" s="18" t="n"/>
-      <c r="K498" s="18" t="n"/>
-      <c r="L498" s="18" t="n"/>
-      <c r="M498" s="18" t="n"/>
+      <c r="E498" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F498" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G498" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H498" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I498" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J498" s="18" t="inlineStr">
+        <is>
+          <t>NCVET under MSDE. Autonomous body.</t>
+        </is>
+      </c>
+      <c r="K498" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L498" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M498" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="499" ht="15.75" customHeight="1" s="16">
       <c r="A499" s="4">
@@ -29299,15 +31067,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E499" s="18" t="n"/>
-      <c r="F499" s="18" t="n"/>
-      <c r="G499" s="18" t="n"/>
-      <c r="H499" s="18" t="n"/>
-      <c r="I499" s="18" t="n"/>
-      <c r="J499" s="18" t="n"/>
-      <c r="K499" s="18" t="n"/>
-      <c r="L499" s="18" t="n"/>
-      <c r="M499" s="18" t="n"/>
+      <c r="E499" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F499" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G499" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H499" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I499" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J499" s="18" t="inlineStr">
+        <is>
+          <t>NSDA under MSDE. Autonomous body.</t>
+        </is>
+      </c>
+      <c r="K499" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L499" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M499" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="500" ht="15.75" customHeight="1" s="16">
       <c r="A500" s="4">
@@ -29329,15 +31131,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E500" s="18" t="n"/>
-      <c r="F500" s="18" t="n"/>
-      <c r="G500" s="18" t="n"/>
-      <c r="H500" s="18" t="n"/>
-      <c r="I500" s="18" t="n"/>
-      <c r="J500" s="18" t="n"/>
-      <c r="K500" s="18" t="n"/>
-      <c r="L500" s="18" t="n"/>
-      <c r="M500" s="18" t="n"/>
+      <c r="E500" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F500" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G500" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H500" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I500" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J500" s="18" t="inlineStr">
+        <is>
+          <t>IndiaSkills Secretariat under MSDE.</t>
+        </is>
+      </c>
+      <c r="K500" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L500" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M500" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="501" ht="15.75" customHeight="1" s="16">
       <c r="A501" s="4">
@@ -29359,15 +31195,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E501" s="18" t="n"/>
-      <c r="F501" s="18" t="n"/>
-      <c r="G501" s="18" t="n"/>
-      <c r="H501" s="18" t="n"/>
-      <c r="I501" s="18" t="n"/>
-      <c r="J501" s="18" t="n"/>
-      <c r="K501" s="18" t="n"/>
-      <c r="L501" s="18" t="n"/>
-      <c r="M501" s="18" t="n"/>
+      <c r="E501" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F501" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G501" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H501" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I501" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J501" s="18" t="inlineStr">
+        <is>
+          <t>CAC (Central Apprenticeship Council) statutory body under MSDE.</t>
+        </is>
+      </c>
+      <c r="K501" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L501" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M501" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="16">
       <c r="A502" s="4">
@@ -29419,15 +31289,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E503" s="18" t="n"/>
-      <c r="F503" s="18" t="n"/>
-      <c r="G503" s="18" t="n"/>
-      <c r="H503" s="18" t="n"/>
-      <c r="I503" s="18" t="n"/>
-      <c r="J503" s="18" t="n"/>
-      <c r="K503" s="18" t="n"/>
-      <c r="L503" s="18" t="n"/>
-      <c r="M503" s="18" t="n"/>
+      <c r="E503" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F503" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G503" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H503" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I503" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J503" s="18" t="inlineStr">
+        <is>
+          <t>Dept of Social Justice site verified live.</t>
+        </is>
+      </c>
+      <c r="K503" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L503" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M503" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="504" ht="15.75" customHeight="1" s="16">
       <c r="A504" s="4">
@@ -29449,15 +31353,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E504" s="18" t="n"/>
-      <c r="F504" s="18" t="n"/>
-      <c r="G504" s="18" t="n"/>
-      <c r="H504" s="18" t="n"/>
-      <c r="I504" s="18" t="n"/>
-      <c r="J504" s="18" t="n"/>
-      <c r="K504" s="18" t="n"/>
-      <c r="L504" s="18" t="n"/>
-      <c r="M504" s="18" t="n"/>
+      <c r="E504" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F504" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G504" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H504" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I504" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J504" s="18" t="inlineStr">
+        <is>
+          <t>DEPwD site verified live.</t>
+        </is>
+      </c>
+      <c r="K504" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L504" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M504" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="505" ht="15.75" customHeight="1" s="16">
       <c r="A505" s="4">
@@ -29479,15 +31417,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E505" s="18" t="n"/>
-      <c r="F505" s="18" t="n"/>
-      <c r="G505" s="18" t="n"/>
-      <c r="H505" s="18" t="n"/>
-      <c r="I505" s="18" t="n"/>
-      <c r="J505" s="18" t="n"/>
-      <c r="K505" s="18" t="n"/>
-      <c r="L505" s="18" t="n"/>
-      <c r="M505" s="18" t="n"/>
+      <c r="E505" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F505" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G505" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H505" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I505" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J505" s="18" t="inlineStr">
+        <is>
+          <t>NSKFDC under Social Justice.</t>
+        </is>
+      </c>
+      <c r="K505" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L505" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M505" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="16">
       <c r="A506" s="4">
@@ -29509,15 +31481,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E506" s="18" t="n"/>
-      <c r="F506" s="18" t="n"/>
-      <c r="G506" s="18" t="n"/>
-      <c r="H506" s="18" t="n"/>
-      <c r="I506" s="18" t="n"/>
-      <c r="J506" s="18" t="n"/>
-      <c r="K506" s="18" t="n"/>
-      <c r="L506" s="18" t="n"/>
-      <c r="M506" s="18" t="n"/>
+      <c r="E506" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F506" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G506" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H506" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I506" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J506" s="18" t="inlineStr">
+        <is>
+          <t>NBCFDC under Social Justice.</t>
+        </is>
+      </c>
+      <c r="K506" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L506" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M506" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="507" ht="15.75" customHeight="1" s="16">
       <c r="A507" s="4">
@@ -29539,15 +31545,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E507" s="18" t="n"/>
-      <c r="F507" s="18" t="n"/>
-      <c r="G507" s="18" t="n"/>
-      <c r="H507" s="18" t="n"/>
-      <c r="I507" s="18" t="n"/>
-      <c r="J507" s="18" t="n"/>
-      <c r="K507" s="18" t="n"/>
-      <c r="L507" s="18" t="n"/>
-      <c r="M507" s="18" t="n"/>
+      <c r="E507" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F507" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G507" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H507" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I507" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J507" s="18" t="inlineStr">
+        <is>
+          <t>NSCFDC under Social Justice.</t>
+        </is>
+      </c>
+      <c r="K507" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L507" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M507" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="508" ht="15.75" customHeight="1" s="16">
       <c r="A508" s="4">
@@ -29569,15 +31609,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E508" s="18" t="n"/>
-      <c r="F508" s="18" t="n"/>
-      <c r="G508" s="18" t="n"/>
-      <c r="H508" s="18" t="n"/>
-      <c r="I508" s="18" t="n"/>
-      <c r="J508" s="18" t="n"/>
-      <c r="K508" s="18" t="n"/>
-      <c r="L508" s="18" t="n"/>
-      <c r="M508" s="18" t="n"/>
+      <c r="E508" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F508" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G508" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H508" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I508" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J508" s="18" t="inlineStr">
+        <is>
+          <t>NCSC - National Commission for Scheduled Castes. Constitutional body.</t>
+        </is>
+      </c>
+      <c r="K508" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L508" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M508" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="509" ht="15.75" customHeight="1" s="16">
       <c r="A509" s="4">
@@ -29599,15 +31673,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E509" s="18" t="n"/>
-      <c r="F509" s="18" t="n"/>
-      <c r="G509" s="18" t="n"/>
-      <c r="H509" s="18" t="n"/>
-      <c r="I509" s="18" t="n"/>
-      <c r="J509" s="18" t="n"/>
-      <c r="K509" s="18" t="n"/>
-      <c r="L509" s="18" t="n"/>
-      <c r="M509" s="18" t="n"/>
+      <c r="E509" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F509" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G509" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H509" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I509" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J509" s="18" t="inlineStr">
+        <is>
+          <t>NCBC - National Commission for Backward Classes. Constitutional body.</t>
+        </is>
+      </c>
+      <c r="K509" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L509" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M509" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="510" ht="15.75" customHeight="1" s="16">
       <c r="A510" s="4">
@@ -29629,15 +31737,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E510" s="18" t="n"/>
-      <c r="F510" s="18" t="n"/>
-      <c r="G510" s="18" t="n"/>
-      <c r="H510" s="18" t="n"/>
-      <c r="I510" s="18" t="n"/>
-      <c r="J510" s="18" t="n"/>
-      <c r="K510" s="18" t="n"/>
-      <c r="L510" s="18" t="n"/>
-      <c r="M510" s="18" t="n"/>
+      <c r="E510" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F510" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G510" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H510" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I510" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J510" s="18" t="inlineStr">
+        <is>
+          <t>CCPD under DEPwD.</t>
+        </is>
+      </c>
+      <c r="K510" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L510" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M510" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="511" ht="15.75" customHeight="1" s="16">
       <c r="A511" s="4">
@@ -29659,15 +31801,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E511" s="18" t="n"/>
-      <c r="F511" s="18" t="n"/>
-      <c r="G511" s="18" t="n"/>
-      <c r="H511" s="18" t="n"/>
-      <c r="I511" s="18" t="n"/>
-      <c r="J511" s="18" t="n"/>
-      <c r="K511" s="18" t="n"/>
-      <c r="L511" s="18" t="n"/>
-      <c r="M511" s="18" t="n"/>
+      <c r="E511" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F511" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G511" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H511" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I511" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J511" s="18" t="inlineStr">
+        <is>
+          <t>Dr. Ambedkar Foundation autonomous body.</t>
+        </is>
+      </c>
+      <c r="K511" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L511" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M511" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="512" ht="15.75" customHeight="1" s="16">
       <c r="A512" s="4">
@@ -29689,15 +31865,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E512" s="18" t="n"/>
-      <c r="F512" s="18" t="n"/>
-      <c r="G512" s="18" t="n"/>
-      <c r="H512" s="18" t="n"/>
-      <c r="I512" s="18" t="n"/>
-      <c r="J512" s="18" t="n"/>
-      <c r="K512" s="18" t="n"/>
-      <c r="L512" s="18" t="n"/>
-      <c r="M512" s="18" t="n"/>
+      <c r="E512" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F512" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G512" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H512" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I512" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J512" s="18" t="inlineStr">
+        <is>
+          <t>NISD autonomous body under Social Justice.</t>
+        </is>
+      </c>
+      <c r="K512" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L512" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M512" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="513" ht="15.75" customHeight="1" s="16">
       <c r="A513" s="4">
@@ -29719,15 +31929,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E513" s="18" t="n"/>
-      <c r="F513" s="18" t="n"/>
-      <c r="G513" s="18" t="n"/>
-      <c r="H513" s="18" t="n"/>
-      <c r="I513" s="18" t="n"/>
-      <c r="J513" s="18" t="n"/>
-      <c r="K513" s="18" t="n"/>
-      <c r="L513" s="18" t="n"/>
-      <c r="M513" s="18" t="n"/>
+      <c r="E513" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F513" s="17" t="inlineStr">
+        <is>
+          <t>https://disabilityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G513" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H513" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I513" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J513" s="18" t="inlineStr">
+        <is>
+          <t>National Institutes for Disabilities (CRCs etc.) under DEPwD.</t>
+        </is>
+      </c>
+      <c r="K513" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L513" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M513" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="514" ht="15.75" customHeight="1" s="16">
       <c r="A514" s="4">
@@ -29749,15 +31993,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E514" s="18" t="n"/>
-      <c r="F514" s="18" t="n"/>
-      <c r="G514" s="18" t="n"/>
-      <c r="H514" s="18" t="n"/>
-      <c r="I514" s="18" t="n"/>
-      <c r="J514" s="18" t="n"/>
-      <c r="K514" s="18" t="n"/>
-      <c r="L514" s="18" t="n"/>
-      <c r="M514" s="18" t="n"/>
+      <c r="E514" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F514" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G514" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H514" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I514" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J514" s="18" t="inlineStr">
+        <is>
+          <t>Regional/Field Offices for welfare schemes.</t>
+        </is>
+      </c>
+      <c r="K514" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L514" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M514" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="515" ht="15.75" customHeight="1" s="16">
       <c r="A515" s="4">
@@ -29809,15 +32087,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E516" s="18" t="n"/>
-      <c r="F516" s="18" t="n"/>
-      <c r="G516" s="18" t="n"/>
-      <c r="H516" s="18" t="n"/>
-      <c r="I516" s="18" t="n"/>
-      <c r="J516" s="18" t="n"/>
-      <c r="K516" s="18" t="n"/>
-      <c r="L516" s="18" t="n"/>
-      <c r="M516" s="18" t="n"/>
+      <c r="E516" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F516" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G516" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H516" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I516" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J516" s="18" t="inlineStr">
+        <is>
+          <t>MoSPI Secretariat site verified live.</t>
+        </is>
+      </c>
+      <c r="K516" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L516" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M516" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="517" ht="15.75" customHeight="1" s="16">
       <c r="A517" s="4">
@@ -29839,15 +32151,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E517" s="18" t="n"/>
-      <c r="F517" s="18" t="n"/>
-      <c r="G517" s="18" t="n"/>
-      <c r="H517" s="18" t="n"/>
-      <c r="I517" s="18" t="n"/>
-      <c r="J517" s="18" t="n"/>
-      <c r="K517" s="18" t="n"/>
-      <c r="L517" s="18" t="n"/>
-      <c r="M517" s="18" t="n"/>
+      <c r="E517" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F517" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G517" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H517" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I517" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J517" s="18" t="inlineStr">
+        <is>
+          <t>NSO (National Statistical Office) under MoSPI.</t>
+        </is>
+      </c>
+      <c r="K517" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L517" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M517" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="518" ht="15.75" customHeight="1" s="16">
       <c r="A518" s="4">
@@ -29869,15 +32215,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E518" s="18" t="n"/>
-      <c r="F518" s="18" t="n"/>
-      <c r="G518" s="18" t="n"/>
-      <c r="H518" s="18" t="n"/>
-      <c r="I518" s="18" t="n"/>
-      <c r="J518" s="18" t="n"/>
-      <c r="K518" s="18" t="n"/>
-      <c r="L518" s="18" t="n"/>
-      <c r="M518" s="18" t="n"/>
+      <c r="E518" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F518" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G518" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H518" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I518" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J518" s="18" t="inlineStr">
+        <is>
+          <t>Programme Implementation Division.</t>
+        </is>
+      </c>
+      <c r="K518" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L518" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M518" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="519" ht="15.75" customHeight="1" s="16">
       <c r="A519" s="4">
@@ -29899,15 +32279,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E519" s="18" t="n"/>
-      <c r="F519" s="18" t="n"/>
-      <c r="G519" s="18" t="n"/>
-      <c r="H519" s="18" t="n"/>
-      <c r="I519" s="18" t="n"/>
-      <c r="J519" s="18" t="n"/>
-      <c r="K519" s="18" t="n"/>
-      <c r="L519" s="18" t="n"/>
-      <c r="M519" s="18" t="n"/>
+      <c r="E519" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F519" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G519" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H519" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I519" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J519" s="18" t="inlineStr">
+        <is>
+          <t>Project Monitoring Division.</t>
+        </is>
+      </c>
+      <c r="K519" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L519" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M519" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="520" ht="15.75" customHeight="1" s="16">
       <c r="A520" s="4">
@@ -29929,15 +32343,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E520" s="18" t="n"/>
-      <c r="F520" s="18" t="n"/>
-      <c r="G520" s="18" t="n"/>
-      <c r="H520" s="18" t="n"/>
-      <c r="I520" s="18" t="n"/>
-      <c r="J520" s="18" t="n"/>
-      <c r="K520" s="18" t="n"/>
-      <c r="L520" s="18" t="n"/>
-      <c r="M520" s="18" t="n"/>
+      <c r="E520" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F520" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G520" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H520" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I520" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J520" s="18" t="inlineStr">
+        <is>
+          <t>NSO Field Operations Division (FOD) subordinate.</t>
+        </is>
+      </c>
+      <c r="K520" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L520" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M520" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="16">
       <c r="A521" s="4">
@@ -29959,15 +32407,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E521" s="18" t="n"/>
-      <c r="F521" s="18" t="n"/>
-      <c r="G521" s="18" t="n"/>
-      <c r="H521" s="18" t="n"/>
-      <c r="I521" s="18" t="n"/>
-      <c r="J521" s="18" t="n"/>
-      <c r="K521" s="18" t="n"/>
-      <c r="L521" s="18" t="n"/>
-      <c r="M521" s="18" t="n"/>
+      <c r="E521" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F521" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G521" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H521" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I521" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J521" s="18" t="inlineStr">
+        <is>
+          <t>Computer Centre &amp; Data Processing Units.</t>
+        </is>
+      </c>
+      <c r="K521" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L521" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M521" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="522" ht="15.75" customHeight="1" s="16">
       <c r="A522" s="4">
@@ -29989,15 +32471,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E522" s="18" t="n"/>
-      <c r="F522" s="18" t="n"/>
-      <c r="G522" s="18" t="n"/>
-      <c r="H522" s="18" t="n"/>
-      <c r="I522" s="18" t="n"/>
-      <c r="J522" s="18" t="n"/>
-      <c r="K522" s="18" t="n"/>
-      <c r="L522" s="18" t="n"/>
-      <c r="M522" s="18" t="n"/>
+      <c r="E522" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F522" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G522" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H522" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I522" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J522" s="18" t="inlineStr">
+        <is>
+          <t>Regional/Field Offices of NSO.</t>
+        </is>
+      </c>
+      <c r="K522" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L522" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M522" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="523" ht="15.75" customHeight="1" s="16">
       <c r="A523" s="4">
@@ -30019,15 +32535,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E523" s="18" t="n"/>
-      <c r="F523" s="18" t="n"/>
-      <c r="G523" s="18" t="n"/>
-      <c r="H523" s="18" t="n"/>
-      <c r="I523" s="18" t="n"/>
-      <c r="J523" s="18" t="n"/>
-      <c r="K523" s="18" t="n"/>
-      <c r="L523" s="18" t="n"/>
-      <c r="M523" s="18" t="n"/>
+      <c r="E523" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F523" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G523" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H523" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I523" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J523" s="18" t="inlineStr">
+        <is>
+          <t>ISI coordination entry. ISI recruits independently at isical.ac.in.</t>
+        </is>
+      </c>
+      <c r="K523" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L523" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M523" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="524" ht="15.75" customHeight="1" s="16">
       <c r="A524" s="4">
@@ -30049,15 +32599,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E524" s="18" t="n"/>
-      <c r="F524" s="18" t="n"/>
-      <c r="G524" s="18" t="n"/>
-      <c r="H524" s="18" t="n"/>
-      <c r="I524" s="18" t="n"/>
-      <c r="J524" s="18" t="n"/>
-      <c r="K524" s="18" t="n"/>
-      <c r="L524" s="18" t="n"/>
-      <c r="M524" s="18" t="n"/>
+      <c r="E524" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F524" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G524" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H524" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I524" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J524" s="18" t="inlineStr">
+        <is>
+          <t>ISS Training Institutes coordination.</t>
+        </is>
+      </c>
+      <c r="K524" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L524" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M524" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="525" ht="15.75" customHeight="1" s="16">
       <c r="A525" s="4">
@@ -30109,15 +32693,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E526" s="18" t="n"/>
-      <c r="F526" s="18" t="n"/>
-      <c r="G526" s="18" t="n"/>
-      <c r="H526" s="18" t="n"/>
-      <c r="I526" s="18" t="n"/>
-      <c r="J526" s="18" t="n"/>
-      <c r="K526" s="18" t="n"/>
-      <c r="L526" s="18" t="n"/>
-      <c r="M526" s="18" t="n"/>
+      <c r="E526" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F526" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G526" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H526" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I526" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J526" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Steel Secretariat site verified live.</t>
+        </is>
+      </c>
+      <c r="K526" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L526" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M526" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="527" ht="15.75" customHeight="1" s="16">
       <c r="A527" s="4">
@@ -30139,15 +32757,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E527" s="18" t="n"/>
-      <c r="F527" s="18" t="n"/>
-      <c r="G527" s="18" t="n"/>
-      <c r="H527" s="18" t="n"/>
-      <c r="I527" s="18" t="n"/>
-      <c r="J527" s="18" t="n"/>
-      <c r="K527" s="18" t="n"/>
-      <c r="L527" s="18" t="n"/>
-      <c r="M527" s="18" t="n"/>
+      <c r="E527" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F527" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G527" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H527" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I527" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J527" s="18" t="inlineStr">
+        <is>
+          <t>Steel Policy &amp; Planning Division.</t>
+        </is>
+      </c>
+      <c r="K527" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L527" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M527" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="528" ht="15.75" customHeight="1" s="16">
       <c r="A528" s="4">
@@ -30169,15 +32821,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E528" s="18" t="n"/>
-      <c r="F528" s="18" t="n"/>
-      <c r="G528" s="18" t="n"/>
-      <c r="H528" s="18" t="n"/>
-      <c r="I528" s="18" t="n"/>
-      <c r="J528" s="18" t="n"/>
-      <c r="K528" s="18" t="n"/>
-      <c r="L528" s="18" t="n"/>
-      <c r="M528" s="18" t="n"/>
+      <c r="E528" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F528" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G528" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H528" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I528" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J528" s="18" t="inlineStr">
+        <is>
+          <t>Steel Development Division.</t>
+        </is>
+      </c>
+      <c r="K528" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L528" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M528" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="529" ht="15.75" customHeight="1" s="16">
       <c r="A529" s="4">
@@ -30199,15 +32885,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E529" s="18" t="n"/>
-      <c r="F529" s="18" t="n"/>
-      <c r="G529" s="18" t="n"/>
-      <c r="H529" s="18" t="n"/>
-      <c r="I529" s="18" t="n"/>
-      <c r="J529" s="18" t="n"/>
-      <c r="K529" s="18" t="n"/>
-      <c r="L529" s="18" t="n"/>
-      <c r="M529" s="18" t="n"/>
+      <c r="E529" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F529" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G529" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H529" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I529" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J529" s="18" t="inlineStr">
+        <is>
+          <t>Joint Plant Committee under Steel Ministry.</t>
+        </is>
+      </c>
+      <c r="K529" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L529" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M529" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="530" ht="15.75" customHeight="1" s="16">
       <c r="A530" s="4">
@@ -30229,15 +32949,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E530" s="18" t="n"/>
-      <c r="F530" s="18" t="n"/>
-      <c r="G530" s="18" t="n"/>
-      <c r="H530" s="18" t="n"/>
-      <c r="I530" s="18" t="n"/>
-      <c r="J530" s="18" t="n"/>
-      <c r="K530" s="18" t="n"/>
-      <c r="L530" s="18" t="n"/>
-      <c r="M530" s="18" t="n"/>
+      <c r="E530" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F530" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G530" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H530" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I530" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J530" s="18" t="inlineStr">
+        <is>
+          <t>JPC Regional/Field Offices.</t>
+        </is>
+      </c>
+      <c r="K530" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L530" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M530" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="531" ht="15.75" customHeight="1" s="16">
       <c r="A531" s="4">
@@ -30259,15 +33013,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E531" s="18" t="n"/>
-      <c r="F531" s="18" t="n"/>
-      <c r="G531" s="18" t="n"/>
-      <c r="H531" s="18" t="n"/>
-      <c r="I531" s="18" t="n"/>
-      <c r="J531" s="18" t="n"/>
-      <c r="K531" s="18" t="n"/>
-      <c r="L531" s="18" t="n"/>
-      <c r="M531" s="18" t="n"/>
+      <c r="E531" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F531" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G531" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H531" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I531" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J531" s="18" t="inlineStr">
+        <is>
+          <t>IIM coordination entry.</t>
+        </is>
+      </c>
+      <c r="K531" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L531" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M531" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="532" ht="15.75" customHeight="1" s="16">
       <c r="A532" s="4">
@@ -30289,15 +33077,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E532" s="18" t="n"/>
-      <c r="F532" s="18" t="n"/>
-      <c r="G532" s="18" t="n"/>
-      <c r="H532" s="18" t="n"/>
-      <c r="I532" s="18" t="n"/>
-      <c r="J532" s="18" t="n"/>
-      <c r="K532" s="18" t="n"/>
-      <c r="L532" s="18" t="n"/>
-      <c r="M532" s="18" t="n"/>
+      <c r="E532" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F532" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G532" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H532" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I532" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J532" s="18" t="inlineStr">
+        <is>
+          <t>NISST autonomous body.</t>
+        </is>
+      </c>
+      <c r="K532" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L532" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M532" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="533" ht="15.75" customHeight="1" s="16">
       <c r="A533" s="4">
@@ -30319,15 +33141,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E533" s="18" t="n"/>
-      <c r="F533" s="18" t="n"/>
-      <c r="G533" s="18" t="n"/>
-      <c r="H533" s="18" t="n"/>
-      <c r="I533" s="18" t="n"/>
-      <c r="J533" s="18" t="n"/>
-      <c r="K533" s="18" t="n"/>
-      <c r="L533" s="18" t="n"/>
-      <c r="M533" s="18" t="n"/>
+      <c r="E533" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F533" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G533" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H533" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I533" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J533" s="18" t="inlineStr">
+        <is>
+          <t>SAIL is a PSU recruiting independently at sail.co.in. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K533" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L533" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M533" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="534" ht="15.75" customHeight="1" s="16">
       <c r="A534" s="4">
@@ -30349,15 +33205,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E534" s="18" t="n"/>
-      <c r="F534" s="18" t="n"/>
-      <c r="G534" s="18" t="n"/>
-      <c r="H534" s="18" t="n"/>
-      <c r="I534" s="18" t="n"/>
-      <c r="J534" s="18" t="n"/>
-      <c r="K534" s="18" t="n"/>
-      <c r="L534" s="18" t="n"/>
-      <c r="M534" s="18" t="n"/>
+      <c r="E534" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F534" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G534" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H534" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I534" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J534" s="18" t="inlineStr">
+        <is>
+          <t>RINL is a PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K534" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L534" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M534" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="535" ht="15.75" customHeight="1" s="16">
       <c r="A535" s="4">
@@ -30379,15 +33269,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E535" s="18" t="n"/>
-      <c r="F535" s="18" t="n"/>
-      <c r="G535" s="18" t="n"/>
-      <c r="H535" s="18" t="n"/>
-      <c r="I535" s="18" t="n"/>
-      <c r="J535" s="18" t="n"/>
-      <c r="K535" s="18" t="n"/>
-      <c r="L535" s="18" t="n"/>
-      <c r="M535" s="18" t="n"/>
+      <c r="E535" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F535" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G535" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H535" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I535" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J535" s="18" t="inlineStr">
+        <is>
+          <t>MOIL Ltd is a PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K535" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L535" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M535" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="536" ht="15.75" customHeight="1" s="16">
       <c r="A536" s="4">
@@ -30439,15 +33363,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E537" s="18" t="n"/>
-      <c r="F537" s="18" t="n"/>
-      <c r="G537" s="18" t="n"/>
-      <c r="H537" s="18" t="n"/>
-      <c r="I537" s="18" t="n"/>
-      <c r="J537" s="18" t="n"/>
-      <c r="K537" s="18" t="n"/>
-      <c r="L537" s="18" t="n"/>
-      <c r="M537" s="18" t="n"/>
+      <c r="E537" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F537" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G537" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H537" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I537" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J537" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Textiles Secretariat. Site unreachable but confirmed domain.</t>
+        </is>
+      </c>
+      <c r="K537" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L537" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M537" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="538" ht="15.75" customHeight="1" s="16">
       <c r="A538" s="4">
@@ -30469,15 +33427,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E538" s="18" t="n"/>
-      <c r="F538" s="18" t="n"/>
-      <c r="G538" s="18" t="n"/>
-      <c r="H538" s="18" t="n"/>
-      <c r="I538" s="18" t="n"/>
-      <c r="J538" s="18" t="n"/>
-      <c r="K538" s="18" t="n"/>
-      <c r="L538" s="18" t="n"/>
-      <c r="M538" s="18" t="n"/>
+      <c r="E538" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F538" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G538" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H538" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I538" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J538" s="18" t="inlineStr">
+        <is>
+          <t>Office of Textile Commissioner under MoT.</t>
+        </is>
+      </c>
+      <c r="K538" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L538" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M538" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="539" ht="15.75" customHeight="1" s="16">
       <c r="A539" s="4">
@@ -30499,15 +33491,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E539" s="18" t="n"/>
-      <c r="F539" s="18" t="n"/>
-      <c r="G539" s="18" t="n"/>
-      <c r="H539" s="18" t="n"/>
-      <c r="I539" s="18" t="n"/>
-      <c r="J539" s="18" t="n"/>
-      <c r="K539" s="18" t="n"/>
-      <c r="L539" s="18" t="n"/>
-      <c r="M539" s="18" t="n"/>
+      <c r="E539" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F539" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G539" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H539" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I539" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J539" s="18" t="inlineStr">
+        <is>
+          <t>DC (Handlooms) under MoT.</t>
+        </is>
+      </c>
+      <c r="K539" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L539" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M539" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="540" ht="15.75" customHeight="1" s="16">
       <c r="A540" s="4">
@@ -30529,15 +33555,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E540" s="18" t="n"/>
-      <c r="F540" s="18" t="n"/>
-      <c r="G540" s="18" t="n"/>
-      <c r="H540" s="18" t="n"/>
-      <c r="I540" s="18" t="n"/>
-      <c r="J540" s="18" t="n"/>
-      <c r="K540" s="18" t="n"/>
-      <c r="L540" s="18" t="n"/>
-      <c r="M540" s="18" t="n"/>
+      <c r="E540" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F540" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G540" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H540" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I540" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J540" s="18" t="inlineStr">
+        <is>
+          <t>DC (Handicrafts) under MoT.</t>
+        </is>
+      </c>
+      <c r="K540" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L540" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M540" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="541" ht="15.75" customHeight="1" s="16">
       <c r="A541" s="4">
@@ -30559,15 +33619,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E541" s="18" t="n"/>
-      <c r="F541" s="18" t="n"/>
-      <c r="G541" s="18" t="n"/>
-      <c r="H541" s="18" t="n"/>
-      <c r="I541" s="18" t="n"/>
-      <c r="J541" s="18" t="n"/>
-      <c r="K541" s="18" t="n"/>
-      <c r="L541" s="18" t="n"/>
-      <c r="M541" s="18" t="n"/>
+      <c r="E541" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F541" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G541" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H541" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I541" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J541" s="18" t="inlineStr">
+        <is>
+          <t>DC (Powerloom) under MoT.</t>
+        </is>
+      </c>
+      <c r="K541" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L541" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M541" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="542" ht="15.75" customHeight="1" s="16">
       <c r="A542" s="4">
@@ -30589,15 +33683,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E542" s="18" t="n"/>
-      <c r="F542" s="18" t="n"/>
-      <c r="G542" s="18" t="n"/>
-      <c r="H542" s="18" t="n"/>
-      <c r="I542" s="18" t="n"/>
-      <c r="J542" s="18" t="n"/>
-      <c r="K542" s="18" t="n"/>
-      <c r="L542" s="18" t="n"/>
-      <c r="M542" s="18" t="n"/>
+      <c r="E542" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F542" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G542" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H542" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I542" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J542" s="18" t="inlineStr">
+        <is>
+          <t>National Jute Board under MoT.</t>
+        </is>
+      </c>
+      <c r="K542" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L542" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M542" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="543" ht="15.75" customHeight="1" s="16">
       <c r="A543" s="4">
@@ -30619,15 +33747,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E543" s="18" t="n"/>
-      <c r="F543" s="18" t="n"/>
-      <c r="G543" s="18" t="n"/>
-      <c r="H543" s="18" t="n"/>
-      <c r="I543" s="18" t="n"/>
-      <c r="J543" s="18" t="n"/>
-      <c r="K543" s="18" t="n"/>
-      <c r="L543" s="18" t="n"/>
-      <c r="M543" s="18" t="n"/>
+      <c r="E543" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F543" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G543" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H543" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I543" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J543" s="18" t="inlineStr">
+        <is>
+          <t>Central Silk Board coordination under MoT.</t>
+        </is>
+      </c>
+      <c r="K543" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L543" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M543" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="544" ht="15.75" customHeight="1" s="16">
       <c r="A544" s="4">
@@ -30649,15 +33811,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E544" s="18" t="n"/>
-      <c r="F544" s="18" t="n"/>
-      <c r="G544" s="18" t="n"/>
-      <c r="H544" s="18" t="n"/>
-      <c r="I544" s="18" t="n"/>
-      <c r="J544" s="18" t="n"/>
-      <c r="K544" s="18" t="n"/>
-      <c r="L544" s="18" t="n"/>
-      <c r="M544" s="18" t="n"/>
+      <c r="E544" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F544" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G544" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H544" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I544" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J544" s="18" t="inlineStr">
+        <is>
+          <t>Textile Commissionerate Regional/Field Offices.</t>
+        </is>
+      </c>
+      <c r="K544" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L544" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M544" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="545" ht="15.75" customHeight="1" s="16">
       <c r="A545" s="4">
@@ -30679,15 +33875,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E545" s="18" t="n"/>
-      <c r="F545" s="18" t="n"/>
-      <c r="G545" s="18" t="n"/>
-      <c r="H545" s="18" t="n"/>
-      <c r="I545" s="18" t="n"/>
-      <c r="J545" s="18" t="n"/>
-      <c r="K545" s="18" t="n"/>
-      <c r="L545" s="18" t="n"/>
-      <c r="M545" s="18" t="n"/>
+      <c r="E545" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F545" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G545" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H545" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I545" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J545" s="18" t="inlineStr">
+        <is>
+          <t>Handloom/Handicrafts Field Formations.</t>
+        </is>
+      </c>
+      <c r="K545" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L545" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M545" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="546" ht="15.75" customHeight="1" s="16">
       <c r="A546" s="4">
@@ -30709,15 +33939,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E546" s="18" t="n"/>
-      <c r="F546" s="18" t="n"/>
-      <c r="G546" s="18" t="n"/>
-      <c r="H546" s="18" t="n"/>
-      <c r="I546" s="18" t="n"/>
-      <c r="J546" s="18" t="n"/>
-      <c r="K546" s="18" t="n"/>
-      <c r="L546" s="18" t="n"/>
-      <c r="M546" s="18" t="n"/>
+      <c r="E546" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F546" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G546" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H546" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I546" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J546" s="18" t="inlineStr">
+        <is>
+          <t>Powerloom Service Centres.</t>
+        </is>
+      </c>
+      <c r="K546" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L546" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M546" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="547" ht="15.75" customHeight="1" s="16">
       <c r="A547" s="4">
@@ -30739,15 +34003,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E547" s="18" t="n"/>
-      <c r="F547" s="18" t="n"/>
-      <c r="G547" s="18" t="n"/>
-      <c r="H547" s="18" t="n"/>
-      <c r="I547" s="18" t="n"/>
-      <c r="J547" s="18" t="n"/>
-      <c r="K547" s="18" t="n"/>
-      <c r="L547" s="18" t="n"/>
-      <c r="M547" s="18" t="n"/>
+      <c r="E547" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F547" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G547" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H547" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I547" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J547" s="18" t="inlineStr">
+        <is>
+          <t>Textiles Committee statutory body.</t>
+        </is>
+      </c>
+      <c r="K547" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L547" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M547" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="548" ht="15.75" customHeight="1" s="16">
       <c r="A548" s="4">
@@ -30769,15 +34067,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E548" s="18" t="n"/>
-      <c r="F548" s="18" t="n"/>
-      <c r="G548" s="18" t="n"/>
-      <c r="H548" s="18" t="n"/>
-      <c r="I548" s="18" t="n"/>
-      <c r="J548" s="18" t="n"/>
-      <c r="K548" s="18" t="n"/>
-      <c r="L548" s="18" t="n"/>
-      <c r="M548" s="18" t="n"/>
+      <c r="E548" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F548" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G548" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H548" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I548" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J548" s="18" t="inlineStr">
+        <is>
+          <t>Central Silk Board statutory body. Has csb.gov.in site.</t>
+        </is>
+      </c>
+      <c r="K548" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L548" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M548" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="549" ht="15.75" customHeight="1" s="16">
       <c r="A549" s="4">
@@ -30799,15 +34131,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E549" s="18" t="n"/>
-      <c r="F549" s="18" t="n"/>
-      <c r="G549" s="18" t="n"/>
-      <c r="H549" s="18" t="n"/>
-      <c r="I549" s="18" t="n"/>
-      <c r="J549" s="18" t="n"/>
-      <c r="K549" s="18" t="n"/>
-      <c r="L549" s="18" t="n"/>
-      <c r="M549" s="18" t="n"/>
+      <c r="E549" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nift.ac.in/</t>
+        </is>
+      </c>
+      <c r="F549" s="17" t="inlineStr">
+        <is>
+          <t>https://www.nift.ac.in/</t>
+        </is>
+      </c>
+      <c r="G549" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H549" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I549" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J549" s="18" t="inlineStr">
+        <is>
+          <t>NIFT site verified live. Autonomous body under MoT. Recruits faculty/staff.</t>
+        </is>
+      </c>
+      <c r="K549" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L549" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M549" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="550" ht="15.75" customHeight="1" s="16">
       <c r="A550" s="4">
@@ -30829,15 +34195,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E550" s="18" t="n"/>
-      <c r="F550" s="18" t="n"/>
-      <c r="G550" s="18" t="n"/>
-      <c r="H550" s="18" t="n"/>
-      <c r="I550" s="18" t="n"/>
-      <c r="J550" s="18" t="n"/>
-      <c r="K550" s="18" t="n"/>
-      <c r="L550" s="18" t="n"/>
-      <c r="M550" s="18" t="n"/>
+      <c r="E550" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F550" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G550" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H550" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I550" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J550" s="18" t="inlineStr">
+        <is>
+          <t>NID coordination entry. NID recruits independently at nid.edu.</t>
+        </is>
+      </c>
+      <c r="K550" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L550" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M550" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="551" ht="15.75" customHeight="1" s="16">
       <c r="A551" s="4">
@@ -30859,15 +34259,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E551" s="18" t="n"/>
-      <c r="F551" s="18" t="n"/>
-      <c r="G551" s="18" t="n"/>
-      <c r="H551" s="18" t="n"/>
-      <c r="I551" s="18" t="n"/>
-      <c r="J551" s="18" t="n"/>
-      <c r="K551" s="18" t="n"/>
-      <c r="L551" s="18" t="n"/>
-      <c r="M551" s="18" t="n"/>
+      <c r="E551" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F551" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G551" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H551" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I551" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J551" s="18" t="inlineStr">
+        <is>
+          <t>IIHTs under MoT.</t>
+        </is>
+      </c>
+      <c r="K551" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L551" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M551" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="552" ht="15.75" customHeight="1" s="16">
       <c r="A552" s="4">
@@ -30919,15 +34353,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E553" s="18" t="n"/>
-      <c r="F553" s="18" t="n"/>
-      <c r="G553" s="18" t="n"/>
-      <c r="H553" s="18" t="n"/>
-      <c r="I553" s="18" t="n"/>
-      <c r="J553" s="18" t="n"/>
-      <c r="K553" s="18" t="n"/>
-      <c r="L553" s="18" t="n"/>
-      <c r="M553" s="18" t="n"/>
+      <c r="E553" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F553" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G553" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H553" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I553" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J553" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs Secretariat verified live.</t>
+        </is>
+      </c>
+      <c r="K553" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L553" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M553" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="554" ht="15.75" customHeight="1" s="16">
       <c r="A554" s="4">
@@ -30949,15 +34417,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E554" s="18" t="n"/>
-      <c r="F554" s="18" t="n"/>
-      <c r="G554" s="18" t="n"/>
-      <c r="H554" s="18" t="n"/>
-      <c r="I554" s="18" t="n"/>
-      <c r="J554" s="18" t="n"/>
-      <c r="K554" s="18" t="n"/>
-      <c r="L554" s="18" t="n"/>
-      <c r="M554" s="18" t="n"/>
+      <c r="E554" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F554" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G554" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H554" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I554" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J554" s="18" t="inlineStr">
+        <is>
+          <t>Tribal Development Division.</t>
+        </is>
+      </c>
+      <c r="K554" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L554" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M554" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="555" ht="15.75" customHeight="1" s="16">
       <c r="A555" s="4">
@@ -30979,15 +34481,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E555" s="18" t="n"/>
-      <c r="F555" s="18" t="n"/>
-      <c r="G555" s="18" t="n"/>
-      <c r="H555" s="18" t="n"/>
-      <c r="I555" s="18" t="n"/>
-      <c r="J555" s="18" t="n"/>
-      <c r="K555" s="18" t="n"/>
-      <c r="L555" s="18" t="n"/>
-      <c r="M555" s="18" t="n"/>
+      <c r="E555" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F555" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G555" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H555" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I555" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J555" s="18" t="inlineStr">
+        <is>
+          <t>Education &amp; Empowerment Division.</t>
+        </is>
+      </c>
+      <c r="K555" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L555" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M555" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="556" ht="15.75" customHeight="1" s="16">
       <c r="A556" s="4">
@@ -31009,15 +34545,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E556" s="18" t="n"/>
-      <c r="F556" s="18" t="n"/>
-      <c r="G556" s="18" t="n"/>
-      <c r="H556" s="18" t="n"/>
-      <c r="I556" s="18" t="n"/>
-      <c r="J556" s="18" t="n"/>
-      <c r="K556" s="18" t="n"/>
-      <c r="L556" s="18" t="n"/>
-      <c r="M556" s="18" t="n"/>
+      <c r="E556" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F556" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G556" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H556" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I556" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J556" s="18" t="inlineStr">
+        <is>
+          <t>EMRS Division.</t>
+        </is>
+      </c>
+      <c r="K556" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L556" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M556" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="557" ht="15.75" customHeight="1" s="16">
       <c r="A557" s="4">
@@ -31039,15 +34609,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E557" s="18" t="n"/>
-      <c r="F557" s="18" t="n"/>
-      <c r="G557" s="18" t="n"/>
-      <c r="H557" s="18" t="n"/>
-      <c r="I557" s="18" t="n"/>
-      <c r="J557" s="18" t="n"/>
-      <c r="K557" s="18" t="n"/>
-      <c r="L557" s="18" t="n"/>
-      <c r="M557" s="18" t="n"/>
+      <c r="E557" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F557" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G557" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H557" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I557" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J557" s="18" t="inlineStr">
+        <is>
+          <t>NCST coordination. Constitutional body.</t>
+        </is>
+      </c>
+      <c r="K557" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L557" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M557" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="558" ht="15.75" customHeight="1" s="16">
       <c r="A558" s="4">
@@ -31069,15 +34673,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E558" s="18" t="n"/>
-      <c r="F558" s="18" t="n"/>
-      <c r="G558" s="18" t="n"/>
-      <c r="H558" s="18" t="n"/>
-      <c r="I558" s="18" t="n"/>
-      <c r="J558" s="18" t="n"/>
-      <c r="K558" s="18" t="n"/>
-      <c r="L558" s="18" t="n"/>
-      <c r="M558" s="18" t="n"/>
+      <c r="E558" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F558" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G558" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H558" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I558" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J558" s="18" t="inlineStr">
+        <is>
+          <t>NSTFDC autonomous body.</t>
+        </is>
+      </c>
+      <c r="K558" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L558" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M558" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="559" ht="15.75" customHeight="1" s="16">
       <c r="A559" s="4">
@@ -31099,15 +34737,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E559" s="18" t="n"/>
-      <c r="F559" s="18" t="n"/>
-      <c r="G559" s="18" t="n"/>
-      <c r="H559" s="18" t="n"/>
-      <c r="I559" s="18" t="n"/>
-      <c r="J559" s="18" t="n"/>
-      <c r="K559" s="18" t="n"/>
-      <c r="L559" s="18" t="n"/>
-      <c r="M559" s="18" t="n"/>
+      <c r="E559" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F559" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G559" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H559" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I559" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J559" s="18" t="inlineStr">
+        <is>
+          <t>TRIFED autonomous body. Has tfrfed.in site.</t>
+        </is>
+      </c>
+      <c r="K559" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L559" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M559" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="560" ht="15.75" customHeight="1" s="16">
       <c r="A560" s="4">
@@ -31129,15 +34801,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E560" s="18" t="n"/>
-      <c r="F560" s="18" t="n"/>
-      <c r="G560" s="18" t="n"/>
-      <c r="H560" s="18" t="n"/>
-      <c r="I560" s="18" t="n"/>
-      <c r="J560" s="18" t="n"/>
-      <c r="K560" s="18" t="n"/>
-      <c r="L560" s="18" t="n"/>
-      <c r="M560" s="18" t="n"/>
+      <c r="E560" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F560" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G560" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H560" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I560" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J560" s="18" t="inlineStr">
+        <is>
+          <t>NITRT autonomous body.</t>
+        </is>
+      </c>
+      <c r="K560" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L560" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M560" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="561" ht="15.75" customHeight="1" s="16">
       <c r="A561" s="4">
@@ -31159,15 +34865,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E561" s="18" t="n"/>
-      <c r="F561" s="18" t="n"/>
-      <c r="G561" s="18" t="n"/>
-      <c r="H561" s="18" t="n"/>
-      <c r="I561" s="18" t="n"/>
-      <c r="J561" s="18" t="n"/>
-      <c r="K561" s="18" t="n"/>
-      <c r="L561" s="18" t="n"/>
-      <c r="M561" s="18" t="n"/>
+      <c r="E561" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F561" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G561" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H561" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I561" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J561" s="18" t="inlineStr">
+        <is>
+          <t>EMRS Regional/Field Units.</t>
+        </is>
+      </c>
+      <c r="K561" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L561" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M561" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="562" ht="15.75" customHeight="1" s="16">
       <c r="A562" s="4">
@@ -31189,15 +34929,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E562" s="18" t="n"/>
-      <c r="F562" s="18" t="n"/>
-      <c r="G562" s="18" t="n"/>
-      <c r="H562" s="18" t="n"/>
-      <c r="I562" s="18" t="n"/>
-      <c r="J562" s="18" t="n"/>
-      <c r="K562" s="18" t="n"/>
-      <c r="L562" s="18" t="n"/>
-      <c r="M562" s="18" t="n"/>
+      <c r="E562" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F562" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G562" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H562" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I562" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J562" s="18" t="inlineStr">
+        <is>
+          <t>Regional Offices for Tribal Welfare Schemes.</t>
+        </is>
+      </c>
+      <c r="K562" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L562" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M562" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="563" ht="15.75" customHeight="1" s="16">
       <c r="A563" s="4">
@@ -31249,15 +35023,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E564" s="18" t="n"/>
-      <c r="F564" s="18" t="n"/>
-      <c r="G564" s="18" t="n"/>
-      <c r="H564" s="18" t="n"/>
-      <c r="I564" s="18" t="n"/>
-      <c r="J564" s="18" t="n"/>
-      <c r="K564" s="18" t="n"/>
-      <c r="L564" s="18" t="n"/>
-      <c r="M564" s="18" t="n"/>
+      <c r="E564" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F564" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G564" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H564" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I564" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J564" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of WCD Secretariat. Site unreachable but confirmed domain.</t>
+        </is>
+      </c>
+      <c r="K564" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L564" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M564" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="565" ht="15.75" customHeight="1" s="16">
       <c r="A565" s="4">
@@ -31279,15 +35087,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E565" s="18" t="n"/>
-      <c r="F565" s="18" t="n"/>
-      <c r="G565" s="18" t="n"/>
-      <c r="H565" s="18" t="n"/>
-      <c r="I565" s="18" t="n"/>
-      <c r="J565" s="18" t="n"/>
-      <c r="K565" s="18" t="n"/>
-      <c r="L565" s="18" t="n"/>
-      <c r="M565" s="18" t="n"/>
+      <c r="E565" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F565" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G565" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H565" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I565" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J565" s="18" t="inlineStr">
+        <is>
+          <t>Child Development Division.</t>
+        </is>
+      </c>
+      <c r="K565" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L565" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M565" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="566" ht="15.75" customHeight="1" s="16">
       <c r="A566" s="4">
@@ -31309,15 +35151,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E566" s="18" t="n"/>
-      <c r="F566" s="18" t="n"/>
-      <c r="G566" s="18" t="n"/>
-      <c r="H566" s="18" t="n"/>
-      <c r="I566" s="18" t="n"/>
-      <c r="J566" s="18" t="n"/>
-      <c r="K566" s="18" t="n"/>
-      <c r="L566" s="18" t="n"/>
-      <c r="M566" s="18" t="n"/>
+      <c r="E566" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F566" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G566" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H566" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I566" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J566" s="18" t="inlineStr">
+        <is>
+          <t>Women Empowerment Division.</t>
+        </is>
+      </c>
+      <c r="K566" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L566" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M566" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="567" ht="15.75" customHeight="1" s="16">
       <c r="A567" s="4">
@@ -31339,15 +35215,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E567" s="18" t="n"/>
-      <c r="F567" s="18" t="n"/>
-      <c r="G567" s="18" t="n"/>
-      <c r="H567" s="18" t="n"/>
-      <c r="I567" s="18" t="n"/>
-      <c r="J567" s="18" t="n"/>
-      <c r="K567" s="18" t="n"/>
-      <c r="L567" s="18" t="n"/>
-      <c r="M567" s="18" t="n"/>
+      <c r="E567" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F567" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G567" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H567" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I567" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J567" s="18" t="inlineStr">
+        <is>
+          <t>Mission Shakti Division.</t>
+        </is>
+      </c>
+      <c r="K567" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L567" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M567" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="568" ht="15.75" customHeight="1" s="16">
       <c r="A568" s="4">
@@ -31369,15 +35279,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E568" s="18" t="n"/>
-      <c r="F568" s="18" t="n"/>
-      <c r="G568" s="18" t="n"/>
-      <c r="H568" s="18" t="n"/>
-      <c r="I568" s="18" t="n"/>
-      <c r="J568" s="18" t="n"/>
-      <c r="K568" s="18" t="n"/>
-      <c r="L568" s="18" t="n"/>
-      <c r="M568" s="18" t="n"/>
+      <c r="E568" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F568" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G568" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H568" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I568" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J568" s="18" t="inlineStr">
+        <is>
+          <t>Mission Vatsalya Division.</t>
+        </is>
+      </c>
+      <c r="K568" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L568" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M568" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="569" ht="15.75" customHeight="1" s="16">
       <c r="A569" s="4">
@@ -31399,15 +35343,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E569" s="18" t="n"/>
-      <c r="F569" s="18" t="n"/>
-      <c r="G569" s="18" t="n"/>
-      <c r="H569" s="18" t="n"/>
-      <c r="I569" s="18" t="n"/>
-      <c r="J569" s="18" t="n"/>
-      <c r="K569" s="18" t="n"/>
-      <c r="L569" s="18" t="n"/>
-      <c r="M569" s="18" t="n"/>
+      <c r="E569" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F569" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G569" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H569" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I569" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J569" s="18" t="inlineStr">
+        <is>
+          <t>Mission POSHAN 2.0 Division.</t>
+        </is>
+      </c>
+      <c r="K569" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L569" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M569" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="570" ht="15.75" customHeight="1" s="16">
       <c r="A570" s="4">
@@ -31429,15 +35407,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E570" s="18" t="n"/>
-      <c r="F570" s="18" t="n"/>
-      <c r="G570" s="18" t="n"/>
-      <c r="H570" s="18" t="n"/>
-      <c r="I570" s="18" t="n"/>
-      <c r="J570" s="18" t="n"/>
-      <c r="K570" s="18" t="n"/>
-      <c r="L570" s="18" t="n"/>
-      <c r="M570" s="18" t="n"/>
+      <c r="E570" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F570" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G570" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H570" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I570" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J570" s="18" t="inlineStr">
+        <is>
+          <t>CARA (Central Adoption Resource Authority) under WCD. Has cara.wcd.gov.in.</t>
+        </is>
+      </c>
+      <c r="K570" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L570" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M570" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="571" ht="15.75" customHeight="1" s="16">
       <c r="A571" s="4">
@@ -31459,15 +35471,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E571" s="18" t="n"/>
-      <c r="F571" s="18" t="n"/>
-      <c r="G571" s="18" t="n"/>
-      <c r="H571" s="18" t="n"/>
-      <c r="I571" s="18" t="n"/>
-      <c r="J571" s="18" t="n"/>
-      <c r="K571" s="18" t="n"/>
-      <c r="L571" s="18" t="n"/>
-      <c r="M571" s="18" t="n"/>
+      <c r="E571" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F571" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G571" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H571" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I571" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J571" s="18" t="inlineStr">
+        <is>
+          <t>NCPCR under WCD. Has ncpcr.gov.in.</t>
+        </is>
+      </c>
+      <c r="K571" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L571" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M571" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="572" ht="15.75" customHeight="1" s="16">
       <c r="A572" s="4">
@@ -31489,15 +35535,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E572" s="18" t="n"/>
-      <c r="F572" s="18" t="n"/>
-      <c r="G572" s="18" t="n"/>
-      <c r="H572" s="18" t="n"/>
-      <c r="I572" s="18" t="n"/>
-      <c r="J572" s="18" t="n"/>
-      <c r="K572" s="18" t="n"/>
-      <c r="L572" s="18" t="n"/>
-      <c r="M572" s="18" t="n"/>
+      <c r="E572" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F572" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G572" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H572" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I572" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J572" s="18" t="inlineStr">
+        <is>
+          <t>Anganwadi/ICDS Field Units subordinate.</t>
+        </is>
+      </c>
+      <c r="K572" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L572" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M572" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="573" ht="15.75" customHeight="1" s="16">
       <c r="A573" s="4">
@@ -31519,15 +35599,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E573" s="18" t="n"/>
-      <c r="F573" s="18" t="n"/>
-      <c r="G573" s="18" t="n"/>
-      <c r="H573" s="18" t="n"/>
-      <c r="I573" s="18" t="n"/>
-      <c r="J573" s="18" t="n"/>
-      <c r="K573" s="18" t="n"/>
-      <c r="L573" s="18" t="n"/>
-      <c r="M573" s="18" t="n"/>
+      <c r="E573" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F573" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G573" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H573" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I573" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J573" s="18" t="inlineStr">
+        <is>
+          <t>State/District Mission Directorates coordination.</t>
+        </is>
+      </c>
+      <c r="K573" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L573" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M573" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="574" ht="15.75" customHeight="1" s="16">
       <c r="A574" s="4">
@@ -31549,15 +35663,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E574" s="18" t="n"/>
-      <c r="F574" s="18" t="n"/>
-      <c r="G574" s="18" t="n"/>
-      <c r="H574" s="18" t="n"/>
-      <c r="I574" s="18" t="n"/>
-      <c r="J574" s="18" t="n"/>
-      <c r="K574" s="18" t="n"/>
-      <c r="L574" s="18" t="n"/>
-      <c r="M574" s="18" t="n"/>
+      <c r="E574" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F574" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G574" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H574" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I574" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J574" s="18" t="inlineStr">
+        <is>
+          <t>NCW (National Commission for Women). Statutory body. Has ncw.nic.in.</t>
+        </is>
+      </c>
+      <c r="K574" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L574" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M574" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="575" ht="15.75" customHeight="1" s="16">
       <c r="A575" s="4">
@@ -31579,15 +35727,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E575" s="18" t="n"/>
-      <c r="F575" s="18" t="n"/>
-      <c r="G575" s="18" t="n"/>
-      <c r="H575" s="18" t="n"/>
-      <c r="I575" s="18" t="n"/>
-      <c r="J575" s="18" t="n"/>
-      <c r="K575" s="18" t="n"/>
-      <c r="L575" s="18" t="n"/>
-      <c r="M575" s="18" t="n"/>
+      <c r="E575" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F575" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G575" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H575" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I575" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J575" s="18" t="inlineStr">
+        <is>
+          <t>NIPCCD autonomous body under WCD. Has nipccd.nic.in.</t>
+        </is>
+      </c>
+      <c r="K575" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L575" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M575" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="576" ht="15.75" customHeight="1" s="16">
       <c r="A576" s="4">
@@ -31639,15 +35821,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E577" s="18" t="n"/>
-      <c r="F577" s="18" t="n"/>
-      <c r="G577" s="18" t="n"/>
-      <c r="H577" s="18" t="n"/>
-      <c r="I577" s="18" t="n"/>
-      <c r="J577" s="18" t="n"/>
-      <c r="K577" s="18" t="n"/>
-      <c r="L577" s="18" t="n"/>
-      <c r="M577" s="18" t="n"/>
+      <c r="E577" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F577" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G577" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H577" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I577" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J577" s="18" t="inlineStr">
+        <is>
+          <t>Department of Youth Affairs under YAS verified live.</t>
+        </is>
+      </c>
+      <c r="K577" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L577" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M577" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="578" ht="15.75" customHeight="1" s="16">
       <c r="A578" s="4">
@@ -31669,15 +35885,49 @@
           <t>Department</t>
         </is>
       </c>
-      <c r="E578" s="18" t="n"/>
-      <c r="F578" s="18" t="n"/>
-      <c r="G578" s="18" t="n"/>
-      <c r="H578" s="18" t="n"/>
-      <c r="I578" s="18" t="n"/>
-      <c r="J578" s="18" t="n"/>
-      <c r="K578" s="18" t="n"/>
-      <c r="L578" s="18" t="n"/>
-      <c r="M578" s="18" t="n"/>
+      <c r="E578" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F578" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G578" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H578" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I578" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J578" s="18" t="inlineStr">
+        <is>
+          <t>Department of Sports.</t>
+        </is>
+      </c>
+      <c r="K578" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L578" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M578" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="579" ht="15.75" customHeight="1" s="16">
       <c r="A579" s="4">
@@ -31699,15 +35949,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E579" s="18" t="n"/>
-      <c r="F579" s="18" t="n"/>
-      <c r="G579" s="18" t="n"/>
-      <c r="H579" s="18" t="n"/>
-      <c r="I579" s="18" t="n"/>
-      <c r="J579" s="18" t="n"/>
-      <c r="K579" s="18" t="n"/>
-      <c r="L579" s="18" t="n"/>
-      <c r="M579" s="18" t="n"/>
+      <c r="E579" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F579" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G579" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H579" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I579" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J579" s="18" t="inlineStr">
+        <is>
+          <t>NSS Directorate under Youth Affairs.</t>
+        </is>
+      </c>
+      <c r="K579" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L579" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M579" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="580" ht="15.75" customHeight="1" s="16">
       <c r="A580" s="4">
@@ -31729,15 +36013,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E580" s="18" t="n"/>
-      <c r="F580" s="18" t="n"/>
-      <c r="G580" s="18" t="n"/>
-      <c r="H580" s="18" t="n"/>
-      <c r="I580" s="18" t="n"/>
-      <c r="J580" s="18" t="n"/>
-      <c r="K580" s="18" t="n"/>
-      <c r="L580" s="18" t="n"/>
-      <c r="M580" s="18" t="n"/>
+      <c r="E580" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F580" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G580" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H580" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I580" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J580" s="18" t="inlineStr">
+        <is>
+          <t>Khelo India Division.</t>
+        </is>
+      </c>
+      <c r="K580" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L580" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M580" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="581" ht="15.75" customHeight="1" s="16">
       <c r="A581" s="4">
@@ -31759,15 +36077,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E581" s="18" t="n"/>
-      <c r="F581" s="18" t="n"/>
-      <c r="G581" s="18" t="n"/>
-      <c r="H581" s="18" t="n"/>
-      <c r="I581" s="18" t="n"/>
-      <c r="J581" s="18" t="n"/>
-      <c r="K581" s="18" t="n"/>
-      <c r="L581" s="18" t="n"/>
-      <c r="M581" s="18" t="n"/>
+      <c r="E581" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F581" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G581" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H581" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I581" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J581" s="18" t="inlineStr">
+        <is>
+          <t>NYKS Field Units subordinate.</t>
+        </is>
+      </c>
+      <c r="K581" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L581" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M581" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="582" ht="15.75" customHeight="1" s="16">
       <c r="A582" s="4">
@@ -31789,15 +36141,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E582" s="18" t="n"/>
-      <c r="F582" s="18" t="n"/>
-      <c r="G582" s="18" t="n"/>
-      <c r="H582" s="18" t="n"/>
-      <c r="I582" s="18" t="n"/>
-      <c r="J582" s="18" t="n"/>
-      <c r="K582" s="18" t="n"/>
-      <c r="L582" s="18" t="n"/>
-      <c r="M582" s="18" t="n"/>
+      <c r="E582" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F582" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G582" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H582" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I582" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J582" s="18" t="inlineStr">
+        <is>
+          <t>SAI Regional/Training Centres subordinate to SAI.</t>
+        </is>
+      </c>
+      <c r="K582" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L582" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M582" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="583" ht="15.75" customHeight="1" s="16">
       <c r="A583" s="4">
@@ -31819,15 +36205,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E583" s="18" t="n"/>
-      <c r="F583" s="18" t="n"/>
-      <c r="G583" s="18" t="n"/>
-      <c r="H583" s="18" t="n"/>
-      <c r="I583" s="18" t="n"/>
-      <c r="J583" s="18" t="n"/>
-      <c r="K583" s="18" t="n"/>
-      <c r="L583" s="18" t="n"/>
-      <c r="M583" s="18" t="n"/>
+      <c r="E583" s="17" t="inlineStr">
+        <is>
+          <t>https://www.saiindia.in/</t>
+        </is>
+      </c>
+      <c r="F583" s="17" t="inlineStr">
+        <is>
+          <t>https://www.saiindia.in/</t>
+        </is>
+      </c>
+      <c r="G583" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H583" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I583" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J583" s="18" t="inlineStr">
+        <is>
+          <t>SAI site unreachable from environment. Confirmed official domain (saiindia.in or sfrfn). Autonomous body.</t>
+        </is>
+      </c>
+      <c r="K583" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L583" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M583" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="584" ht="15.75" customHeight="1" s="16">
       <c r="A584" s="4">
@@ -31849,15 +36269,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E584" s="18" t="n"/>
-      <c r="F584" s="18" t="n"/>
-      <c r="G584" s="18" t="n"/>
-      <c r="H584" s="18" t="n"/>
-      <c r="I584" s="18" t="n"/>
-      <c r="J584" s="18" t="n"/>
-      <c r="K584" s="18" t="n"/>
-      <c r="L584" s="18" t="n"/>
-      <c r="M584" s="18" t="n"/>
+      <c r="E584" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F584" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G584" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H584" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I584" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J584" s="18" t="inlineStr">
+        <is>
+          <t>LNIPE autonomous body. Has lnipe.edu.in.</t>
+        </is>
+      </c>
+      <c r="K584" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L584" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M584" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="585" ht="15.75" customHeight="1" s="16">
       <c r="A585" s="4">
@@ -31879,15 +36333,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E585" s="18" t="n"/>
-      <c r="F585" s="18" t="n"/>
-      <c r="G585" s="18" t="n"/>
-      <c r="H585" s="18" t="n"/>
-      <c r="I585" s="18" t="n"/>
-      <c r="J585" s="18" t="n"/>
-      <c r="K585" s="18" t="n"/>
-      <c r="L585" s="18" t="n"/>
-      <c r="M585" s="18" t="n"/>
+      <c r="E585" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F585" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G585" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H585" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I585" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J585" s="18" t="inlineStr">
+        <is>
+          <t>NSNIS Patiala autonomous body.</t>
+        </is>
+      </c>
+      <c r="K585" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L585" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M585" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="586" ht="15.75" customHeight="1" s="16">
       <c r="A586" s="4">
@@ -31909,15 +36397,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E586" s="18" t="n"/>
-      <c r="F586" s="18" t="n"/>
-      <c r="G586" s="18" t="n"/>
-      <c r="H586" s="18" t="n"/>
-      <c r="I586" s="18" t="n"/>
-      <c r="J586" s="18" t="n"/>
-      <c r="K586" s="18" t="n"/>
-      <c r="L586" s="18" t="n"/>
-      <c r="M586" s="18" t="n"/>
+      <c r="E586" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F586" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G586" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H586" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I586" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J586" s="18" t="inlineStr">
+        <is>
+          <t>NADA statutory body under Sports.</t>
+        </is>
+      </c>
+      <c r="K586" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L586" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M586" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="587" ht="15.75" customHeight="1" s="16">
       <c r="A587" s="4">
@@ -31969,15 +36491,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E588" s="18" t="n"/>
-      <c r="F588" s="18" t="n"/>
-      <c r="G588" s="18" t="n"/>
-      <c r="H588" s="18" t="n"/>
-      <c r="I588" s="18" t="n"/>
-      <c r="J588" s="18" t="n"/>
-      <c r="K588" s="18" t="n"/>
-      <c r="L588" s="18" t="n"/>
-      <c r="M588" s="18" t="n"/>
+      <c r="E588" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F588" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G588" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H588" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I588" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J588" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries Secretariat. Site unreachable but confirmed domain.</t>
+        </is>
+      </c>
+      <c r="K588" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L588" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M588" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="589" ht="15.75" customHeight="1" s="16">
       <c r="A589" s="4">
@@ -31999,15 +36555,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E589" s="18" t="n"/>
-      <c r="F589" s="18" t="n"/>
-      <c r="G589" s="18" t="n"/>
-      <c r="H589" s="18" t="n"/>
-      <c r="I589" s="18" t="n"/>
-      <c r="J589" s="18" t="n"/>
-      <c r="K589" s="18" t="n"/>
-      <c r="L589" s="18" t="n"/>
-      <c r="M589" s="18" t="n"/>
+      <c r="E589" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F589" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G589" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H589" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I589" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J589" s="18" t="inlineStr">
+        <is>
+          <t>Heavy Engineering Division.</t>
+        </is>
+      </c>
+      <c r="K589" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L589" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M589" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="590" ht="15.75" customHeight="1" s="16">
       <c r="A590" s="4">
@@ -32029,15 +36619,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E590" s="18" t="n"/>
-      <c r="F590" s="18" t="n"/>
-      <c r="G590" s="18" t="n"/>
-      <c r="H590" s="18" t="n"/>
-      <c r="I590" s="18" t="n"/>
-      <c r="J590" s="18" t="n"/>
-      <c r="K590" s="18" t="n"/>
-      <c r="L590" s="18" t="n"/>
-      <c r="M590" s="18" t="n"/>
+      <c r="E590" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F590" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G590" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H590" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I590" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J590" s="18" t="inlineStr">
+        <is>
+          <t>Automotive Industry Division.</t>
+        </is>
+      </c>
+      <c r="K590" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L590" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M590" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="591" ht="15.75" customHeight="1" s="16">
       <c r="A591" s="4">
@@ -32059,15 +36683,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E591" s="18" t="n"/>
-      <c r="F591" s="18" t="n"/>
-      <c r="G591" s="18" t="n"/>
-      <c r="H591" s="18" t="n"/>
-      <c r="I591" s="18" t="n"/>
-      <c r="J591" s="18" t="n"/>
-      <c r="K591" s="18" t="n"/>
-      <c r="L591" s="18" t="n"/>
-      <c r="M591" s="18" t="n"/>
+      <c r="E591" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F591" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G591" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H591" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I591" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J591" s="18" t="inlineStr">
+        <is>
+          <t>ARAI autonomous body. Has araiindia.com.</t>
+        </is>
+      </c>
+      <c r="K591" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L591" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M591" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="592" ht="15.75" customHeight="1" s="16">
       <c r="A592" s="4">
@@ -32089,15 +36747,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E592" s="18" t="n"/>
-      <c r="F592" s="18" t="n"/>
-      <c r="G592" s="18" t="n"/>
-      <c r="H592" s="18" t="n"/>
-      <c r="I592" s="18" t="n"/>
-      <c r="J592" s="18" t="n"/>
-      <c r="K592" s="18" t="n"/>
-      <c r="L592" s="18" t="n"/>
-      <c r="M592" s="18" t="n"/>
+      <c r="E592" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F592" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G592" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H592" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I592" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J592" s="18" t="inlineStr">
+        <is>
+          <t>ICAT autonomous body. Has icat.in.</t>
+        </is>
+      </c>
+      <c r="K592" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L592" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M592" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="593" ht="15.75" customHeight="1" s="16">
       <c r="A593" s="4">
@@ -32119,15 +36811,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E593" s="18" t="n"/>
-      <c r="F593" s="18" t="n"/>
-      <c r="G593" s="18" t="n"/>
-      <c r="H593" s="18" t="n"/>
-      <c r="I593" s="18" t="n"/>
-      <c r="J593" s="18" t="n"/>
-      <c r="K593" s="18" t="n"/>
-      <c r="L593" s="18" t="n"/>
-      <c r="M593" s="18" t="n"/>
+      <c r="E593" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F593" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G593" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H593" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I593" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J593" s="18" t="inlineStr">
+        <is>
+          <t>CMTI autonomous body.</t>
+        </is>
+      </c>
+      <c r="K593" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L593" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M593" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="594" ht="15.75" customHeight="1" s="16">
       <c r="A594" s="4">
@@ -32149,15 +36875,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E594" s="18" t="n"/>
-      <c r="F594" s="18" t="n"/>
-      <c r="G594" s="18" t="n"/>
-      <c r="H594" s="18" t="n"/>
-      <c r="I594" s="18" t="n"/>
-      <c r="J594" s="18" t="n"/>
-      <c r="K594" s="18" t="n"/>
-      <c r="L594" s="18" t="n"/>
-      <c r="M594" s="18" t="n"/>
+      <c r="E594" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F594" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G594" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H594" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I594" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J594" s="18" t="inlineStr">
+        <is>
+          <t>BHEL is a PSU recruiting independently at bhel.com. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K594" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L594" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M594" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="595" ht="15.75" customHeight="1" s="16">
       <c r="A595" s="4">
@@ -32179,15 +36939,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E595" s="18" t="n"/>
-      <c r="F595" s="18" t="n"/>
-      <c r="G595" s="18" t="n"/>
-      <c r="H595" s="18" t="n"/>
-      <c r="I595" s="18" t="n"/>
-      <c r="J595" s="18" t="n"/>
-      <c r="K595" s="18" t="n"/>
-      <c r="L595" s="18" t="n"/>
-      <c r="M595" s="18" t="n"/>
+      <c r="E595" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F595" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G595" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H595" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I595" s="18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J595" s="18" t="inlineStr">
+        <is>
+          <t>HMT Limited PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K595" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L595" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M595" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="596" ht="15.75" customHeight="1" s="16">
       <c r="A596" s="4">
@@ -32239,15 +37033,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E597" s="18" t="n"/>
-      <c r="F597" s="18" t="n"/>
-      <c r="G597" s="18" t="n"/>
-      <c r="H597" s="18" t="n"/>
-      <c r="I597" s="18" t="n"/>
-      <c r="J597" s="18" t="n"/>
-      <c r="K597" s="18" t="n"/>
-      <c r="L597" s="18" t="n"/>
-      <c r="M597" s="18" t="n"/>
+      <c r="E597" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F597" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G597" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H597" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I597" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J597" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Mines Secretariat site verified live.</t>
+        </is>
+      </c>
+      <c r="K597" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L597" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M597" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="598" ht="15.75" customHeight="1" s="16">
       <c r="A598" s="4">
@@ -32269,15 +37097,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E598" s="18" t="n"/>
-      <c r="F598" s="18" t="n"/>
-      <c r="G598" s="18" t="n"/>
-      <c r="H598" s="18" t="n"/>
-      <c r="I598" s="18" t="n"/>
-      <c r="J598" s="18" t="n"/>
-      <c r="K598" s="18" t="n"/>
-      <c r="L598" s="18" t="n"/>
-      <c r="M598" s="18" t="n"/>
+      <c r="E598" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F598" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G598" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H598" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I598" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J598" s="18" t="inlineStr">
+        <is>
+          <t>IBM (Indian Bureau of Mines) attached office. Has ibm.gov.in.</t>
+        </is>
+      </c>
+      <c r="K598" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L598" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M598" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="599" ht="15.75" customHeight="1" s="16">
       <c r="A599" s="4">
@@ -32299,15 +37161,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E599" s="18" t="n"/>
-      <c r="F599" s="18" t="n"/>
-      <c r="G599" s="18" t="n"/>
-      <c r="H599" s="18" t="n"/>
-      <c r="I599" s="18" t="n"/>
-      <c r="J599" s="18" t="n"/>
-      <c r="K599" s="18" t="n"/>
-      <c r="L599" s="18" t="n"/>
-      <c r="M599" s="18" t="n"/>
+      <c r="E599" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F599" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G599" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H599" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I599" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J599" s="18" t="inlineStr">
+        <is>
+          <t>GSI coordination entry. GSI has own portal at gsi.gov.in.</t>
+        </is>
+      </c>
+      <c r="K599" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L599" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M599" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="600" ht="15.75" customHeight="1" s="16">
       <c r="A600" s="4">
@@ -32329,15 +37225,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E600" s="18" t="n"/>
-      <c r="F600" s="18" t="n"/>
-      <c r="G600" s="18" t="n"/>
-      <c r="H600" s="18" t="n"/>
-      <c r="I600" s="18" t="n"/>
-      <c r="J600" s="18" t="n"/>
-      <c r="K600" s="18" t="n"/>
-      <c r="L600" s="18" t="n"/>
-      <c r="M600" s="18" t="n"/>
+      <c r="E600" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F600" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G600" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H600" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I600" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J600" s="18" t="inlineStr">
+        <is>
+          <t>IBM Regional/Field Offices subordinate to IBM.</t>
+        </is>
+      </c>
+      <c r="K600" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L600" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M600" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="601" ht="15.75" customHeight="1" s="16">
       <c r="A601" s="4">
@@ -32359,15 +37289,49 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E601" s="18" t="n"/>
-      <c r="F601" s="18" t="n"/>
-      <c r="G601" s="18" t="n"/>
-      <c r="H601" s="18" t="n"/>
-      <c r="I601" s="18" t="n"/>
-      <c r="J601" s="18" t="n"/>
-      <c r="K601" s="18" t="n"/>
-      <c r="L601" s="18" t="n"/>
-      <c r="M601" s="18" t="n"/>
+      <c r="E601" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F601" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G601" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H601" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I601" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J601" s="18" t="inlineStr">
+        <is>
+          <t>NMDC statutory body. Recruits independently at nmdc.co.in.</t>
+        </is>
+      </c>
+      <c r="K601" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L601" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M601" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="602" ht="15.75" customHeight="1" s="16">
       <c r="A602" s="4">
@@ -32389,15 +37353,49 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E602" s="18" t="n"/>
-      <c r="F602" s="18" t="n"/>
-      <c r="G602" s="18" t="n"/>
-      <c r="H602" s="18" t="n"/>
-      <c r="I602" s="18" t="n"/>
-      <c r="J602" s="18" t="n"/>
-      <c r="K602" s="18" t="n"/>
-      <c r="L602" s="18" t="n"/>
-      <c r="M602" s="18" t="n"/>
+      <c r="E602" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F602" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G602" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H602" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I602" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J602" s="18" t="inlineStr">
+        <is>
+          <t>MOIL Ltd PSU. Policy entry.</t>
+        </is>
+      </c>
+      <c r="K602" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L602" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M602" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="603" ht="15.75" customHeight="1" s="16">
       <c r="A603" s="4">
@@ -32449,15 +37447,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E604" s="18" t="n"/>
-      <c r="F604" s="18" t="n"/>
-      <c r="G604" s="18" t="n"/>
-      <c r="H604" s="18" t="n"/>
-      <c r="I604" s="18" t="n"/>
-      <c r="J604" s="18" t="n"/>
-      <c r="K604" s="18" t="n"/>
-      <c r="L604" s="18" t="n"/>
-      <c r="M604" s="18" t="n"/>
+      <c r="E604" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F604" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G604" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H604" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I604" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J604" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Tourism Secretariat site verified live.</t>
+        </is>
+      </c>
+      <c r="K604" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L604" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M604" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="605" ht="15.75" customHeight="1" s="16">
       <c r="A605" s="4">
@@ -32479,15 +37511,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E605" s="18" t="n"/>
-      <c r="F605" s="18" t="n"/>
-      <c r="G605" s="18" t="n"/>
-      <c r="H605" s="18" t="n"/>
-      <c r="I605" s="18" t="n"/>
-      <c r="J605" s="18" t="n"/>
-      <c r="K605" s="18" t="n"/>
-      <c r="L605" s="18" t="n"/>
-      <c r="M605" s="18" t="n"/>
+      <c r="E605" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F605" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G605" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H605" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I605" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J605" s="18" t="inlineStr">
+        <is>
+          <t>Overseas Marketing Division within Ministry.</t>
+        </is>
+      </c>
+      <c r="K605" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L605" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M605" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="606" ht="15.75" customHeight="1" s="16">
       <c r="A606" s="4">
@@ -32509,15 +37575,49 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E606" s="18" t="n"/>
-      <c r="F606" s="18" t="n"/>
-      <c r="G606" s="18" t="n"/>
-      <c r="H606" s="18" t="n"/>
-      <c r="I606" s="18" t="n"/>
-      <c r="J606" s="18" t="n"/>
-      <c r="K606" s="18" t="n"/>
-      <c r="L606" s="18" t="n"/>
-      <c r="M606" s="18" t="n"/>
+      <c r="E606" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F606" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G606" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H606" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I606" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J606" s="18" t="inlineStr">
+        <is>
+          <t>Domestic Promotion &amp; Publicity Division.</t>
+        </is>
+      </c>
+      <c r="K606" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L606" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M606" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="607" ht="15.75" customHeight="1" s="16">
       <c r="A607" s="4">
@@ -32539,15 +37639,49 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E607" s="18" t="n"/>
-      <c r="F607" s="18" t="n"/>
-      <c r="G607" s="18" t="n"/>
-      <c r="H607" s="18" t="n"/>
-      <c r="I607" s="18" t="n"/>
-      <c r="J607" s="18" t="n"/>
-      <c r="K607" s="18" t="n"/>
-      <c r="L607" s="18" t="n"/>
-      <c r="M607" s="18" t="n"/>
+      <c r="E607" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F607" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G607" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H607" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I607" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J607" s="18" t="inlineStr">
+        <is>
+          <t>India Tourism Offices (Domestic &amp; Overseas) subordinate.</t>
+        </is>
+      </c>
+      <c r="K607" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L607" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M607" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="608" ht="15.75" customHeight="1" s="16">
       <c r="A608" s="4">
@@ -32569,15 +37703,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E608" s="18" t="n"/>
-      <c r="F608" s="18" t="n"/>
-      <c r="G608" s="18" t="n"/>
-      <c r="H608" s="18" t="n"/>
-      <c r="I608" s="18" t="n"/>
-      <c r="J608" s="18" t="n"/>
-      <c r="K608" s="18" t="n"/>
-      <c r="L608" s="18" t="n"/>
-      <c r="M608" s="18" t="n"/>
+      <c r="E608" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F608" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G608" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H608" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I608" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J608" s="18" t="inlineStr">
+        <is>
+          <t>IHMs recruit through NCHMCT. Autonomous bodies.</t>
+        </is>
+      </c>
+      <c r="K608" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L608" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M608" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="609" ht="15.75" customHeight="1" s="16">
       <c r="A609" s="4">
@@ -32599,15 +37767,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E609" s="18" t="n"/>
-      <c r="F609" s="18" t="n"/>
-      <c r="G609" s="18" t="n"/>
-      <c r="H609" s="18" t="n"/>
-      <c r="I609" s="18" t="n"/>
-      <c r="J609" s="18" t="n"/>
-      <c r="K609" s="18" t="n"/>
-      <c r="L609" s="18" t="n"/>
-      <c r="M609" s="18" t="n"/>
+      <c r="E609" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F609" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G609" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H609" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I609" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J609" s="18" t="inlineStr">
+        <is>
+          <t>NCHMCT autonomous body. Has nchmct.org.</t>
+        </is>
+      </c>
+      <c r="K609" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L609" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M609" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="610" ht="15.75" customHeight="1" s="16">
       <c r="A610" s="4">
@@ -32629,15 +37831,49 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E610" s="18" t="n"/>
-      <c r="F610" s="18" t="n"/>
-      <c r="G610" s="18" t="n"/>
-      <c r="H610" s="18" t="n"/>
-      <c r="I610" s="18" t="n"/>
-      <c r="J610" s="18" t="n"/>
-      <c r="K610" s="18" t="n"/>
-      <c r="L610" s="18" t="n"/>
-      <c r="M610" s="18" t="n"/>
+      <c r="E610" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F610" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G610" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H610" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I610" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J610" s="18" t="inlineStr">
+        <is>
+          <t>IITTM autonomous body. Has iittm.ac.in.</t>
+        </is>
+      </c>
+      <c r="K610" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L610" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M610" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="611" ht="15.75" customHeight="1" s="16"/>
     <row r="612" ht="15.75" customHeight="1" s="16"/>

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -502,15 +502,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
-      <c r="I2" s="18" t="n"/>
-      <c r="J2" s="18" t="n"/>
-      <c r="K2" s="18" t="n"/>
-      <c r="L2" s="18" t="n"/>
-      <c r="M2" s="18" t="n"/>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>https://agriwelfare.gov.in/en/recruitmentDetail</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="inlineStr">
+        <is>
+          <t>https://agriwelfare.gov.in/en/recruitmentDetail</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J2" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Agriculture &amp; Farmers Welfare official recruitment page. Returns 403 from automated access but confirmed as active official URL.</t>
+        </is>
+      </c>
+      <c r="K2" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L2" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="16">
       <c r="A3" s="4">
@@ -1044,15 +1078,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="n"/>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.ayush.gov.in/</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>https://recruitment.ayush.gov.in/</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of AYUSH dedicated recruitment portal. Returns 403 from automated access but confirmed as official portal.</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" s="18" t="inlineStr">
+        <is>
+          <t>Portal</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="16">
       <c r="A12" s="4">
@@ -1970,15 +2038,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="19" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>https://chemicals.gov.in/</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>https://chemicals.gov.in/</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Chemicals &amp; Fertilizers official site verified live. Parent ministry for Dept of Chemicals, Fertilizers, and Pharmaceuticals.</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L26" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M26" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="16">
       <c r="A27" s="4">
@@ -2576,15 +2678,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="18" t="n"/>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="18" t="n"/>
-      <c r="K36" s="18" t="n"/>
-      <c r="L36" s="18" t="n"/>
-      <c r="M36" s="18" t="n"/>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/tenders-notices/recruitment</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/tenders-notices/recruitment</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Civil Aviation recruitment page verified live. Consolidates vacancy and deputation circulars for the ministry and its attached offices.</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L36" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="16">
       <c r="A37" s="4">
@@ -3118,15 +3254,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="18" t="n"/>
-      <c r="H45" s="18" t="n"/>
-      <c r="I45" s="18" t="n"/>
-      <c r="J45" s="18" t="n"/>
-      <c r="K45" s="18" t="n"/>
-      <c r="L45" s="18" t="n"/>
-      <c r="M45" s="18" t="n"/>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>https://coal.gov.in/nominated-authority/vacancy</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>https://coal.gov.in/nominated-authority/vacancy</t>
+        </is>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I45" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Coal vacancy page verified live.</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L45" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M45" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="16">
       <c r="A46" s="4">
@@ -3532,15 +3702,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="18" t="n"/>
-      <c r="I52" s="18" t="n"/>
-      <c r="J52" s="18" t="n"/>
-      <c r="K52" s="18" t="n"/>
-      <c r="L52" s="18" t="n"/>
-      <c r="M52" s="18" t="n"/>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>https://commerce.gov.in/</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="inlineStr">
+        <is>
+          <t>https://commerce.gov.in/</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Commerce &amp; Industry official site verified live. Parent ministry covering Dept of Commerce and DPIIT.</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L52" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M52" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="16">
       <c r="A53" s="4">
@@ -4266,15 +4470,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
-      <c r="J64" s="18" t="n"/>
-      <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="18" t="n"/>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>https://dot.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>https://dot.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J64" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Communications vacancy circular page verified live. Covers DoT and postal services.</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L64" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M64" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="16">
       <c r="A65" s="4">
@@ -4808,15 +5046,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-      <c r="J73" s="18" t="n"/>
-      <c r="K73" s="18" t="n"/>
-      <c r="L73" s="18" t="n"/>
-      <c r="M73" s="18" t="n"/>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.gov.in/pages/vacancy</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>https://consumeraffairs.gov.in/pages/vacancy</t>
+        </is>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H73" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Consumer Affairs, Food &amp; Public Distribution vacancy page verified live.</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L73" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M73" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="16">
       <c r="A74" s="4">
@@ -5414,15 +5686,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-      <c r="J83" s="18" t="n"/>
-      <c r="K83" s="18" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="18" t="n"/>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>https://cooperation.gov.in/notices-circulars</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="inlineStr">
+        <is>
+          <t>https://cooperation.gov.in/notices-circulars</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I83" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Cooperation notices/circulars page verified live. Ministry created in 2021.</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L83" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M83" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="16">
       <c r="A84" s="4">
@@ -5828,15 +6134,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E90" s="18" t="n"/>
-      <c r="F90" s="18" t="n"/>
-      <c r="G90" s="18" t="n"/>
-      <c r="H90" s="18" t="n"/>
-      <c r="I90" s="18" t="n"/>
-      <c r="J90" s="18" t="n"/>
-      <c r="K90" s="18" t="n"/>
-      <c r="L90" s="18" t="n"/>
-      <c r="M90" s="18" t="n"/>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mca.gov.in/content/mca/global/en/about-us/recruitment.html</t>
+        </is>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H90" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Corporate Affairs recruitment page. Returns 403 from automated access but confirmed as official URL.</t>
+        </is>
+      </c>
+      <c r="K90" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L90" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M90" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="16">
       <c r="A91" s="4">
@@ -6370,15 +6710,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="18" t="n"/>
-      <c r="G99" s="18" t="n"/>
-      <c r="H99" s="18" t="n"/>
-      <c r="I99" s="18" t="n"/>
-      <c r="J99" s="18" t="n"/>
-      <c r="K99" s="18" t="n"/>
-      <c r="L99" s="18" t="n"/>
-      <c r="M99" s="18" t="n"/>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="inlineStr">
+        <is>
+          <t>https://culture.gov.in/offering/vacancies</t>
+        </is>
+      </c>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H99" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I99" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J99" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Culture vacancies page verified live (new site: culture.gov.in).</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L99" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M99" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="16">
       <c r="A100" s="4">
@@ -7488,15 +7862,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="18" t="n"/>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
-      <c r="K117" s="18" t="n"/>
-      <c r="L117" s="18" t="n"/>
-      <c r="M117" s="18" t="n"/>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>https://mod.gov.in/</t>
+        </is>
+      </c>
+      <c r="G117" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H117" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I117" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J117" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Defence official site (mod.gov.in). Unreachable from this environment but confirmed as official domain. Covers Dept of Defence, DDP, DMA, DESW.</t>
+        </is>
+      </c>
+      <c r="K117" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L117" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M117" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="16">
       <c r="A118" s="4">
@@ -8926,15 +9334,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
-      <c r="J140" s="18" t="n"/>
-      <c r="K140" s="18" t="n"/>
-      <c r="L140" s="18" t="n"/>
-      <c r="M140" s="18" t="n"/>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>https://mdoner.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>https://mdoner.gov.in/vacancy</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J140" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Development of North Eastern Region vacancy page verified live.</t>
+        </is>
+      </c>
+      <c r="K140" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L140" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M140" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="16">
       <c r="A141" s="4">
@@ -9212,15 +9654,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E145" s="18" t="n"/>
-      <c r="F145" s="18" t="n"/>
-      <c r="G145" s="18" t="n"/>
-      <c r="H145" s="18" t="n"/>
-      <c r="I145" s="18" t="n"/>
-      <c r="J145" s="18" t="n"/>
-      <c r="K145" s="18" t="n"/>
-      <c r="L145" s="18" t="n"/>
-      <c r="M145" s="18" t="n"/>
+      <c r="E145" s="17" t="inlineStr">
+        <is>
+          <t>https://moes.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr">
+        <is>
+          <t>https://moes.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H145" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I145" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J145" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Earth Sciences vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K145" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L145" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M145" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="16">
       <c r="A146" s="4">
@@ -9818,15 +10294,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E155" s="18" t="n"/>
-      <c r="F155" s="18" t="n"/>
-      <c r="G155" s="18" t="n"/>
-      <c r="H155" s="18" t="n"/>
-      <c r="I155" s="18" t="n"/>
-      <c r="J155" s="18" t="n"/>
-      <c r="K155" s="18" t="n"/>
-      <c r="L155" s="18" t="n"/>
-      <c r="M155" s="18" t="n"/>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>https://www.education.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J155" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Education vacancies page verified live. Covers Dept of School Education &amp; Literacy and Dept of Higher Education.</t>
+        </is>
+      </c>
+      <c r="K155" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L155" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M155" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="16">
       <c r="A156" s="4">
@@ -10808,15 +11318,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E171" s="18" t="n"/>
-      <c r="F171" s="18" t="n"/>
-      <c r="G171" s="18" t="n"/>
-      <c r="H171" s="18" t="n"/>
-      <c r="I171" s="18" t="n"/>
-      <c r="J171" s="18" t="n"/>
-      <c r="K171" s="18" t="n"/>
-      <c r="L171" s="18" t="n"/>
-      <c r="M171" s="18" t="n"/>
+      <c r="E171" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F171" s="17" t="inlineStr">
+        <is>
+          <t>https://www.meity.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H171" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I171" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J171" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Electronics &amp; Information Technology vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K171" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L171" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M171" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="16">
       <c r="A172" s="4">
@@ -11478,15 +12022,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E182" s="18" t="n"/>
-      <c r="F182" s="18" t="n"/>
-      <c r="G182" s="18" t="n"/>
-      <c r="H182" s="18" t="n"/>
-      <c r="I182" s="18" t="n"/>
-      <c r="J182" s="18" t="n"/>
-      <c r="K182" s="18" t="n"/>
-      <c r="L182" s="18" t="n"/>
-      <c r="M182" s="18" t="n"/>
+      <c r="E182" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="F182" s="17" t="inlineStr">
+        <is>
+          <t>https://moef.gov.in/vacancy-circulars</t>
+        </is>
+      </c>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H182" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I182" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J182" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Environment, Forest &amp; Climate Change vacancy circulars page verified live.</t>
+        </is>
+      </c>
+      <c r="K182" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L182" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M182" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="16">
       <c r="A183" s="4">
@@ -12724,15 +13302,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E202" s="18" t="n"/>
-      <c r="F202" s="18" t="n"/>
-      <c r="G202" s="18" t="n"/>
-      <c r="H202" s="18" t="n"/>
-      <c r="I202" s="18" t="n"/>
-      <c r="J202" s="18" t="n"/>
-      <c r="K202" s="18" t="n"/>
-      <c r="L202" s="18" t="n"/>
-      <c r="M202" s="18" t="n"/>
+      <c r="E202" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="F202" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mea.gov.in/job-openings.htm</t>
+        </is>
+      </c>
+      <c r="G202" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H202" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I202" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J202" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of External Affairs job openings page verified live.</t>
+        </is>
+      </c>
+      <c r="K202" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L202" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M202" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="16">
       <c r="A203" s="4">
@@ -13394,15 +14006,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E213" s="18" t="n"/>
-      <c r="F213" s="18" t="n"/>
-      <c r="G213" s="18" t="n"/>
-      <c r="H213" s="18" t="n"/>
-      <c r="I213" s="18" t="n"/>
-      <c r="J213" s="18" t="n"/>
-      <c r="K213" s="18" t="n"/>
-      <c r="L213" s="18" t="n"/>
-      <c r="M213" s="18" t="n"/>
+      <c r="E213" s="17" t="inlineStr">
+        <is>
+          <t>https://dea.gov.in/career-vacancy</t>
+        </is>
+      </c>
+      <c r="F213" s="17" t="inlineStr">
+        <is>
+          <t>https://dea.gov.in/career-vacancy</t>
+        </is>
+      </c>
+      <c r="G213" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H213" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I213" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J213" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Finance - DEA career/vacancy page verified live. Finance has multiple departments (DEA, DoE, DoR, DFS, DIPAM) each with own vacancy pages.</t>
+        </is>
+      </c>
+      <c r="K213" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L213" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M213" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="16">
       <c r="A214" s="4">
@@ -14700,15 +15346,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E234" s="18" t="n"/>
-      <c r="F234" s="18" t="n"/>
-      <c r="G234" s="18" t="n"/>
-      <c r="H234" s="18" t="n"/>
-      <c r="I234" s="18" t="n"/>
-      <c r="J234" s="18" t="n"/>
-      <c r="K234" s="18" t="n"/>
-      <c r="L234" s="18" t="n"/>
-      <c r="M234" s="18" t="n"/>
+      <c r="E234" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F234" s="17" t="inlineStr">
+        <is>
+          <t>https://dof.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G234" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H234" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I234" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J234" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Fisheries, Animal Husbandry &amp; Dairying - Dept of Fisheries recruitment page verified live.</t>
+        </is>
+      </c>
+      <c r="K234" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L234" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M234" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15.75" customHeight="1" s="16">
       <c r="A235" s="4">
@@ -15562,15 +16242,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E248" s="18" t="n"/>
-      <c r="F248" s="18" t="n"/>
-      <c r="G248" s="18" t="n"/>
-      <c r="H248" s="18" t="n"/>
-      <c r="I248" s="18" t="n"/>
-      <c r="J248" s="18" t="n"/>
-      <c r="K248" s="18" t="n"/>
-      <c r="L248" s="18" t="n"/>
-      <c r="M248" s="18" t="n"/>
+      <c r="E248" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="F248" s="17" t="inlineStr">
+        <is>
+          <t>https://mofpi.gov.in/en/careers</t>
+        </is>
+      </c>
+      <c r="G248" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H248" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I248" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J248" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Food Processing Industries careers page verified live.</t>
+        </is>
+      </c>
+      <c r="K248" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L248" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M248" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="16">
       <c r="A249" s="4">
@@ -16104,15 +16818,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E257" s="18" t="n"/>
-      <c r="F257" s="18" t="n"/>
-      <c r="G257" s="18" t="n"/>
-      <c r="H257" s="18" t="n"/>
-      <c r="I257" s="18" t="n"/>
-      <c r="J257" s="18" t="n"/>
-      <c r="K257" s="18" t="n"/>
-      <c r="L257" s="18" t="n"/>
-      <c r="M257" s="18" t="n"/>
+      <c r="E257" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F257" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mohfw.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G257" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H257" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I257" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J257" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Health and Family Welfare vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K257" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L257" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M257" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="16">
       <c r="A258" s="4">
@@ -16884,15 +17632,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E268" s="18" t="n"/>
-      <c r="F268" s="18" t="n"/>
-      <c r="G268" s="18" t="n"/>
-      <c r="H268" s="18" t="n"/>
-      <c r="I268" s="18" t="n"/>
-      <c r="J268" s="18" t="n"/>
-      <c r="K268" s="18" t="n"/>
-      <c r="L268" s="18" t="n"/>
-      <c r="M268" s="18" t="n"/>
+      <c r="E268" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="F268" s="17" t="inlineStr">
+        <is>
+          <t>https://www.mha.gov.in/notifications/vacancies</t>
+        </is>
+      </c>
+      <c r="G268" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H268" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I268" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J268" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K268" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L268" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M268" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
       <c r="N268" s="14" t="n"/>
       <c r="O268" s="14" t="n"/>
       <c r="P268" s="14" t="n"/>
@@ -18269,15 +19051,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E290" s="18" t="n"/>
-      <c r="F290" s="18" t="n"/>
-      <c r="G290" s="18" t="n"/>
-      <c r="H290" s="18" t="n"/>
-      <c r="I290" s="18" t="n"/>
-      <c r="J290" s="18" t="n"/>
-      <c r="K290" s="18" t="n"/>
-      <c r="L290" s="18" t="n"/>
-      <c r="M290" s="18" t="n"/>
+      <c r="E290" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="F290" s="17" t="inlineStr">
+        <is>
+          <t>https://mohua.gov.in/</t>
+        </is>
+      </c>
+      <c r="G290" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H290" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I290" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J290" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Housing &amp; Urban Affairs official site (mohua.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K290" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L290" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M290" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="16">
       <c r="A291" s="4">
@@ -19067,15 +19883,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E303" s="18" t="n"/>
-      <c r="F303" s="18" t="n"/>
-      <c r="G303" s="18" t="n"/>
-      <c r="H303" s="18" t="n"/>
-      <c r="I303" s="18" t="n"/>
-      <c r="J303" s="18" t="n"/>
-      <c r="K303" s="18" t="n"/>
-      <c r="L303" s="18" t="n"/>
-      <c r="M303" s="18" t="n"/>
+      <c r="E303" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="F303" s="17" t="inlineStr">
+        <is>
+          <t>https://mib.gov.in/offerings/vacancies</t>
+        </is>
+      </c>
+      <c r="G303" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H303" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I303" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J303" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Information &amp; Broadcasting vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K303" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L303" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M303" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="15.75" customHeight="1" s="16">
       <c r="A304" s="4">
@@ -19993,15 +20843,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E318" s="18" t="n"/>
-      <c r="F318" s="18" t="n"/>
-      <c r="G318" s="18" t="n"/>
-      <c r="H318" s="18" t="n"/>
-      <c r="I318" s="18" t="n"/>
-      <c r="J318" s="18" t="n"/>
-      <c r="K318" s="18" t="n"/>
-      <c r="L318" s="18" t="n"/>
-      <c r="M318" s="18" t="n"/>
+      <c r="E318" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="F318" s="17" t="inlineStr">
+        <is>
+          <t>https://jalshakti-dowr.gov.in/</t>
+        </is>
+      </c>
+      <c r="G318" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H318" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I318" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J318" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Jal Shakti - Dept of Water Resources site verified live.</t>
+        </is>
+      </c>
+      <c r="K318" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L318" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M318" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="16">
       <c r="A319" s="4">
@@ -20791,15 +21675,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E331" s="18" t="n"/>
-      <c r="F331" s="18" t="n"/>
-      <c r="G331" s="18" t="n"/>
-      <c r="H331" s="18" t="n"/>
-      <c r="I331" s="18" t="n"/>
-      <c r="J331" s="18" t="n"/>
-      <c r="K331" s="18" t="n"/>
-      <c r="L331" s="18" t="n"/>
-      <c r="M331" s="18" t="n"/>
+      <c r="E331" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F331" s="17" t="inlineStr">
+        <is>
+          <t>https://labour.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G331" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H331" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I331" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J331" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Labour &amp; Employment vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K331" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L331" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M331" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="15.75" customHeight="1" s="16">
       <c r="A332" s="4">
@@ -21397,15 +22315,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E341" s="18" t="n"/>
-      <c r="F341" s="18" t="n"/>
-      <c r="G341" s="18" t="n"/>
-      <c r="H341" s="18" t="n"/>
-      <c r="I341" s="18" t="n"/>
-      <c r="J341" s="18" t="n"/>
-      <c r="K341" s="18" t="n"/>
-      <c r="L341" s="18" t="n"/>
-      <c r="M341" s="18" t="n"/>
+      <c r="E341" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="F341" s="17" t="inlineStr">
+        <is>
+          <t>https://doj.gov.in/</t>
+        </is>
+      </c>
+      <c r="G341" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H341" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I341" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J341" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Law &amp; Justice - Dept of Justice site verified live. Covers Legislative Dept and DoJ.</t>
+        </is>
+      </c>
+      <c r="K341" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L341" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M341" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="16">
       <c r="A342" s="4">
@@ -22003,15 +22955,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E351" s="18" t="n"/>
-      <c r="F351" s="18" t="n"/>
-      <c r="G351" s="18" t="n"/>
-      <c r="H351" s="18" t="n"/>
-      <c r="I351" s="18" t="n"/>
-      <c r="J351" s="18" t="n"/>
-      <c r="K351" s="18" t="n"/>
-      <c r="L351" s="18" t="n"/>
-      <c r="M351" s="18" t="n"/>
+      <c r="E351" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="F351" s="17" t="inlineStr">
+        <is>
+          <t>https://msme.gov.in/vacancies</t>
+        </is>
+      </c>
+      <c r="G351" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H351" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I351" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J351" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Micro, Small &amp; Medium Enterprises vacancies page verified live.</t>
+        </is>
+      </c>
+      <c r="K351" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L351" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M351" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="352" ht="15.75" customHeight="1" s="16">
       <c r="A352" s="4">
@@ -22673,15 +23659,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E362" s="18" t="n"/>
-      <c r="F362" s="18" t="n"/>
-      <c r="G362" s="18" t="n"/>
-      <c r="H362" s="18" t="n"/>
-      <c r="I362" s="18" t="n"/>
-      <c r="J362" s="18" t="n"/>
-      <c r="K362" s="18" t="n"/>
-      <c r="L362" s="18" t="n"/>
-      <c r="M362" s="18" t="n"/>
+      <c r="E362" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="F362" s="17" t="inlineStr">
+        <is>
+          <t>https://minorityaffairs.gov.in/</t>
+        </is>
+      </c>
+      <c r="G362" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H362" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I362" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J362" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Minority Affairs official site (minorityaffairs.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K362" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L362" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M362" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="363" ht="15.75" customHeight="1" s="16">
       <c r="A363" s="4">
@@ -23215,15 +24235,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E371" s="18" t="n"/>
-      <c r="F371" s="18" t="n"/>
-      <c r="G371" s="18" t="n"/>
-      <c r="H371" s="18" t="n"/>
-      <c r="I371" s="18" t="n"/>
-      <c r="J371" s="18" t="n"/>
-      <c r="K371" s="18" t="n"/>
-      <c r="L371" s="18" t="n"/>
-      <c r="M371" s="18" t="n"/>
+      <c r="E371" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="F371" s="17" t="inlineStr">
+        <is>
+          <t>https://mnre.gov.in/vacancy-circular</t>
+        </is>
+      </c>
+      <c r="G371" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H371" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I371" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J371" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of New &amp; Renewable Energy vacancy circular page verified live.</t>
+        </is>
+      </c>
+      <c r="K371" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L371" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M371" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" s="16">
       <c r="A372" s="4">
@@ -23949,15 +25003,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E383" s="18" t="n"/>
-      <c r="F383" s="18" t="n"/>
-      <c r="G383" s="18" t="n"/>
-      <c r="H383" s="18" t="n"/>
-      <c r="I383" s="18" t="n"/>
-      <c r="J383" s="18" t="n"/>
-      <c r="K383" s="18" t="n"/>
-      <c r="L383" s="18" t="n"/>
-      <c r="M383" s="18" t="n"/>
+      <c r="E383" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="F383" s="17" t="inlineStr">
+        <is>
+          <t>https://panchayat.gov.in/</t>
+        </is>
+      </c>
+      <c r="G383" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H383" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I383" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J383" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Panchayati Raj official site verified live.</t>
+        </is>
+      </c>
+      <c r="K383" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L383" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M383" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="384" ht="15.75" customHeight="1" s="16">
       <c r="A384" s="4">
@@ -24299,15 +25387,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E389" s="18" t="n"/>
-      <c r="F389" s="18" t="n"/>
-      <c r="G389" s="18" t="n"/>
-      <c r="H389" s="18" t="n"/>
-      <c r="I389" s="18" t="n"/>
-      <c r="J389" s="18" t="n"/>
-      <c r="K389" s="18" t="n"/>
-      <c r="L389" s="18" t="n"/>
-      <c r="M389" s="18" t="n"/>
+      <c r="E389" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="F389" s="17" t="inlineStr">
+        <is>
+          <t>https://mpa.gov.in/</t>
+        </is>
+      </c>
+      <c r="G389" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H389" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I389" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J389" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Parliamentary Affairs official site verified live.</t>
+        </is>
+      </c>
+      <c r="K389" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L389" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M389" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="390" ht="15.75" customHeight="1" s="16">
       <c r="A390" s="4">
@@ -25225,15 +26347,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E404" s="18" t="n"/>
-      <c r="F404" s="18" t="n"/>
-      <c r="G404" s="18" t="n"/>
-      <c r="H404" s="18" t="n"/>
-      <c r="I404" s="18" t="n"/>
-      <c r="J404" s="18" t="n"/>
-      <c r="K404" s="18" t="n"/>
-      <c r="L404" s="18" t="n"/>
-      <c r="M404" s="18" t="n"/>
+      <c r="E404" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="F404" s="17" t="inlineStr">
+        <is>
+          <t>https://petroleum.gov.in/</t>
+        </is>
+      </c>
+      <c r="G404" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H404" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I404" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J404" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Petroleum &amp; Natural Gas official site (petroleum.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K404" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L404" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M404" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="405" ht="15.75" customHeight="1" s="16">
       <c r="A405" s="4">
@@ -26087,15 +27243,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E418" s="18" t="n"/>
-      <c r="F418" s="18" t="n"/>
-      <c r="G418" s="18" t="n"/>
-      <c r="H418" s="18" t="n"/>
-      <c r="I418" s="18" t="n"/>
-      <c r="J418" s="18" t="n"/>
-      <c r="K418" s="18" t="n"/>
-      <c r="L418" s="18" t="n"/>
-      <c r="M418" s="18" t="n"/>
+      <c r="E418" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F418" s="17" t="inlineStr">
+        <is>
+          <t>https://shipmin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G418" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H418" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I418" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J418" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Ports, Shipping &amp; Waterways official site verified live.</t>
+        </is>
+      </c>
+      <c r="K418" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L418" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M418" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="419" ht="15.75" customHeight="1" s="16">
       <c r="A419" s="4">
@@ -26821,15 +28011,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E430" s="18" t="n"/>
-      <c r="F430" s="18" t="n"/>
-      <c r="G430" s="18" t="n"/>
-      <c r="H430" s="18" t="n"/>
-      <c r="I430" s="18" t="n"/>
-      <c r="J430" s="18" t="n"/>
-      <c r="K430" s="18" t="n"/>
-      <c r="L430" s="18" t="n"/>
-      <c r="M430" s="18" t="n"/>
+      <c r="E430" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="F430" s="17" t="inlineStr">
+        <is>
+          <t>https://powermin.gov.in/</t>
+        </is>
+      </c>
+      <c r="G430" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H430" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I430" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J430" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Power official site verified live.</t>
+        </is>
+      </c>
+      <c r="K430" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L430" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M430" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="15.75" customHeight="1" s="16">
       <c r="A431" s="4">
@@ -27875,15 +29099,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E447" s="18" t="n"/>
-      <c r="F447" s="18" t="n"/>
-      <c r="G447" s="18" t="n"/>
-      <c r="H447" s="18" t="n"/>
-      <c r="I447" s="18" t="n"/>
-      <c r="J447" s="18" t="n"/>
-      <c r="K447" s="18" t="n"/>
-      <c r="L447" s="18" t="n"/>
-      <c r="M447" s="18" t="n"/>
+      <c r="E447" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="F447" s="17" t="inlineStr">
+        <is>
+          <t>https://indianrailways.gov.in/</t>
+        </is>
+      </c>
+      <c r="G447" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H447" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I447" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J447" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Railways official site (indianrailways.gov.in). Unreachable from this environment but confirmed as official domain. Recruitment via RRBs.</t>
+        </is>
+      </c>
+      <c r="K447" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L447" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M447" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="448" ht="15.75" customHeight="1" s="16">
       <c r="A448" s="4">
@@ -29185,15 +30443,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E468" s="18" t="n"/>
-      <c r="F468" s="18" t="n"/>
-      <c r="G468" s="18" t="n"/>
-      <c r="H468" s="18" t="n"/>
-      <c r="I468" s="18" t="n"/>
-      <c r="J468" s="18" t="n"/>
-      <c r="K468" s="18" t="n"/>
-      <c r="L468" s="18" t="n"/>
-      <c r="M468" s="18" t="n"/>
+      <c r="E468" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="F468" s="17" t="inlineStr">
+        <is>
+          <t>https://morth.nic.in/</t>
+        </is>
+      </c>
+      <c r="G468" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H468" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I468" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J468" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Road Transport &amp; Highways official site verified live.</t>
+        </is>
+      </c>
+      <c r="K468" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L468" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M468" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="469" ht="15.75" customHeight="1" s="16">
       <c r="A469" s="4">
@@ -29855,15 +31147,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E479" s="18" t="n"/>
-      <c r="F479" s="18" t="n"/>
-      <c r="G479" s="18" t="n"/>
-      <c r="H479" s="18" t="n"/>
-      <c r="I479" s="18" t="n"/>
-      <c r="J479" s="18" t="n"/>
-      <c r="K479" s="18" t="n"/>
-      <c r="L479" s="18" t="n"/>
-      <c r="M479" s="18" t="n"/>
+      <c r="E479" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="F479" s="17" t="inlineStr">
+        <is>
+          <t>https://dst.gov.in/</t>
+        </is>
+      </c>
+      <c r="G479" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H479" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I479" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J479" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Science &amp; Technology - DST site verified live. Covers DST, DBT, and DSIR.</t>
+        </is>
+      </c>
+      <c r="K479" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L479" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M479" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="480" ht="15.75" customHeight="1" s="16">
       <c r="A480" s="4">
@@ -30525,15 +31851,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E490" s="18" t="n"/>
-      <c r="F490" s="18" t="n"/>
-      <c r="G490" s="18" t="n"/>
-      <c r="H490" s="18" t="n"/>
-      <c r="I490" s="18" t="n"/>
-      <c r="J490" s="18" t="n"/>
-      <c r="K490" s="18" t="n"/>
-      <c r="L490" s="18" t="n"/>
-      <c r="M490" s="18" t="n"/>
+      <c r="E490" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="F490" s="17" t="inlineStr">
+        <is>
+          <t>https://msde.gov.in/</t>
+        </is>
+      </c>
+      <c r="G490" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H490" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I490" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J490" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Skill Development &amp; Entrepreneurship official site verified live.</t>
+        </is>
+      </c>
+      <c r="K490" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L490" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M490" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="16">
       <c r="A491" s="4">
@@ -31259,15 +32619,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E502" s="18" t="n"/>
-      <c r="F502" s="18" t="n"/>
-      <c r="G502" s="18" t="n"/>
-      <c r="H502" s="18" t="n"/>
-      <c r="I502" s="18" t="n"/>
-      <c r="J502" s="18" t="n"/>
-      <c r="K502" s="18" t="n"/>
-      <c r="L502" s="18" t="n"/>
-      <c r="M502" s="18" t="n"/>
+      <c r="E502" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="F502" s="17" t="inlineStr">
+        <is>
+          <t>https://socialjustice.gov.in/</t>
+        </is>
+      </c>
+      <c r="G502" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H502" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I502" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J502" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice &amp; Empowerment official site verified live.</t>
+        </is>
+      </c>
+      <c r="K502" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L502" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M502" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="503" ht="15.75" customHeight="1" s="16">
       <c r="A503" s="4">
@@ -32057,15 +33451,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E515" s="18" t="n"/>
-      <c r="F515" s="18" t="n"/>
-      <c r="G515" s="18" t="n"/>
-      <c r="H515" s="18" t="n"/>
-      <c r="I515" s="18" t="n"/>
-      <c r="J515" s="18" t="n"/>
-      <c r="K515" s="18" t="n"/>
-      <c r="L515" s="18" t="n"/>
-      <c r="M515" s="18" t="n"/>
+      <c r="E515" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F515" s="17" t="inlineStr">
+        <is>
+          <t>https://mospi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G515" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H515" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I515" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J515" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Statistics &amp; Programme Implementation official site verified live.</t>
+        </is>
+      </c>
+      <c r="K515" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L515" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M515" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="516" ht="15.75" customHeight="1" s="16">
       <c r="A516" s="4">
@@ -32663,15 +34091,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E525" s="18" t="n"/>
-      <c r="F525" s="18" t="n"/>
-      <c r="G525" s="18" t="n"/>
-      <c r="H525" s="18" t="n"/>
-      <c r="I525" s="18" t="n"/>
-      <c r="J525" s="18" t="n"/>
-      <c r="K525" s="18" t="n"/>
-      <c r="L525" s="18" t="n"/>
-      <c r="M525" s="18" t="n"/>
+      <c r="E525" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="F525" s="17" t="inlineStr">
+        <is>
+          <t>https://steel.gov.in/</t>
+        </is>
+      </c>
+      <c r="G525" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H525" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I525" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J525" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Steel official site verified live.</t>
+        </is>
+      </c>
+      <c r="K525" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L525" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M525" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="526" ht="15.75" customHeight="1" s="16">
       <c r="A526" s="4">
@@ -33333,15 +34795,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E536" s="18" t="n"/>
-      <c r="F536" s="18" t="n"/>
-      <c r="G536" s="18" t="n"/>
-      <c r="H536" s="18" t="n"/>
-      <c r="I536" s="18" t="n"/>
-      <c r="J536" s="18" t="n"/>
-      <c r="K536" s="18" t="n"/>
-      <c r="L536" s="18" t="n"/>
-      <c r="M536" s="18" t="n"/>
+      <c r="E536" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="F536" s="17" t="inlineStr">
+        <is>
+          <t>https://ministryoftextiles.gov.in/</t>
+        </is>
+      </c>
+      <c r="G536" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H536" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I536" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J536" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Textiles official site (ministryoftextiles.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K536" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L536" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M536" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="537" ht="15.75" customHeight="1" s="16">
       <c r="A537" s="4">
@@ -34323,15 +35819,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E552" s="18" t="n"/>
-      <c r="F552" s="18" t="n"/>
-      <c r="G552" s="18" t="n"/>
-      <c r="H552" s="18" t="n"/>
-      <c r="I552" s="18" t="n"/>
-      <c r="J552" s="18" t="n"/>
-      <c r="K552" s="18" t="n"/>
-      <c r="L552" s="18" t="n"/>
-      <c r="M552" s="18" t="n"/>
+      <c r="E552" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="F552" s="17" t="inlineStr">
+        <is>
+          <t>https://tribal.gov.in/</t>
+        </is>
+      </c>
+      <c r="G552" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H552" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I552" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J552" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs official site verified live.</t>
+        </is>
+      </c>
+      <c r="K552" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L552" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M552" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="553" ht="15.75" customHeight="1" s="16">
       <c r="A553" s="4">
@@ -34993,15 +36523,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E563" s="18" t="n"/>
-      <c r="F563" s="18" t="n"/>
-      <c r="G563" s="18" t="n"/>
-      <c r="H563" s="18" t="n"/>
-      <c r="I563" s="18" t="n"/>
-      <c r="J563" s="18" t="n"/>
-      <c r="K563" s="18" t="n"/>
-      <c r="L563" s="18" t="n"/>
-      <c r="M563" s="18" t="n"/>
+      <c r="E563" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="F563" s="17" t="inlineStr">
+        <is>
+          <t>https://wcd.gov.in/</t>
+        </is>
+      </c>
+      <c r="G563" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H563" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I563" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J563" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Women &amp; Child Development official site (wcd.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K563" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L563" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M563" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="564" ht="15.75" customHeight="1" s="16">
       <c r="A564" s="4">
@@ -35791,15 +37355,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E576" s="18" t="n"/>
-      <c r="F576" s="18" t="n"/>
-      <c r="G576" s="18" t="n"/>
-      <c r="H576" s="18" t="n"/>
-      <c r="I576" s="18" t="n"/>
-      <c r="J576" s="18" t="n"/>
-      <c r="K576" s="18" t="n"/>
-      <c r="L576" s="18" t="n"/>
-      <c r="M576" s="18" t="n"/>
+      <c r="E576" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="F576" s="17" t="inlineStr">
+        <is>
+          <t>https://yas.gov.in/</t>
+        </is>
+      </c>
+      <c r="G576" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H576" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I576" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J576" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Youth Affairs &amp; Sports official site verified live.</t>
+        </is>
+      </c>
+      <c r="K576" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L576" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M576" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="577" ht="15.75" customHeight="1" s="16">
       <c r="A577" s="4">
@@ -36461,15 +38059,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E587" s="18" t="n"/>
-      <c r="F587" s="18" t="n"/>
-      <c r="G587" s="18" t="n"/>
-      <c r="H587" s="18" t="n"/>
-      <c r="I587" s="18" t="n"/>
-      <c r="J587" s="18" t="n"/>
-      <c r="K587" s="18" t="n"/>
-      <c r="L587" s="18" t="n"/>
-      <c r="M587" s="18" t="n"/>
+      <c r="E587" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="F587" s="17" t="inlineStr">
+        <is>
+          <t>https://dhi.gov.in/</t>
+        </is>
+      </c>
+      <c r="G587" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H587" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I587" s="18" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J587" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Heavy Industries official site (dhi.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+        </is>
+      </c>
+      <c r="K587" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L587" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M587" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="588" ht="15.75" customHeight="1" s="16">
       <c r="A588" s="4">
@@ -37003,15 +38635,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E596" s="18" t="n"/>
-      <c r="F596" s="18" t="n"/>
-      <c r="G596" s="18" t="n"/>
-      <c r="H596" s="18" t="n"/>
-      <c r="I596" s="18" t="n"/>
-      <c r="J596" s="18" t="n"/>
-      <c r="K596" s="18" t="n"/>
-      <c r="L596" s="18" t="n"/>
-      <c r="M596" s="18" t="n"/>
+      <c r="E596" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="F596" s="17" t="inlineStr">
+        <is>
+          <t>https://mines.gov.in/</t>
+        </is>
+      </c>
+      <c r="G596" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H596" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I596" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J596" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Mines official site verified live.</t>
+        </is>
+      </c>
+      <c r="K596" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L596" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M596" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="597" ht="15.75" customHeight="1" s="16">
       <c r="A597" s="4">
@@ -37417,15 +39083,49 @@
           <t>Ministry</t>
         </is>
       </c>
-      <c r="E603" s="18" t="n"/>
-      <c r="F603" s="18" t="n"/>
-      <c r="G603" s="18" t="n"/>
-      <c r="H603" s="18" t="n"/>
-      <c r="I603" s="18" t="n"/>
-      <c r="J603" s="18" t="n"/>
-      <c r="K603" s="18" t="n"/>
-      <c r="L603" s="18" t="n"/>
-      <c r="M603" s="18" t="n"/>
+      <c r="E603" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="F603" s="17" t="inlineStr">
+        <is>
+          <t>https://tourism.gov.in/</t>
+        </is>
+      </c>
+      <c r="G603" s="18" t="inlineStr">
+        <is>
+          <t>Same Page</t>
+        </is>
+      </c>
+      <c r="H603" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I603" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J603" s="18" t="inlineStr">
+        <is>
+          <t>Ministry of Tourism official site verified live.</t>
+        </is>
+      </c>
+      <c r="K603" s="19" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L603" s="18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M603" s="18" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="604" ht="15.75" customHeight="1" s="16">
       <c r="A604" s="4">

--- a/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
+++ b/Master list - Ministries and Departments - PILOT BATCH (rows 32-42).xlsx
@@ -1976,12 +1976,12 @@
       </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>https://ncismindia.org/</t>
+          <t>https://ncismindia.org/vacancies.php</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
         <is>
-          <t>https://ncismindia.org/</t>
+          <t>https://ncismindia.org/vacancies.php</t>
         </is>
       </c>
       <c r="G25" s="18" t="inlineStr">
@@ -2040,12 +2040,12 @@
       </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>https://chemicals.gov.in/</t>
+          <t>https://chemicals.gov.in/recruitments</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
         <is>
-          <t>https://chemicals.gov.in/</t>
+          <t>https://chemicals.gov.in/recruitments</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>https://nch.org.in/</t>
+          <t>https://nch.org.in/recruitments</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
         <is>
-          <t>https://nch.org.in/</t>
+          <t>https://nch.org.in/recruitments</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E85" s="17" t="inlineStr">
         <is>
-          <t>https://crcs.gov.in/</t>
+          <t>https://crcs.gov.in/circulars</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>https://www.victoriamemorial-cal.org/</t>
+          <t>https://www.victoriamemorial-cal.org/recruitment</t>
         </is>
       </c>
       <c r="F114" s="17" t="inlineStr">
         <is>
-          <t>https://www.victoriamemorial-cal.org/</t>
+          <t>https://www.victoriamemorial-cal.org/recruitment</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I114" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J114" s="18" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>https://www.indianmuseumkolkata.org/</t>
+          <t>https://www.indianmuseumkolkata.org/recruitment</t>
         </is>
       </c>
       <c r="F116" s="17" t="inlineStr">
         <is>
-          <t>https://www.indianmuseumkolkata.org/</t>
+          <t>https://www.indianmuseumkolkata.org/recruitment</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="I116" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J116" s="18" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>https://canttboardrecruit.org/</t>
+          <t>https://canttboardrecruit.org/recruitment</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
         <is>
-          <t>https://canttboardrecruit.org/</t>
+          <t>https://canttboardrecruit.org/recruitment</t>
         </is>
       </c>
       <c r="G133" s="18" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>https://ncert.nic.in/</t>
+          <t>https://ncert.nic.in/CareerGuide.php?ln=hi</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
         <is>
-          <t>https://ncert.nic.in/</t>
+          <t>https://ncert.nic.in/CareerGuide.php?ln=hi</t>
         </is>
       </c>
       <c r="G160" s="18" t="inlineStr">
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E169" s="17" t="inlineStr">
         <is>
-          <t>https://nta.ac.in/</t>
+          <t>https://ntarecruitment.ntaonline.in/</t>
         </is>
       </c>
       <c r="F169" s="17" t="inlineStr">
         <is>
-          <t>https://nta.ac.in/</t>
+          <t>https://ntarecruitment.ntaonline.in/</t>
         </is>
       </c>
       <c r="G169" s="18" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="I169" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J169" s="18" t="inlineStr">
@@ -11576,12 +11576,12 @@
       </c>
       <c r="E175" s="17" t="inlineStr">
         <is>
-          <t>https://cca.gov.in/</t>
+          <t>https://cca.gov.in/recruitment.html</t>
         </is>
       </c>
       <c r="F175" s="17" t="inlineStr">
         <is>
-          <t>https://cca.gov.in/</t>
+          <t>https://cca.gov.in/recruitment.html</t>
         </is>
       </c>
       <c r="G175" s="18" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="E177" s="17" t="inlineStr">
         <is>
-          <t>https://negd.gov.in/</t>
+          <t>https://negd.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F177" s="17" t="inlineStr">
         <is>
-          <t>https://negd.gov.in/</t>
+          <t>https://negd.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G177" s="18" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="I177" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J177" s="18" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="E178" s="17" t="inlineStr">
         <is>
-          <t>https://www.sameer.gov.in/</t>
+          <t>https://www.sameer.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F178" s="17" t="inlineStr">
         <is>
-          <t>https://www.sameer.gov.in/</t>
+          <t>https://www.sameer.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G178" s="18" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="E179" s="17" t="inlineStr">
         <is>
-          <t>https://www.cert-in.org.in/</t>
+          <t>https://www.cert-in.org.in/recruitment</t>
         </is>
       </c>
       <c r="F179" s="17" t="inlineStr">
         <is>
-          <t>https://www.cert-in.org.in/</t>
+          <t>https://www.cert-in.org.in/recruitment</t>
         </is>
       </c>
       <c r="G179" s="18" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J179" s="18" t="inlineStr">
@@ -12472,12 +12472,12 @@
       </c>
       <c r="E189" s="17" t="inlineStr">
         <is>
-          <t>https://zsi.gov.in/</t>
+          <t>https://zsi.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F189" s="17" t="inlineStr">
         <is>
-          <t>https://zsi.gov.in/</t>
+          <t>https://zsi.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G189" s="18" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="I189" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J189" s="18" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="E190" s="17" t="inlineStr">
         <is>
-          <t>https://fsi.nic.in/</t>
+          <t>https://fsi.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F190" s="17" t="inlineStr">
         <is>
-          <t>https://fsi.nic.in/</t>
+          <t>https://fsi.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G190" s="18" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="I190" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J190" s="18" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="E198" s="17" t="inlineStr">
         <is>
-          <t>https://neeri.res.in/</t>
+          <t>https://neeri.res.in/divisions/details/general-administration-recruitment--assessment-section</t>
         </is>
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>https://neeri.res.in/</t>
+          <t>https://neeri.res.in/divisions/details/general-administration-recruitment--assessment-section</t>
         </is>
       </c>
       <c r="G198" s="18" t="inlineStr">
@@ -14328,12 +14328,12 @@
       </c>
       <c r="E218" s="17" t="inlineStr">
         <is>
-          <t>https://dipam.gov.in/</t>
+          <t>https://dipam.gov.in/circular</t>
         </is>
       </c>
       <c r="F218" s="17" t="inlineStr">
         <is>
-          <t>https://dipam.gov.in/</t>
+          <t>https://dipam.gov.in/circular</t>
         </is>
       </c>
       <c r="G218" s="18" t="inlineStr">
@@ -14348,7 +14348,7 @@
       </c>
       <c r="I218" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J218" s="18" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="E220" s="17" t="inlineStr">
         <is>
-          <t>https://www.cbic.gov.in/</t>
+          <t>https://www.cbic.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F220" s="17" t="inlineStr">
         <is>
-          <t>https://www.cbic.gov.in/</t>
+          <t>https://www.cbic.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G220" s="18" t="inlineStr">
@@ -14580,12 +14580,12 @@
       </c>
       <c r="E222" s="17" t="inlineStr">
         <is>
-          <t>https://www.cbic.gov.in/</t>
+          <t>https://www.cbic.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F222" s="17" t="inlineStr">
         <is>
-          <t>https://www.cbic.gov.in/</t>
+          <t>https://www.cbic.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G222" s="18" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="E223" s="17" t="inlineStr">
         <is>
-          <t>https://cga.nic.in/</t>
+          <t>https://cga.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F223" s="17" t="inlineStr">
         <is>
-          <t>https://cga.nic.in/</t>
+          <t>https://cga.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G223" s="18" t="inlineStr">
@@ -15092,12 +15092,12 @@
       </c>
       <c r="E230" s="17" t="inlineStr">
         <is>
-          <t>https://nifm.ac.in/</t>
+          <t>https://nifm.ac.in/vacancy</t>
         </is>
       </c>
       <c r="F230" s="17" t="inlineStr">
         <is>
-          <t>https://nifm.ac.in/</t>
+          <t>https://nifm.ac.in/vacancy</t>
         </is>
       </c>
       <c r="G230" s="18" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="I230" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J230" s="18" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="E231" s="17" t="inlineStr">
         <is>
-          <t>https://www.iibf.org.in/</t>
+          <t>https://www.iibf.org.in/career</t>
         </is>
       </c>
       <c r="F231" s="17" t="inlineStr">
         <is>
-          <t>https://www.iibf.org.in/</t>
+          <t>https://www.iibf.org.in/career</t>
         </is>
       </c>
       <c r="G231" s="18" t="inlineStr">
@@ -15860,12 +15860,12 @@
       </c>
       <c r="E242" s="17" t="inlineStr">
         <is>
-          <t>https://www.nddb.coop/</t>
+          <t>https://www.nddb.coop/opportunities/career</t>
         </is>
       </c>
       <c r="F242" s="17" t="inlineStr">
         <is>
-          <t>https://www.nddb.coop/</t>
+          <t>https://www.nddb.coop/opportunities/career</t>
         </is>
       </c>
       <c r="G242" s="18" t="inlineStr">
@@ -18221,12 +18221,12 @@
       </c>
       <c r="E277" s="17" t="inlineStr">
         <is>
-          <t>https://www.ncrb.gov.in/</t>
+          <t>https://www.ncrb.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F277" s="17" t="inlineStr">
         <is>
-          <t>https://www.ncrb.gov.in/</t>
+          <t>https://www.ncrb.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G277" s="18" t="inlineStr">
@@ -19757,12 +19757,12 @@
       </c>
       <c r="E301" s="17" t="inlineStr">
         <is>
-          <t>https://niua.in/</t>
+          <t>https://niua.in/career</t>
         </is>
       </c>
       <c r="F301" s="17" t="inlineStr">
         <is>
-          <t>https://niua.in/</t>
+          <t>https://niua.in/career</t>
         </is>
       </c>
       <c r="G301" s="18" t="inlineStr">
@@ -20013,12 +20013,12 @@
       </c>
       <c r="E305" s="17" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/</t>
+          <t>https://pib.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F305" s="17" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/</t>
+          <t>https://pib.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G305" s="18" t="inlineStr">
@@ -20033,7 +20033,7 @@
       </c>
       <c r="I305" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J305" s="18" t="inlineStr">
@@ -20205,12 +20205,12 @@
       </c>
       <c r="E308" s="17" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/</t>
+          <t>https://pib.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F308" s="17" t="inlineStr">
         <is>
-          <t>https://pib.gov.in/</t>
+          <t>https://pib.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G308" s="18" t="inlineStr">
@@ -20845,12 +20845,12 @@
       </c>
       <c r="E318" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F318" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G318" s="18" t="inlineStr">
@@ -20909,12 +20909,12 @@
       </c>
       <c r="E319" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F319" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G319" s="18" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="I319" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J319" s="18" t="inlineStr">
@@ -20973,12 +20973,12 @@
       </c>
       <c r="E320" s="17" t="inlineStr">
         <is>
-          <t>https://swachhbharatmission.gov.in/</t>
+          <t>https://swachhbharatmission.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F320" s="17" t="inlineStr">
         <is>
-          <t>https://swachhbharatmission.gov.in/</t>
+          <t>https://swachhbharatmission.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G320" s="18" t="inlineStr">
@@ -20993,7 +20993,7 @@
       </c>
       <c r="I320" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J320" s="18" t="inlineStr">
@@ -21421,12 +21421,12 @@
       </c>
       <c r="E327" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F327" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G327" s="18" t="inlineStr">
@@ -21485,12 +21485,12 @@
       </c>
       <c r="E328" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F328" s="17" t="inlineStr">
         <is>
-          <t>https://jalshakti-dowr.gov.in/</t>
+          <t>https://jalshakti-dowr.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G328" s="18" t="inlineStr">
@@ -21549,12 +21549,12 @@
       </c>
       <c r="E329" s="17" t="inlineStr">
         <is>
-          <t>https://www.nihroorkee.gov.in/</t>
+          <t>https://www.nihroorkee.gov.in/career-opportunity.html</t>
         </is>
       </c>
       <c r="F329" s="17" t="inlineStr">
         <is>
-          <t>https://www.nihroorkee.gov.in/</t>
+          <t>https://www.nihroorkee.gov.in/career-opportunity.html</t>
         </is>
       </c>
       <c r="G329" s="18" t="inlineStr">
@@ -21933,12 +21933,12 @@
       </c>
       <c r="E335" s="17" t="inlineStr">
         <is>
-          <t>https://dgms.gov.in/</t>
+          <t>https://dgms.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F335" s="17" t="inlineStr">
         <is>
-          <t>https://dgms.gov.in/</t>
+          <t>https://dgms.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G335" s="18" t="inlineStr">
@@ -22253,12 +22253,12 @@
       </c>
       <c r="E340" s="17" t="inlineStr">
         <is>
-          <t>https://vvgnli.gov.in/</t>
+          <t>https://vvgnli.gov.in/vacancies</t>
         </is>
       </c>
       <c r="F340" s="17" t="inlineStr">
         <is>
-          <t>https://vvgnli.gov.in/</t>
+          <t>https://vvgnli.gov.in/vacancies</t>
         </is>
       </c>
       <c r="G340" s="18" t="inlineStr">
@@ -22317,12 +22317,12 @@
       </c>
       <c r="E341" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F341" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G341" s="18" t="inlineStr">
@@ -22381,12 +22381,12 @@
       </c>
       <c r="E342" s="17" t="inlineStr">
         <is>
-          <t>https://legalaffairs.gov.in/</t>
+          <t>https://legalaffairs.gov.in/vacancy-circulars</t>
         </is>
       </c>
       <c r="F342" s="17" t="inlineStr">
         <is>
-          <t>https://legalaffairs.gov.in/</t>
+          <t>https://legalaffairs.gov.in/vacancy-circulars</t>
         </is>
       </c>
       <c r="G342" s="18" t="inlineStr">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="I342" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J342" s="18" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E343" s="17" t="inlineStr">
         <is>
-          <t>https://legislative.gov.in/</t>
+          <t>https://legislative.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F343" s="17" t="inlineStr">
         <is>
-          <t>https://legislative.gov.in/</t>
+          <t>https://legislative.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G343" s="18" t="inlineStr">
@@ -22509,12 +22509,12 @@
       </c>
       <c r="E344" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F344" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G344" s="18" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E345" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F345" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G345" s="18" t="inlineStr">
@@ -22637,12 +22637,12 @@
       </c>
       <c r="E346" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F346" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G346" s="18" t="inlineStr">
@@ -22701,12 +22701,12 @@
       </c>
       <c r="E347" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F347" s="17" t="inlineStr">
         <is>
-          <t>https://doj.gov.in/</t>
+          <t>https://doj.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G347" s="18" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="E348" s="17" t="inlineStr">
         <is>
-          <t>https://nalsa.gov.in/</t>
+          <t>https://nalsa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F348" s="17" t="inlineStr">
         <is>
-          <t>https://nalsa.gov.in/</t>
+          <t>https://nalsa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G348" s="18" t="inlineStr">
@@ -22829,12 +22829,12 @@
       </c>
       <c r="E349" s="17" t="inlineStr">
         <is>
-          <t>https://nalsa.gov.in/</t>
+          <t>https://nalsa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F349" s="17" t="inlineStr">
         <is>
-          <t>https://nalsa.gov.in/</t>
+          <t>https://nalsa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G349" s="18" t="inlineStr">
@@ -22893,12 +22893,12 @@
       </c>
       <c r="E350" s="17" t="inlineStr">
         <is>
-          <t>https://ili.ac.in/</t>
+          <t>https://ili.ac.in/recruitment</t>
         </is>
       </c>
       <c r="F350" s="17" t="inlineStr">
         <is>
-          <t>https://ili.ac.in/</t>
+          <t>https://ili.ac.in/recruitment</t>
         </is>
       </c>
       <c r="G350" s="18" t="inlineStr">
@@ -23405,12 +23405,12 @@
       </c>
       <c r="E358" s="17" t="inlineStr">
         <is>
-          <t>https://kvic.gov.in/</t>
+          <t>https://kvic.gov.in/vacancies.php</t>
         </is>
       </c>
       <c r="F358" s="17" t="inlineStr">
         <is>
-          <t>https://kvic.gov.in/</t>
+          <t>https://kvic.gov.in/vacancies.php</t>
         </is>
       </c>
       <c r="G358" s="18" t="inlineStr">
@@ -23533,12 +23533,12 @@
       </c>
       <c r="E360" s="17" t="inlineStr">
         <is>
-          <t>https://www.nsic.co.in/</t>
+          <t>https://www.nsic.co.in/recruitment</t>
         </is>
       </c>
       <c r="F360" s="17" t="inlineStr">
         <is>
-          <t>https://www.nsic.co.in/</t>
+          <t>https://www.nsic.co.in/recruitment</t>
         </is>
       </c>
       <c r="G360" s="18" t="inlineStr">
@@ -24045,12 +24045,12 @@
       </c>
       <c r="E368" s="17" t="inlineStr">
         <is>
-          <t>https://www.amu.ac.in/</t>
+          <t>https://www.amu.ac.in/recruitment</t>
         </is>
       </c>
       <c r="F368" s="17" t="inlineStr">
         <is>
-          <t>https://www.amu.ac.in/</t>
+          <t>https://www.amu.ac.in/recruitment</t>
         </is>
       </c>
       <c r="G368" s="18" t="inlineStr">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="I368" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J368" s="18" t="inlineStr">
@@ -24109,12 +24109,12 @@
       </c>
       <c r="E369" s="17" t="inlineStr">
         <is>
-          <t>https://www.jmi.ac.in/</t>
+          <t>https://www.jmi.ac.in/BULLETIN-BOARD/Jobs/Careers@JMI</t>
         </is>
       </c>
       <c r="F369" s="17" t="inlineStr">
         <is>
-          <t>https://www.jmi.ac.in/</t>
+          <t>https://www.jmi.ac.in/BULLETIN-BOARD/Jobs/Careers@JMI</t>
         </is>
       </c>
       <c r="G369" s="18" t="inlineStr">
@@ -24685,12 +24685,12 @@
       </c>
       <c r="E378" s="17" t="inlineStr">
         <is>
-          <t>https://nise.res.in/</t>
+          <t>https://career.nise.res.in/</t>
         </is>
       </c>
       <c r="F378" s="17" t="inlineStr">
         <is>
-          <t>https://nise.res.in/</t>
+          <t>https://career.nise.res.in/</t>
         </is>
       </c>
       <c r="G378" s="18" t="inlineStr">
@@ -24749,12 +24749,12 @@
       </c>
       <c r="E379" s="17" t="inlineStr">
         <is>
-          <t>https://niwe.res.in/</t>
+          <t>https://niwe.res.in/recruitment</t>
         </is>
       </c>
       <c r="F379" s="17" t="inlineStr">
         <is>
-          <t>https://niwe.res.in/</t>
+          <t>https://niwe.res.in/recruitment</t>
         </is>
       </c>
       <c r="G379" s="18" t="inlineStr">
@@ -24877,12 +24877,12 @@
       </c>
       <c r="E381" s="17" t="inlineStr">
         <is>
-          <t>https://www.ireda.in/</t>
+          <t>https://www.ireda.in/recruitment</t>
         </is>
       </c>
       <c r="F381" s="17" t="inlineStr">
         <is>
-          <t>https://www.ireda.in/</t>
+          <t>https://www.ireda.in/recruitment</t>
         </is>
       </c>
       <c r="G381" s="18" t="inlineStr">
@@ -25005,12 +25005,12 @@
       </c>
       <c r="E383" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F383" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G383" s="18" t="inlineStr">
@@ -25069,12 +25069,12 @@
       </c>
       <c r="E384" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F384" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G384" s="18" t="inlineStr">
@@ -25133,12 +25133,12 @@
       </c>
       <c r="E385" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F385" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G385" s="18" t="inlineStr">
@@ -25197,12 +25197,12 @@
       </c>
       <c r="E386" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F386" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G386" s="18" t="inlineStr">
@@ -25261,12 +25261,12 @@
       </c>
       <c r="E387" s="17" t="inlineStr">
         <is>
-          <t>https://www.nirdpr.org.in/</t>
+          <t>https://www.nirdpr.org.in/recruitment</t>
         </is>
       </c>
       <c r="F387" s="17" t="inlineStr">
         <is>
-          <t>https://www.nirdpr.org.in/</t>
+          <t>https://www.nirdpr.org.in/recruitment</t>
         </is>
       </c>
       <c r="G387" s="18" t="inlineStr">
@@ -25325,12 +25325,12 @@
       </c>
       <c r="E388" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="F388" s="17" t="inlineStr">
         <is>
-          <t>https://panchayat.gov.in/</t>
+          <t>https://panchayat.gov.in/vacancy</t>
         </is>
       </c>
       <c r="G388" s="18" t="inlineStr">
@@ -25389,12 +25389,12 @@
       </c>
       <c r="E389" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F389" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G389" s="18" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="E390" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F390" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G390" s="18" t="inlineStr">
@@ -25517,12 +25517,12 @@
       </c>
       <c r="E391" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F391" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G391" s="18" t="inlineStr">
@@ -25581,12 +25581,12 @@
       </c>
       <c r="E392" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F392" s="17" t="inlineStr">
         <is>
-          <t>https://mpa.gov.in/</t>
+          <t>https://mpa.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G392" s="18" t="inlineStr">
@@ -25709,12 +25709,12 @@
       </c>
       <c r="E394" s="17" t="inlineStr">
         <is>
-          <t>https://darpg.gov.in/</t>
+          <t>https://darpg.gov.in/circulars</t>
         </is>
       </c>
       <c r="F394" s="17" t="inlineStr">
         <is>
-          <t>https://darpg.gov.in/</t>
+          <t>https://darpg.gov.in/circulars</t>
         </is>
       </c>
       <c r="G394" s="18" t="inlineStr">
@@ -25773,12 +25773,12 @@
       </c>
       <c r="E395" s="17" t="inlineStr">
         <is>
-          <t>https://doppw.gov.in/</t>
+          <t>https://doppw.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F395" s="17" t="inlineStr">
         <is>
-          <t>https://doppw.gov.in/</t>
+          <t>https://doppw.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G395" s="18" t="inlineStr">
@@ -25837,12 +25837,12 @@
       </c>
       <c r="E396" s="17" t="inlineStr">
         <is>
-          <t>https://www.upsc.gov.in/</t>
+          <t>https://www.upsc.gov.in/vacancy-circulars</t>
         </is>
       </c>
       <c r="F396" s="17" t="inlineStr">
         <is>
-          <t>https://www.upsc.gov.in/</t>
+          <t>https://www.upsc.gov.in/vacancy-circulars</t>
         </is>
       </c>
       <c r="G396" s="18" t="inlineStr">
@@ -25965,12 +25965,12 @@
       </c>
       <c r="E398" s="17" t="inlineStr">
         <is>
-          <t>https://ssc.nic.in/</t>
+          <t>https://ssc.gov.in/check-notice-board</t>
         </is>
       </c>
       <c r="F398" s="17" t="inlineStr">
         <is>
-          <t>https://ssc.nic.in/</t>
+          <t>https://ssc.gov.in/check-notice-board</t>
         </is>
       </c>
       <c r="G398" s="18" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="I398" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J398" s="18" t="inlineStr">
@@ -26093,12 +26093,12 @@
       </c>
       <c r="E400" s="17" t="inlineStr">
         <is>
-          <t>https://cic.gov.in/</t>
+          <t>https://cic.gov.in/quicktabs/nojs/recruitment_and_internship_home/0</t>
         </is>
       </c>
       <c r="F400" s="17" t="inlineStr">
         <is>
-          <t>https://cic.gov.in/</t>
+          <t>https://cic.gov.in/quicktabs/nojs/recruitment_and_internship_home/0</t>
         </is>
       </c>
       <c r="G400" s="18" t="inlineStr">
@@ -26733,12 +26733,12 @@
       </c>
       <c r="E410" s="17" t="inlineStr">
         <is>
-          <t>https://www.dghindia.gov.in/</t>
+          <t>https://www.dghindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F410" s="17" t="inlineStr">
         <is>
-          <t>https://www.dghindia.gov.in/</t>
+          <t>https://www.dghindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G410" s="18" t="inlineStr">
@@ -26797,12 +26797,12 @@
       </c>
       <c r="E411" s="17" t="inlineStr">
         <is>
-          <t>https://www.ppac.gov.in/</t>
+          <t>https://www.ppac.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F411" s="17" t="inlineStr">
         <is>
-          <t>https://www.ppac.gov.in/</t>
+          <t>https://www.ppac.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G411" s="18" t="inlineStr">
@@ -26861,12 +26861,12 @@
       </c>
       <c r="E412" s="17" t="inlineStr">
         <is>
-          <t>https://www.dghindia.gov.in/</t>
+          <t>https://www.dghindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F412" s="17" t="inlineStr">
         <is>
-          <t>https://www.dghindia.gov.in/</t>
+          <t>https://www.dghindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G412" s="18" t="inlineStr">
@@ -26925,12 +26925,12 @@
       </c>
       <c r="E413" s="17" t="inlineStr">
         <is>
-          <t>https://www.ppac.gov.in/</t>
+          <t>https://www.ppac.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F413" s="17" t="inlineStr">
         <is>
-          <t>https://www.ppac.gov.in/</t>
+          <t>https://www.ppac.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G413" s="18" t="inlineStr">
@@ -27245,12 +27245,12 @@
       </c>
       <c r="E418" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F418" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G418" s="18" t="inlineStr">
@@ -27309,12 +27309,12 @@
       </c>
       <c r="E419" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F419" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G419" s="18" t="inlineStr">
@@ -27373,12 +27373,12 @@
       </c>
       <c r="E420" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F420" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G420" s="18" t="inlineStr">
@@ -27437,12 +27437,12 @@
       </c>
       <c r="E421" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F421" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G421" s="18" t="inlineStr">
@@ -27501,12 +27501,12 @@
       </c>
       <c r="E422" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F422" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G422" s="18" t="inlineStr">
@@ -27629,12 +27629,12 @@
       </c>
       <c r="E424" s="17" t="inlineStr">
         <is>
-          <t>https://iwai.nic.in/</t>
+          <t>https://iwai.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F424" s="17" t="inlineStr">
         <is>
-          <t>https://iwai.nic.in/</t>
+          <t>https://iwai.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G424" s="18" t="inlineStr">
@@ -27757,12 +27757,12 @@
       </c>
       <c r="E426" s="17" t="inlineStr">
         <is>
-          <t>https://iwai.nic.in/</t>
+          <t>https://iwai.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F426" s="17" t="inlineStr">
         <is>
-          <t>https://iwai.nic.in/</t>
+          <t>https://iwai.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G426" s="18" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="E427" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F427" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G427" s="18" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E429" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="F429" s="17" t="inlineStr">
         <is>
-          <t>https://shipmin.gov.in/</t>
+          <t>https://shipmin.gov.in/orders/vacancies</t>
         </is>
       </c>
       <c r="G429" s="18" t="inlineStr">
@@ -28013,12 +28013,12 @@
       </c>
       <c r="E430" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F430" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G430" s="18" t="inlineStr">
@@ -28077,12 +28077,12 @@
       </c>
       <c r="E431" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F431" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G431" s="18" t="inlineStr">
@@ -28141,12 +28141,12 @@
       </c>
       <c r="E432" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F432" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G432" s="18" t="inlineStr">
@@ -28205,12 +28205,12 @@
       </c>
       <c r="E433" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F433" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G433" s="18" t="inlineStr">
@@ -28269,12 +28269,12 @@
       </c>
       <c r="E434" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F434" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G434" s="18" t="inlineStr">
@@ -28333,12 +28333,12 @@
       </c>
       <c r="E435" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F435" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G435" s="18" t="inlineStr">
@@ -28397,12 +28397,12 @@
       </c>
       <c r="E436" s="17" t="inlineStr">
         <is>
-          <t>https://cea.nic.in/</t>
+          <t>https://cea.nic.in/vacancy</t>
         </is>
       </c>
       <c r="F436" s="17" t="inlineStr">
         <is>
-          <t>https://cea.nic.in/</t>
+          <t>https://cea.nic.in/vacancy</t>
         </is>
       </c>
       <c r="G436" s="18" t="inlineStr">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="I436" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J436" s="18" t="inlineStr">
@@ -28461,12 +28461,12 @@
       </c>
       <c r="E437" s="17" t="inlineStr">
         <is>
-          <t>https://beeindia.gov.in/</t>
+          <t>https://beeindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F437" s="17" t="inlineStr">
         <is>
-          <t>https://beeindia.gov.in/</t>
+          <t>https://beeindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G437" s="18" t="inlineStr">
@@ -28525,12 +28525,12 @@
       </c>
       <c r="E438" s="17" t="inlineStr">
         <is>
-          <t>https://cea.nic.in/</t>
+          <t>https://cea.nic.in/vacancy</t>
         </is>
       </c>
       <c r="F438" s="17" t="inlineStr">
         <is>
-          <t>https://cea.nic.in/</t>
+          <t>https://cea.nic.in/vacancy</t>
         </is>
       </c>
       <c r="G438" s="18" t="inlineStr">
@@ -28589,12 +28589,12 @@
       </c>
       <c r="E439" s="17" t="inlineStr">
         <is>
-          <t>https://beeindia.gov.in/</t>
+          <t>https://beeindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F439" s="17" t="inlineStr">
         <is>
-          <t>https://beeindia.gov.in/</t>
+          <t>https://beeindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G439" s="18" t="inlineStr">
@@ -28653,12 +28653,12 @@
       </c>
       <c r="E440" s="17" t="inlineStr">
         <is>
-          <t>https://cercind.gov.in/</t>
+          <t>https://cercind.gov.in/vacancy.html</t>
         </is>
       </c>
       <c r="F440" s="17" t="inlineStr">
         <is>
-          <t>https://cercind.gov.in/</t>
+          <t>https://cercind.gov.in/vacancy.html</t>
         </is>
       </c>
       <c r="G440" s="18" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E441" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F441" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G441" s="18" t="inlineStr">
@@ -28781,12 +28781,12 @@
       </c>
       <c r="E442" s="17" t="inlineStr">
         <is>
-          <t>https://www.cpri.res.in/</t>
+          <t>https://www.cpri.res.in/hi/careers/career-results</t>
         </is>
       </c>
       <c r="F442" s="17" t="inlineStr">
         <is>
-          <t>https://www.cpri.res.in/</t>
+          <t>https://www.cpri.res.in/hi/careers/career-results</t>
         </is>
       </c>
       <c r="G442" s="18" t="inlineStr">
@@ -28845,12 +28845,12 @@
       </c>
       <c r="E443" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F443" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G443" s="18" t="inlineStr">
@@ -28909,12 +28909,12 @@
       </c>
       <c r="E444" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F444" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G444" s="18" t="inlineStr">
@@ -28973,12 +28973,12 @@
       </c>
       <c r="E445" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F445" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G445" s="18" t="inlineStr">
@@ -29037,12 +29037,12 @@
       </c>
       <c r="E446" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F446" s="17" t="inlineStr">
         <is>
-          <t>https://powermin.gov.in/</t>
+          <t>https://powermin.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G446" s="18" t="inlineStr">
@@ -30445,12 +30445,12 @@
       </c>
       <c r="E468" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F468" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G468" s="18" t="inlineStr">
@@ -30509,12 +30509,12 @@
       </c>
       <c r="E469" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F469" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G469" s="18" t="inlineStr">
@@ -30573,12 +30573,12 @@
       </c>
       <c r="E470" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F470" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G470" s="18" t="inlineStr">
@@ -30637,12 +30637,12 @@
       </c>
       <c r="E471" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F471" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G471" s="18" t="inlineStr">
@@ -30701,12 +30701,12 @@
       </c>
       <c r="E472" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F472" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G472" s="18" t="inlineStr">
@@ -30765,12 +30765,12 @@
       </c>
       <c r="E473" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F473" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G473" s="18" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E474" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F474" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G474" s="18" t="inlineStr">
@@ -30893,12 +30893,12 @@
       </c>
       <c r="E475" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F475" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G475" s="18" t="inlineStr">
@@ -31021,12 +31021,12 @@
       </c>
       <c r="E477" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F477" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G477" s="18" t="inlineStr">
@@ -31085,12 +31085,12 @@
       </c>
       <c r="E478" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="F478" s="17" t="inlineStr">
         <is>
-          <t>https://morth.nic.in/</t>
+          <t>https://morth.nic.in/recruitment</t>
         </is>
       </c>
       <c r="G478" s="18" t="inlineStr">
@@ -31149,12 +31149,12 @@
       </c>
       <c r="E479" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F479" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G479" s="18" t="inlineStr">
@@ -31213,12 +31213,12 @@
       </c>
       <c r="E480" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F480" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G480" s="18" t="inlineStr">
@@ -31277,12 +31277,12 @@
       </c>
       <c r="E481" s="17" t="inlineStr">
         <is>
-          <t>https://dbtindia.gov.in/</t>
+          <t>https://dbtindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F481" s="17" t="inlineStr">
         <is>
-          <t>https://dbtindia.gov.in/</t>
+          <t>https://dbtindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G481" s="18" t="inlineStr">
@@ -31341,12 +31341,12 @@
       </c>
       <c r="E482" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F482" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G482" s="18" t="inlineStr">
@@ -31405,12 +31405,12 @@
       </c>
       <c r="E483" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F483" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G483" s="18" t="inlineStr">
@@ -31469,12 +31469,12 @@
       </c>
       <c r="E484" s="17" t="inlineStr">
         <is>
-          <t>https://www.csir.res.in/</t>
+          <t>https://www.csir.res.in/hi/career-opportunities/recruitment</t>
         </is>
       </c>
       <c r="F484" s="17" t="inlineStr">
         <is>
-          <t>https://www.csir.res.in/</t>
+          <t>https://www.csir.res.in/hi/career-opportunities/recruitment</t>
         </is>
       </c>
       <c r="G484" s="18" t="inlineStr">
@@ -31533,12 +31533,12 @@
       </c>
       <c r="E485" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F485" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G485" s="18" t="inlineStr">
@@ -31597,12 +31597,12 @@
       </c>
       <c r="E486" s="17" t="inlineStr">
         <is>
-          <t>https://dbtindia.gov.in/</t>
+          <t>https://dbtindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F486" s="17" t="inlineStr">
         <is>
-          <t>https://dbtindia.gov.in/</t>
+          <t>https://dbtindia.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G486" s="18" t="inlineStr">
@@ -31661,12 +31661,12 @@
       </c>
       <c r="E487" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F487" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G487" s="18" t="inlineStr">
@@ -31725,12 +31725,12 @@
       </c>
       <c r="E488" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F488" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G488" s="18" t="inlineStr">
@@ -31789,12 +31789,12 @@
       </c>
       <c r="E489" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="F489" s="17" t="inlineStr">
         <is>
-          <t>https://dst.gov.in/</t>
+          <t>https://dst.gov.in/circulars</t>
         </is>
       </c>
       <c r="G489" s="18" t="inlineStr">
@@ -31853,12 +31853,12 @@
       </c>
       <c r="E490" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F490" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G490" s="18" t="inlineStr">
@@ -31917,12 +31917,12 @@
       </c>
       <c r="E491" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F491" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G491" s="18" t="inlineStr">
@@ -31981,12 +31981,12 @@
       </c>
       <c r="E492" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F492" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G492" s="18" t="inlineStr">
@@ -32001,7 +32001,7 @@
       </c>
       <c r="I492" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J492" s="18" t="inlineStr">
@@ -32045,12 +32045,12 @@
       </c>
       <c r="E493" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F493" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G493" s="18" t="inlineStr">
@@ -32109,12 +32109,12 @@
       </c>
       <c r="E494" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F494" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G494" s="18" t="inlineStr">
@@ -32173,12 +32173,12 @@
       </c>
       <c r="E495" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F495" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G495" s="18" t="inlineStr">
@@ -32237,12 +32237,12 @@
       </c>
       <c r="E496" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F496" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G496" s="18" t="inlineStr">
@@ -32301,12 +32301,12 @@
       </c>
       <c r="E497" s="17" t="inlineStr">
         <is>
-          <t>https://www.nsdc.in/</t>
+          <t>https://nsdcindia.org/careers</t>
         </is>
       </c>
       <c r="F497" s="17" t="inlineStr">
         <is>
-          <t>https://www.nsdc.in/</t>
+          <t>https://nsdcindia.org/careers</t>
         </is>
       </c>
       <c r="G497" s="18" t="inlineStr">
@@ -32321,7 +32321,7 @@
       </c>
       <c r="I497" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J497" s="18" t="inlineStr">
@@ -32365,12 +32365,12 @@
       </c>
       <c r="E498" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F498" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G498" s="18" t="inlineStr">
@@ -32429,12 +32429,12 @@
       </c>
       <c r="E499" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F499" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G499" s="18" t="inlineStr">
@@ -32493,12 +32493,12 @@
       </c>
       <c r="E500" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F500" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G500" s="18" t="inlineStr">
@@ -32557,12 +32557,12 @@
       </c>
       <c r="E501" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F501" s="17" t="inlineStr">
         <is>
-          <t>https://msde.gov.in/</t>
+          <t>https://msde.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G501" s="18" t="inlineStr">
@@ -32621,12 +32621,12 @@
       </c>
       <c r="E502" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F502" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G502" s="18" t="inlineStr">
@@ -32685,12 +32685,12 @@
       </c>
       <c r="E503" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F503" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G503" s="18" t="inlineStr">
@@ -32749,12 +32749,12 @@
       </c>
       <c r="E504" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F504" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G504" s="18" t="inlineStr">
@@ -32813,12 +32813,12 @@
       </c>
       <c r="E505" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F505" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G505" s="18" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E506" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F506" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G506" s="18" t="inlineStr">
@@ -32941,12 +32941,12 @@
       </c>
       <c r="E507" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F507" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G507" s="18" t="inlineStr">
@@ -33005,12 +33005,12 @@
       </c>
       <c r="E508" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F508" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G508" s="18" t="inlineStr">
@@ -33069,12 +33069,12 @@
       </c>
       <c r="E509" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F509" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G509" s="18" t="inlineStr">
@@ -33133,12 +33133,12 @@
       </c>
       <c r="E510" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F510" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G510" s="18" t="inlineStr">
@@ -33197,12 +33197,12 @@
       </c>
       <c r="E511" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F511" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G511" s="18" t="inlineStr">
@@ -33261,12 +33261,12 @@
       </c>
       <c r="E512" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F512" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G512" s="18" t="inlineStr">
@@ -33325,12 +33325,12 @@
       </c>
       <c r="E513" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F513" s="17" t="inlineStr">
         <is>
-          <t>https://disabilityaffairs.gov.in/</t>
+          <t>https://disabilityaffairs.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G513" s="18" t="inlineStr">
@@ -33389,12 +33389,12 @@
       </c>
       <c r="E514" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F514" s="17" t="inlineStr">
         <is>
-          <t>https://socialjustice.gov.in/</t>
+          <t>https://socialjustice.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G514" s="18" t="inlineStr">
@@ -33453,12 +33453,12 @@
       </c>
       <c r="E515" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F515" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G515" s="18" t="inlineStr">
@@ -33517,12 +33517,12 @@
       </c>
       <c r="E516" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F516" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G516" s="18" t="inlineStr">
@@ -33581,12 +33581,12 @@
       </c>
       <c r="E517" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F517" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G517" s="18" t="inlineStr">
@@ -33645,12 +33645,12 @@
       </c>
       <c r="E518" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F518" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G518" s="18" t="inlineStr">
@@ -33709,12 +33709,12 @@
       </c>
       <c r="E519" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F519" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G519" s="18" t="inlineStr">
@@ -33773,12 +33773,12 @@
       </c>
       <c r="E520" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F520" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G520" s="18" t="inlineStr">
@@ -33837,12 +33837,12 @@
       </c>
       <c r="E521" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F521" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G521" s="18" t="inlineStr">
@@ -33901,12 +33901,12 @@
       </c>
       <c r="E522" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F522" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G522" s="18" t="inlineStr">
@@ -33965,12 +33965,12 @@
       </c>
       <c r="E523" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F523" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G523" s="18" t="inlineStr">
@@ -34029,12 +34029,12 @@
       </c>
       <c r="E524" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F524" s="17" t="inlineStr">
         <is>
-          <t>https://mospi.gov.in/</t>
+          <t>https://mospi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G524" s="18" t="inlineStr">
@@ -34093,12 +34093,12 @@
       </c>
       <c r="E525" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F525" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G525" s="18" t="inlineStr">
@@ -34157,12 +34157,12 @@
       </c>
       <c r="E526" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F526" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G526" s="18" t="inlineStr">
@@ -34221,12 +34221,12 @@
       </c>
       <c r="E527" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F527" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G527" s="18" t="inlineStr">
@@ -34285,12 +34285,12 @@
       </c>
       <c r="E528" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F528" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G528" s="18" t="inlineStr">
@@ -34349,12 +34349,12 @@
       </c>
       <c r="E529" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F529" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G529" s="18" t="inlineStr">
@@ -34413,12 +34413,12 @@
       </c>
       <c r="E530" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F530" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G530" s="18" t="inlineStr">
@@ -34477,12 +34477,12 @@
       </c>
       <c r="E531" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F531" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G531" s="18" t="inlineStr">
@@ -34541,12 +34541,12 @@
       </c>
       <c r="E532" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F532" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G532" s="18" t="inlineStr">
@@ -34605,12 +34605,12 @@
       </c>
       <c r="E533" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F533" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G533" s="18" t="inlineStr">
@@ -34669,12 +34669,12 @@
       </c>
       <c r="E534" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F534" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G534" s="18" t="inlineStr">
@@ -34733,12 +34733,12 @@
       </c>
       <c r="E535" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F535" s="17" t="inlineStr">
         <is>
-          <t>https://steel.gov.in/</t>
+          <t>https://steel.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G535" s="18" t="inlineStr">
@@ -35629,12 +35629,12 @@
       </c>
       <c r="E549" s="17" t="inlineStr">
         <is>
-          <t>https://www.nift.ac.in/</t>
+          <t>https://www.nift.ac.in/careers</t>
         </is>
       </c>
       <c r="F549" s="17" t="inlineStr">
         <is>
-          <t>https://www.nift.ac.in/</t>
+          <t>https://www.nift.ac.in/careers</t>
         </is>
       </c>
       <c r="G549" s="18" t="inlineStr">
@@ -35821,12 +35821,12 @@
       </c>
       <c r="E552" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F552" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G552" s="18" t="inlineStr">
@@ -35885,12 +35885,12 @@
       </c>
       <c r="E553" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F553" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G553" s="18" t="inlineStr">
@@ -35949,12 +35949,12 @@
       </c>
       <c r="E554" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F554" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G554" s="18" t="inlineStr">
@@ -36013,12 +36013,12 @@
       </c>
       <c r="E555" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F555" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G555" s="18" t="inlineStr">
@@ -36077,12 +36077,12 @@
       </c>
       <c r="E556" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F556" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G556" s="18" t="inlineStr">
@@ -36141,12 +36141,12 @@
       </c>
       <c r="E557" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F557" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G557" s="18" t="inlineStr">
@@ -36205,12 +36205,12 @@
       </c>
       <c r="E558" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F558" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G558" s="18" t="inlineStr">
@@ -36269,12 +36269,12 @@
       </c>
       <c r="E559" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F559" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G559" s="18" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E560" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F560" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G560" s="18" t="inlineStr">
@@ -36397,12 +36397,12 @@
       </c>
       <c r="E561" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F561" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G561" s="18" t="inlineStr">
@@ -36461,12 +36461,12 @@
       </c>
       <c r="E562" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="F562" s="17" t="inlineStr">
         <is>
-          <t>https://tribal.gov.in/</t>
+          <t>https://tribal.gov.in/circular</t>
         </is>
       </c>
       <c r="G562" s="18" t="inlineStr">
@@ -36550,7 +36550,7 @@
       </c>
       <c r="J563" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Women &amp; Child Development official site (wcd.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>Ministry of Women &amp; Child Development official site (wcd.gov.in). Unreachable from this environment but confirmed as official domain. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K563" s="19" t="n">
@@ -36614,7 +36614,7 @@
       </c>
       <c r="J564" s="18" t="inlineStr">
         <is>
-          <t>Ministry of WCD Secretariat. Site unreachable but confirmed domain.</t>
+          <t>Ministry of WCD Secretariat. Site unreachable but confirmed domain. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K564" s="19" t="n">
@@ -36678,7 +36678,7 @@
       </c>
       <c r="J565" s="18" t="inlineStr">
         <is>
-          <t>Child Development Division.</t>
+          <t>Child Development Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K565" s="19" t="n">
@@ -36742,7 +36742,7 @@
       </c>
       <c r="J566" s="18" t="inlineStr">
         <is>
-          <t>Women Empowerment Division.</t>
+          <t>Women Empowerment Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K566" s="19" t="n">
@@ -36806,7 +36806,7 @@
       </c>
       <c r="J567" s="18" t="inlineStr">
         <is>
-          <t>Mission Shakti Division.</t>
+          <t>Mission Shakti Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K567" s="19" t="n">
@@ -36870,7 +36870,7 @@
       </c>
       <c r="J568" s="18" t="inlineStr">
         <is>
-          <t>Mission Vatsalya Division.</t>
+          <t>Mission Vatsalya Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K568" s="19" t="n">
@@ -36934,7 +36934,7 @@
       </c>
       <c r="J569" s="18" t="inlineStr">
         <is>
-          <t>Mission POSHAN 2.0 Division.</t>
+          <t>Mission POSHAN 2.0 Division. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K569" s="19" t="n">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="J570" s="18" t="inlineStr">
         <is>
-          <t>CARA (Central Adoption Resource Authority) under WCD. Has cara.wcd.gov.in.</t>
+          <t>CARA (Central Adoption Resource Authority) under WCD. Has cara.wcd.gov.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K570" s="19" t="n">
@@ -37062,7 +37062,7 @@
       </c>
       <c r="J571" s="18" t="inlineStr">
         <is>
-          <t>NCPCR under WCD. Has ncpcr.gov.in.</t>
+          <t>NCPCR under WCD. Has ncpcr.gov.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K571" s="19" t="n">
@@ -37126,7 +37126,7 @@
       </c>
       <c r="J572" s="18" t="inlineStr">
         <is>
-          <t>Anganwadi/ICDS Field Units subordinate.</t>
+          <t>Anganwadi/ICDS Field Units subordinate. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K572" s="19" t="n">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="J573" s="18" t="inlineStr">
         <is>
-          <t>State/District Mission Directorates coordination.</t>
+          <t>State/District Mission Directorates coordination. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K573" s="19" t="n">
@@ -37254,7 +37254,7 @@
       </c>
       <c r="J574" s="18" t="inlineStr">
         <is>
-          <t>NCW (National Commission for Women). Statutory body. Has ncw.nic.in.</t>
+          <t>NCW (National Commission for Women). Statutory body. Has ncw.nic.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K574" s="19" t="n">
@@ -37318,7 +37318,7 @@
       </c>
       <c r="J575" s="18" t="inlineStr">
         <is>
-          <t>NIPCCD autonomous body under WCD. Has nipccd.nic.in.</t>
+          <t>NIPCCD autonomous body under WCD. Has nipccd.nic.in. [Verified: WCD has no dedicated central recruitment listing page; career section (wcd.gov.in/offerings/career) is internship-focused. Central posts via SSC/deputation; ICDS/Anganwadi recruitment is state-level.]</t>
         </is>
       </c>
       <c r="K575" s="19" t="n">
@@ -37357,12 +37357,12 @@
       </c>
       <c r="E576" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F576" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G576" s="18" t="inlineStr">
@@ -37421,12 +37421,12 @@
       </c>
       <c r="E577" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F577" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G577" s="18" t="inlineStr">
@@ -37485,12 +37485,12 @@
       </c>
       <c r="E578" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F578" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G578" s="18" t="inlineStr">
@@ -37549,12 +37549,12 @@
       </c>
       <c r="E579" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F579" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G579" s="18" t="inlineStr">
@@ -37613,12 +37613,12 @@
       </c>
       <c r="E580" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F580" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G580" s="18" t="inlineStr">
@@ -37677,12 +37677,12 @@
       </c>
       <c r="E581" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F581" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G581" s="18" t="inlineStr">
@@ -37741,12 +37741,12 @@
       </c>
       <c r="E582" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F582" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G582" s="18" t="inlineStr">
@@ -37869,12 +37869,12 @@
       </c>
       <c r="E584" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F584" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G584" s="18" t="inlineStr">
@@ -37933,12 +37933,12 @@
       </c>
       <c r="E585" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F585" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G585" s="18" t="inlineStr">
@@ -37997,12 +37997,12 @@
       </c>
       <c r="E586" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="F586" s="17" t="inlineStr">
         <is>
-          <t>https://yas.gov.in/</t>
+          <t>https://yas.gov.in/circular</t>
         </is>
       </c>
       <c r="G586" s="18" t="inlineStr">
@@ -38061,12 +38061,12 @@
       </c>
       <c r="E587" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F587" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G587" s="18" t="inlineStr">
@@ -38086,7 +38086,7 @@
       </c>
       <c r="J587" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Heavy Industries official site (dhi.gov.in). Unreachable from this environment but confirmed as official domain.</t>
+          <t>Ministry of Heavy Industries official site (heavyindustries.gov.in). Unreachable from this environment but confirmed as official domain. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K587" s="19" t="n">
@@ -38125,12 +38125,12 @@
       </c>
       <c r="E588" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F588" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G588" s="18" t="inlineStr">
@@ -38150,7 +38150,7 @@
       </c>
       <c r="J588" s="18" t="inlineStr">
         <is>
-          <t>Ministry of Heavy Industries Secretariat. Site unreachable but confirmed domain.</t>
+          <t>Ministry of Heavy Industries Secretariat. Site unreachable but confirmed domain. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K588" s="19" t="n">
@@ -38189,12 +38189,12 @@
       </c>
       <c r="E589" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F589" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G589" s="18" t="inlineStr">
@@ -38214,7 +38214,7 @@
       </c>
       <c r="J589" s="18" t="inlineStr">
         <is>
-          <t>Heavy Engineering Division.</t>
+          <t>Heavy Engineering Division. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K589" s="19" t="n">
@@ -38253,12 +38253,12 @@
       </c>
       <c r="E590" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F590" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G590" s="18" t="inlineStr">
@@ -38278,7 +38278,7 @@
       </c>
       <c r="J590" s="18" t="inlineStr">
         <is>
-          <t>Automotive Industry Division.</t>
+          <t>Automotive Industry Division. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K590" s="19" t="n">
@@ -38317,12 +38317,12 @@
       </c>
       <c r="E591" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F591" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G591" s="18" t="inlineStr">
@@ -38342,7 +38342,7 @@
       </c>
       <c r="J591" s="18" t="inlineStr">
         <is>
-          <t>ARAI autonomous body. Has araiindia.com.</t>
+          <t>ARAI autonomous body. Has araiindia.com. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K591" s="19" t="n">
@@ -38381,12 +38381,12 @@
       </c>
       <c r="E592" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F592" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G592" s="18" t="inlineStr">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="J592" s="18" t="inlineStr">
         <is>
-          <t>ICAT autonomous body. Has icat.in.</t>
+          <t>ICAT autonomous body. Has icat.in. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K592" s="19" t="n">
@@ -38445,12 +38445,12 @@
       </c>
       <c r="E593" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F593" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G593" s="18" t="inlineStr">
@@ -38470,7 +38470,7 @@
       </c>
       <c r="J593" s="18" t="inlineStr">
         <is>
-          <t>CMTI autonomous body.</t>
+          <t>CMTI autonomous body. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K593" s="19" t="n">
@@ -38509,12 +38509,12 @@
       </c>
       <c r="E594" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F594" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G594" s="18" t="inlineStr">
@@ -38534,7 +38534,7 @@
       </c>
       <c r="J594" s="18" t="inlineStr">
         <is>
-          <t>BHEL is a PSU recruiting independently at bhel.com. Policy entry.</t>
+          <t>BHEL is a PSU recruiting independently at bhel.com. Policy entry. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K594" s="19" t="n">
@@ -38573,12 +38573,12 @@
       </c>
       <c r="E595" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="F595" s="17" t="inlineStr">
         <is>
-          <t>https://dhi.gov.in/</t>
+          <t>https://heavyindustries.gov.in/en/whats-new</t>
         </is>
       </c>
       <c r="G595" s="18" t="inlineStr">
@@ -38598,7 +38598,7 @@
       </c>
       <c r="J595" s="18" t="inlineStr">
         <is>
-          <t>HMT Limited PSU. Policy entry.</t>
+          <t>HMT Limited PSU. Policy entry. [Corrected: domain is heavyindustries.gov.in (dhi.gov.in deprecated); vacancy notices posted under What's New.]</t>
         </is>
       </c>
       <c r="K595" s="19" t="n">
@@ -38637,12 +38637,12 @@
       </c>
       <c r="E596" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F596" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G596" s="18" t="inlineStr">
@@ -38701,12 +38701,12 @@
       </c>
       <c r="E597" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F597" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G597" s="18" t="inlineStr">
@@ -38765,12 +38765,12 @@
       </c>
       <c r="E598" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F598" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G598" s="18" t="inlineStr">
@@ -38785,7 +38785,7 @@
       </c>
       <c r="I598" s="18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J598" s="18" t="inlineStr">
@@ -38829,12 +38829,12 @@
       </c>
       <c r="E599" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F599" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G599" s="18" t="inlineStr">
@@ -38893,12 +38893,12 @@
       </c>
       <c r="E600" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F600" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G600" s="18" t="inlineStr">
@@ -38957,12 +38957,12 @@
       </c>
       <c r="E601" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F601" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G601" s="18" t="inlineStr">
@@ -39021,12 +39021,12 @@
       </c>
       <c r="E602" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="F602" s="17" t="inlineStr">
         <is>
-          <t>https://mines.gov.in/</t>
+          <t>https://mines.gov.in/webportal/recruitment</t>
         </is>
       </c>
       <c r="G602" s="18" t="inlineStr">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E603" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F603" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G603" s="18" t="inlineStr">
@@ -39149,12 +39149,12 @@
       </c>
       <c r="E604" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F604" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G604" s="18" t="inlineStr">
@@ -39213,12 +39213,12 @@
       </c>
       <c r="E605" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F605" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G605" s="18" t="inlineStr">
@@ -39277,12 +39277,12 @@
       </c>
       <c r="E606" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F606" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G606" s="18" t="inlineStr">
@@ -39341,12 +39341,12 @@
       </c>
       <c r="E607" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F607" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G607" s="18" t="inlineStr">
@@ -39405,12 +39405,12 @@
       </c>
       <c r="E608" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F608" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G608" s="18" t="inlineStr">
@@ -39469,12 +39469,12 @@
       </c>
       <c r="E609" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F609" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G609" s="18" t="inlineStr">
@@ -39533,12 +39533,12 @@
       </c>
       <c r="E610" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F610" s="17" t="inlineStr">
         <is>
-          <t>https://tourism.gov.in/</t>
+          <t>https://tourism.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G610" s="18" t="inlineStr">
